--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{081C4787-EA4E-4208-973C-216B51DE8D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -919,9 +925,6 @@
     <t>Musée de l'Ermitage</t>
   </si>
   <si>
-    <t>Musée Salzillo, Procession du Vendredi Saint</t>
-  </si>
-  <si>
     <t>Musée de San Martino</t>
   </si>
   <si>
@@ -2306,13 +2309,16 @@
   </si>
   <si>
     <t>belge</t>
+  </si>
+  <si>
+    <t>Musée Salzillo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2357,18 +2363,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2406,7 +2420,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2440,6 +2454,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2474,9 +2489,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2649,11 +2665,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X109"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="11" max="11" width="22.85546875" customWidth="1"/>
+    <col min="12" max="12" width="20.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2727,7 +2749,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -2747,31 +2769,31 @@
         <v>249</v>
       </c>
       <c r="M2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="U2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="V2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="W2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -2794,31 +2816,31 @@
         <v>250</v>
       </c>
       <c r="M3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="S3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="U3" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="V3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="W3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -2838,34 +2860,34 @@
         <v>251</v>
       </c>
       <c r="L4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="S4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="U4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="V4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="W4" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -2888,31 +2910,31 @@
         <v>250</v>
       </c>
       <c r="M5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="S5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="U5" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="V5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="W5" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -2935,31 +2957,31 @@
         <v>250</v>
       </c>
       <c r="M6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="S6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T6" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="U6" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="V6" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="W6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -2982,28 +3004,28 @@
         <v>252</v>
       </c>
       <c r="L7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="S7" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="T7" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="W7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="X7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -3026,34 +3048,34 @@
         <v>253</v>
       </c>
       <c r="M8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q8" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="S8" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T8" t="s">
+        <v>617</v>
+      </c>
+      <c r="U8" t="s">
+        <v>680</v>
+      </c>
+      <c r="V8" t="s">
         <v>618</v>
       </c>
-      <c r="U8" t="s">
-        <v>681</v>
-      </c>
-      <c r="V8" t="s">
-        <v>619</v>
-      </c>
       <c r="W8" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="X8">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -3076,37 +3098,37 @@
         <v>254</v>
       </c>
       <c r="L9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q9" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="S9" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="T9" t="s">
+        <v>618</v>
+      </c>
+      <c r="U9" t="s">
+        <v>693</v>
+      </c>
+      <c r="V9" t="s">
         <v>619</v>
       </c>
-      <c r="U9" t="s">
-        <v>694</v>
-      </c>
-      <c r="V9" t="s">
-        <v>620</v>
-      </c>
       <c r="W9" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="X9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -3129,34 +3151,34 @@
         <v>255</v>
       </c>
       <c r="M10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="S10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="U10" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="V10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="W10" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="X10">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -3179,34 +3201,34 @@
         <v>256</v>
       </c>
       <c r="M11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Q11" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="S11" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T11" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="U11" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="V11" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="W11" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="X11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -3229,31 +3251,31 @@
         <v>250</v>
       </c>
       <c r="M12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="S12" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T12" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="U12" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="V12" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="W12" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -3276,34 +3298,34 @@
         <v>257</v>
       </c>
       <c r="L13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="S13" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="T13" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="U13" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="V13" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="W13" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -3326,31 +3348,31 @@
         <v>250</v>
       </c>
       <c r="M14" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="S14" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="T14" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="U14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="V14" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="W14" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -3370,34 +3392,34 @@
         <v>251</v>
       </c>
       <c r="L15" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M15" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="S15" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T15" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="U15" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="V15" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="W15" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X15">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -3420,31 +3442,31 @@
         <v>250</v>
       </c>
       <c r="M16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="S16" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T16" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="U16" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="V16" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="W16" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -3467,34 +3489,34 @@
         <v>258</v>
       </c>
       <c r="M17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Q17" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="S17" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="T17" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="U17" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="V17" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="W17" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -3517,34 +3539,34 @@
         <v>250</v>
       </c>
       <c r="M18" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Q18" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="S18" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T18" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="U18" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="V18" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="W18" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -3567,34 +3589,34 @@
         <v>250</v>
       </c>
       <c r="M19" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q19" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="S19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T19" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="U19" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="V19" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="W19" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X19">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -3617,37 +3639,37 @@
         <v>259</v>
       </c>
       <c r="L20" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M20" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q20" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="S20" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T20" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="U20" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="V20" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="W20" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -3670,28 +3692,28 @@
         <v>260</v>
       </c>
       <c r="M21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="S21" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="T21" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="U21" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="W21" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="X21">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -3714,31 +3736,31 @@
         <v>261</v>
       </c>
       <c r="L22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M22" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="S22" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T22" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="U22" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="W22" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -3761,25 +3783,25 @@
         <v>262</v>
       </c>
       <c r="M23" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="S23" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="T23" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W23" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="X23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -3802,31 +3824,31 @@
         <v>263</v>
       </c>
       <c r="M24" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="S24" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="T24" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="U24" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="V24" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="W24" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X24">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -3849,34 +3871,34 @@
         <v>264</v>
       </c>
       <c r="M25" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q25" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="S25" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T25" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="U25" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="V25" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="W25" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X25">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -3899,34 +3921,34 @@
         <v>250</v>
       </c>
       <c r="M26" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q26" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="S26" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T26" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="U26" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="V26" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="W26" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -3949,34 +3971,34 @@
         <v>265</v>
       </c>
       <c r="M27" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Q27" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="S27" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T27" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="U27" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="V27" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="W27" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X27">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -3999,34 +4021,34 @@
         <v>266</v>
       </c>
       <c r="M28" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="Q28" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="S28" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T28" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="U28" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="V28" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="W28" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X28">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -4049,37 +4071,37 @@
         <v>267</v>
       </c>
       <c r="L29" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M29" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q29" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="S29" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T29" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="U29" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="V29" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="W29" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X29">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -4102,34 +4124,34 @@
         <v>268</v>
       </c>
       <c r="M30" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q30" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="S30" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T30" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="U30" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="V30" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="W30" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X30">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -4152,34 +4174,34 @@
         <v>269</v>
       </c>
       <c r="M31" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="Q31" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="S31" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T31" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="U31" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="V31" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="W31" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X31">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -4202,31 +4224,31 @@
         <v>270</v>
       </c>
       <c r="M32" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="S32" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="T32" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="U32" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="V32" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="W32" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="X32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -4249,31 +4271,31 @@
         <v>271</v>
       </c>
       <c r="M33" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="S33" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="T33" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="U33" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="V33" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="W33" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X33">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -4296,31 +4318,31 @@
         <v>263</v>
       </c>
       <c r="M34" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="S34" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T34" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="U34" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="V34" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="W34" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -4343,25 +4365,25 @@
         <v>264</v>
       </c>
       <c r="M35" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="S35" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T35" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="W35" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="X35">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -4384,31 +4406,31 @@
         <v>272</v>
       </c>
       <c r="M36" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="Q36" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="S36" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T36" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="U36" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="W36" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="X36">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -4431,31 +4453,31 @@
         <v>250</v>
       </c>
       <c r="M37" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="S37" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T37" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="U37" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="V37" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="W37" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X37">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -4478,34 +4500,34 @@
         <v>250</v>
       </c>
       <c r="L38" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M38" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="S38" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T38" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="U38" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="V38" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="W38" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>45</v>
       </c>
@@ -4528,31 +4550,31 @@
         <v>250</v>
       </c>
       <c r="M39" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="S39" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T39" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="U39" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="V39" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="W39" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X39">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>46</v>
       </c>
@@ -4575,25 +4597,25 @@
         <v>259</v>
       </c>
       <c r="M40" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="S40" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T40" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="W40" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="X40">
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -4616,37 +4638,37 @@
         <v>273</v>
       </c>
       <c r="L41" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M41" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Q41" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="S41" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T41" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="U41" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="V41" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="W41" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -4669,34 +4691,34 @@
         <v>274</v>
       </c>
       <c r="L42" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M42" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="S42" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T42" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="U42" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="V42" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="W42" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="X42">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -4719,34 +4741,34 @@
         <v>275</v>
       </c>
       <c r="M43" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="Q43" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="S43" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="T43" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="U43" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="V43" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="W43" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="X43">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -4769,25 +4791,25 @@
         <v>276</v>
       </c>
       <c r="M44" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="S44" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="T44" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="W44" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="X44">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -4810,31 +4832,31 @@
         <v>250</v>
       </c>
       <c r="M45" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="S45" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T45" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="U45" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="V45" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="W45" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X45">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -4857,31 +4879,31 @@
         <v>250</v>
       </c>
       <c r="M46" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="S46" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T46" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="U46" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="V46" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="W46" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X46">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -4904,34 +4926,34 @@
         <v>277</v>
       </c>
       <c r="M47" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q47" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="S47" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="T47" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="U47" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="V47" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="W47" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X47">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -4954,37 +4976,37 @@
         <v>278</v>
       </c>
       <c r="L48" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M48" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="Q48" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="S48" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="T48" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="U48" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="V48" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="W48" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="X48">
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>29</v>
       </c>
@@ -5007,31 +5029,31 @@
         <v>279</v>
       </c>
       <c r="M49" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S49" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="T49" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="U49" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="V49" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="W49" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="X49">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>29</v>
       </c>
@@ -5054,34 +5076,34 @@
         <v>280</v>
       </c>
       <c r="M50" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="Q50" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="S50" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T50" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="U50" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="V50" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="W50" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="X50">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -5104,31 +5126,31 @@
         <v>256</v>
       </c>
       <c r="M51" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="S51" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="T51" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="U51" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="V51" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="W51" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="X51">
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -5151,31 +5173,31 @@
         <v>250</v>
       </c>
       <c r="M52" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="S52" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T52" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="U52" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="V52" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="W52" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X52">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -5198,34 +5220,34 @@
         <v>281</v>
       </c>
       <c r="L53" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M53" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="S53" t="s">
         <v>59</v>
       </c>
       <c r="T53" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="U53" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="V53" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="W53" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="X53">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -5248,31 +5270,31 @@
         <v>282</v>
       </c>
       <c r="M54" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="S54" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="T54" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="U54" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="V54" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="W54" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X54">
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -5295,34 +5317,34 @@
         <v>262</v>
       </c>
       <c r="M55" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q55" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="S55" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="T55" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="U55" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="V55" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="W55" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="X55">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -5345,37 +5367,37 @@
         <v>283</v>
       </c>
       <c r="L56" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M56" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q56" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="S56" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="T56" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="U56" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="V56" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="W56" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="X56">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -5398,34 +5420,34 @@
         <v>284</v>
       </c>
       <c r="L57" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M57" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="S57" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="U57" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="V57" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="W57" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X57">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -5448,31 +5470,31 @@
         <v>250</v>
       </c>
       <c r="M58" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="S58" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="T58" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="U58" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="V58" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="W58" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X58">
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -5495,31 +5517,31 @@
         <v>250</v>
       </c>
       <c r="M59" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="S59" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="T59" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="U59" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="V59" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="W59" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X59">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -5542,31 +5564,31 @@
         <v>285</v>
       </c>
       <c r="M60" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="S60" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T60" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="U60" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="V60" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="W60" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X60">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -5589,31 +5611,31 @@
         <v>250</v>
       </c>
       <c r="M61" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="S61" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T61" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="U61" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="V61" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="W61" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X61">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>59</v>
       </c>
@@ -5636,31 +5658,31 @@
         <v>286</v>
       </c>
       <c r="M62" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="S62" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T62" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="U62" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="V62" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="W62" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X62">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>46</v>
       </c>
@@ -5683,37 +5705,37 @@
         <v>287</v>
       </c>
       <c r="L63" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M63" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q63" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="S63" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T63" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="U63" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="V63" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="W63" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X63">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>60</v>
       </c>
@@ -5736,34 +5758,34 @@
         <v>276</v>
       </c>
       <c r="M64" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Q64" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="S64" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="T64" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="U64" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V64" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="W64" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="X64">
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:24">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>61</v>
       </c>
@@ -5786,31 +5808,31 @@
         <v>288</v>
       </c>
       <c r="M65" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="S65" t="s">
         <v>59</v>
       </c>
       <c r="T65" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="U65" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="V65" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="W65" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X65">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:24">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>62</v>
       </c>
@@ -5830,31 +5852,31 @@
         <v>251</v>
       </c>
       <c r="M66" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="S66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T66" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="U66" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="V66" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="W66" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X66">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:24">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>52</v>
       </c>
@@ -5877,25 +5899,25 @@
         <v>264</v>
       </c>
       <c r="M67" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="S67" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T67" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="W67" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="X67">
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:24">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>63</v>
       </c>
@@ -5918,34 +5940,34 @@
         <v>289</v>
       </c>
       <c r="M68" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="O68" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="S68" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="T68" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="U68" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="V68" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="W68" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="X68">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:24">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>64</v>
       </c>
@@ -5971,31 +5993,31 @@
         <v>290</v>
       </c>
       <c r="M69" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="S69" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="T69" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="U69" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="V69" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="W69" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X69">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:24">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>65</v>
       </c>
@@ -6018,31 +6040,31 @@
         <v>271</v>
       </c>
       <c r="M70" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="S70" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="T70" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="U70" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="V70" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="W70" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X70">
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:24">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>66</v>
       </c>
@@ -6065,34 +6087,34 @@
         <v>291</v>
       </c>
       <c r="M71" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="Q71" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="S71" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="T71" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="U71" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="V71" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="W71" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="X71">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:24">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>52</v>
       </c>
@@ -6115,25 +6137,25 @@
         <v>292</v>
       </c>
       <c r="M72" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S72" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T72" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="W72" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="X72">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:24">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>67</v>
       </c>
@@ -6153,28 +6175,28 @@
         <v>293</v>
       </c>
       <c r="M73" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S73" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="T73" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="U73" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="W73" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="X73">
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:24">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>41</v>
       </c>
@@ -6197,31 +6219,31 @@
         <v>294</v>
       </c>
       <c r="M74" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="S74" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T74" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="U74" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="V74" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="W74" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="X74">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:24">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>68</v>
       </c>
@@ -6244,31 +6266,31 @@
         <v>250</v>
       </c>
       <c r="M75" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="S75" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T75" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="U75" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="V75" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="W75" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X75">
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:24">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>68</v>
       </c>
@@ -6291,31 +6313,31 @@
         <v>295</v>
       </c>
       <c r="M76" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="S76" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T76" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="U76" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="V76" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="W76" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X76">
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:24">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>68</v>
       </c>
@@ -6338,31 +6360,31 @@
         <v>250</v>
       </c>
       <c r="M77" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="S77" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T77" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="U77" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="V77" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="W77" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X77">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:24">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>68</v>
       </c>
@@ -6385,31 +6407,31 @@
         <v>250</v>
       </c>
       <c r="M78" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="S78" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T78" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="U78" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="V78" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="W78" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X78">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:24">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>69</v>
       </c>
@@ -6432,25 +6454,25 @@
         <v>296</v>
       </c>
       <c r="M79" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="S79" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T79" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="W79" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="X79">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:24">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>62</v>
       </c>
@@ -6473,31 +6495,31 @@
         <v>250</v>
       </c>
       <c r="M80" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="S80" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T80" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="U80" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="V80" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="W80" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X80">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:24">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>62</v>
       </c>
@@ -6520,31 +6542,31 @@
         <v>297</v>
       </c>
       <c r="M81" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S81" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="T81" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="U81" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="V81" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="W81" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X81">
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:24">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>62</v>
       </c>
@@ -6567,31 +6589,31 @@
         <v>250</v>
       </c>
       <c r="M82" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S82" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T82" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="U82" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="V82" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="W82" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X82">
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:24">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>62</v>
       </c>
@@ -6614,31 +6636,31 @@
         <v>298</v>
       </c>
       <c r="M83" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S83" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="T83" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="U83" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="V83" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="W83" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X83">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:24">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>62</v>
       </c>
@@ -6661,31 +6683,31 @@
         <v>250</v>
       </c>
       <c r="M84" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S84" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T84" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="U84" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="V84" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="W84" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X84">
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:24">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>70</v>
       </c>
@@ -6708,34 +6730,34 @@
         <v>272</v>
       </c>
       <c r="M85" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="Q85" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="S85" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="T85" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="U85" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="V85" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="W85" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X85">
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:24">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>71</v>
       </c>
@@ -6758,34 +6780,34 @@
         <v>299</v>
       </c>
       <c r="M86" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Q86" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="S86" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="T86" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="U86" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="V86" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="W86" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="X86">
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:24">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>72</v>
       </c>
@@ -6808,34 +6830,34 @@
         <v>253</v>
       </c>
       <c r="M87" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="Q87" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="S87" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T87" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="U87" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="V87" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="W87" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X87">
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:24">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>73</v>
       </c>
@@ -6858,25 +6880,25 @@
         <v>300</v>
       </c>
       <c r="M88" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="S88" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="T88" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="W88" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="X88">
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:24">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>73</v>
       </c>
@@ -6899,37 +6921,37 @@
         <v>273</v>
       </c>
       <c r="M89" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="O89" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="Q89" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="S89" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T89" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="U89" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="V89" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="W89" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X89">
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:24">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>74</v>
       </c>
@@ -6952,25 +6974,25 @@
         <v>253</v>
       </c>
       <c r="M90" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="S90" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T90" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="W90" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="X90">
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:24">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>75</v>
       </c>
@@ -6993,31 +7015,31 @@
         <v>250</v>
       </c>
       <c r="M91" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="S91" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T91" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="U91" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="V91" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="W91" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X91">
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:24">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>76</v>
       </c>
@@ -7037,34 +7059,34 @@
         <v>244</v>
       </c>
       <c r="J92" t="s">
-        <v>301</v>
+        <v>763</v>
       </c>
       <c r="M92" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="S92" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="T92" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="U92" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="V92" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="W92" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="X92">
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:24">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>77</v>
       </c>
@@ -7087,34 +7109,34 @@
         <v>272</v>
       </c>
       <c r="M93" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="Q93" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="S93" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T93" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="U93" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="V93" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="W93" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X93">
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:24">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>77</v>
       </c>
@@ -7134,37 +7156,37 @@
         <v>225</v>
       </c>
       <c r="J94" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="M94" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Q94" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="S94" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T94" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="U94" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="V94" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="W94" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X94">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:24">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>78</v>
       </c>
@@ -7184,28 +7206,28 @@
         <v>245</v>
       </c>
       <c r="J95" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M95" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="S95" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T95" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="W95" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="X95">
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:24">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>79</v>
       </c>
@@ -7225,31 +7247,31 @@
         <v>246</v>
       </c>
       <c r="J96" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="M96" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="S96" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T96" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="U96" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="W96" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="X96">
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:24">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>80</v>
       </c>
@@ -7269,37 +7291,37 @@
         <v>245</v>
       </c>
       <c r="J97" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M97" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="Q97" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="S97" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="T97" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="U97" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="V97" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="W97" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="X97">
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:24">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>81</v>
       </c>
@@ -7319,37 +7341,37 @@
         <v>247</v>
       </c>
       <c r="J98" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M98" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q98" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="S98" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="T98" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="U98" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="V98" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="W98" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X98">
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:24">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>81</v>
       </c>
@@ -7369,37 +7391,37 @@
         <v>247</v>
       </c>
       <c r="J99" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M99" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="Q99" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="S99" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="T99" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="U99" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="V99" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="W99" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X99">
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:24">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>82</v>
       </c>
@@ -7425,34 +7447,34 @@
         <v>264</v>
       </c>
       <c r="M100" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="Q100" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="S100" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T100" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="U100" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="V100" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="W100" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X100">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:24">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>82</v>
       </c>
@@ -7475,34 +7497,34 @@
         <v>214</v>
       </c>
       <c r="J101" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M101" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="S101" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="T101" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="U101" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="V101" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="W101" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X101">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:24">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>62</v>
       </c>
@@ -7525,31 +7547,31 @@
         <v>250</v>
       </c>
       <c r="M102" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="S102" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T102" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="U102" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="V102" t="s">
+        <v>746</v>
+      </c>
+      <c r="W102" t="s">
         <v>747</v>
-      </c>
-      <c r="W102" t="s">
-        <v>748</v>
       </c>
       <c r="X102">
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:24">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>62</v>
       </c>
@@ -7572,31 +7594,31 @@
         <v>250</v>
       </c>
       <c r="M103" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="S103" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T103" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="U103" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="V103" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="W103" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="X103">
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:24">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>83</v>
       </c>
@@ -7613,28 +7635,28 @@
         <v>211</v>
       </c>
       <c r="J104" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M104" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="S104" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="T104" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="W104" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="X104">
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:24">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>46</v>
       </c>
@@ -7654,37 +7676,37 @@
         <v>225</v>
       </c>
       <c r="J105" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M105" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="Q105" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="S105" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="T105" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="U105" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="V105" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="W105" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X105">
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:24">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>84</v>
       </c>
@@ -7704,37 +7726,37 @@
         <v>245</v>
       </c>
       <c r="J106" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M106" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="Q106" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="S106" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T106" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="U106" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V106" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="W106" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="X106">
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:24">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>85</v>
       </c>
@@ -7751,28 +7773,28 @@
         <v>212</v>
       </c>
       <c r="J107" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M107" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="S107" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="T107" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="W107" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="X107">
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:24">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>77</v>
       </c>
@@ -7792,34 +7814,34 @@
         <v>240</v>
       </c>
       <c r="J108" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="M108" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="S108" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T108" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="U108" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="V108" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="W108" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="X108">
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:24">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>86</v>
       </c>
@@ -7842,28 +7864,28 @@
         <v>261</v>
       </c>
       <c r="M109" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="N109" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q109" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="S109" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="T109" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="U109" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="V109" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="W109" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="X109">
         <v>1</v>
@@ -7871,114 +7893,114 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N2" r:id="rId1"/>
-    <hyperlink ref="N3" r:id="rId2"/>
-    <hyperlink ref="N4" r:id="rId3"/>
-    <hyperlink ref="N5" r:id="rId4"/>
-    <hyperlink ref="N6" r:id="rId5"/>
-    <hyperlink ref="N7" r:id="rId6"/>
-    <hyperlink ref="N8" r:id="rId7"/>
-    <hyperlink ref="N9" r:id="rId8"/>
-    <hyperlink ref="N10" r:id="rId9"/>
-    <hyperlink ref="N11" r:id="rId10"/>
-    <hyperlink ref="N12" r:id="rId11"/>
-    <hyperlink ref="N13" r:id="rId12"/>
-    <hyperlink ref="N14" r:id="rId13"/>
-    <hyperlink ref="N15" r:id="rId14"/>
-    <hyperlink ref="N16" r:id="rId15"/>
-    <hyperlink ref="N17" r:id="rId16"/>
-    <hyperlink ref="N18" r:id="rId17"/>
-    <hyperlink ref="N19" r:id="rId18"/>
-    <hyperlink ref="N20" r:id="rId19"/>
-    <hyperlink ref="N21" r:id="rId20"/>
-    <hyperlink ref="N22" r:id="rId21"/>
-    <hyperlink ref="N23" r:id="rId22"/>
-    <hyperlink ref="N24" r:id="rId23"/>
-    <hyperlink ref="N25" r:id="rId24"/>
-    <hyperlink ref="N26" r:id="rId25"/>
-    <hyperlink ref="N27" r:id="rId26"/>
-    <hyperlink ref="N28" r:id="rId27"/>
-    <hyperlink ref="N29" r:id="rId28"/>
-    <hyperlink ref="N30" r:id="rId29"/>
-    <hyperlink ref="N31" r:id="rId30"/>
-    <hyperlink ref="N32" r:id="rId31"/>
-    <hyperlink ref="N33" r:id="rId32"/>
-    <hyperlink ref="N34" r:id="rId33"/>
-    <hyperlink ref="N35" r:id="rId34"/>
-    <hyperlink ref="N36" r:id="rId35"/>
-    <hyperlink ref="N37" r:id="rId36"/>
-    <hyperlink ref="N38" r:id="rId37"/>
-    <hyperlink ref="N39" r:id="rId38"/>
-    <hyperlink ref="N40" r:id="rId39"/>
-    <hyperlink ref="N41" r:id="rId40"/>
-    <hyperlink ref="N42" r:id="rId41"/>
-    <hyperlink ref="N43" r:id="rId42"/>
-    <hyperlink ref="N44" r:id="rId43"/>
-    <hyperlink ref="N45" r:id="rId44"/>
-    <hyperlink ref="N46" r:id="rId45"/>
-    <hyperlink ref="N47" r:id="rId46"/>
-    <hyperlink ref="N48" r:id="rId47"/>
-    <hyperlink ref="N49" r:id="rId48"/>
-    <hyperlink ref="N50" r:id="rId49"/>
-    <hyperlink ref="N51" r:id="rId50"/>
-    <hyperlink ref="N52" r:id="rId51"/>
-    <hyperlink ref="N53" r:id="rId52"/>
-    <hyperlink ref="N54" r:id="rId53"/>
-    <hyperlink ref="N55" r:id="rId54"/>
-    <hyperlink ref="N56" r:id="rId55"/>
-    <hyperlink ref="N57" r:id="rId56"/>
-    <hyperlink ref="N58" r:id="rId57"/>
-    <hyperlink ref="N59" r:id="rId58"/>
-    <hyperlink ref="N60" r:id="rId59"/>
-    <hyperlink ref="N61" r:id="rId60"/>
-    <hyperlink ref="N62" r:id="rId61"/>
-    <hyperlink ref="N63" r:id="rId62"/>
-    <hyperlink ref="N64" r:id="rId63"/>
-    <hyperlink ref="N65" r:id="rId64"/>
-    <hyperlink ref="N66" r:id="rId65"/>
-    <hyperlink ref="N67" r:id="rId66"/>
-    <hyperlink ref="N68" r:id="rId67"/>
-    <hyperlink ref="N69" r:id="rId68"/>
-    <hyperlink ref="N70" r:id="rId69"/>
-    <hyperlink ref="N71" r:id="rId70"/>
-    <hyperlink ref="N72" r:id="rId71"/>
-    <hyperlink ref="N73" r:id="rId72"/>
-    <hyperlink ref="N74" r:id="rId73"/>
-    <hyperlink ref="N75" r:id="rId74"/>
-    <hyperlink ref="N76" r:id="rId75"/>
-    <hyperlink ref="N77" r:id="rId76"/>
-    <hyperlink ref="N78" r:id="rId77"/>
-    <hyperlink ref="N79" r:id="rId78"/>
-    <hyperlink ref="N80" r:id="rId79"/>
-    <hyperlink ref="N81" r:id="rId80"/>
-    <hyperlink ref="N82" r:id="rId81"/>
-    <hyperlink ref="N83" r:id="rId82"/>
-    <hyperlink ref="N84" r:id="rId83"/>
-    <hyperlink ref="N85" r:id="rId84"/>
-    <hyperlink ref="N86" r:id="rId85"/>
-    <hyperlink ref="N87" r:id="rId86"/>
-    <hyperlink ref="N88" r:id="rId87"/>
-    <hyperlink ref="N89" r:id="rId88"/>
-    <hyperlink ref="N90" r:id="rId89"/>
-    <hyperlink ref="N91" r:id="rId90"/>
-    <hyperlink ref="N92" r:id="rId91"/>
-    <hyperlink ref="N93" r:id="rId92"/>
-    <hyperlink ref="N94" r:id="rId93"/>
-    <hyperlink ref="N95" r:id="rId94"/>
-    <hyperlink ref="N96" r:id="rId95"/>
-    <hyperlink ref="N97" r:id="rId96"/>
-    <hyperlink ref="N98" r:id="rId97"/>
-    <hyperlink ref="N99" r:id="rId98"/>
-    <hyperlink ref="N100" r:id="rId99"/>
-    <hyperlink ref="N101" r:id="rId100"/>
-    <hyperlink ref="N102" r:id="rId101"/>
-    <hyperlink ref="N103" r:id="rId102"/>
-    <hyperlink ref="N104" r:id="rId103"/>
-    <hyperlink ref="N105" r:id="rId104"/>
-    <hyperlink ref="N106" r:id="rId105"/>
-    <hyperlink ref="N107" r:id="rId106"/>
-    <hyperlink ref="N108" r:id="rId107"/>
-    <hyperlink ref="N109" r:id="rId108"/>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="N5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="N6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="N17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="N18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="N22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="N23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="N24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="N25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="N28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="N31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="N32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="N33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="N35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="N36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="N37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="N38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="N39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="N40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="N41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="N42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="N43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="N44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="N45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="N46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="N47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="N48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="N49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="N50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="N51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="N52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="N53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="N54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="N55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="N56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="N57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="N58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="N59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="N60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="N61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="N62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="N63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="N64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="N65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="N66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="N67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="N68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="N69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="N70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="N71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="N72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="N73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="N74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="N75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="N76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="N77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="N78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="N79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="N80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="N81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="N82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="N83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="N84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="N85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="N86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="N87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="N88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="N89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="N90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="N91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="N92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="N93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="N94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="N95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="N96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="N97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="N98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="N99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="N100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="N101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="N102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="N103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="N104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="N105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="N106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="N107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="N108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="N109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D92A665-3063-4EA3-A973-1A35A9202761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E5B540-9BA1-4D6C-96C5-4B95F7C0355B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="613">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -1853,6 +1853,12 @@
   </si>
   <si>
     <t>Bois de chêne</t>
+  </si>
+  <si>
+    <t>Ronde-bosse</t>
+  </si>
+  <si>
+    <t>Moument funéraire</t>
   </si>
 </sst>
 </file>
@@ -1905,66 +1911,24 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4B183"/>
-          <bgColor rgb="FFF4B183"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6E0B4"/>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4B183"/>
-          <bgColor rgb="FFF4B183"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6E0B4"/>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2263,9 +2227,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V109"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="11" max="11" width="9.140625" style="2"/>
+    <col min="17" max="17" width="28.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2296,7 +2264,7 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -2333,7 +2301,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -2349,8 +2317,11 @@
       <c r="I2" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="3" t="s">
         <v>27</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>611</v>
       </c>
       <c r="R2" t="s">
         <v>28</v>
@@ -2368,7 +2339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -2387,8 +2358,11 @@
       <c r="I3" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="3" t="s">
         <v>34</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>611</v>
       </c>
       <c r="R3" t="s">
         <v>28</v>
@@ -2406,7 +2380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -2425,8 +2399,11 @@
       <c r="I4" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="3" t="s">
         <v>38</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>611</v>
       </c>
       <c r="R4" t="s">
         <v>39</v>
@@ -2444,7 +2421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -2463,8 +2440,11 @@
       <c r="I5" t="s">
         <v>42</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="3" t="s">
         <v>43</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>611</v>
       </c>
       <c r="R5" t="s">
         <v>28</v>
@@ -2482,7 +2462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -2501,8 +2481,11 @@
       <c r="I6" t="s">
         <v>47</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>611</v>
       </c>
       <c r="R6" t="s">
         <v>28</v>
@@ -2520,7 +2503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -2542,8 +2525,11 @@
       <c r="I7" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" s="3" t="s">
         <v>56</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>611</v>
       </c>
       <c r="R7" t="s">
         <v>57</v>
@@ -2555,7 +2541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -2577,8 +2563,11 @@
       <c r="J8" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" s="3" t="s">
         <v>65</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>611</v>
       </c>
       <c r="R8" t="s">
         <v>28</v>
@@ -2596,7 +2585,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>59</v>
       </c>
@@ -2621,8 +2610,11 @@
       <c r="J9" t="s">
         <v>69</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" s="3" t="s">
         <v>70</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>611</v>
       </c>
       <c r="R9" t="s">
         <v>71</v>
@@ -2640,7 +2632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>59</v>
       </c>
@@ -2662,8 +2654,11 @@
       <c r="J10" t="s">
         <v>74</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10" s="3" t="s">
         <v>75</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>611</v>
       </c>
       <c r="R10" t="s">
         <v>28</v>
@@ -2681,7 +2676,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>76</v>
       </c>
@@ -2703,8 +2698,11 @@
       <c r="J11" t="s">
         <v>80</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" s="3" t="s">
         <v>81</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>611</v>
       </c>
       <c r="R11" t="s">
         <v>28</v>
@@ -2722,7 +2720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>82</v>
       </c>
@@ -2741,8 +2739,11 @@
       <c r="I12" t="s">
         <v>85</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" s="3" t="s">
         <v>86</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>611</v>
       </c>
       <c r="R12" t="s">
         <v>28</v>
@@ -2760,7 +2761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>82</v>
       </c>
@@ -2782,8 +2783,11 @@
       <c r="I13" t="s">
         <v>90</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" s="3" t="s">
         <v>91</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>611</v>
       </c>
       <c r="R13" t="s">
         <v>92</v>
@@ -2801,7 +2805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -2820,8 +2824,11 @@
       <c r="I14" t="s">
         <v>95</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" s="3" t="s">
         <v>96</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>611</v>
       </c>
       <c r="R14" t="s">
         <v>97</v>
@@ -2839,7 +2846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>93</v>
       </c>
@@ -2858,8 +2865,11 @@
       <c r="I15" t="s">
         <v>99</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" s="3" t="s">
         <v>100</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>611</v>
       </c>
       <c r="R15" t="s">
         <v>28</v>
@@ -2877,7 +2887,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>93</v>
       </c>
@@ -2896,8 +2906,11 @@
       <c r="I16" t="s">
         <v>102</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" s="3" t="s">
         <v>103</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>611</v>
       </c>
       <c r="R16" t="s">
         <v>28</v>
@@ -2915,7 +2928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>104</v>
       </c>
@@ -2937,8 +2950,11 @@
       <c r="J17" t="s">
         <v>109</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" s="3" t="s">
         <v>110</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>611</v>
       </c>
       <c r="R17" t="s">
         <v>111</v>
@@ -2956,7 +2972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>104</v>
       </c>
@@ -2978,8 +2994,11 @@
       <c r="J18" t="s">
         <v>113</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" s="3" t="s">
         <v>114</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>611</v>
       </c>
       <c r="R18" t="s">
         <v>28</v>
@@ -2997,7 +3016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>104</v>
       </c>
@@ -3019,8 +3038,11 @@
       <c r="J19" t="s">
         <v>116</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" s="3" t="s">
         <v>117</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>611</v>
       </c>
       <c r="R19" t="s">
         <v>28</v>
@@ -3038,7 +3060,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>118</v>
       </c>
@@ -3063,8 +3085,11 @@
       <c r="J20" t="s">
         <v>124</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="K20" s="3" t="s">
         <v>125</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>611</v>
       </c>
       <c r="R20" t="s">
         <v>28</v>
@@ -3082,7 +3107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>126</v>
       </c>
@@ -3101,8 +3126,11 @@
       <c r="I21" t="s">
         <v>131</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K21" s="3" t="s">
         <v>132</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>611</v>
       </c>
       <c r="R21" t="s">
         <v>133</v>
@@ -3117,7 +3145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>134</v>
       </c>
@@ -3139,8 +3167,11 @@
       <c r="I22" t="s">
         <v>55</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K22" s="3" t="s">
         <v>138</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>611</v>
       </c>
       <c r="R22" t="s">
         <v>28</v>
@@ -3155,7 +3186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>139</v>
       </c>
@@ -3174,8 +3205,11 @@
       <c r="I23" t="s">
         <v>144</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="K23" s="3" t="s">
         <v>145</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>611</v>
       </c>
       <c r="R23" t="s">
         <v>146</v>
@@ -3187,7 +3221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>147</v>
       </c>
@@ -3206,8 +3240,11 @@
       <c r="I24" t="s">
         <v>152</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" s="3" t="s">
         <v>153</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>611</v>
       </c>
       <c r="R24" t="s">
         <v>154</v>
@@ -3225,7 +3262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>155</v>
       </c>
@@ -3247,8 +3284,11 @@
       <c r="J25" t="s">
         <v>160</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" s="3" t="s">
         <v>161</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>611</v>
       </c>
       <c r="R25" t="s">
         <v>28</v>
@@ -3266,7 +3306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>155</v>
       </c>
@@ -3288,8 +3328,11 @@
       <c r="J26" t="s">
         <v>164</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="K26" s="3" t="s">
         <v>165</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>611</v>
       </c>
       <c r="R26" t="s">
         <v>28</v>
@@ -3307,7 +3350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>155</v>
       </c>
@@ -3329,8 +3372,11 @@
       <c r="J27" t="s">
         <v>168</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="K27" s="3" t="s">
         <v>169</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>611</v>
       </c>
       <c r="R27" t="s">
         <v>28</v>
@@ -3348,7 +3394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>155</v>
       </c>
@@ -3370,8 +3416,11 @@
       <c r="J28" t="s">
         <v>174</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="K28" s="3" t="s">
         <v>175</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>611</v>
       </c>
       <c r="R28" t="s">
         <v>28</v>
@@ -3389,7 +3438,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>155</v>
       </c>
@@ -3414,8 +3463,11 @@
       <c r="J29" t="s">
         <v>180</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="K29" s="3" t="s">
         <v>181</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>611</v>
       </c>
       <c r="R29" t="s">
         <v>28</v>
@@ -3433,7 +3485,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>155</v>
       </c>
@@ -3455,8 +3507,11 @@
       <c r="J30" t="s">
         <v>185</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="K30" s="3" t="s">
         <v>186</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>611</v>
       </c>
       <c r="R30" t="s">
         <v>28</v>
@@ -3474,7 +3529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>155</v>
       </c>
@@ -3496,8 +3551,11 @@
       <c r="J31" t="s">
         <v>191</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="K31" s="3" t="s">
         <v>192</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>611</v>
       </c>
       <c r="R31" t="s">
         <v>28</v>
@@ -3515,7 +3573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>193</v>
       </c>
@@ -3534,8 +3592,11 @@
       <c r="I32" t="s">
         <v>198</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="K32" s="3" t="s">
         <v>199</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>611</v>
       </c>
       <c r="R32" t="s">
         <v>200</v>
@@ -3553,7 +3614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>201</v>
       </c>
@@ -3572,8 +3633,11 @@
       <c r="I33" t="s">
         <v>205</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="K33" s="3" t="s">
         <v>206</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>611</v>
       </c>
       <c r="R33" t="s">
         <v>154</v>
@@ -3591,7 +3655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>207</v>
       </c>
@@ -3610,8 +3674,11 @@
       <c r="I34" t="s">
         <v>211</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="K34" s="3" t="s">
         <v>212</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>611</v>
       </c>
       <c r="R34" t="s">
         <v>28</v>
@@ -3629,7 +3696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>213</v>
       </c>
@@ -3648,8 +3715,11 @@
       <c r="I35" t="s">
         <v>216</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="K35" s="3" t="s">
         <v>217</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>611</v>
       </c>
       <c r="R35" t="s">
         <v>28</v>
@@ -3661,7 +3731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>155</v>
       </c>
@@ -3683,8 +3753,11 @@
       <c r="J36" t="s">
         <v>222</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K36" s="3" t="s">
         <v>223</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>611</v>
       </c>
       <c r="R36" t="s">
         <v>28</v>
@@ -3699,7 +3772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>224</v>
       </c>
@@ -3718,8 +3791,11 @@
       <c r="I37" t="s">
         <v>227</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="K37" s="3" t="s">
         <v>228</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>611</v>
       </c>
       <c r="R37" t="s">
         <v>28</v>
@@ -3737,7 +3813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>229</v>
       </c>
@@ -3759,8 +3835,11 @@
       <c r="I38" t="s">
         <v>233</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="K38" s="3" t="s">
         <v>234</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>611</v>
       </c>
       <c r="R38" t="s">
         <v>28</v>
@@ -3778,7 +3857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>229</v>
       </c>
@@ -3797,8 +3876,11 @@
       <c r="I39" t="s">
         <v>237</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="K39" s="3" t="s">
         <v>238</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>611</v>
       </c>
       <c r="R39" t="s">
         <v>28</v>
@@ -3816,7 +3898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>239</v>
       </c>
@@ -3835,8 +3917,11 @@
       <c r="I40" t="s">
         <v>242</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="K40" s="3" t="s">
         <v>243</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>611</v>
       </c>
       <c r="R40" t="s">
         <v>28</v>
@@ -3848,7 +3933,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>239</v>
       </c>
@@ -3873,8 +3958,11 @@
       <c r="J41" t="s">
         <v>248</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="K41" s="3" t="s">
         <v>249</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>611</v>
       </c>
       <c r="R41" t="s">
         <v>28</v>
@@ -3892,7 +3980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>250</v>
       </c>
@@ -3914,8 +4002,11 @@
       <c r="I42" t="s">
         <v>255</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="K42" s="3" t="s">
         <v>256</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>611</v>
       </c>
       <c r="R42" t="s">
         <v>28</v>
@@ -3933,7 +4024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>257</v>
       </c>
@@ -3955,8 +4046,11 @@
       <c r="J43" t="s">
         <v>261</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="K43" s="3" t="s">
         <v>262</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>611</v>
       </c>
       <c r="R43" t="s">
         <v>263</v>
@@ -3974,7 +4068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>264</v>
       </c>
@@ -3993,8 +4087,11 @@
       <c r="I44" t="s">
         <v>269</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="K44" s="3" t="s">
         <v>270</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>611</v>
       </c>
       <c r="R44" t="s">
         <v>271</v>
@@ -4006,7 +4103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>272</v>
       </c>
@@ -4025,8 +4122,11 @@
       <c r="I45" t="s">
         <v>274</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="K45" s="3" t="s">
         <v>275</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>611</v>
       </c>
       <c r="R45" t="s">
         <v>28</v>
@@ -4044,7 +4144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>272</v>
       </c>
@@ -4063,8 +4163,11 @@
       <c r="I46" t="s">
         <v>276</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="K46" s="3" t="s">
         <v>277</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>611</v>
       </c>
       <c r="R46" t="s">
         <v>28</v>
@@ -4082,7 +4185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>272</v>
       </c>
@@ -4104,8 +4207,11 @@
       <c r="J47" t="s">
         <v>281</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="K47" s="3" t="s">
         <v>282</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>611</v>
       </c>
       <c r="R47" t="s">
         <v>71</v>
@@ -4123,7 +4229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>283</v>
       </c>
@@ -4148,8 +4254,11 @@
       <c r="J48" t="s">
         <v>290</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="K48" s="3" t="s">
         <v>291</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>611</v>
       </c>
       <c r="R48" t="s">
         <v>292</v>
@@ -4167,7 +4276,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>59</v>
       </c>
@@ -4186,8 +4295,11 @@
       <c r="I49" t="s">
         <v>297</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="K49" s="3" t="s">
         <v>298</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>611</v>
       </c>
       <c r="R49" t="s">
         <v>299</v>
@@ -4205,7 +4317,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>59</v>
       </c>
@@ -4227,8 +4339,11 @@
       <c r="J50" t="s">
         <v>302</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="K50" s="3" t="s">
         <v>303</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>611</v>
       </c>
       <c r="R50" t="s">
         <v>28</v>
@@ -4246,7 +4361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>304</v>
       </c>
@@ -4265,8 +4380,11 @@
       <c r="I51" t="s">
         <v>307</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="K51" s="3" t="s">
         <v>308</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>611</v>
       </c>
       <c r="R51" t="s">
         <v>71</v>
@@ -4284,7 +4402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>309</v>
       </c>
@@ -4303,8 +4421,11 @@
       <c r="I52" t="s">
         <v>311</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="K52" s="3" t="s">
         <v>312</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>611</v>
       </c>
       <c r="R52" t="s">
         <v>28</v>
@@ -4322,7 +4443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>313</v>
       </c>
@@ -4344,8 +4465,11 @@
       <c r="I53" t="s">
         <v>317</v>
       </c>
-      <c r="K53" s="1" t="s">
+      <c r="K53" s="3" t="s">
         <v>318</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>611</v>
       </c>
       <c r="R53" t="s">
         <v>319</v>
@@ -4363,7 +4487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>320</v>
       </c>
@@ -4382,8 +4506,11 @@
       <c r="I54" t="s">
         <v>324</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="K54" s="3" t="s">
         <v>325</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>611</v>
       </c>
       <c r="R54" t="s">
         <v>263</v>
@@ -4401,7 +4528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>326</v>
       </c>
@@ -4423,8 +4550,11 @@
       <c r="J55" t="s">
         <v>330</v>
       </c>
-      <c r="K55" s="1" t="s">
+      <c r="K55" s="3" t="s">
         <v>331</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>611</v>
       </c>
       <c r="R55" t="s">
         <v>332</v>
@@ -4442,7 +4572,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>333</v>
       </c>
@@ -4467,8 +4597,11 @@
       <c r="J56" t="s">
         <v>337</v>
       </c>
-      <c r="K56" s="1" t="s">
+      <c r="K56" s="3" t="s">
         <v>338</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>611</v>
       </c>
       <c r="R56" t="s">
         <v>332</v>
@@ -4486,7 +4619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>339</v>
       </c>
@@ -4508,8 +4641,11 @@
       <c r="I57" t="s">
         <v>343</v>
       </c>
-      <c r="K57" s="1" t="s">
+      <c r="K57" s="3" t="s">
         <v>344</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>611</v>
       </c>
       <c r="R57" t="s">
         <v>28</v>
@@ -4527,7 +4663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>339</v>
       </c>
@@ -4546,8 +4682,11 @@
       <c r="I58" t="s">
         <v>345</v>
       </c>
-      <c r="K58" s="1" t="s">
+      <c r="K58" s="3" t="s">
         <v>346</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>611</v>
       </c>
       <c r="R58" t="s">
         <v>154</v>
@@ -4565,7 +4704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>339</v>
       </c>
@@ -4584,8 +4723,11 @@
       <c r="I59" t="s">
         <v>347</v>
       </c>
-      <c r="K59" s="1" t="s">
+      <c r="K59" s="3" t="s">
         <v>348</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>611</v>
       </c>
       <c r="R59" t="s">
         <v>349</v>
@@ -4603,7 +4745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>339</v>
       </c>
@@ -4622,8 +4764,11 @@
       <c r="I60" t="s">
         <v>352</v>
       </c>
-      <c r="K60" s="1" t="s">
+      <c r="K60" s="3" t="s">
         <v>353</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>611</v>
       </c>
       <c r="R60" t="s">
         <v>28</v>
@@ -4641,7 +4786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>319</v>
       </c>
@@ -4660,8 +4805,11 @@
       <c r="I61" t="s">
         <v>355</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="K61" s="3" t="s">
         <v>356</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>611</v>
       </c>
       <c r="R61" t="s">
         <v>28</v>
@@ -4679,45 +4827,48 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
+    <row r="62" spans="1:22" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="1">
         <v>1787</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="E62" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="I62" s="2" t="s">
+      <c r="I62" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="K62" s="3" t="s">
+      <c r="K62" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="R62" s="2" t="s">
+      <c r="Q62" t="s">
+        <v>611</v>
+      </c>
+      <c r="R62" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="S62" s="2">
+      <c r="S62" s="1">
         <v>173</v>
       </c>
-      <c r="T62" s="2">
+      <c r="T62" s="1">
         <v>105</v>
       </c>
-      <c r="U62" s="2">
+      <c r="U62" s="1">
         <v>80</v>
       </c>
-      <c r="V62" s="2">
+      <c r="V62" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>239</v>
       </c>
@@ -4742,8 +4893,11 @@
       <c r="J63" t="s">
         <v>366</v>
       </c>
-      <c r="K63" s="1" t="s">
+      <c r="K63" s="3" t="s">
         <v>367</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>611</v>
       </c>
       <c r="R63" t="s">
         <v>28</v>
@@ -4761,7 +4915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>368</v>
       </c>
@@ -4783,8 +4937,11 @@
       <c r="J64" t="s">
         <v>372</v>
       </c>
-      <c r="K64" s="1" t="s">
+      <c r="K64" s="3" t="s">
         <v>373</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>611</v>
       </c>
       <c r="R64" t="s">
         <v>374</v>
@@ -4802,7 +4959,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>375</v>
       </c>
@@ -4821,8 +4978,11 @@
       <c r="I65" t="s">
         <v>379</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="K65" s="3" t="s">
         <v>380</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>611</v>
       </c>
       <c r="R65" t="s">
         <v>319</v>
@@ -4840,7 +5000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>381</v>
       </c>
@@ -4856,8 +5016,11 @@
       <c r="I66" t="s">
         <v>384</v>
       </c>
-      <c r="K66" s="1" t="s">
+      <c r="K66" s="3" t="s">
         <v>385</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>611</v>
       </c>
       <c r="R66" t="s">
         <v>28</v>
@@ -4875,7 +5038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>304</v>
       </c>
@@ -4894,8 +5057,11 @@
       <c r="I67" t="s">
         <v>388</v>
       </c>
-      <c r="K67" s="1" t="s">
+      <c r="K67" s="3" t="s">
         <v>389</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>611</v>
       </c>
       <c r="R67" t="s">
         <v>28</v>
@@ -4907,7 +5073,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>390</v>
       </c>
@@ -4926,12 +5092,15 @@
       <c r="I68" t="s">
         <v>395</v>
       </c>
-      <c r="K68" s="1" t="s">
+      <c r="K68" s="3" t="s">
         <v>396</v>
       </c>
       <c r="L68" t="s">
         <v>397</v>
       </c>
+      <c r="Q68" t="s">
+        <v>611</v>
+      </c>
       <c r="R68" t="s">
         <v>398</v>
       </c>
@@ -4948,7 +5117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>399</v>
       </c>
@@ -4967,8 +5136,11 @@
       <c r="I69" t="s">
         <v>404</v>
       </c>
-      <c r="K69" s="1" t="s">
+      <c r="K69" s="3" t="s">
         <v>405</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>611</v>
       </c>
       <c r="R69" t="s">
         <v>154</v>
@@ -4986,7 +5158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>406</v>
       </c>
@@ -5005,8 +5177,11 @@
       <c r="I70" t="s">
         <v>409</v>
       </c>
-      <c r="K70" s="1" t="s">
+      <c r="K70" s="3" t="s">
         <v>410</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>611</v>
       </c>
       <c r="R70" t="s">
         <v>154</v>
@@ -5024,7 +5199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>411</v>
       </c>
@@ -5046,8 +5221,11 @@
       <c r="J71" t="s">
         <v>415</v>
       </c>
-      <c r="K71" s="1" t="s">
+      <c r="K71" s="3" t="s">
         <v>416</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>611</v>
       </c>
       <c r="R71" t="s">
         <v>417</v>
@@ -5065,7 +5243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>304</v>
       </c>
@@ -5084,8 +5262,11 @@
       <c r="I72" t="s">
         <v>422</v>
       </c>
-      <c r="K72" s="1" t="s">
+      <c r="K72" s="3" t="s">
         <v>423</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>611</v>
       </c>
       <c r="R72" t="s">
         <v>28</v>
@@ -5097,7 +5278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>425</v>
       </c>
@@ -5113,8 +5294,11 @@
       <c r="I73" t="s">
         <v>429</v>
       </c>
-      <c r="K73" s="1" t="s">
+      <c r="K73" s="3" t="s">
         <v>430</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>612</v>
       </c>
       <c r="R73" t="s">
         <v>431</v>
@@ -5129,7 +5313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>201</v>
       </c>
@@ -5148,8 +5332,11 @@
       <c r="I74" t="s">
         <v>434</v>
       </c>
-      <c r="K74" s="1" t="s">
+      <c r="K74" s="3" t="s">
         <v>435</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>611</v>
       </c>
       <c r="R74" t="s">
         <v>28</v>
@@ -5167,7 +5354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>436</v>
       </c>
@@ -5186,8 +5373,11 @@
       <c r="I75" t="s">
         <v>438</v>
       </c>
-      <c r="K75" s="1" t="s">
+      <c r="K75" s="3" t="s">
         <v>439</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>611</v>
       </c>
       <c r="R75" t="s">
         <v>28</v>
@@ -5205,7 +5395,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>436</v>
       </c>
@@ -5224,8 +5414,11 @@
       <c r="I76" t="s">
         <v>442</v>
       </c>
-      <c r="K76" s="1" t="s">
+      <c r="K76" s="3" t="s">
         <v>443</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>611</v>
       </c>
       <c r="R76" t="s">
         <v>28</v>
@@ -5243,7 +5436,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>436</v>
       </c>
@@ -5262,8 +5455,11 @@
       <c r="I77" t="s">
         <v>444</v>
       </c>
-      <c r="K77" s="1" t="s">
+      <c r="K77" s="3" t="s">
         <v>445</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>611</v>
       </c>
       <c r="R77" t="s">
         <v>28</v>
@@ -5281,7 +5477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>436</v>
       </c>
@@ -5300,8 +5496,11 @@
       <c r="I78" t="s">
         <v>446</v>
       </c>
-      <c r="K78" s="1" t="s">
+      <c r="K78" s="3" t="s">
         <v>447</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>611</v>
       </c>
       <c r="R78" t="s">
         <v>28</v>
@@ -5319,7 +5518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>448</v>
       </c>
@@ -5338,8 +5537,11 @@
       <c r="I79" t="s">
         <v>452</v>
       </c>
-      <c r="K79" s="1" t="s">
+      <c r="K79" s="3" t="s">
         <v>453</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>611</v>
       </c>
       <c r="R79" t="s">
         <v>28</v>
@@ -5351,7 +5553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>381</v>
       </c>
@@ -5370,8 +5572,11 @@
       <c r="I80" t="s">
         <v>455</v>
       </c>
-      <c r="K80" s="1" t="s">
+      <c r="K80" s="3" t="s">
         <v>456</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>611</v>
       </c>
       <c r="R80" t="s">
         <v>28</v>
@@ -5389,7 +5594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>381</v>
       </c>
@@ -5408,8 +5613,11 @@
       <c r="I81" t="s">
         <v>460</v>
       </c>
-      <c r="K81" s="1" t="s">
+      <c r="K81" s="3" t="s">
         <v>461</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>611</v>
       </c>
       <c r="R81" t="s">
         <v>462</v>
@@ -5427,7 +5635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>381</v>
       </c>
@@ -5446,8 +5654,11 @@
       <c r="I82" t="s">
         <v>463</v>
       </c>
-      <c r="K82" s="1" t="s">
+      <c r="K82" s="3" t="s">
         <v>464</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>611</v>
       </c>
       <c r="R82" t="s">
         <v>28</v>
@@ -5465,7 +5676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>381</v>
       </c>
@@ -5484,8 +5695,11 @@
       <c r="I83" t="s">
         <v>467</v>
       </c>
-      <c r="K83" s="1" t="s">
+      <c r="K83" s="3" t="s">
         <v>468</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>611</v>
       </c>
       <c r="R83" t="s">
         <v>71</v>
@@ -5503,7 +5717,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>381</v>
       </c>
@@ -5522,8 +5736,11 @@
       <c r="I84" t="s">
         <v>469</v>
       </c>
-      <c r="K84" s="1" t="s">
+      <c r="K84" s="3" t="s">
         <v>470</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>611</v>
       </c>
       <c r="R84" t="s">
         <v>28</v>
@@ -5541,7 +5758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>471</v>
       </c>
@@ -5563,8 +5780,11 @@
       <c r="J85" t="s">
         <v>475</v>
       </c>
-      <c r="K85" s="1" t="s">
+      <c r="K85" s="3" t="s">
         <v>476</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>611</v>
       </c>
       <c r="R85" t="s">
         <v>477</v>
@@ -5582,7 +5802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>478</v>
       </c>
@@ -5604,8 +5824,11 @@
       <c r="J86" t="s">
         <v>482</v>
       </c>
-      <c r="K86" s="1" t="s">
+      <c r="K86" s="3" t="s">
         <v>483</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>611</v>
       </c>
       <c r="R86" t="s">
         <v>71</v>
@@ -5623,7 +5846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>484</v>
       </c>
@@ -5645,8 +5868,11 @@
       <c r="J87" t="s">
         <v>487</v>
       </c>
-      <c r="K87" s="1" t="s">
+      <c r="K87" s="3" t="s">
         <v>488</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>611</v>
       </c>
       <c r="R87" t="s">
         <v>28</v>
@@ -5664,7 +5890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>489</v>
       </c>
@@ -5683,8 +5909,11 @@
       <c r="I88" t="s">
         <v>493</v>
       </c>
-      <c r="K88" s="1" t="s">
+      <c r="K88" s="3" t="s">
         <v>494</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>611</v>
       </c>
       <c r="R88" t="s">
         <v>154</v>
@@ -5696,7 +5925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>489</v>
       </c>
@@ -5718,12 +5947,15 @@
       <c r="J89" t="s">
         <v>496</v>
       </c>
-      <c r="K89" s="1" t="s">
+      <c r="K89" s="3" t="s">
         <v>497</v>
       </c>
       <c r="L89" t="s">
         <v>498</v>
       </c>
+      <c r="Q89" t="s">
+        <v>611</v>
+      </c>
       <c r="R89" t="s">
         <v>28</v>
       </c>
@@ -5740,7 +5972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>499</v>
       </c>
@@ -5759,8 +5991,11 @@
       <c r="I90" t="s">
         <v>502</v>
       </c>
-      <c r="K90" s="1" t="s">
+      <c r="K90" s="3" t="s">
         <v>503</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>611</v>
       </c>
       <c r="R90" t="s">
         <v>28</v>
@@ -5772,7 +6007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>505</v>
       </c>
@@ -5791,8 +6026,11 @@
       <c r="I91" t="s">
         <v>508</v>
       </c>
-      <c r="K91" s="1" t="s">
+      <c r="K91" s="3" t="s">
         <v>509</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>611</v>
       </c>
       <c r="R91" t="s">
         <v>28</v>
@@ -5810,7 +6048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>510</v>
       </c>
@@ -5829,8 +6067,11 @@
       <c r="I92" t="s">
         <v>515</v>
       </c>
-      <c r="K92" s="1" t="s">
+      <c r="K92" s="3" t="s">
         <v>516</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>611</v>
       </c>
       <c r="R92" t="s">
         <v>200</v>
@@ -5848,7 +6089,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>517</v>
       </c>
@@ -5870,8 +6111,11 @@
       <c r="J93" t="s">
         <v>520</v>
       </c>
-      <c r="K93" s="1" t="s">
+      <c r="K93" s="3" t="s">
         <v>521</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>611</v>
       </c>
       <c r="R93" t="s">
         <v>28</v>
@@ -5889,7 +6133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>517</v>
       </c>
@@ -5911,8 +6155,11 @@
       <c r="J94" t="s">
         <v>524</v>
       </c>
-      <c r="K94" s="1" t="s">
+      <c r="K94" s="3" t="s">
         <v>525</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>611</v>
       </c>
       <c r="R94" t="s">
         <v>28</v>
@@ -5930,7 +6177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>526</v>
       </c>
@@ -5949,8 +6196,11 @@
       <c r="I95" t="s">
         <v>531</v>
       </c>
-      <c r="K95" s="1" t="s">
+      <c r="K95" s="3" t="s">
         <v>532</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>611</v>
       </c>
       <c r="R95" t="s">
         <v>28</v>
@@ -5962,7 +6212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>533</v>
       </c>
@@ -5981,8 +6231,11 @@
       <c r="I96" t="s">
         <v>538</v>
       </c>
-      <c r="K96" s="1" t="s">
+      <c r="K96" s="3" t="s">
         <v>539</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>611</v>
       </c>
       <c r="R96" t="s">
         <v>28</v>
@@ -5997,7 +6250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>540</v>
       </c>
@@ -6019,8 +6272,11 @@
       <c r="J97" t="s">
         <v>544</v>
       </c>
-      <c r="K97" s="1" t="s">
+      <c r="K97" s="3" t="s">
         <v>545</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>611</v>
       </c>
       <c r="R97" t="s">
         <v>71</v>
@@ -6038,7 +6294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>546</v>
       </c>
@@ -6060,8 +6316,11 @@
       <c r="J98" t="s">
         <v>551</v>
       </c>
-      <c r="K98" s="1" t="s">
+      <c r="K98" s="3" t="s">
         <v>552</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>611</v>
       </c>
       <c r="R98" t="s">
         <v>553</v>
@@ -6079,7 +6338,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>546</v>
       </c>
@@ -6101,8 +6360,11 @@
       <c r="J99" t="s">
         <v>557</v>
       </c>
-      <c r="K99" s="1" t="s">
+      <c r="K99" s="3" t="s">
         <v>558</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>611</v>
       </c>
       <c r="R99" t="s">
         <v>559</v>
@@ -6120,7 +6382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>560</v>
       </c>
@@ -6142,8 +6404,11 @@
       <c r="J100" t="s">
         <v>563</v>
       </c>
-      <c r="K100" s="1" t="s">
+      <c r="K100" s="3" t="s">
         <v>564</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>611</v>
       </c>
       <c r="R100" t="s">
         <v>28</v>
@@ -6161,7 +6426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>560</v>
       </c>
@@ -6180,8 +6445,11 @@
       <c r="I101" t="s">
         <v>566</v>
       </c>
-      <c r="K101" s="1" t="s">
+      <c r="K101" s="3" t="s">
         <v>567</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>611</v>
       </c>
       <c r="R101" t="s">
         <v>462</v>
@@ -6199,7 +6467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>381</v>
       </c>
@@ -6218,8 +6486,11 @@
       <c r="I102" t="s">
         <v>570</v>
       </c>
-      <c r="K102" s="1" t="s">
+      <c r="K102" s="3" t="s">
         <v>571</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>611</v>
       </c>
       <c r="R102" t="s">
         <v>28</v>
@@ -6237,7 +6508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>381</v>
       </c>
@@ -6256,8 +6527,11 @@
       <c r="I103" t="s">
         <v>572</v>
       </c>
-      <c r="K103" s="1" t="s">
+      <c r="K103" s="3" t="s">
         <v>573</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>611</v>
       </c>
       <c r="R103" t="s">
         <v>28</v>
@@ -6275,7 +6549,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>574</v>
       </c>
@@ -6291,8 +6565,11 @@
       <c r="I104" t="s">
         <v>578</v>
       </c>
-      <c r="K104" s="1" t="s">
+      <c r="K104" s="3" t="s">
         <v>579</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>611</v>
       </c>
       <c r="R104" t="s">
         <v>580</v>
@@ -6304,7 +6581,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>239</v>
       </c>
@@ -6326,8 +6603,11 @@
       <c r="J105" t="s">
         <v>584</v>
       </c>
-      <c r="K105" s="1" t="s">
+      <c r="K105" s="3" t="s">
         <v>585</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>611</v>
       </c>
       <c r="R105" t="s">
         <v>97</v>
@@ -6345,7 +6625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>586</v>
       </c>
@@ -6367,8 +6647,11 @@
       <c r="J106" t="s">
         <v>590</v>
       </c>
-      <c r="K106" s="1" t="s">
+      <c r="K106" s="3" t="s">
         <v>591</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>611</v>
       </c>
       <c r="R106" t="s">
         <v>28</v>
@@ -6386,7 +6669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>592</v>
       </c>
@@ -6402,8 +6685,11 @@
       <c r="I107" t="s">
         <v>596</v>
       </c>
-      <c r="K107" s="1" t="s">
+      <c r="K107" s="3" t="s">
         <v>597</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>611</v>
       </c>
       <c r="R107" t="s">
         <v>598</v>
@@ -6415,7 +6701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>517</v>
       </c>
@@ -6434,8 +6720,11 @@
       <c r="I108" t="s">
         <v>602</v>
       </c>
-      <c r="K108" s="1" t="s">
+      <c r="K108" s="3" t="s">
         <v>603</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>611</v>
       </c>
       <c r="R108" t="s">
         <v>28</v>
@@ -6453,7 +6742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>604</v>
       </c>
@@ -6475,7 +6764,7 @@
       <c r="J109" t="s">
         <v>608</v>
       </c>
-      <c r="K109" s="1" t="s">
+      <c r="K109" s="3" t="s">
         <v>609</v>
       </c>
       <c r="R109" t="s">

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E5B540-9BA1-4D6C-96C5-4B95F7C0355B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AAAA73-0AE1-47E3-AA4B-766645273F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="615">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -1859,6 +1859,12 @@
   </si>
   <si>
     <t>Moument funéraire</t>
+  </si>
+  <si>
+    <t>Mobilier liturgique</t>
+  </si>
+  <si>
+    <t>Monument funéraire</t>
   </si>
 </sst>
 </file>
@@ -2567,7 +2573,7 @@
         <v>65</v>
       </c>
       <c r="Q8" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="R8" t="s">
         <v>28</v>
@@ -3288,7 +3294,7 @@
         <v>161</v>
       </c>
       <c r="Q25" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="R25" t="s">
         <v>28</v>
@@ -3420,7 +3426,7 @@
         <v>175</v>
       </c>
       <c r="Q28" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="R28" t="s">
         <v>28</v>
@@ -5617,7 +5623,7 @@
         <v>461</v>
       </c>
       <c r="Q81" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="R81" t="s">
         <v>462</v>
@@ -5872,7 +5878,7 @@
         <v>488</v>
       </c>
       <c r="Q87" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="R87" t="s">
         <v>28</v>
@@ -6766,6 +6772,9 @@
       </c>
       <c r="K109" s="3" t="s">
         <v>609</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>613</v>
       </c>
       <c r="R109" t="s">
         <v>610</v>

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -3833,7 +3833,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ignaz</t>
+          <t>Franz Ignaz</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -15,7 +15,20 @@
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513D4E87-A803-41E0-A4DB-D22790207692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8DAAE9-FA99-4150-ADD7-0BB7B7ED975B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="744">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2028,6 +2028,243 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/%C3%89tienne_Maurice_Falconet-Winter-Hermitage.jpg/960px-%C3%89tienne_Maurice_Falconet-Winter-Hermitage.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>1793</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Chichester</t>
+  </si>
+  <si>
+    <t>Cathédrale de la Sainte-Trinité</t>
+  </si>
+  <si>
+    <t>Monument à William Collins</t>
+  </si>
+  <si>
+    <t>Monument to William Collins</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/78/Tribute_to_William_Collins_at_Chichester_Cathedral.jpg/960px-Tribute_to_William_Collins_at_Chichester_Cathedral.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Bas-relief / Monument funéraire</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>1795-1801</t>
+  </si>
+  <si>
+    <t>Monument à Lord Mansfield</t>
+  </si>
+  <si>
+    <t>Monument to Lord Mansfield</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Monument_to_Lord_Mansfield%2C_Westminster_Abbey_01.jpg/960px-Monument_to_Lord_Mansfield%2C_Westminster_Abbey_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>450</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>British Museum</t>
+  </si>
+  <si>
+    <t>Plaque de l'Apothéose d'Homère</t>
+  </si>
+  <si>
+    <t>The Apotheosis of Homer Plaque</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Homer_wedgwood.jpg/1280px-Homer_wedgwood.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>1798</t>
+  </si>
+  <si>
+    <t>Monument à Jane et Henrietta Browne</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Badger_church_-_Jane_and_Henrietta_Browne.jpg/500px-Badger_church_-_Jane_and_Henrietta_Browne.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>1790</t>
+  </si>
+  <si>
+    <t>Port Sunlight</t>
+  </si>
+  <si>
+    <t>Lady Lever Art Gallery</t>
+  </si>
+  <si>
+    <t>Céphale et Procris</t>
+  </si>
+  <si>
+    <t>Cephalus and Procris</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/10/John_Flaxman_%281755-1826%29_-_Cephalus_and_Aurora_%281789-90%29_front%2C_Lady_Lever_Art_Gallery%2C_Port_Sunlight%2C_Cheshire%2C_June_2013_%289103113142%29.png/500px-John_Flaxman_%281755-1826%29_-_Cephalus_and_Aurora_%281789-90%29_front%2C_Lady_Lever_Art_Gallery%2C_Port_Sunlight%2C_Cheshire%2C_June_2013_%289103113142%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>1758-1759</t>
+  </si>
+  <si>
+    <t>Rott am Inn</t>
+  </si>
+  <si>
+    <t>Église abbatiale Saints-Marinus-et-Anianus</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/23/St._Peter_und_Paul_%28Neustift%29_Hochaltar_1.jpg/960px-St._Peter_und_Paul_%28Neustift%29_Hochaltar_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Saint Pierre</t>
+  </si>
+  <si>
+    <t>Heiliger Petrus</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg/960px-St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Bois peint en blanc et doré</t>
+  </si>
+  <si>
+    <t>Saint Paul</t>
+  </si>
+  <si>
+    <t>Heiliger Paulus</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/St._Paulus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg/960px-St._Paulus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>1781</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>1788</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Musée Fabre</t>
+  </si>
+  <si>
+    <t>L'Écorché</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/06/Houdon_Jean_Antoine%2C_L%27%C3%A9corch%C3%A9_bras_lev%C3%A9%2C_Mus%C3%A9e_Fabre%2C_Montpellier.jpg/960px-Houdon_Jean_Antoine%2C_L%27%C3%A9corch%C3%A9_bras_lev%C3%A9%2C_Mus%C3%A9e_Fabre%2C_Montpellier.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Plâtre</t>
+  </si>
+  <si>
+    <t>Tours</t>
+  </si>
+  <si>
+    <t>Diane chasseresse</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/ToursMBA_DianeHoudon.jpg/960px-ToursMBA_DianeHoudon.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>1775</t>
+  </si>
+  <si>
+    <t>Buste de Sophie Arnould</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/50/Houdon_Sophie_Arnould_Iphig%C3%A9nie.jpg/960px-Houdon_Sophie_Arnould_Iphig%C3%A9nie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>La Frileuse</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/67/Jean-Antoine_Houdon-La_frileuse.JPG/960px-Jean-Antoine_Houdon-La_frileuse.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>Pluton enchaînant Cerbère</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0f/Pajou_-_Pluton_encha%C3%AEnant_Cerb%C3%A8re_01.jpg/960px-Pajou_-_Pluton_encha%C3%AEnant_Cerb%C3%A8re_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Buste de Élisabeth Vigée Le Brun</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/18/Mme_Vig%C3%A9e_Le_Brun_par_Pajou.JPG/960px-Mme_Vig%C3%A9e_Le_Brun_par_Pajou.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>26</t>
   </si>
 </sst>
 </file>
@@ -2129,7 +2366,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2173,6 +2410,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2476,7 +2714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y206"/>
+  <dimension ref="A1:Y205"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" style="7" customWidth="1"/>
@@ -2487,8 +2725,8 @@
     <col min="13" max="17" width="9.140625" style="7"/>
     <col min="18" max="18" width="28.85546875" style="7" customWidth="1"/>
     <col min="20" max="23" width="9.140625" style="1"/>
-    <col min="24" max="24" width="15.140625" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2561,10 +2799,10 @@
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2688,10 +2926,10 @@
       <c r="W3" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X3" t="s">
+      <c r="X3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Y3" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2738,10 +2976,10 @@
       <c r="W4" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X4" t="s">
+      <c r="X4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Y4" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2788,10 +3026,10 @@
       <c r="W5" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X5" t="s">
+      <c r="X5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Y5" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2838,10 +3076,10 @@
       <c r="W6" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X6" t="s">
+      <c r="X6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="Y6" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2888,10 +3126,10 @@
       <c r="W7" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X7" t="s">
+      <c r="X7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="Y7" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2938,10 +3176,10 @@
       <c r="W8" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X8" t="s">
+      <c r="X8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="Y8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2985,10 +3223,10 @@
       <c r="W9" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X9" t="s">
+      <c r="X9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Y9" t="s">
+      <c r="Y9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3029,10 +3267,10 @@
       <c r="W10" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X10" t="s">
+      <c r="X10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Y10" t="s">
+      <c r="Y10" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3076,10 +3314,10 @@
       <c r="W11" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X11" t="s">
+      <c r="X11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Y11" t="s">
+      <c r="Y11" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3123,10 +3361,10 @@
       <c r="W12" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X12" t="s">
+      <c r="X12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Y12" t="s">
+      <c r="Y12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3170,10 +3408,10 @@
       <c r="W13" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X13" t="s">
+      <c r="X13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="Y13" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3217,10 +3455,10 @@
       <c r="W14" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X14" t="s">
+      <c r="X14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="Y14" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3264,10 +3502,10 @@
       <c r="W15" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X15" t="s">
+      <c r="X15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Y15" t="s">
+      <c r="Y15" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3311,10 +3549,10 @@
       <c r="W16" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X16" t="s">
+      <c r="X16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="Y16" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3373,10 +3611,10 @@
       <c r="W21" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="X21" t="s">
+      <c r="X21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="Y21" t="s">
+      <c r="Y21" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3423,10 +3661,10 @@
       <c r="W22" s="1">
         <v>3</v>
       </c>
-      <c r="X22" t="s">
+      <c r="X22" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="Y22" t="s">
+      <c r="Y22" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3473,10 +3711,10 @@
       <c r="W23" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="X23" t="s">
+      <c r="X23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="Y23" t="s">
+      <c r="Y23" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3523,10 +3761,10 @@
       <c r="W24" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="X24" t="s">
+      <c r="X24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="Y24" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3573,10 +3811,10 @@
       <c r="W25" s="1">
         <v>2</v>
       </c>
-      <c r="X25" t="s">
+      <c r="X25" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="Y25" t="s">
+      <c r="Y25" s="1" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3623,10 +3861,10 @@
       <c r="W26" s="1">
         <v>2</v>
       </c>
-      <c r="X26" t="s">
+      <c r="X26" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="Y26" s="1" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3676,10 +3914,10 @@
       <c r="W27" s="1">
         <v>2</v>
       </c>
-      <c r="X27" t="s">
+      <c r="X27" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="Y27" t="s">
+      <c r="Y27" s="1" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3726,10 +3964,10 @@
       <c r="W28" s="1">
         <v>2</v>
       </c>
-      <c r="X28" t="s">
+      <c r="X28" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="Y28" t="s">
+      <c r="Y28" s="1" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3782,10 +4020,10 @@
       <c r="W31" s="1">
         <v>1</v>
       </c>
-      <c r="X31" t="s">
+      <c r="X31" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Y31" t="s">
+      <c r="Y31" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3832,10 +4070,10 @@
       <c r="W32" s="1">
         <v>1</v>
       </c>
-      <c r="X32" t="s">
+      <c r="X32" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Y32" t="s">
+      <c r="Y32" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3882,10 +4120,10 @@
       <c r="W33" s="1">
         <v>1</v>
       </c>
-      <c r="X33" t="s">
+      <c r="X33" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Y33" t="s">
+      <c r="Y33" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3935,10 +4173,10 @@
       <c r="W34" s="1">
         <v>1</v>
       </c>
-      <c r="X34" t="s">
+      <c r="X34" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Y34" t="s">
+      <c r="Y34" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3985,10 +4223,10 @@
       <c r="W35" s="1">
         <v>1</v>
       </c>
-      <c r="X35" t="s">
+      <c r="X35" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Y35" t="s">
+      <c r="Y35" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4035,10 +4273,10 @@
       <c r="W36" s="1">
         <v>1</v>
       </c>
-      <c r="X36" t="s">
+      <c r="X36" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Y36" t="s">
+      <c r="Y36" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4091,10 +4329,10 @@
       <c r="W37" s="1">
         <v>1</v>
       </c>
-      <c r="X37" t="s">
+      <c r="X37" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Y37" t="s">
+      <c r="Y37" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4147,10 +4385,10 @@
       <c r="W38" s="1">
         <v>1</v>
       </c>
-      <c r="X38" t="s">
+      <c r="X38" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Y38" t="s">
+      <c r="Y38" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4206,10 +4444,10 @@
       <c r="W39" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="X39" t="s">
+      <c r="X39" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="Y39" t="s">
+      <c r="Y39" s="1" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4259,10 +4497,10 @@
       <c r="W40" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="X40" t="s">
+      <c r="X40" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="Y40" t="s">
+      <c r="Y40" s="1" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4315,10 +4553,10 @@
       <c r="W41" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="X41" t="s">
+      <c r="X41" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="Y41" t="s">
+      <c r="Y41" s="1" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4365,10 +4603,10 @@
       <c r="W42" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X42" t="s">
+      <c r="X42" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="Y42" t="s">
+      <c r="Y42" s="1" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4412,10 +4650,10 @@
       <c r="W43" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X43" t="s">
+      <c r="X43" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="Y43" t="s">
+      <c r="Y43" s="1" t="s">
         <v>95</v>
       </c>
     </row>
@@ -4459,10 +4697,10 @@
       <c r="W44" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X44" t="s">
+      <c r="X44" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="Y44" t="s">
+      <c r="Y44" s="1" t="s">
         <v>95</v>
       </c>
     </row>
@@ -4506,10 +4744,10 @@
       <c r="W45" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X45" t="s">
+      <c r="X45" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="Y45" t="s">
+      <c r="Y45" s="1" t="s">
         <v>95</v>
       </c>
     </row>
@@ -4553,10 +4791,10 @@
       <c r="W46" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="X46" t="s">
+      <c r="X46" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="Y46" t="s">
+      <c r="Y46" s="1" t="s">
         <v>95</v>
       </c>
     </row>
@@ -4600,10 +4838,10 @@
       <c r="W47" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X47" t="s">
+      <c r="X47" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="Y47" t="s">
+      <c r="Y47" s="1" t="s">
         <v>95</v>
       </c>
     </row>
@@ -4647,10 +4885,10 @@
       <c r="W48" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X48" t="s">
+      <c r="X48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="Y48" t="s">
+      <c r="Y48" s="1" t="s">
         <v>95</v>
       </c>
     </row>
@@ -4697,10 +4935,10 @@
       <c r="W49" s="1">
         <v>1</v>
       </c>
-      <c r="X49" t="s">
+      <c r="X49" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y49" t="s">
+      <c r="Y49" s="1" t="s">
         <v>103</v>
       </c>
     </row>
@@ -4747,10 +4985,10 @@
       <c r="W50" s="1">
         <v>1</v>
       </c>
-      <c r="X50" t="s">
+      <c r="X50" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y50" t="s">
+      <c r="Y50" s="1" t="s">
         <v>103</v>
       </c>
     </row>
@@ -4797,10 +5035,10 @@
       <c r="W51" s="1">
         <v>1</v>
       </c>
-      <c r="X51" t="s">
+      <c r="X51" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y51" t="s">
+      <c r="Y51" s="1" t="s">
         <v>103</v>
       </c>
     </row>
@@ -4847,10 +5085,10 @@
       <c r="W52" s="1">
         <v>1</v>
       </c>
-      <c r="X52" t="s">
+      <c r="X52" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y52" t="s">
+      <c r="Y52" s="1" t="s">
         <v>103</v>
       </c>
     </row>
@@ -4900,10 +5138,10 @@
       <c r="W53" s="1">
         <v>1</v>
       </c>
-      <c r="X53" t="s">
+      <c r="X53" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y53" t="s">
+      <c r="Y53" s="1" t="s">
         <v>103</v>
       </c>
     </row>
@@ -4950,10 +5188,10 @@
       <c r="W54" s="1">
         <v>1</v>
       </c>
-      <c r="X54" t="s">
+      <c r="X54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y54" t="s">
+      <c r="Y54" s="1" t="s">
         <v>103</v>
       </c>
     </row>
@@ -5000,10 +5238,10 @@
       <c r="W55" s="1">
         <v>1</v>
       </c>
-      <c r="X55" t="s">
+      <c r="X55" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y55" t="s">
+      <c r="Y55" s="1" t="s">
         <v>103</v>
       </c>
     </row>
@@ -5050,10 +5288,10 @@
       <c r="W56" s="1">
         <v>1</v>
       </c>
-      <c r="X56" t="s">
+      <c r="X56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y56" t="s">
+      <c r="Y56" s="1" t="s">
         <v>103</v>
       </c>
     </row>
@@ -5097,10 +5335,10 @@
       <c r="W57" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X57" t="s">
+      <c r="X57" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="Y57" t="s">
+      <c r="Y57" s="1" t="s">
         <v>141</v>
       </c>
     </row>
@@ -5138,10 +5376,10 @@
       <c r="W58" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X58" t="s">
+      <c r="X58" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="Y58" t="s">
+      <c r="Y58" s="1" t="s">
         <v>141</v>
       </c>
     </row>
@@ -5182,10 +5420,10 @@
       <c r="W59" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="X59" t="s">
+      <c r="X59" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="Y59" t="s">
+      <c r="Y59" s="1" t="s">
         <v>141</v>
       </c>
     </row>
@@ -5232,10 +5470,10 @@
       <c r="W61" s="1">
         <v>3</v>
       </c>
-      <c r="X61" t="s">
+      <c r="X61" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y61" t="s">
+      <c r="Y61" s="1" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5282,10 +5520,10 @@
       <c r="W62" s="1">
         <v>3</v>
       </c>
-      <c r="X62" t="s">
+      <c r="X62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y62" t="s">
+      <c r="Y62" s="1" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5332,10 +5570,10 @@
       <c r="W63" s="1">
         <v>3</v>
       </c>
-      <c r="X63" t="s">
+      <c r="X63" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y63" t="s">
+      <c r="Y63" s="1" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5373,10 +5611,10 @@
       <c r="W64" s="1">
         <v>3</v>
       </c>
-      <c r="X64" t="s">
+      <c r="X64" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y64" t="s">
+      <c r="Y64" s="1" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5420,10 +5658,10 @@
       <c r="W65" s="1">
         <v>2</v>
       </c>
-      <c r="X65" t="s">
+      <c r="X65" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="Y65" t="s">
+      <c r="Y65" s="1" t="s">
         <v>155</v>
       </c>
     </row>
@@ -5467,10 +5705,10 @@
       <c r="W66" s="1">
         <v>2</v>
       </c>
-      <c r="X66" t="s">
+      <c r="X66" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="Y66" t="s">
+      <c r="Y66" s="1" t="s">
         <v>155</v>
       </c>
     </row>
@@ -5517,10 +5755,10 @@
       <c r="W67" s="1">
         <v>2</v>
       </c>
-      <c r="X67" t="s">
+      <c r="X67" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="Y67" t="s">
+      <c r="Y67" s="1" t="s">
         <v>155</v>
       </c>
     </row>
@@ -5567,10 +5805,10 @@
       <c r="W68" s="1">
         <v>2</v>
       </c>
-      <c r="X68" t="s">
+      <c r="X68" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="Y68" t="s">
+      <c r="Y68" s="1" t="s">
         <v>155</v>
       </c>
     </row>
@@ -5614,10 +5852,10 @@
       <c r="W69" s="1">
         <v>2</v>
       </c>
-      <c r="X69" t="s">
+      <c r="X69" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="Y69" t="s">
+      <c r="Y69" s="1" t="s">
         <v>159</v>
       </c>
     </row>
@@ -5664,10 +5902,10 @@
       <c r="W70" s="1">
         <v>2</v>
       </c>
-      <c r="X70" t="s">
+      <c r="X70" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="Y70" t="s">
+      <c r="Y70" s="1" t="s">
         <v>159</v>
       </c>
     </row>
@@ -5714,10 +5952,10 @@
       <c r="W71" s="1">
         <v>2</v>
       </c>
-      <c r="X71" t="s">
+      <c r="X71" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="Y71" t="s">
+      <c r="Y71" s="1" t="s">
         <v>159</v>
       </c>
     </row>
@@ -5761,10 +5999,10 @@
       <c r="W72" s="1">
         <v>2</v>
       </c>
-      <c r="X72" t="s">
+      <c r="X72" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="Y72" t="s">
+      <c r="Y72" s="1" t="s">
         <v>159</v>
       </c>
     </row>
@@ -5799,10 +6037,10 @@
       <c r="W73" s="1">
         <v>2</v>
       </c>
-      <c r="X73" t="s">
+      <c r="X73" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="Y73" t="s">
+      <c r="Y73" s="1" t="s">
         <v>159</v>
       </c>
     </row>
@@ -5846,10 +6084,10 @@
       <c r="W74" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="X74" t="s">
+      <c r="X74" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="Y74" t="s">
+      <c r="Y74" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5890,10 +6128,10 @@
       <c r="W75" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="X75" t="s">
+      <c r="X75" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="Y75" t="s">
+      <c r="Y75" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5934,10 +6172,10 @@
       <c r="W76" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="X76" t="s">
+      <c r="X76" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="Y76" t="s">
+      <c r="Y76" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5978,10 +6216,10 @@
       <c r="W77" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="X77" t="s">
+      <c r="X77" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="Y77" t="s">
+      <c r="Y77" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -6034,10 +6272,10 @@
       <c r="W83" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="X83" t="s">
+      <c r="X83" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="Y83" t="s">
+      <c r="Y83" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -6087,10 +6325,10 @@
       <c r="W84" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="X84" t="s">
+      <c r="X84" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="Y84" t="s">
+      <c r="Y84" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -6134,10 +6372,10 @@
       <c r="W85" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="X85" t="s">
+      <c r="X85" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="Y85" t="s">
+      <c r="Y85" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -6181,10 +6419,10 @@
       <c r="W86" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="X86" t="s">
+      <c r="X86" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="Y86" t="s">
+      <c r="Y86" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -6231,10 +6469,10 @@
       <c r="W87" s="1">
         <v>3</v>
       </c>
-      <c r="X87" t="s">
+      <c r="X87" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="Y87" t="s">
+      <c r="Y87" s="1" t="s">
         <v>179</v>
       </c>
     </row>
@@ -6275,10 +6513,10 @@
       <c r="W88" s="1">
         <v>3</v>
       </c>
-      <c r="X88" t="s">
+      <c r="X88" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="Y88" t="s">
+      <c r="Y88" s="1" t="s">
         <v>179</v>
       </c>
     </row>
@@ -6322,10 +6560,10 @@
       <c r="W89" s="1">
         <v>3</v>
       </c>
-      <c r="X89" t="s">
+      <c r="X89" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="Y89" t="s">
+      <c r="Y89" s="1" t="s">
         <v>179</v>
       </c>
     </row>
@@ -6366,10 +6604,10 @@
       <c r="W90" s="1">
         <v>3</v>
       </c>
-      <c r="X90" t="s">
+      <c r="X90" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="Y90" t="s">
+      <c r="Y90" s="1" t="s">
         <v>179</v>
       </c>
     </row>
@@ -6425,10 +6663,10 @@
       <c r="W91" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="X91" s="3" t="s">
+      <c r="X91" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="Y91" s="3" t="s">
+      <c r="Y91" s="4" t="s">
         <v>185</v>
       </c>
     </row>
@@ -6482,10 +6720,10 @@
       <c r="W92" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="X92" s="3" t="s">
+      <c r="X92" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="Y92" s="3" t="s">
+      <c r="Y92" s="4" t="s">
         <v>185</v>
       </c>
     </row>
@@ -6541,10 +6779,10 @@
       <c r="W93" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="X93" s="3" t="s">
+      <c r="X93" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="Y93" s="3" t="s">
+      <c r="Y93" s="4" t="s">
         <v>185</v>
       </c>
     </row>
@@ -6600,10 +6838,10 @@
       <c r="W94" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="X94" s="3" t="s">
+      <c r="X94" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="Y94" s="3" t="s">
+      <c r="Y94" s="4" t="s">
         <v>185</v>
       </c>
     </row>
@@ -6990,478 +7228,1146 @@
       </c>
     </row>
     <row r="103" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="7" t="s">
+      <c r="A103" t="s">
         <v>46</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="B103" t="s">
         <v>201</v>
       </c>
-      <c r="D103" s="7" t="s">
+      <c r="C103"/>
+      <c r="D103" t="s">
         <v>202</v>
       </c>
-      <c r="E103" s="7" t="s">
+      <c r="E103" t="s">
         <v>203</v>
       </c>
-      <c r="F103" s="7" t="s">
+      <c r="F103" t="s">
         <v>204</v>
       </c>
-      <c r="J103" s="7" t="s">
+      <c r="G103"/>
+      <c r="H103"/>
+      <c r="I103"/>
+      <c r="J103" t="s">
         <v>205</v>
       </c>
-      <c r="L103" s="13" t="s">
+      <c r="K103"/>
+      <c r="L103" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="R103" s="7" t="s">
+      <c r="M103"/>
+      <c r="N103"/>
+      <c r="O103"/>
+      <c r="P103"/>
+      <c r="Q103"/>
+      <c r="R103" t="s">
         <v>24</v>
       </c>
       <c r="S103" t="s">
         <v>207</v>
       </c>
-      <c r="T103" s="1">
+      <c r="T103" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="U103" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="V103" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="W103" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="X103" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="U103" s="1">
-        <v>24</v>
-      </c>
-      <c r="V103" s="1">
-        <v>24</v>
-      </c>
-      <c r="W103" s="1">
-        <v>1</v>
-      </c>
-      <c r="X103" t="s">
+      <c r="Y103" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>46</v>
       </c>
-      <c r="Y103" t="s">
+      <c r="B104" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="104" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B104" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D104" s="7">
-        <v>1793</v>
-      </c>
-      <c r="E104" s="7" t="s">
+      <c r="C104"/>
+      <c r="D104" t="s">
+        <v>667</v>
+      </c>
+      <c r="E104" t="s">
         <v>48</v>
       </c>
-      <c r="F104" s="7" t="s">
+      <c r="F104" t="s">
         <v>208</v>
       </c>
-      <c r="J104" s="7" t="s">
+      <c r="G104"/>
+      <c r="H104"/>
+      <c r="I104"/>
+      <c r="J104" t="s">
         <v>209</v>
       </c>
-      <c r="K104" s="7" t="s">
+      <c r="K104" t="s">
         <v>210</v>
       </c>
-      <c r="L104" s="13" t="s">
+      <c r="L104" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="R104" s="7" t="s">
+      <c r="M104"/>
+      <c r="N104"/>
+      <c r="O104"/>
+      <c r="P104"/>
+      <c r="Q104"/>
+      <c r="R104" t="s">
         <v>24</v>
       </c>
       <c r="S104" t="s">
         <v>25</v>
       </c>
-      <c r="T104" s="1">
-        <v>195</v>
-      </c>
-      <c r="U104" s="1">
-        <v>210</v>
-      </c>
-      <c r="V104" s="1">
-        <v>110</v>
-      </c>
-      <c r="W104" s="1">
-        <v>1</v>
-      </c>
-      <c r="X104" t="s">
+      <c r="T104" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="U104" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="V104" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="W104" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="X104" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="Y104" t="s">
+      <c r="Y104" s="1" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="105" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L105" s="13"/>
+      <c r="A105" t="s">
+        <v>46</v>
+      </c>
+      <c r="B105" t="s">
+        <v>201</v>
+      </c>
+      <c r="C105"/>
+      <c r="D105" t="s">
+        <v>433</v>
+      </c>
+      <c r="E105" t="s">
+        <v>670</v>
+      </c>
+      <c r="F105" t="s">
+        <v>671</v>
+      </c>
+      <c r="G105"/>
+      <c r="H105"/>
+      <c r="I105"/>
+      <c r="J105" t="s">
+        <v>672</v>
+      </c>
+      <c r="K105" t="s">
+        <v>673</v>
+      </c>
+      <c r="L105" s="15" t="s">
+        <v>674</v>
+      </c>
+      <c r="M105"/>
+      <c r="N105"/>
+      <c r="O105"/>
+      <c r="P105"/>
+      <c r="Q105"/>
+      <c r="R105" t="s">
+        <v>675</v>
+      </c>
+      <c r="S105" t="s">
+        <v>25</v>
+      </c>
+      <c r="T105" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="U105" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="V105" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="W105" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="X105" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y105" s="1" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="106" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L106" s="13"/>
+      <c r="A106" t="s">
+        <v>46</v>
+      </c>
+      <c r="B106" t="s">
+        <v>201</v>
+      </c>
+      <c r="C106"/>
+      <c r="D106" t="s">
+        <v>678</v>
+      </c>
+      <c r="E106" t="s">
+        <v>48</v>
+      </c>
+      <c r="F106" t="s">
+        <v>49</v>
+      </c>
+      <c r="G106"/>
+      <c r="H106"/>
+      <c r="I106"/>
+      <c r="J106" t="s">
+        <v>679</v>
+      </c>
+      <c r="K106" t="s">
+        <v>680</v>
+      </c>
+      <c r="L106" s="15" t="s">
+        <v>681</v>
+      </c>
+      <c r="M106"/>
+      <c r="N106"/>
+      <c r="O106"/>
+      <c r="P106"/>
+      <c r="Q106"/>
+      <c r="R106" t="s">
+        <v>631</v>
+      </c>
+      <c r="S106" t="s">
+        <v>25</v>
+      </c>
+      <c r="T106" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="U106" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="V106" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="W106" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="X106" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y106" s="1" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="107" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L107" s="13"/>
+      <c r="A107" t="s">
+        <v>46</v>
+      </c>
+      <c r="B107" t="s">
+        <v>201</v>
+      </c>
+      <c r="C107"/>
+      <c r="D107" t="s">
+        <v>424</v>
+      </c>
+      <c r="E107" t="s">
+        <v>48</v>
+      </c>
+      <c r="F107" t="s">
+        <v>684</v>
+      </c>
+      <c r="G107"/>
+      <c r="H107"/>
+      <c r="I107"/>
+      <c r="J107" t="s">
+        <v>685</v>
+      </c>
+      <c r="K107" t="s">
+        <v>686</v>
+      </c>
+      <c r="L107" s="15" t="s">
+        <v>687</v>
+      </c>
+      <c r="M107"/>
+      <c r="N107"/>
+      <c r="O107"/>
+      <c r="P107"/>
+      <c r="Q107"/>
+      <c r="R107" t="s">
+        <v>472</v>
+      </c>
+      <c r="S107" t="s">
+        <v>207</v>
+      </c>
+      <c r="T107" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="U107" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="V107" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="W107" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="X107" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y107" s="1" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="108" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L108" s="13"/>
+      <c r="A108" t="s">
+        <v>46</v>
+      </c>
+      <c r="B108" t="s">
+        <v>201</v>
+      </c>
+      <c r="C108"/>
+      <c r="D108" t="s">
+        <v>689</v>
+      </c>
+      <c r="E108" t="s">
+        <v>670</v>
+      </c>
+      <c r="F108" t="s">
+        <v>671</v>
+      </c>
+      <c r="G108"/>
+      <c r="H108"/>
+      <c r="I108"/>
+      <c r="J108" t="s">
+        <v>690</v>
+      </c>
+      <c r="K108"/>
+      <c r="L108" s="15" t="s">
+        <v>691</v>
+      </c>
+      <c r="M108"/>
+      <c r="N108"/>
+      <c r="O108"/>
+      <c r="P108"/>
+      <c r="Q108"/>
+      <c r="R108" t="s">
+        <v>675</v>
+      </c>
+      <c r="S108" t="s">
+        <v>25</v>
+      </c>
+      <c r="T108" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="U108" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="V108" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="W108" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="X108" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y108" s="1" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="109" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L109" s="13"/>
+      <c r="A109" t="s">
+        <v>46</v>
+      </c>
+      <c r="B109" t="s">
+        <v>201</v>
+      </c>
+      <c r="C109"/>
+      <c r="D109" t="s">
+        <v>693</v>
+      </c>
+      <c r="E109" t="s">
+        <v>694</v>
+      </c>
+      <c r="F109" t="s">
+        <v>695</v>
+      </c>
+      <c r="G109"/>
+      <c r="H109"/>
+      <c r="I109"/>
+      <c r="J109" t="s">
+        <v>696</v>
+      </c>
+      <c r="K109" t="s">
+        <v>697</v>
+      </c>
+      <c r="L109" s="15" t="s">
+        <v>698</v>
+      </c>
+      <c r="M109"/>
+      <c r="N109"/>
+      <c r="O109"/>
+      <c r="P109"/>
+      <c r="Q109"/>
+      <c r="R109" t="s">
+        <v>24</v>
+      </c>
+      <c r="S109" t="s">
+        <v>25</v>
+      </c>
+      <c r="T109" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="U109" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="V109" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="W109" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="X109" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y109" s="1" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="110" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L110" s="13"/>
+      <c r="A110" t="s">
+        <v>213</v>
+      </c>
+      <c r="B110" t="s">
+        <v>214</v>
+      </c>
+      <c r="C110"/>
+      <c r="D110" t="s">
+        <v>215</v>
+      </c>
+      <c r="E110" t="s">
+        <v>92</v>
+      </c>
+      <c r="F110" t="s">
+        <v>93</v>
+      </c>
+      <c r="G110"/>
+      <c r="H110"/>
+      <c r="I110"/>
+      <c r="J110" t="s">
+        <v>216</v>
+      </c>
+      <c r="K110" t="s">
+        <v>217</v>
+      </c>
+      <c r="L110" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="M110"/>
+      <c r="N110"/>
+      <c r="O110"/>
+      <c r="P110"/>
+      <c r="Q110"/>
+      <c r="R110" t="s">
+        <v>24</v>
+      </c>
+      <c r="S110" t="s">
+        <v>219</v>
+      </c>
+      <c r="T110" s="1">
+        <v>182</v>
+      </c>
+      <c r="U110" s="1">
+        <v>95</v>
+      </c>
+      <c r="V110" s="1">
+        <v>75</v>
+      </c>
+      <c r="W110" s="1">
+        <v>3</v>
+      </c>
+      <c r="X110" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="Y110" s="1" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="111" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="7" t="s">
+      <c r="A111" t="s">
         <v>213</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="B111" t="s">
         <v>214</v>
       </c>
-      <c r="D111" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="E111" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="F111" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="J111" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="K111" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="L111" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="R111" s="7" t="s">
+      <c r="C111"/>
+      <c r="D111" t="s">
+        <v>654</v>
+      </c>
+      <c r="E111" t="s">
+        <v>220</v>
+      </c>
+      <c r="F111" t="s">
+        <v>221</v>
+      </c>
+      <c r="G111"/>
+      <c r="H111" t="s">
+        <v>45</v>
+      </c>
+      <c r="I111"/>
+      <c r="J111" t="s">
+        <v>222</v>
+      </c>
+      <c r="K111" t="s">
+        <v>223</v>
+      </c>
+      <c r="L111" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="M111"/>
+      <c r="N111"/>
+      <c r="O111"/>
+      <c r="P111"/>
+      <c r="Q111"/>
+      <c r="R111" t="s">
         <v>24</v>
       </c>
       <c r="S111" t="s">
         <v>219</v>
       </c>
       <c r="T111" s="1">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="U111" s="1">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="V111" s="1">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="W111" s="1">
         <v>3</v>
       </c>
-      <c r="X111" t="s">
+      <c r="X111" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="Y111" t="s">
+      <c r="Y111" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="7" t="s">
+    <row r="112" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>213</v>
       </c>
-      <c r="B112" s="7" t="s">
+      <c r="B112" t="s">
         <v>214</v>
       </c>
-      <c r="D112" s="7">
-        <v>1763</v>
-      </c>
-      <c r="E112" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="F112" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="H112" s="7" t="s">
+      <c r="C112"/>
+      <c r="D112" t="s">
+        <v>701</v>
+      </c>
+      <c r="E112" t="s">
+        <v>702</v>
+      </c>
+      <c r="F112" t="s">
+        <v>703</v>
+      </c>
+      <c r="G112"/>
+      <c r="H112" t="s">
         <v>45</v>
       </c>
-      <c r="J112" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="K112" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="L112" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="R112" s="7" t="s">
+      <c r="I112" s="15" t="s">
+        <v>704</v>
+      </c>
+      <c r="J112" t="s">
+        <v>705</v>
+      </c>
+      <c r="K112" t="s">
+        <v>706</v>
+      </c>
+      <c r="L112" s="15" t="s">
+        <v>707</v>
+      </c>
+      <c r="M112"/>
+      <c r="N112"/>
+      <c r="O112"/>
+      <c r="P112"/>
+      <c r="Q112"/>
+      <c r="R112" t="s">
         <v>24</v>
       </c>
       <c r="S112" t="s">
-        <v>219</v>
+        <v>708</v>
       </c>
       <c r="T112" s="1">
-        <v>165</v>
-      </c>
-      <c r="U112" s="1">
-        <v>110</v>
-      </c>
-      <c r="V112" s="1">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="W112" s="1">
         <v>3</v>
       </c>
-      <c r="X112" t="s">
+      <c r="X112" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="Y112" t="s">
+      <c r="Y112" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L113" s="13"/>
+    <row r="113" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>213</v>
+      </c>
+      <c r="B113" t="s">
+        <v>214</v>
+      </c>
+      <c r="C113"/>
+      <c r="D113" t="s">
+        <v>701</v>
+      </c>
+      <c r="E113" t="s">
+        <v>702</v>
+      </c>
+      <c r="F113" t="s">
+        <v>703</v>
+      </c>
+      <c r="G113"/>
+      <c r="H113" t="s">
+        <v>45</v>
+      </c>
+      <c r="I113" s="15" t="s">
+        <v>704</v>
+      </c>
+      <c r="J113" t="s">
+        <v>709</v>
+      </c>
+      <c r="K113" t="s">
+        <v>710</v>
+      </c>
+      <c r="L113" s="15" t="s">
+        <v>711</v>
+      </c>
+      <c r="M113"/>
+      <c r="N113"/>
+      <c r="O113"/>
+      <c r="P113"/>
+      <c r="Q113"/>
+      <c r="R113" t="s">
+        <v>24</v>
+      </c>
+      <c r="S113" t="s">
+        <v>708</v>
+      </c>
+      <c r="T113" s="1">
+        <v>215</v>
+      </c>
+      <c r="W113" s="1">
+        <v>3</v>
+      </c>
+      <c r="X113" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="Y113" s="1" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="114" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L114" s="13"/>
+      <c r="A114" t="s">
+        <v>225</v>
+      </c>
+      <c r="B114" t="s">
+        <v>226</v>
+      </c>
+      <c r="C114"/>
+      <c r="D114" t="s">
+        <v>424</v>
+      </c>
+      <c r="E114" t="s">
+        <v>28</v>
+      </c>
+      <c r="F114" t="s">
+        <v>227</v>
+      </c>
+      <c r="G114"/>
+      <c r="H114" t="s">
+        <v>228</v>
+      </c>
+      <c r="I114"/>
+      <c r="J114" t="s">
+        <v>229</v>
+      </c>
+      <c r="K114"/>
+      <c r="L114" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="M114"/>
+      <c r="N114"/>
+      <c r="O114"/>
+      <c r="P114"/>
+      <c r="Q114"/>
+      <c r="R114" t="s">
+        <v>24</v>
+      </c>
+      <c r="S114" t="s">
+        <v>25</v>
+      </c>
+      <c r="T114" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="U114" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="V114" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="W114" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="X114" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y114" s="1" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="115" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="7" t="s">
+      <c r="A115" t="s">
         <v>225</v>
       </c>
-      <c r="B115" s="7" t="s">
+      <c r="B115" t="s">
         <v>226</v>
       </c>
-      <c r="D115" s="7">
-        <v>1778</v>
-      </c>
-      <c r="E115" s="7" t="s">
+      <c r="C115"/>
+      <c r="D115" t="s">
+        <v>424</v>
+      </c>
+      <c r="E115" t="s">
         <v>28</v>
       </c>
-      <c r="F115" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="H115" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="J115" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="L115" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="R115" s="7" t="s">
+      <c r="F115" t="s">
+        <v>29</v>
+      </c>
+      <c r="G115"/>
+      <c r="H115"/>
+      <c r="I115"/>
+      <c r="J115" t="s">
+        <v>231</v>
+      </c>
+      <c r="K115"/>
+      <c r="L115" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="M115"/>
+      <c r="N115"/>
+      <c r="O115"/>
+      <c r="P115"/>
+      <c r="Q115"/>
+      <c r="R115" t="s">
         <v>24</v>
       </c>
       <c r="S115" t="s">
+        <v>101</v>
+      </c>
+      <c r="T115" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="U115" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="V115" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="W115" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="X115" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y115" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>225</v>
+      </c>
+      <c r="B116" t="s">
+        <v>226</v>
+      </c>
+      <c r="C116"/>
+      <c r="D116" t="s">
+        <v>716</v>
+      </c>
+      <c r="E116" t="s">
+        <v>28</v>
+      </c>
+      <c r="F116" t="s">
+        <v>29</v>
+      </c>
+      <c r="G116"/>
+      <c r="H116"/>
+      <c r="I116"/>
+      <c r="J116" t="s">
+        <v>233</v>
+      </c>
+      <c r="K116"/>
+      <c r="L116" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="M116"/>
+      <c r="N116"/>
+      <c r="O116"/>
+      <c r="P116"/>
+      <c r="Q116"/>
+      <c r="R116" t="s">
+        <v>24</v>
+      </c>
+      <c r="S116" t="s">
+        <v>235</v>
+      </c>
+      <c r="T116" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="U116" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="V116" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="W116" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="X116" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y116" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>225</v>
+      </c>
+      <c r="B117" t="s">
+        <v>226</v>
+      </c>
+      <c r="C117"/>
+      <c r="D117" t="s">
+        <v>719</v>
+      </c>
+      <c r="E117" t="s">
+        <v>236</v>
+      </c>
+      <c r="F117" t="s">
+        <v>237</v>
+      </c>
+      <c r="G117"/>
+      <c r="H117"/>
+      <c r="I117"/>
+      <c r="J117" t="s">
+        <v>238</v>
+      </c>
+      <c r="K117"/>
+      <c r="L117" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="M117"/>
+      <c r="N117"/>
+      <c r="O117"/>
+      <c r="P117"/>
+      <c r="Q117"/>
+      <c r="R117" t="s">
+        <v>24</v>
+      </c>
+      <c r="S117" t="s">
         <v>25</v>
       </c>
-      <c r="T115" s="1">
-        <v>138</v>
-      </c>
-      <c r="U115" s="1">
-        <v>90</v>
-      </c>
-      <c r="V115" s="1">
-        <v>100</v>
-      </c>
-      <c r="W115" s="1">
-        <v>1</v>
-      </c>
-      <c r="X115" t="s">
+      <c r="T117" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="U117" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="V117" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="W117" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="X117" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="Y115" t="s">
+      <c r="Y117" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="7" t="s">
+    <row r="118" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
         <v>225</v>
       </c>
-      <c r="B116" s="7" t="s">
+      <c r="B118" t="s">
         <v>226</v>
       </c>
-      <c r="D116" s="7">
-        <v>1778</v>
-      </c>
-      <c r="E116" s="7" t="s">
+      <c r="C118"/>
+      <c r="D118">
+        <v>1767</v>
+      </c>
+      <c r="E118" t="s">
+        <v>722</v>
+      </c>
+      <c r="F118" t="s">
+        <v>723</v>
+      </c>
+      <c r="G118"/>
+      <c r="H118"/>
+      <c r="I118"/>
+      <c r="J118" t="s">
+        <v>724</v>
+      </c>
+      <c r="K118"/>
+      <c r="L118" s="15" t="s">
+        <v>725</v>
+      </c>
+      <c r="M118"/>
+      <c r="N118"/>
+      <c r="O118"/>
+      <c r="P118"/>
+      <c r="Q118"/>
+      <c r="R118" t="s">
+        <v>24</v>
+      </c>
+      <c r="S118" t="s">
+        <v>726</v>
+      </c>
+      <c r="T118" s="1">
+        <v>185</v>
+      </c>
+      <c r="U118" s="1">
+        <v>80</v>
+      </c>
+      <c r="W118" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="X118" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y118" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>225</v>
+      </c>
+      <c r="B119" t="s">
+        <v>226</v>
+      </c>
+      <c r="C119"/>
+      <c r="D119">
+        <v>1776</v>
+      </c>
+      <c r="E119" t="s">
+        <v>727</v>
+      </c>
+      <c r="F119" t="s">
+        <v>98</v>
+      </c>
+      <c r="G119"/>
+      <c r="H119"/>
+      <c r="I119"/>
+      <c r="J119" t="s">
+        <v>728</v>
+      </c>
+      <c r="K119"/>
+      <c r="L119" s="15" t="s">
+        <v>729</v>
+      </c>
+      <c r="M119"/>
+      <c r="N119"/>
+      <c r="O119"/>
+      <c r="P119"/>
+      <c r="Q119"/>
+      <c r="R119" t="s">
+        <v>24</v>
+      </c>
+      <c r="S119" t="s">
+        <v>58</v>
+      </c>
+      <c r="T119" s="1">
+        <v>206</v>
+      </c>
+      <c r="U119" s="1">
+        <v>80</v>
+      </c>
+      <c r="V119" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="W119" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="X119" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y119" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>225</v>
+      </c>
+      <c r="B120" t="s">
+        <v>226</v>
+      </c>
+      <c r="C120"/>
+      <c r="D120" t="s">
+        <v>731</v>
+      </c>
+      <c r="E120" t="s">
         <v>28</v>
       </c>
-      <c r="F116" s="7" t="s">
+      <c r="F120" t="s">
         <v>29</v>
       </c>
-      <c r="J116" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="L116" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="R116" s="7" t="s">
+      <c r="G120"/>
+      <c r="H120"/>
+      <c r="I120"/>
+      <c r="J120" t="s">
+        <v>732</v>
+      </c>
+      <c r="K120"/>
+      <c r="L120" s="15" t="s">
+        <v>733</v>
+      </c>
+      <c r="M120"/>
+      <c r="N120"/>
+      <c r="O120"/>
+      <c r="P120"/>
+      <c r="Q120"/>
+      <c r="R120" t="s">
         <v>24</v>
       </c>
-      <c r="S116" t="s">
-        <v>101</v>
-      </c>
-      <c r="T116" s="1">
-        <v>53</v>
-      </c>
-      <c r="U116" s="1">
-        <v>42</v>
-      </c>
-      <c r="V116" s="1">
+      <c r="S120" t="s">
+        <v>25</v>
+      </c>
+      <c r="T120" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="W120" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="X120" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y120" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>225</v>
+      </c>
+      <c r="B121" t="s">
+        <v>226</v>
+      </c>
+      <c r="C121"/>
+      <c r="D121">
+        <v>1783</v>
+      </c>
+      <c r="E121" t="s">
+        <v>722</v>
+      </c>
+      <c r="F121" t="s">
+        <v>723</v>
+      </c>
+      <c r="G121"/>
+      <c r="H121"/>
+      <c r="I121"/>
+      <c r="J121" t="s">
+        <v>735</v>
+      </c>
+      <c r="K121"/>
+      <c r="L121" s="15" t="s">
+        <v>736</v>
+      </c>
+      <c r="M121"/>
+      <c r="N121"/>
+      <c r="O121"/>
+      <c r="P121"/>
+      <c r="Q121"/>
+      <c r="R121" t="s">
+        <v>24</v>
+      </c>
+      <c r="S121" t="s">
+        <v>25</v>
+      </c>
+      <c r="T121" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="U121" s="1">
+        <v>57</v>
+      </c>
+      <c r="V121" s="1">
+        <v>64</v>
+      </c>
+      <c r="W121" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="X121" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y121" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="E122" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="W116" s="1">
-        <v>1</v>
-      </c>
-      <c r="X116" t="s">
-        <v>225</v>
-      </c>
-      <c r="Y116" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="117" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="D117" s="7">
-        <v>1781</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F117" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J117" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="L117" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="R117" s="7" t="s">
+      <c r="F122" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="J122" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="L122" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="R122" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="S117" t="s">
-        <v>235</v>
-      </c>
-      <c r="T117" s="1">
-        <v>51</v>
-      </c>
-      <c r="U117" s="1">
-        <v>30</v>
-      </c>
-      <c r="V117" s="1">
+      <c r="S122" t="s">
+        <v>212</v>
+      </c>
+      <c r="T122" s="1">
+        <v>400</v>
+      </c>
+      <c r="U122" s="1">
+        <v>485</v>
+      </c>
+      <c r="V122" s="1">
         <v>25</v>
       </c>
-      <c r="W117" s="1">
-        <v>1</v>
-      </c>
-      <c r="X117" t="s">
-        <v>225</v>
-      </c>
-      <c r="Y117" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="118" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="D118" s="7">
-        <v>1788</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="J118" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="L118" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="R118" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S118" t="s">
-        <v>25</v>
-      </c>
-      <c r="T118" s="1">
-        <v>203</v>
-      </c>
-      <c r="U118" s="1">
-        <v>105</v>
-      </c>
-      <c r="V118" s="1">
-        <v>90</v>
-      </c>
-      <c r="W118" s="1">
-        <v>1</v>
-      </c>
-      <c r="X118" t="s">
-        <v>225</v>
-      </c>
-      <c r="Y118" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="119" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L119" s="13"/>
-    </row>
-    <row r="120" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L120" s="13"/>
-    </row>
-    <row r="121" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L121" s="13"/>
-    </row>
-    <row r="122" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L122" s="13"/>
-    </row>
-    <row r="123" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="7" t="s">
+      <c r="W122" s="1">
+        <v>2</v>
+      </c>
+      <c r="X122" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B123" s="7" t="s">
+      <c r="Y122" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D123" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="E123" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F123" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="J123" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="L123" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="R123" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S123" t="s">
-        <v>212</v>
-      </c>
-      <c r="T123" s="1">
-        <v>400</v>
-      </c>
-      <c r="U123" s="1">
-        <v>485</v>
-      </c>
-      <c r="V123" s="1">
-        <v>25</v>
-      </c>
-      <c r="W123" s="1">
-        <v>2</v>
-      </c>
-      <c r="X123" t="s">
-        <v>240</v>
-      </c>
-      <c r="Y123" t="s">
-        <v>241</v>
-      </c>
+    </row>
+    <row r="123" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L123" s="13"/>
     </row>
     <row r="124" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L124" s="13"/>
@@ -7476,51 +8382,51 @@
       <c r="L127" s="13"/>
     </row>
     <row r="128" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L128" s="13"/>
+      <c r="A128" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J128" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="L128" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="R128" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S128" t="s">
+        <v>25</v>
+      </c>
+      <c r="T128" s="1">
+        <v>79</v>
+      </c>
+      <c r="U128" s="1">
+        <v>58</v>
+      </c>
+      <c r="V128" s="1">
+        <v>37</v>
+      </c>
+      <c r="W128" s="1">
+        <v>2</v>
+      </c>
+      <c r="X128" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="Y128" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="129" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="B129" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="F129" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J129" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="L129" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="R129" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S129" t="s">
-        <v>25</v>
-      </c>
-      <c r="T129" s="1">
-        <v>79</v>
-      </c>
-      <c r="U129" s="1">
-        <v>58</v>
-      </c>
-      <c r="V129" s="1">
-        <v>37</v>
-      </c>
-      <c r="W129" s="1">
-        <v>2</v>
-      </c>
-      <c r="X129" t="s">
-        <v>246</v>
-      </c>
-      <c r="Y129" t="s">
-        <v>247</v>
-      </c>
+      <c r="L129" s="13"/>
     </row>
     <row r="130" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L130" s="13"/>
@@ -7535,57 +8441,57 @@
       <c r="L133" s="13"/>
     </row>
     <row r="134" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L134" s="13"/>
+      <c r="A134" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="J134" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="L134" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="M134" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="R134" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S134" t="s">
+        <v>259</v>
+      </c>
+      <c r="T134" s="1">
+        <v>42</v>
+      </c>
+      <c r="U134" s="1">
+        <v>22</v>
+      </c>
+      <c r="V134" s="1">
+        <v>26</v>
+      </c>
+      <c r="W134" s="1">
+        <v>3</v>
+      </c>
+      <c r="X134" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y134" s="1" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="135" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="D135" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E135" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="F135" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="J135" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="L135" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="M135" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="R135" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S135" t="s">
-        <v>259</v>
-      </c>
-      <c r="T135" s="1">
-        <v>42</v>
-      </c>
-      <c r="U135" s="1">
-        <v>22</v>
-      </c>
-      <c r="V135" s="1">
-        <v>26</v>
-      </c>
-      <c r="W135" s="1">
-        <v>3</v>
-      </c>
-      <c r="X135" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y135" t="s">
-        <v>252</v>
-      </c>
+      <c r="L135" s="13"/>
     </row>
     <row r="136" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L136" s="13"/>
@@ -7594,54 +8500,54 @@
       <c r="L137" s="13"/>
     </row>
     <row r="138" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L138" s="13"/>
+      <c r="A138" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="J138" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="L138" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="R138" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S138" t="s">
+        <v>101</v>
+      </c>
+      <c r="T138" s="1">
+        <v>58</v>
+      </c>
+      <c r="U138" s="1">
+        <v>27</v>
+      </c>
+      <c r="V138" s="1">
+        <v>23</v>
+      </c>
+      <c r="W138" s="1">
+        <v>1</v>
+      </c>
+      <c r="X138" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="Y138" s="1" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="139" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="B139" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="D139" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E139" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="F139" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="J139" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="L139" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="R139" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S139" t="s">
-        <v>101</v>
-      </c>
-      <c r="T139" s="1">
-        <v>58</v>
-      </c>
-      <c r="U139" s="1">
-        <v>27</v>
-      </c>
-      <c r="V139" s="1">
-        <v>23</v>
-      </c>
-      <c r="W139" s="1">
-        <v>1</v>
-      </c>
-      <c r="X139" t="s">
-        <v>260</v>
-      </c>
-      <c r="Y139" t="s">
-        <v>261</v>
-      </c>
+      <c r="L139" s="13"/>
     </row>
     <row r="140" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L140" s="13"/>
@@ -7662,54 +8568,54 @@
       <c r="L145" s="13"/>
     </row>
     <row r="146" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L146" s="13"/>
+      <c r="A146" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E146" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F146" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="J146" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="L146" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="R146" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S146" t="s">
+        <v>25</v>
+      </c>
+      <c r="T146" s="1">
+        <v>73</v>
+      </c>
+      <c r="U146" s="1">
+        <v>52</v>
+      </c>
+      <c r="V146" s="1">
+        <v>30</v>
+      </c>
+      <c r="W146" s="1">
+        <v>3</v>
+      </c>
+      <c r="X146" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y146" s="1" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="147" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D147" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="E147" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F147" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="J147" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="L147" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="R147" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S147" t="s">
-        <v>25</v>
-      </c>
-      <c r="T147" s="1">
-        <v>73</v>
-      </c>
-      <c r="U147" s="1">
-        <v>52</v>
-      </c>
-      <c r="V147" s="1">
-        <v>30</v>
-      </c>
-      <c r="W147" s="1">
-        <v>3</v>
-      </c>
-      <c r="X147" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y147" t="s">
-        <v>267</v>
-      </c>
+      <c r="L147" s="13"/>
     </row>
     <row r="148" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L148" s="13"/>
@@ -7718,7 +8624,51 @@
       <c r="L149" s="13"/>
     </row>
     <row r="150" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L150" s="13"/>
+      <c r="A150" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D150" s="7">
+        <v>1769</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F150" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J150" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="L150" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="R150" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S150" t="s">
+        <v>25</v>
+      </c>
+      <c r="T150" s="1">
+        <v>76</v>
+      </c>
+      <c r="U150" s="1">
+        <v>54</v>
+      </c>
+      <c r="V150" s="1">
+        <v>45</v>
+      </c>
+      <c r="W150" s="1">
+        <v>2</v>
+      </c>
+      <c r="X150" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="Y150" s="1" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="151" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
@@ -7728,19 +8678,19 @@
         <v>272</v>
       </c>
       <c r="D151" s="7">
-        <v>1769</v>
+        <v>1773</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>28</v>
+        <v>275</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>29</v>
+        <v>276</v>
       </c>
       <c r="J151" s="7" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L151" s="13" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="R151" s="7" t="s">
         <v>24</v>
@@ -7749,21 +8699,21 @@
         <v>25</v>
       </c>
       <c r="T151" s="1">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="U151" s="1">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="V151" s="1">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="W151" s="1">
         <v>2</v>
       </c>
-      <c r="X151" t="s">
+      <c r="X151" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="Y151" t="s">
+      <c r="Y151" s="1" t="s">
         <v>272</v>
       </c>
     </row>
@@ -7775,19 +8725,19 @@
         <v>272</v>
       </c>
       <c r="D152" s="7">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>275</v>
+        <v>28</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>276</v>
+        <v>29</v>
       </c>
       <c r="J152" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L152" s="13" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="R152" s="7" t="s">
         <v>24</v>
@@ -7796,21 +8746,21 @@
         <v>25</v>
       </c>
       <c r="T152" s="1">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U152" s="1">
+        <v>50</v>
+      </c>
+      <c r="V152" s="1">
         <v>45</v>
-      </c>
-      <c r="V152" s="1">
-        <v>32</v>
       </c>
       <c r="W152" s="1">
         <v>2</v>
       </c>
-      <c r="X152" t="s">
+      <c r="X152" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="Y152" t="s">
+      <c r="Y152" s="1" t="s">
         <v>272</v>
       </c>
     </row>
@@ -7822,7 +8772,7 @@
         <v>272</v>
       </c>
       <c r="D153" s="7">
-        <v>1775</v>
+        <v>1783</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>28</v>
@@ -7831,10 +8781,10 @@
         <v>29</v>
       </c>
       <c r="J153" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L153" s="13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="R153" s="7" t="s">
         <v>24</v>
@@ -7843,76 +8793,184 @@
         <v>25</v>
       </c>
       <c r="T153" s="1">
-        <v>75</v>
+        <v>178</v>
       </c>
       <c r="U153" s="1">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="V153" s="1">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="W153" s="1">
         <v>2</v>
       </c>
-      <c r="X153" t="s">
+      <c r="X153" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="Y153" t="s">
+      <c r="Y153" s="1" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="154" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="7" t="s">
+      <c r="A154" t="s">
         <v>271</v>
       </c>
-      <c r="B154" s="7" t="s">
+      <c r="B154" t="s">
         <v>272</v>
       </c>
-      <c r="D154" s="7">
-        <v>1783</v>
-      </c>
-      <c r="E154" s="7" t="s">
+      <c r="C154"/>
+      <c r="D154">
+        <v>1760</v>
+      </c>
+      <c r="E154" t="s">
         <v>28</v>
       </c>
-      <c r="F154" s="7" t="s">
+      <c r="F154" t="s">
         <v>29</v>
       </c>
-      <c r="J154" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="L154" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="R154" s="7" t="s">
+      <c r="G154"/>
+      <c r="H154"/>
+      <c r="I154"/>
+      <c r="J154" t="s">
+        <v>738</v>
+      </c>
+      <c r="K154"/>
+      <c r="L154" s="15" t="s">
+        <v>739</v>
+      </c>
+      <c r="M154"/>
+      <c r="N154"/>
+      <c r="O154"/>
+      <c r="P154"/>
+      <c r="Q154"/>
+      <c r="R154" t="s">
         <v>24</v>
       </c>
       <c r="S154" t="s">
         <v>25</v>
       </c>
       <c r="T154" s="1">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="U154" s="1">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="V154" s="1">
-        <v>82</v>
-      </c>
-      <c r="W154" s="1">
-        <v>2</v>
-      </c>
-      <c r="X154" t="s">
+        <v>50</v>
+      </c>
+      <c r="W154" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="X154" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="Y154" t="s">
+      <c r="Y154" s="1" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="155" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L155" s="13"/>
+      <c r="A155" t="s">
+        <v>271</v>
+      </c>
+      <c r="B155" t="s">
+        <v>272</v>
+      </c>
+      <c r="C155"/>
+      <c r="D155" t="s">
+        <v>202</v>
+      </c>
+      <c r="E155" t="s">
+        <v>28</v>
+      </c>
+      <c r="F155" t="s">
+        <v>29</v>
+      </c>
+      <c r="G155"/>
+      <c r="H155"/>
+      <c r="I155"/>
+      <c r="J155" t="s">
+        <v>740</v>
+      </c>
+      <c r="K155"/>
+      <c r="L155" s="15" t="s">
+        <v>741</v>
+      </c>
+      <c r="M155"/>
+      <c r="N155"/>
+      <c r="O155"/>
+      <c r="P155"/>
+      <c r="Q155"/>
+      <c r="R155" t="s">
+        <v>24</v>
+      </c>
+      <c r="S155" t="s">
+        <v>101</v>
+      </c>
+      <c r="T155" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="U155" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="V155" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="W155" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="X155" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="Y155" s="1" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="156" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L156" s="13"/>
+      <c r="A156" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D156" s="7">
+        <v>1744</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F156" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J156" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="L156" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="R156" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S156" t="s">
+        <v>25</v>
+      </c>
+      <c r="T156" s="1">
+        <v>58</v>
+      </c>
+      <c r="U156" s="1">
+        <v>35</v>
+      </c>
+      <c r="V156" s="1">
+        <v>38</v>
+      </c>
+      <c r="W156" s="1">
+        <v>1</v>
+      </c>
+      <c r="X156" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="Y156" s="1" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="157" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
@@ -7921,43 +8979,43 @@
       <c r="B157" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="D157" s="7">
-        <v>1744</v>
+      <c r="D157" s="7" t="s">
+        <v>286</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>28</v>
+        <v>287</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>29</v>
+        <v>288</v>
       </c>
       <c r="J157" s="7" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="L157" s="13" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="R157" s="7" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="S157" t="s">
-        <v>25</v>
+        <v>291</v>
       </c>
       <c r="T157" s="1">
-        <v>58</v>
+        <v>610</v>
       </c>
       <c r="U157" s="1">
-        <v>35</v>
+        <v>480</v>
       </c>
       <c r="V157" s="1">
-        <v>38</v>
+        <v>280</v>
       </c>
       <c r="W157" s="1">
         <v>1</v>
       </c>
-      <c r="X157" t="s">
+      <c r="X157" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="Y157" t="s">
+      <c r="Y157" s="1" t="s">
         <v>283</v>
       </c>
     </row>
@@ -7968,43 +9026,43 @@
       <c r="B158" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="D158" s="7" t="s">
-        <v>286</v>
+      <c r="D158" s="7">
+        <v>1759</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>287</v>
+        <v>28</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>288</v>
+        <v>29</v>
       </c>
       <c r="J158" s="7" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L158" s="13" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="R158" s="7" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="S158" t="s">
-        <v>291</v>
+        <v>25</v>
       </c>
       <c r="T158" s="1">
-        <v>610</v>
+        <v>48</v>
       </c>
       <c r="U158" s="1">
-        <v>480</v>
+        <v>32</v>
       </c>
       <c r="V158" s="1">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="W158" s="1">
         <v>1</v>
       </c>
-      <c r="X158" t="s">
+      <c r="X158" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="Y158" t="s">
+      <c r="Y158" s="1" t="s">
         <v>283</v>
       </c>
     </row>
@@ -8016,42 +9074,42 @@
         <v>283</v>
       </c>
       <c r="D159" s="7">
-        <v>1759</v>
+        <v>1770</v>
       </c>
       <c r="E159" s="7" t="s">
-        <v>28</v>
+        <v>294</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>29</v>
+        <v>295</v>
       </c>
       <c r="J159" s="7" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="L159" s="13" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="R159" s="7" t="s">
         <v>24</v>
       </c>
       <c r="S159" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="T159" s="1">
-        <v>48</v>
+        <v>380</v>
       </c>
       <c r="U159" s="1">
-        <v>32</v>
+        <v>250</v>
       </c>
       <c r="V159" s="1">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="W159" s="1">
         <v>1</v>
       </c>
-      <c r="X159" t="s">
+      <c r="X159" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="Y159" t="s">
+      <c r="Y159" s="1" t="s">
         <v>283</v>
       </c>
     </row>
@@ -8063,91 +9121,47 @@
         <v>283</v>
       </c>
       <c r="D160" s="7">
-        <v>1770</v>
+        <v>1776</v>
       </c>
       <c r="E160" s="7" t="s">
-        <v>294</v>
+        <v>28</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>295</v>
+        <v>29</v>
       </c>
       <c r="J160" s="7" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L160" s="13" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="R160" s="7" t="s">
         <v>24</v>
       </c>
       <c r="S160" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="T160" s="1">
-        <v>380</v>
+        <v>150</v>
       </c>
       <c r="U160" s="1">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="V160" s="1">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="W160" s="1">
         <v>1</v>
       </c>
-      <c r="X160" t="s">
+      <c r="X160" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="Y160" t="s">
+      <c r="Y160" s="1" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="161" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="B161" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="D161" s="7">
-        <v>1776</v>
-      </c>
-      <c r="E161" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F161" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J161" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="L161" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="R161" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S161" t="s">
-        <v>25</v>
-      </c>
-      <c r="T161" s="1">
-        <v>150</v>
-      </c>
-      <c r="U161" s="1">
-        <v>85</v>
-      </c>
-      <c r="V161" s="1">
-        <v>80</v>
-      </c>
-      <c r="W161" s="1">
-        <v>1</v>
-      </c>
-      <c r="X161" t="s">
-        <v>246</v>
-      </c>
-      <c r="Y161" t="s">
-        <v>283</v>
-      </c>
+      <c r="L161" s="13"/>
     </row>
     <row r="162" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L162" s="13"/>
@@ -8156,57 +9170,57 @@
       <c r="L163" s="13"/>
     </row>
     <row r="164" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L164" s="13"/>
+      <c r="A164" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="E164" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F164" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="J164" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="K164" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="L164" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="R164" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S164" t="s">
+        <v>306</v>
+      </c>
+      <c r="T164" s="1">
+        <v>195</v>
+      </c>
+      <c r="U164" s="1">
+        <v>110</v>
+      </c>
+      <c r="V164" s="1">
+        <v>90</v>
+      </c>
+      <c r="W164" s="1">
+        <v>3</v>
+      </c>
+      <c r="X164" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y164" s="1" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="165" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="B165" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="D165" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="E165" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="F165" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="J165" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="K165" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="L165" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="R165" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S165" t="s">
-        <v>306</v>
-      </c>
-      <c r="T165" s="1">
-        <v>195</v>
-      </c>
-      <c r="U165" s="1">
-        <v>110</v>
-      </c>
-      <c r="V165" s="1">
-        <v>90</v>
-      </c>
-      <c r="W165" s="1">
-        <v>3</v>
-      </c>
-      <c r="X165" t="s">
-        <v>300</v>
-      </c>
-      <c r="Y165" t="s">
-        <v>301</v>
-      </c>
+      <c r="L165" s="13"/>
     </row>
     <row r="166" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L166" s="13"/>
@@ -8215,57 +9229,57 @@
       <c r="L167" s="13"/>
     </row>
     <row r="168" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L168" s="13"/>
+      <c r="A168" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="D168" s="7">
+        <v>1761</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F168" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J168" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="K168" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="L168" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="R168" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="S168" t="s">
+        <v>25</v>
+      </c>
+      <c r="T168" s="1">
+        <v>245</v>
+      </c>
+      <c r="U168" s="1">
+        <v>150</v>
+      </c>
+      <c r="V168" s="1">
+        <v>95</v>
+      </c>
+      <c r="W168" s="1">
+        <v>1</v>
+      </c>
+      <c r="X168" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="Y168" s="1" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="169" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="B169" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="D169" s="7">
-        <v>1761</v>
-      </c>
-      <c r="E169" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F169" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J169" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="K169" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="L169" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="R169" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="S169" t="s">
-        <v>25</v>
-      </c>
-      <c r="T169" s="1">
-        <v>245</v>
-      </c>
-      <c r="U169" s="1">
-        <v>150</v>
-      </c>
-      <c r="V169" s="1">
-        <v>95</v>
-      </c>
-      <c r="W169" s="1">
-        <v>1</v>
-      </c>
-      <c r="X169" t="s">
-        <v>307</v>
-      </c>
-      <c r="Y169" t="s">
-        <v>308</v>
-      </c>
+      <c r="L169" s="13"/>
     </row>
     <row r="170" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L170" s="13"/>
@@ -8286,7 +9300,45 @@
       <c r="L175" s="13"/>
     </row>
     <row r="176" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L176" s="13"/>
+      <c r="A176" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="F176" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="J176" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="L176" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="R176" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S176" t="s">
+        <v>101</v>
+      </c>
+      <c r="T176" s="1">
+        <v>84</v>
+      </c>
+      <c r="W176" s="1">
+        <v>3</v>
+      </c>
+      <c r="X176" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="Y176" s="1" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="177" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
@@ -8295,139 +9347,101 @@
       <c r="B177" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="D177" s="7" t="s">
-        <v>314</v>
+      <c r="D177" s="7">
+        <v>1718</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>196</v>
+        <v>86</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>315</v>
+        <v>173</v>
       </c>
       <c r="J177" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
+      </c>
+      <c r="K177" s="7" t="s">
+        <v>319</v>
       </c>
       <c r="L177" s="13" t="s">
-        <v>317</v>
+        <v>320</v>
+      </c>
+      <c r="M177" s="7" t="s">
+        <v>321</v>
       </c>
       <c r="R177" s="7" t="s">
         <v>24</v>
       </c>
       <c r="S177" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="T177" s="1">
-        <v>84</v>
+        <v>420</v>
+      </c>
+      <c r="U177" s="1">
+        <v>180</v>
+      </c>
+      <c r="V177" s="1">
+        <v>160</v>
       </c>
       <c r="W177" s="1">
         <v>3</v>
       </c>
-      <c r="X177" t="s">
+      <c r="X177" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="Y177" t="s">
+      <c r="Y177" s="1" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="B178" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D178" s="7">
-        <v>1718</v>
-      </c>
-      <c r="E178" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F178" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="J178" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="K178" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="L178" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="M178" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="R178" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S178" t="s">
-        <v>25</v>
-      </c>
-      <c r="T178" s="1">
-        <v>420</v>
-      </c>
-      <c r="U178" s="1">
-        <v>180</v>
-      </c>
-      <c r="V178" s="1">
-        <v>160</v>
-      </c>
-      <c r="W178" s="1">
-        <v>3</v>
-      </c>
-      <c r="X178" t="s">
-        <v>312</v>
-      </c>
-      <c r="Y178" t="s">
-        <v>313</v>
-      </c>
+    <row r="178" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L178" s="13"/>
     </row>
     <row r="179" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L179" s="13"/>
     </row>
-    <row r="180" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L180" s="13"/>
+    <row r="180" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="B180" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="D180" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F180" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J180" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="L180" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="R180" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S180" t="s">
+        <v>25</v>
+      </c>
+      <c r="T180" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="W180" s="1">
+        <v>3</v>
+      </c>
+      <c r="X180" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="Y180" s="1" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="181" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="B181" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="D181" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="E181" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F181" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J181" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="L181" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="R181" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S181" t="s">
-        <v>25</v>
-      </c>
-      <c r="T181" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="W181" s="1">
-        <v>3</v>
-      </c>
-      <c r="X181" t="s">
-        <v>322</v>
-      </c>
-      <c r="Y181" t="s">
-        <v>323</v>
-      </c>
+      <c r="L181" s="13"/>
     </row>
     <row r="182" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L182" s="13"/>
@@ -8436,54 +9450,54 @@
       <c r="L183" s="13"/>
     </row>
     <row r="184" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L184" s="13"/>
+      <c r="A184" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E184" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="F184" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="J184" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="L184" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="R184" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S184" t="s">
+        <v>146</v>
+      </c>
+      <c r="T184" s="1">
+        <v>246</v>
+      </c>
+      <c r="U184" s="1">
+        <v>442</v>
+      </c>
+      <c r="V184" s="1">
+        <v>247</v>
+      </c>
+      <c r="W184" s="1">
+        <v>3</v>
+      </c>
+      <c r="X184" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="Y184" s="1" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="185" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="B185" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="D185" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="E185" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="F185" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="J185" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="L185" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="R185" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S185" t="s">
-        <v>146</v>
-      </c>
-      <c r="T185" s="1">
-        <v>246</v>
-      </c>
-      <c r="U185" s="1">
-        <v>442</v>
-      </c>
-      <c r="V185" s="1">
-        <v>247</v>
-      </c>
-      <c r="W185" s="1">
-        <v>3</v>
-      </c>
-      <c r="X185" t="s">
-        <v>328</v>
-      </c>
-      <c r="Y185" t="s">
-        <v>329</v>
-      </c>
+      <c r="L185" s="13"/>
     </row>
     <row r="186" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L186" s="13"/>
@@ -8492,9 +9506,56 @@
       <c r="L187" s="13"/>
     </row>
     <row r="188" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L188" s="13"/>
-    </row>
-    <row r="189" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="B188" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D188" s="7">
+        <v>1753</v>
+      </c>
+      <c r="E188" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F188" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="J188" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="K188" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="L188" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="R188" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S188" t="s">
+        <v>25</v>
+      </c>
+      <c r="T188" s="1">
+        <v>50</v>
+      </c>
+      <c r="U188" s="1">
+        <v>180</v>
+      </c>
+      <c r="V188" s="1">
+        <v>80</v>
+      </c>
+      <c r="W188" s="1">
+        <v>3</v>
+      </c>
+      <c r="X188" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="Y188" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="189" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
         <v>335</v>
       </c>
@@ -8502,22 +9563,22 @@
         <v>336</v>
       </c>
       <c r="D189" s="7">
-        <v>1753</v>
+        <v>1760</v>
       </c>
       <c r="E189" s="7" t="s">
         <v>135</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
       <c r="J189" s="7" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="K189" s="7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="L189" s="13" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="R189" s="7" t="s">
         <v>24</v>
@@ -8526,120 +9587,73 @@
         <v>25</v>
       </c>
       <c r="T189" s="1">
-        <v>50</v>
+        <v>196</v>
       </c>
       <c r="U189" s="1">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="V189" s="1">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="W189" s="1">
         <v>3</v>
       </c>
-      <c r="X189" t="s">
+      <c r="X189" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="Y189" t="s">
+      <c r="Y189" s="1" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="B190" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="D190" s="7">
-        <v>1760</v>
-      </c>
-      <c r="E190" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="F190" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="J190" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="K190" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="L190" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="R190" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S190" t="s">
-        <v>25</v>
-      </c>
-      <c r="T190" s="1">
-        <v>196</v>
-      </c>
-      <c r="U190" s="1">
-        <v>110</v>
-      </c>
-      <c r="V190" s="1">
-        <v>85</v>
-      </c>
-      <c r="W190" s="1">
-        <v>3</v>
-      </c>
-      <c r="X190" t="s">
-        <v>335</v>
-      </c>
-      <c r="Y190" t="s">
-        <v>336</v>
-      </c>
+    <row r="190" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L190" s="13"/>
     </row>
     <row r="191" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L191" s="13"/>
     </row>
     <row r="192" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L192" s="13"/>
+      <c r="A192" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="E192" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="F192" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="J192" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="L192" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="R192" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S192" t="s">
+        <v>25</v>
+      </c>
+      <c r="T192" s="1">
+        <v>172</v>
+      </c>
+      <c r="W192" s="1">
+        <v>3</v>
+      </c>
+      <c r="X192" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="Y192" s="1" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="193" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="B193" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="D193" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="E193" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="F193" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="J193" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="L193" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="R193" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S193" t="s">
-        <v>25</v>
-      </c>
-      <c r="T193" s="1">
-        <v>172</v>
-      </c>
-      <c r="W193" s="1">
-        <v>3</v>
-      </c>
-      <c r="X193" t="s">
-        <v>344</v>
-      </c>
-      <c r="Y193" t="s">
-        <v>345</v>
-      </c>
+      <c r="L193" s="13"/>
     </row>
     <row r="194" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L194" s="13"/>
@@ -8648,44 +9662,91 @@
       <c r="L195" s="13"/>
     </row>
     <row r="196" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L196" s="13"/>
-    </row>
-    <row r="197" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="D196" s="7">
+        <v>1702</v>
+      </c>
+      <c r="E196" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="F196" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="J196" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="K196" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="L196" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="R196" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S196" t="s">
+        <v>358</v>
+      </c>
+      <c r="T196" s="1">
+        <v>185</v>
+      </c>
+      <c r="U196" s="1">
+        <v>72</v>
+      </c>
+      <c r="V196" s="1">
+        <v>50</v>
+      </c>
+      <c r="W196" s="1">
+        <v>2</v>
+      </c>
+      <c r="X196" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="Y196" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="197" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
         <v>351</v>
       </c>
       <c r="B197" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="D197" s="7">
-        <v>1702</v>
+      <c r="D197" s="7" t="s">
+        <v>359</v>
       </c>
       <c r="E197" s="7" t="s">
         <v>353</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="J197" s="7" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="K197" s="7" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="L197" s="13" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="R197" s="7" t="s">
         <v>24</v>
       </c>
       <c r="S197" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="T197" s="1">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="U197" s="1">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V197" s="1">
         <v>50</v>
@@ -8693,74 +9754,74 @@
       <c r="W197" s="1">
         <v>2</v>
       </c>
-      <c r="X197" t="s">
+      <c r="X197" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="Y197" t="s">
+      <c r="Y197" s="1" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="198" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="B198" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="D198" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="E198" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="F198" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="J198" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="K198" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="L198" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="R198" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S198" t="s">
-        <v>364</v>
-      </c>
-      <c r="T198" s="1">
-        <v>180</v>
-      </c>
-      <c r="U198" s="1">
-        <v>70</v>
-      </c>
-      <c r="V198" s="1">
-        <v>50</v>
-      </c>
-      <c r="W198" s="1">
-        <v>2</v>
-      </c>
-      <c r="X198" t="s">
-        <v>351</v>
-      </c>
-      <c r="Y198" t="s">
-        <v>352</v>
-      </c>
+      <c r="L198" s="13"/>
     </row>
     <row r="199" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L199" s="13"/>
     </row>
-    <row r="200" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L200" s="13"/>
     </row>
     <row r="201" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L201" s="13"/>
     </row>
     <row r="202" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L202" s="13"/>
+      <c r="A202" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="B202" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="D202" s="7">
+        <v>1750</v>
+      </c>
+      <c r="E202" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F202" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="J202" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="K202" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="L202" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="R202" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S202" t="s">
+        <v>25</v>
+      </c>
+      <c r="T202" s="1">
+        <v>450</v>
+      </c>
+      <c r="U202" s="1">
+        <v>190</v>
+      </c>
+      <c r="V202" s="1">
+        <v>170</v>
+      </c>
+      <c r="W202" s="1">
+        <v>3</v>
+      </c>
+      <c r="X202" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="Y202" s="1" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="203" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
@@ -8770,100 +9831,50 @@
         <v>366</v>
       </c>
       <c r="D203" s="7">
-        <v>1750</v>
+        <v>1755</v>
       </c>
       <c r="E203" s="7" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>105</v>
+        <v>370</v>
       </c>
       <c r="J203" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="K203" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L203" s="13" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="R203" s="7" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="S203" t="s">
-        <v>25</v>
+        <v>291</v>
       </c>
       <c r="T203" s="1">
-        <v>450</v>
+        <v>320</v>
       </c>
       <c r="U203" s="1">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="V203" s="1">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="W203" s="1">
         <v>3</v>
       </c>
-      <c r="X203" t="s">
+      <c r="X203" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="Y203" t="s">
+      <c r="Y203" s="1" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="204" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="B204" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="D204" s="7">
-        <v>1755</v>
-      </c>
-      <c r="E204" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F204" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="J204" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="L204" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="R204" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="S204" t="s">
-        <v>291</v>
-      </c>
-      <c r="T204" s="1">
-        <v>320</v>
-      </c>
-      <c r="U204" s="1">
-        <v>210</v>
-      </c>
-      <c r="V204" s="1">
-        <v>140</v>
-      </c>
-      <c r="W204" s="1">
-        <v>3</v>
-      </c>
-      <c r="X204" t="s">
-        <v>365</v>
-      </c>
-      <c r="Y204" t="s">
-        <v>366</v>
-      </c>
+      <c r="L204" s="13"/>
     </row>
     <row r="205" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L205" s="13"/>
-    </row>
-    <row r="206" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L206" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -8875,128 +9886,143 @@
     <hyperlink ref="L53" r:id="rId5" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
     <hyperlink ref="L54" r:id="rId6" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
     <hyperlink ref="L55" r:id="rId7" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="L103" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="L104" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="L111" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="L112" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="L115" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="L116" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="L117" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="L118" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="L123" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="L129" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="L135" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="L139" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="L147" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="L151" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="L152" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="L153" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="L154" r:id="rId24" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="L157" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="L158" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="L159" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="L160" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="L161" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="L165" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="L169" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="L177" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="L178" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="L181" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="L185" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="L189" r:id="rId36" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="L190" r:id="rId37" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="L193" r:id="rId38" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="L197" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="L198" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="L203" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="L204" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="L3" r:id="rId43" xr:uid="{C93FFFB4-311C-431D-A81A-5ED783E7D10D}"/>
-    <hyperlink ref="L4" r:id="rId44" xr:uid="{BEE53EB8-5420-4E5B-9125-9EFAF078A599}"/>
-    <hyperlink ref="L7" r:id="rId45" xr:uid="{D9870754-541D-47FC-8A89-370E50BA9055}"/>
-    <hyperlink ref="L6" r:id="rId46" xr:uid="{7D3D2B05-56E6-4E6D-B145-2A3A5AC87887}"/>
-    <hyperlink ref="L5" r:id="rId47" xr:uid="{8DE15AD6-1CFB-408F-8AF9-ED3B39CAC211}"/>
-    <hyperlink ref="L9" r:id="rId48" xr:uid="{410F5B7C-2B6E-4021-AD10-EA3E2911C15B}"/>
-    <hyperlink ref="L12" r:id="rId49" xr:uid="{368E8181-4037-4114-9A18-812E5C911AAE}"/>
-    <hyperlink ref="L13" r:id="rId50" xr:uid="{64060F1C-BE13-4D25-B541-1FD39F322381}"/>
-    <hyperlink ref="L14" r:id="rId51" xr:uid="{98D49299-AAAB-4950-9AAF-B7D85CE54D79}"/>
-    <hyperlink ref="L11" r:id="rId52" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Nancy%2C_%C3%A9glise_baroque_Notre_Dame_de_Bonsecours%2C_mausol%C3%A9e_de_Catherine_Opalinska_1.jpg/960px-Nancy%2C_%C3%A9glise_baroque_Notre_Dame_de_Bonsecours%2C_mausol%C3%A9e_de_Catherine_Opalinska_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C6F5C490-5299-4E39-9A5C-BC39322DEB9D}"/>
-    <hyperlink ref="L10" r:id="rId53" xr:uid="{7D86CCCE-86BB-44CF-878C-EC63C89717B3}"/>
-    <hyperlink ref="L8" r:id="rId54" xr:uid="{CFC1415A-C7E0-46F3-B2F3-16F8EE0787A9}"/>
-    <hyperlink ref="L15" r:id="rId55" xr:uid="{C2A95D2E-EE39-4A59-88F2-AD2A139A9566}"/>
-    <hyperlink ref="L16" r:id="rId56" xr:uid="{9E05E86C-37E4-4FDB-BFF2-1D98FD31D2DA}"/>
-    <hyperlink ref="L21" r:id="rId57" xr:uid="{EEA3D149-41D6-461B-9972-761A5FB77D1C}"/>
-    <hyperlink ref="L22" r:id="rId58" xr:uid="{DA958F5E-84DB-48F0-95EC-1CF07515DCE9}"/>
-    <hyperlink ref="L23" r:id="rId59" xr:uid="{B2981A04-5715-4061-97AC-A9003B0B4825}"/>
-    <hyperlink ref="L24" r:id="rId60" xr:uid="{DB5CBEE9-42A1-4648-91FE-361D772D1E1E}"/>
-    <hyperlink ref="L25" r:id="rId61" xr:uid="{86A56036-B9FE-4287-82FD-EAD58725A247}"/>
-    <hyperlink ref="L27" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Sculpture_of_Shakespeare_in_the_garden_of_New_Place%2C_Stratford-upon-Avon.jpg/960px-Sculpture_of_Shakespeare_in_the_garden_of_New_Place%2C_Stratford-upon-Avon.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B79B2EAA-7972-4EAC-B81F-1D2B558C1EFD}"/>
-    <hyperlink ref="L26" r:id="rId63" xr:uid="{9DEBED11-29C7-47D7-87B2-7BCA972527B4}"/>
-    <hyperlink ref="L28" r:id="rId64" xr:uid="{5E23B361-79FD-47DB-81A8-552B4A92CBF3}"/>
-    <hyperlink ref="L31" r:id="rId65" xr:uid="{EF5F1708-9F84-4150-BB3E-BCB789F37744}"/>
-    <hyperlink ref="L32" r:id="rId66" xr:uid="{C7755D7F-D07E-4747-8FCF-ED7A5756464B}"/>
-    <hyperlink ref="L33" r:id="rId67" xr:uid="{AC2A0C7C-27D4-4067-BD1F-904E5A45511A}"/>
-    <hyperlink ref="L35" r:id="rId68" xr:uid="{C0651B9D-9098-4FFD-82EE-1BACEC606B7F}"/>
-    <hyperlink ref="L34" r:id="rId69" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Portrait_of_Pope_Clemente_XII_%28Lorenzo_Corsini%29_by_Edme_Bouchardon%2C_French%2C_after_1730%2C_tinted_plaster_and_terracotta_-_California_Palace_of_the_Legion_of_Honor_-_DSC07739.JPG/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8B86DBCE-0A72-4760-A47C-0E8B681B3570}"/>
-    <hyperlink ref="L36" r:id="rId70" xr:uid="{8A084969-8958-49B4-853C-3AE75082A12B}"/>
-    <hyperlink ref="L38" r:id="rId71" xr:uid="{CF536289-4EEE-45F1-8084-B0371B565C41}"/>
-    <hyperlink ref="L37" r:id="rId72" xr:uid="{8A257BF5-79FF-4BF8-A978-DF4AA2821305}"/>
-    <hyperlink ref="I38" r:id="rId73" xr:uid="{B4207168-3FEC-425F-A795-F5784DF13615}"/>
-    <hyperlink ref="I37" r:id="rId74" xr:uid="{78A5F208-39F1-4E0D-8845-26F0E123BACC}"/>
-    <hyperlink ref="L39" r:id="rId75" xr:uid="{CCBD85D5-3F49-4572-824C-CA8F88DB5FDC}"/>
-    <hyperlink ref="L40" r:id="rId76" xr:uid="{7DBEBA58-DBE8-4168-8217-CD887A3BCE97}"/>
-    <hyperlink ref="G39" r:id="rId77" xr:uid="{26E871FC-575D-43D6-9F77-54326016822C}"/>
-    <hyperlink ref="I39" r:id="rId78" xr:uid="{99DED6AB-344A-4740-A203-89BBD0FE2617}"/>
-    <hyperlink ref="I41" r:id="rId79" xr:uid="{9FD53BA3-BFCA-4144-BDFF-649BBC5B3558}"/>
-    <hyperlink ref="L41" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9d/05_2023_Napoli_ITA_Duomo_%28Chiesa%29_-_Altare_maggiore%2C_scultura_l%27Assunta_di_Pietro_Bracci_1739_Tardo_Barocco_-_photo_Paolo_Villa_FO231710_correction_with_gimp.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F3102698-B78C-4C21-9039-4341BB078473}"/>
-    <hyperlink ref="L42" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/94/Pietro_bracci%2C_monumento_del_cardinale_carlo_leopoldo_calcagnini%2C_1746_ca._01.jpg/960px-Pietro_bracci%2C_monumento_del_cardinale_carlo_leopoldo_calcagnini%2C_1746_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4D7419BA-CC4A-4779-9436-FB1EA35A4AAD}"/>
-    <hyperlink ref="L43" r:id="rId82" xr:uid="{6433C034-4867-4ED5-87FB-FB4304FA60D4}"/>
-    <hyperlink ref="L45" r:id="rId83" xr:uid="{F2AF0062-C78E-46E8-B793-FB34A67B76CB}"/>
-    <hyperlink ref="L46" r:id="rId84" xr:uid="{3E3EC00B-8ACF-42AB-A745-A4201CABFE7E}"/>
-    <hyperlink ref="L44" r:id="rId85" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/57/Pierre_Corneille%2C_Jean-Jacques_Caffieri%2C_Paris_1723_1792.JPG/960px-Pierre_Corneille%2C_Jean-Jacques_Caffieri%2C_Paris_1723_1792.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E2469EC-8642-4E81-A446-2CC2FAE8B43E}"/>
-    <hyperlink ref="L47" r:id="rId86" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Hope_Nourishes_Love%2C_by_Jean-Jacques_Caffieri_%28Getty_103RR5%29.jpg/960px-Hope_Nourishes_Love%2C_by_Jean-Jacques_Caffieri_%28Getty_103RR5%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{8F832910-E656-4EFB-AC57-3D74592E6676}"/>
-    <hyperlink ref="L48" r:id="rId87" xr:uid="{07CA4426-387E-4AF5-ABAB-4128909EC254}"/>
-    <hyperlink ref="L56" r:id="rId88" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Antonio_Canova-Theseus_and_the_Minotaur-Victoria_and_Albert_Museum.jpg/960px-Antonio_Canova-Theseus_and_the_Minotaur-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2E9A1016-E90D-4659-8209-31B74E3F24C7}"/>
-    <hyperlink ref="L59" r:id="rId89" xr:uid="{6C84B94A-43B1-4D8A-9BF9-CDFE564415F5}"/>
-    <hyperlink ref="L57" r:id="rId90" xr:uid="{B3640A00-3EC5-4C99-82B5-B36103E6C177}"/>
-    <hyperlink ref="L58" r:id="rId91" xr:uid="{A1A250C1-22B8-444E-8FE4-18FD5FB58CF3}"/>
-    <hyperlink ref="L61" r:id="rId92" xr:uid="{5ECC010C-30BE-43F0-A7CA-0260E3CE130D}"/>
-    <hyperlink ref="L62" r:id="rId93" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Antonio_Corradini_-_Dama_Velata_%28Puritas%29_-_Museo_del_Settecento_Veneziano_-_Ca%27_Rezzonico%2C_Venice.jpg/1920px-Antonio_Corradini_-_Dama_Velata_%28Puritas%29_-_Museo_del_Settecento_Veneziano_-_Ca%27_Rezzonico%2C_Venice.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E067AB51-1DFF-4081-BF9C-2160687A1817}"/>
-    <hyperlink ref="L63" r:id="rId94" xr:uid="{40249E18-E873-4187-A04E-BC43AA5870BF}"/>
-    <hyperlink ref="L64" r:id="rId95" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/12/Die_Zeit_enthuellt_die_Wahrheit_Grosser_Garten_Dresden-2.jpg/960px-Die_Zeit_enthuellt_die_Wahrheit_Grosser_Garten_Dresden-2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A3A6C43D-6262-4AB8-8B6D-156B47AA3737}"/>
-    <hyperlink ref="L65" r:id="rId96" xr:uid="{302541C8-469A-4C1B-901B-23B0A5F49E25}"/>
-    <hyperlink ref="L66" r:id="rId97" xr:uid="{63E34BC2-58C7-4CFF-BD2E-20022C208234}"/>
-    <hyperlink ref="L67" r:id="rId98" xr:uid="{8CC71EB9-3199-49EF-A7A9-510A7755A425}"/>
-    <hyperlink ref="L68" r:id="rId99" xr:uid="{DAE8B983-E503-400A-BAF0-FACE83FED6E4}"/>
-    <hyperlink ref="L69" r:id="rId100" xr:uid="{FE11C8C7-7233-40B4-BA5F-1A8528A9B5B6}"/>
-    <hyperlink ref="L71" r:id="rId101" xr:uid="{C60C02F6-E3DE-459C-ABD4-F5D2850BFBFD}"/>
-    <hyperlink ref="L70" r:id="rId102" xr:uid="{C8B23DFB-0783-41B8-ABC2-49EF1E8F4E4C}"/>
-    <hyperlink ref="L72" r:id="rId103" xr:uid="{F6E29A87-A4DE-4D36-A3F6-1EF40D094D20}"/>
-    <hyperlink ref="L73" r:id="rId104" xr:uid="{9C249EE3-FBC9-42B3-ADF3-45DA8444C250}"/>
-    <hyperlink ref="L74" r:id="rId105" xr:uid="{736CB61F-DB8D-4D34-831C-03D972612AD4}"/>
-    <hyperlink ref="L77" r:id="rId106" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/2012--DSC_0253-C%C3%A9notaphe-du-grand-Dauphin-par-Coustou-dans-la-cathedrale-de-Sens.jpg/960px-2012--DSC_0253-C%C3%A9notaphe-du-grand-Dauphin-par-Coustou-dans-la-cathedrale-de-Sens.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8B3A1AC7-EC23-47AE-952E-EBEB844B3107}"/>
-    <hyperlink ref="L75" r:id="rId107" xr:uid="{BAE1A9D4-896A-4274-B7A4-D7851AAFF3E4}"/>
-    <hyperlink ref="L76" r:id="rId108" xr:uid="{0876674F-89FF-491E-A710-E8D816C42436}"/>
-    <hyperlink ref="L83" r:id="rId109" xr:uid="{93422A34-E47F-4EC0-B9B6-C9390AF2A5A4}"/>
-    <hyperlink ref="L84" r:id="rId110" xr:uid="{239D762E-78B0-4394-89DF-444F8993C868}"/>
-    <hyperlink ref="L85" r:id="rId111" xr:uid="{C601465F-6588-4CFC-A32C-1D37F5CFF0E1}"/>
-    <hyperlink ref="L86" r:id="rId112" xr:uid="{0B562E20-DF22-47B8-B6FB-AD1E07393A01}"/>
-    <hyperlink ref="L87" r:id="rId113" xr:uid="{BE4D15ED-CB7B-4449-A950-1A890376BCA4}"/>
-    <hyperlink ref="L90" r:id="rId114" xr:uid="{6AB13AFE-2406-4E93-ADA6-46FDCD31365A}"/>
-    <hyperlink ref="L88" r:id="rId115" xr:uid="{C83A0152-012B-483B-9231-2A1E78BBD9C0}"/>
-    <hyperlink ref="L89" r:id="rId116" xr:uid="{47B42195-9EC3-40B8-9B46-BD6E6B84E07C}"/>
-    <hyperlink ref="L91" r:id="rId117" xr:uid="{FC084A53-72A5-46D6-BA8B-9EDF408325E8}"/>
-    <hyperlink ref="L93" r:id="rId118" xr:uid="{A0209D99-D2A7-4D01-9D4A-1D01BE96F274}"/>
-    <hyperlink ref="L94" r:id="rId119" xr:uid="{87800057-0E6E-4997-AE5C-8E9E992038EC}"/>
-    <hyperlink ref="L92" r:id="rId120" xr:uid="{219B437E-3E02-401E-B8DD-54C18AE1422E}"/>
-    <hyperlink ref="L95" r:id="rId121" xr:uid="{E4D15D0F-4493-49C9-82EC-921ADE7F7649}"/>
-    <hyperlink ref="L96" r:id="rId122" xr:uid="{08D0AD74-167F-460E-9E0D-87B452D8FCDA}"/>
-    <hyperlink ref="L97" r:id="rId123" xr:uid="{79C25996-0268-4345-9482-E6D0D91FBCDB}"/>
-    <hyperlink ref="L98" r:id="rId124" xr:uid="{6A6598FD-AB7A-4377-A28E-D84A11EE770B}"/>
-    <hyperlink ref="G97" r:id="rId125" xr:uid="{4968AB49-790D-4B21-834D-BD88FF405AF0}"/>
-    <hyperlink ref="L99" r:id="rId126" xr:uid="{6F6F2D1A-8AC2-4E8F-AD62-5895107640F4}"/>
-    <hyperlink ref="L102" r:id="rId127" xr:uid="{1A778003-D53A-46C7-9C4F-0866ED4A1FBF}"/>
-    <hyperlink ref="L100" r:id="rId128" xr:uid="{CEBDE0C6-0B4A-4C8F-BAEC-6CA4771D91A9}"/>
-    <hyperlink ref="L101" r:id="rId129" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/07/Venus_of_the_Doves_by_Etienne-Maurice_Falconet%2C_undated_mid_1700s%2C_marble_-_National_Gallery_of_Art%2C_Washington_-_DSC09976.JPG/1280px-Venus_of_the_Doves_by_Etienne-Maurice_Falconet%2C_undated_mid_1700s%2C_marble_-_National_Gallery_of_Art%2C_Washington_-_DSC09976.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{207012E8-F898-42AB-A943-D36FADE8F355}"/>
+    <hyperlink ref="L122" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="L128" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="L134" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="L138" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="L146" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="L150" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="L151" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="L152" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="L153" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="L156" r:id="rId17" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="L157" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="L158" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="L159" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="L160" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="L164" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="L168" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="L176" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="L177" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="L180" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="L184" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="L188" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="L189" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="L192" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="L196" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="L197" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="L202" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="L203" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="L3" r:id="rId35" xr:uid="{C93FFFB4-311C-431D-A81A-5ED783E7D10D}"/>
+    <hyperlink ref="L4" r:id="rId36" xr:uid="{BEE53EB8-5420-4E5B-9125-9EFAF078A599}"/>
+    <hyperlink ref="L7" r:id="rId37" xr:uid="{D9870754-541D-47FC-8A89-370E50BA9055}"/>
+    <hyperlink ref="L6" r:id="rId38" xr:uid="{7D3D2B05-56E6-4E6D-B145-2A3A5AC87887}"/>
+    <hyperlink ref="L5" r:id="rId39" xr:uid="{8DE15AD6-1CFB-408F-8AF9-ED3B39CAC211}"/>
+    <hyperlink ref="L9" r:id="rId40" xr:uid="{410F5B7C-2B6E-4021-AD10-EA3E2911C15B}"/>
+    <hyperlink ref="L12" r:id="rId41" xr:uid="{368E8181-4037-4114-9A18-812E5C911AAE}"/>
+    <hyperlink ref="L13" r:id="rId42" xr:uid="{64060F1C-BE13-4D25-B541-1FD39F322381}"/>
+    <hyperlink ref="L14" r:id="rId43" xr:uid="{98D49299-AAAB-4950-9AAF-B7D85CE54D79}"/>
+    <hyperlink ref="L11" r:id="rId44" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Nancy%2C_%C3%A9glise_baroque_Notre_Dame_de_Bonsecours%2C_mausol%C3%A9e_de_Catherine_Opalinska_1.jpg/960px-Nancy%2C_%C3%A9glise_baroque_Notre_Dame_de_Bonsecours%2C_mausol%C3%A9e_de_Catherine_Opalinska_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C6F5C490-5299-4E39-9A5C-BC39322DEB9D}"/>
+    <hyperlink ref="L10" r:id="rId45" xr:uid="{7D86CCCE-86BB-44CF-878C-EC63C89717B3}"/>
+    <hyperlink ref="L8" r:id="rId46" xr:uid="{CFC1415A-C7E0-46F3-B2F3-16F8EE0787A9}"/>
+    <hyperlink ref="L15" r:id="rId47" xr:uid="{C2A95D2E-EE39-4A59-88F2-AD2A139A9566}"/>
+    <hyperlink ref="L16" r:id="rId48" xr:uid="{9E05E86C-37E4-4FDB-BFF2-1D98FD31D2DA}"/>
+    <hyperlink ref="L21" r:id="rId49" xr:uid="{EEA3D149-41D6-461B-9972-761A5FB77D1C}"/>
+    <hyperlink ref="L22" r:id="rId50" xr:uid="{DA958F5E-84DB-48F0-95EC-1CF07515DCE9}"/>
+    <hyperlink ref="L23" r:id="rId51" xr:uid="{B2981A04-5715-4061-97AC-A9003B0B4825}"/>
+    <hyperlink ref="L24" r:id="rId52" xr:uid="{DB5CBEE9-42A1-4648-91FE-361D772D1E1E}"/>
+    <hyperlink ref="L25" r:id="rId53" xr:uid="{86A56036-B9FE-4287-82FD-EAD58725A247}"/>
+    <hyperlink ref="L27" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Sculpture_of_Shakespeare_in_the_garden_of_New_Place%2C_Stratford-upon-Avon.jpg/960px-Sculpture_of_Shakespeare_in_the_garden_of_New_Place%2C_Stratford-upon-Avon.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B79B2EAA-7972-4EAC-B81F-1D2B558C1EFD}"/>
+    <hyperlink ref="L26" r:id="rId55" xr:uid="{9DEBED11-29C7-47D7-87B2-7BCA972527B4}"/>
+    <hyperlink ref="L28" r:id="rId56" xr:uid="{5E23B361-79FD-47DB-81A8-552B4A92CBF3}"/>
+    <hyperlink ref="L31" r:id="rId57" xr:uid="{EF5F1708-9F84-4150-BB3E-BCB789F37744}"/>
+    <hyperlink ref="L32" r:id="rId58" xr:uid="{C7755D7F-D07E-4747-8FCF-ED7A5756464B}"/>
+    <hyperlink ref="L33" r:id="rId59" xr:uid="{AC2A0C7C-27D4-4067-BD1F-904E5A45511A}"/>
+    <hyperlink ref="L35" r:id="rId60" xr:uid="{C0651B9D-9098-4FFD-82EE-1BACEC606B7F}"/>
+    <hyperlink ref="L34" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Portrait_of_Pope_Clemente_XII_%28Lorenzo_Corsini%29_by_Edme_Bouchardon%2C_French%2C_after_1730%2C_tinted_plaster_and_terracotta_-_California_Palace_of_the_Legion_of_Honor_-_DSC07739.JPG/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8B86DBCE-0A72-4760-A47C-0E8B681B3570}"/>
+    <hyperlink ref="L36" r:id="rId62" xr:uid="{8A084969-8958-49B4-853C-3AE75082A12B}"/>
+    <hyperlink ref="L38" r:id="rId63" xr:uid="{CF536289-4EEE-45F1-8084-B0371B565C41}"/>
+    <hyperlink ref="L37" r:id="rId64" xr:uid="{8A257BF5-79FF-4BF8-A978-DF4AA2821305}"/>
+    <hyperlink ref="I38" r:id="rId65" xr:uid="{B4207168-3FEC-425F-A795-F5784DF13615}"/>
+    <hyperlink ref="I37" r:id="rId66" xr:uid="{78A5F208-39F1-4E0D-8845-26F0E123BACC}"/>
+    <hyperlink ref="L39" r:id="rId67" xr:uid="{CCBD85D5-3F49-4572-824C-CA8F88DB5FDC}"/>
+    <hyperlink ref="L40" r:id="rId68" xr:uid="{7DBEBA58-DBE8-4168-8217-CD887A3BCE97}"/>
+    <hyperlink ref="G39" r:id="rId69" xr:uid="{26E871FC-575D-43D6-9F77-54326016822C}"/>
+    <hyperlink ref="I39" r:id="rId70" xr:uid="{99DED6AB-344A-4740-A203-89BBD0FE2617}"/>
+    <hyperlink ref="I41" r:id="rId71" xr:uid="{9FD53BA3-BFCA-4144-BDFF-649BBC5B3558}"/>
+    <hyperlink ref="L41" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9d/05_2023_Napoli_ITA_Duomo_%28Chiesa%29_-_Altare_maggiore%2C_scultura_l%27Assunta_di_Pietro_Bracci_1739_Tardo_Barocco_-_photo_Paolo_Villa_FO231710_correction_with_gimp.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F3102698-B78C-4C21-9039-4341BB078473}"/>
+    <hyperlink ref="L42" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/94/Pietro_bracci%2C_monumento_del_cardinale_carlo_leopoldo_calcagnini%2C_1746_ca._01.jpg/960px-Pietro_bracci%2C_monumento_del_cardinale_carlo_leopoldo_calcagnini%2C_1746_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4D7419BA-CC4A-4779-9436-FB1EA35A4AAD}"/>
+    <hyperlink ref="L43" r:id="rId74" xr:uid="{6433C034-4867-4ED5-87FB-FB4304FA60D4}"/>
+    <hyperlink ref="L45" r:id="rId75" xr:uid="{F2AF0062-C78E-46E8-B793-FB34A67B76CB}"/>
+    <hyperlink ref="L46" r:id="rId76" xr:uid="{3E3EC00B-8ACF-42AB-A745-A4201CABFE7E}"/>
+    <hyperlink ref="L44" r:id="rId77" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/57/Pierre_Corneille%2C_Jean-Jacques_Caffieri%2C_Paris_1723_1792.JPG/960px-Pierre_Corneille%2C_Jean-Jacques_Caffieri%2C_Paris_1723_1792.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E2469EC-8642-4E81-A446-2CC2FAE8B43E}"/>
+    <hyperlink ref="L47" r:id="rId78" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Hope_Nourishes_Love%2C_by_Jean-Jacques_Caffieri_%28Getty_103RR5%29.jpg/960px-Hope_Nourishes_Love%2C_by_Jean-Jacques_Caffieri_%28Getty_103RR5%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{8F832910-E656-4EFB-AC57-3D74592E6676}"/>
+    <hyperlink ref="L48" r:id="rId79" xr:uid="{07CA4426-387E-4AF5-ABAB-4128909EC254}"/>
+    <hyperlink ref="L56" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Antonio_Canova-Theseus_and_the_Minotaur-Victoria_and_Albert_Museum.jpg/960px-Antonio_Canova-Theseus_and_the_Minotaur-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2E9A1016-E90D-4659-8209-31B74E3F24C7}"/>
+    <hyperlink ref="L59" r:id="rId81" xr:uid="{6C84B94A-43B1-4D8A-9BF9-CDFE564415F5}"/>
+    <hyperlink ref="L57" r:id="rId82" xr:uid="{B3640A00-3EC5-4C99-82B5-B36103E6C177}"/>
+    <hyperlink ref="L58" r:id="rId83" xr:uid="{A1A250C1-22B8-444E-8FE4-18FD5FB58CF3}"/>
+    <hyperlink ref="L61" r:id="rId84" xr:uid="{5ECC010C-30BE-43F0-A7CA-0260E3CE130D}"/>
+    <hyperlink ref="L62" r:id="rId85" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Antonio_Corradini_-_Dama_Velata_%28Puritas%29_-_Museo_del_Settecento_Veneziano_-_Ca%27_Rezzonico%2C_Venice.jpg/1920px-Antonio_Corradini_-_Dama_Velata_%28Puritas%29_-_Museo_del_Settecento_Veneziano_-_Ca%27_Rezzonico%2C_Venice.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E067AB51-1DFF-4081-BF9C-2160687A1817}"/>
+    <hyperlink ref="L63" r:id="rId86" xr:uid="{40249E18-E873-4187-A04E-BC43AA5870BF}"/>
+    <hyperlink ref="L64" r:id="rId87" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/12/Die_Zeit_enthuellt_die_Wahrheit_Grosser_Garten_Dresden-2.jpg/960px-Die_Zeit_enthuellt_die_Wahrheit_Grosser_Garten_Dresden-2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A3A6C43D-6262-4AB8-8B6D-156B47AA3737}"/>
+    <hyperlink ref="L65" r:id="rId88" xr:uid="{302541C8-469A-4C1B-901B-23B0A5F49E25}"/>
+    <hyperlink ref="L66" r:id="rId89" xr:uid="{63E34BC2-58C7-4CFF-BD2E-20022C208234}"/>
+    <hyperlink ref="L67" r:id="rId90" xr:uid="{8CC71EB9-3199-49EF-A7A9-510A7755A425}"/>
+    <hyperlink ref="L68" r:id="rId91" xr:uid="{DAE8B983-E503-400A-BAF0-FACE83FED6E4}"/>
+    <hyperlink ref="L69" r:id="rId92" xr:uid="{FE11C8C7-7233-40B4-BA5F-1A8528A9B5B6}"/>
+    <hyperlink ref="L71" r:id="rId93" xr:uid="{C60C02F6-E3DE-459C-ABD4-F5D2850BFBFD}"/>
+    <hyperlink ref="L70" r:id="rId94" xr:uid="{C8B23DFB-0783-41B8-ABC2-49EF1E8F4E4C}"/>
+    <hyperlink ref="L72" r:id="rId95" xr:uid="{F6E29A87-A4DE-4D36-A3F6-1EF40D094D20}"/>
+    <hyperlink ref="L73" r:id="rId96" xr:uid="{9C249EE3-FBC9-42B3-ADF3-45DA8444C250}"/>
+    <hyperlink ref="L74" r:id="rId97" xr:uid="{736CB61F-DB8D-4D34-831C-03D972612AD4}"/>
+    <hyperlink ref="L77" r:id="rId98" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/2012--DSC_0253-C%C3%A9notaphe-du-grand-Dauphin-par-Coustou-dans-la-cathedrale-de-Sens.jpg/960px-2012--DSC_0253-C%C3%A9notaphe-du-grand-Dauphin-par-Coustou-dans-la-cathedrale-de-Sens.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8B3A1AC7-EC23-47AE-952E-EBEB844B3107}"/>
+    <hyperlink ref="L75" r:id="rId99" xr:uid="{BAE1A9D4-896A-4274-B7A4-D7851AAFF3E4}"/>
+    <hyperlink ref="L76" r:id="rId100" xr:uid="{0876674F-89FF-491E-A710-E8D816C42436}"/>
+    <hyperlink ref="L83" r:id="rId101" xr:uid="{93422A34-E47F-4EC0-B9B6-C9390AF2A5A4}"/>
+    <hyperlink ref="L84" r:id="rId102" xr:uid="{239D762E-78B0-4394-89DF-444F8993C868}"/>
+    <hyperlink ref="L85" r:id="rId103" xr:uid="{C601465F-6588-4CFC-A32C-1D37F5CFF0E1}"/>
+    <hyperlink ref="L86" r:id="rId104" xr:uid="{0B562E20-DF22-47B8-B6FB-AD1E07393A01}"/>
+    <hyperlink ref="L87" r:id="rId105" xr:uid="{BE4D15ED-CB7B-4449-A950-1A890376BCA4}"/>
+    <hyperlink ref="L90" r:id="rId106" xr:uid="{6AB13AFE-2406-4E93-ADA6-46FDCD31365A}"/>
+    <hyperlink ref="L88" r:id="rId107" xr:uid="{C83A0152-012B-483B-9231-2A1E78BBD9C0}"/>
+    <hyperlink ref="L89" r:id="rId108" xr:uid="{47B42195-9EC3-40B8-9B46-BD6E6B84E07C}"/>
+    <hyperlink ref="L91" r:id="rId109" xr:uid="{FC084A53-72A5-46D6-BA8B-9EDF408325E8}"/>
+    <hyperlink ref="L93" r:id="rId110" xr:uid="{A0209D99-D2A7-4D01-9D4A-1D01BE96F274}"/>
+    <hyperlink ref="L94" r:id="rId111" xr:uid="{87800057-0E6E-4997-AE5C-8E9E992038EC}"/>
+    <hyperlink ref="L92" r:id="rId112" xr:uid="{219B437E-3E02-401E-B8DD-54C18AE1422E}"/>
+    <hyperlink ref="L95" r:id="rId113" xr:uid="{E4D15D0F-4493-49C9-82EC-921ADE7F7649}"/>
+    <hyperlink ref="L96" r:id="rId114" xr:uid="{08D0AD74-167F-460E-9E0D-87B452D8FCDA}"/>
+    <hyperlink ref="L97" r:id="rId115" xr:uid="{79C25996-0268-4345-9482-E6D0D91FBCDB}"/>
+    <hyperlink ref="L98" r:id="rId116" xr:uid="{6A6598FD-AB7A-4377-A28E-D84A11EE770B}"/>
+    <hyperlink ref="G97" r:id="rId117" xr:uid="{4968AB49-790D-4B21-834D-BD88FF405AF0}"/>
+    <hyperlink ref="L99" r:id="rId118" xr:uid="{6F6F2D1A-8AC2-4E8F-AD62-5895107640F4}"/>
+    <hyperlink ref="L102" r:id="rId119" xr:uid="{1A778003-D53A-46C7-9C4F-0866ED4A1FBF}"/>
+    <hyperlink ref="L100" r:id="rId120" xr:uid="{CEBDE0C6-0B4A-4C8F-BAEC-6CA4771D91A9}"/>
+    <hyperlink ref="L101" r:id="rId121" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/07/Venus_of_the_Doves_by_Etienne-Maurice_Falconet%2C_undated_mid_1700s%2C_marble_-_National_Gallery_of_Art%2C_Washington_-_DSC09976.JPG/1280px-Venus_of_the_Doves_by_Etienne-Maurice_Falconet%2C_undated_mid_1700s%2C_marble_-_National_Gallery_of_Art%2C_Washington_-_DSC09976.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{207012E8-F898-42AB-A943-D36FADE8F355}"/>
+    <hyperlink ref="L103" r:id="rId122" xr:uid="{BBF98FE5-4DFE-4FDD-A544-E80BC7A25126}"/>
+    <hyperlink ref="L104" r:id="rId123" xr:uid="{FF151DBC-7144-4288-A673-8F481A2C101A}"/>
+    <hyperlink ref="L106" r:id="rId124" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Monument_to_Lord_Mansfield%2C_Westminster_Abbey_01.jpg/960px-Monument_to_Lord_Mansfield%2C_Westminster_Abbey_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{C11B2C6E-208E-4A71-B269-E34EAE7C6083}"/>
+    <hyperlink ref="L107" r:id="rId125" xr:uid="{6ED28258-66B6-4B49-B8D7-3C03B0C1DC7C}"/>
+    <hyperlink ref="L108" r:id="rId126" xr:uid="{88433733-48D0-4D92-93C2-565748FFE72C}"/>
+    <hyperlink ref="L105" r:id="rId127" xr:uid="{DC64D51C-9988-44E8-A744-459093BA68A0}"/>
+    <hyperlink ref="L109" r:id="rId128" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/10/John_Flaxman_%281755-1826%29_-_Cephalus_and_Aurora_%281789-90%29_front%2C_Lady_Lever_Art_Gallery%2C_Port_Sunlight%2C_Cheshire%2C_June_2013_%289103113142%29.png/500px-John_Flaxman_%281755-1826%29_-_Cephalus_and_Aurora_%281789-90%29_front%2C_Lady_Lever_Art_Gallery%2C_Port_Sunlight%2C_Cheshire%2C_June_2013_%289103113142%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B7B496B9-90D1-4969-9870-7B7656D9A169}"/>
+    <hyperlink ref="L110" r:id="rId129" xr:uid="{28CC63AD-0682-4A87-A9F4-B621624C9015}"/>
+    <hyperlink ref="L111" r:id="rId130" xr:uid="{16C08E16-E991-4783-8EF3-C3F1417EEEA6}"/>
+    <hyperlink ref="L112" r:id="rId131" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg/960px-St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FF930F9C-A9AC-4607-A859-3ABD807649A4}"/>
+    <hyperlink ref="L113" r:id="rId132" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/St._Paulus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg/960px-St._Paulus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A801BD6C-0A7D-46EC-AA6B-F1137861AA28}"/>
+    <hyperlink ref="I112" r:id="rId133" xr:uid="{D76F3B05-FA60-432A-A109-15C083FC3E09}"/>
+    <hyperlink ref="I113" r:id="rId134" xr:uid="{82CED098-B306-46C4-9441-0AD55B76FFC2}"/>
+    <hyperlink ref="L114" r:id="rId135" xr:uid="{3B0D8049-B520-4810-B239-50AA43905165}"/>
+    <hyperlink ref="L115" r:id="rId136" xr:uid="{B1606A58-EDCF-48FA-BB29-771BF06A9515}"/>
+    <hyperlink ref="L116" r:id="rId137" xr:uid="{8FD76DC7-7F79-4F5A-83E7-5E8D60AA822D}"/>
+    <hyperlink ref="L117" r:id="rId138" xr:uid="{FA268604-165F-41CF-83A0-B2CBF8A0F863}"/>
+    <hyperlink ref="L120" r:id="rId139" xr:uid="{E764FD93-AA66-476B-ADC0-DCB38775F84F}"/>
+    <hyperlink ref="L118" r:id="rId140" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/06/Houdon_Jean_Antoine%2C_L%27%C3%A9corch%C3%A9_bras_lev%C3%A9%2C_Mus%C3%A9e_Fabre%2C_Montpellier.jpg/960px-Houdon_Jean_Antoine%2C_L%27%C3%A9corch%C3%A9_bras_lev%C3%A9%2C_Mus%C3%A9e_Fabre%2C_Montpellier.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CE4949A3-9DCD-4051-B144-545B5D6AE5FB}"/>
+    <hyperlink ref="L121" r:id="rId141" xr:uid="{D7E3DDA7-E4FC-4310-898E-48047F7A5160}"/>
+    <hyperlink ref="L119" r:id="rId142" xr:uid="{8FB74D72-A77F-4B4B-AE35-582003521528}"/>
+    <hyperlink ref="L154" r:id="rId143" xr:uid="{881AB544-C00A-4F17-BA6D-032A002C02EE}"/>
+    <hyperlink ref="L155" r:id="rId144" xr:uid="{85549018-4524-417C-8A3F-737C6216056C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A3252E-9637-4FE5-8596-E78A34364B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EA0DC1-C0F2-444E-8F71-BCFBE0529FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4950" yWindow="0" windowWidth="16275" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2237" uniqueCount="888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2450" uniqueCount="952">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2697,6 +2697,198 @@
   </si>
   <si>
     <t>Statue</t>
+  </si>
+  <si>
+    <t>1756</t>
+  </si>
+  <si>
+    <t>Le Baiser de Judas (L'Arrestation)</t>
+  </si>
+  <si>
+    <t>El Prendimiento</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/48/El_prendimiento_20231222.jpg/1280px-El_prendimiento_20231222.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>La Flagellation</t>
+  </si>
+  <si>
+    <t>Los Azotes</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/26/Jes%C3%BAs_en_la_columna_20231222_195757_01.jpg/960px-Jes%C3%BAs_en_la_columna_20231222_195757_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>La Chute (Le Christ sur le chemin du Calvaire)</t>
+  </si>
+  <si>
+    <t>La Caída</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5b/La_ca%C3%ADda_20231222_05.jpg/1280px-La_ca%C3%ADda_20231222_05.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>1780-1785</t>
+  </si>
+  <si>
+    <t>Saint François d'Assise</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/91/Giuseppe_sanmartino%2C_san_francesco_in_estasi%2C_da_sant%27eframo_nuovo%2C_inv._427.JPG/960px-Giuseppe_sanmartino%2C_san_francesco_in_estasi%2C_da_sant%27eframo_nuovo%2C_inv._427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Basilique Santa Chiara</t>
+  </si>
+  <si>
+    <t>Monument funéraire de Philip de Bourbon</t>
+  </si>
+  <si>
+    <t>Monumento funebre a Filippo di Borbone</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Tomb_of_Philip_Bourbon_-_Cappella_dei_Borbone_-_Santa_Chiara_-_Naples.jpg/500px-Tomb_of_Philip_Bourbon_-_Cappella_dei_Borbone_-_Santa_Chiara_-_Naples.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Prinzessinnengruppe</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>Porte de Brandebourg</t>
+  </si>
+  <si>
+    <t>Quadrige de la Porte de Brandebourg</t>
+  </si>
+  <si>
+    <t>Quadriga</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/5/57/Brandenburg_gate_sunset_quadriga.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Ronde-bosse (groupe monumental)</t>
+  </si>
+  <si>
+    <t>Cuivre repoussé</t>
+  </si>
+  <si>
+    <t>Monument funéraire du comte Alexandre von der Mark</t>
+  </si>
+  <si>
+    <t>Grabmal des Grafen Alexander von der Mark</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/Johann_gottfried_schadow%2C_monumento_funebre_per_il_conte_alexander_von_der_mark%2C_1788-90%2C_01.jpg/960px-Johann_gottfried_schadow%2C_monumento_funebre_per_il_conte_alexander_von_der_mark%2C_1788-90%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1794</t>
+  </si>
+  <si>
+    <t>Rostock</t>
+  </si>
+  <si>
+    <t>Universitätsplatz</t>
+  </si>
+  <si>
+    <t>Monument à Blücher</t>
+  </si>
+  <si>
+    <t>Blücherdenkmal</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Rostock_Bluecherdenkmal_ohne_Sockel_2011-02-12.jpg/960px-Rostock_Bluecherdenkmal_ohne_Sockel_2011-02-12.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>1711-1717</t>
+  </si>
+  <si>
+    <t>Oratorio del Rosario di San Domenico</t>
+  </si>
+  <si>
+    <t>La Mansuétude</t>
+  </si>
+  <si>
+    <t>La Mansuetudine</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/7f/Mansuetudine_di_Giacomo_Serpotta%2C_Alcamo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>1722</t>
+  </si>
+  <si>
+    <t>Alcamo</t>
+  </si>
+  <si>
+    <t>Chiesa dei Santi Cosma e Damiano</t>
+  </si>
+  <si>
+    <t>La Justice</t>
+  </si>
+  <si>
+    <t>La Giustizia</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/La_Giustizia_di_Giacomo_Serpotta_%28Alcamo%29.jpg/960px-La_Giustizia_di_Giacomo_Serpotta_%28Alcamo%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>1711-1729</t>
+  </si>
+  <si>
+    <t>Chiesa di Sant'Agostino</t>
+  </si>
+  <si>
+    <t>Saint Augustin</t>
+  </si>
+  <si>
+    <t>Sant'Agostino</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/09/SA%26R_%28Palermo%29_15_07_2019_02.jpg/500px-SA%26R_%28Palermo%29_15_07_2019_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de</t>
+  </si>
+  <si>
+    <t>Sainte Monique</t>
+  </si>
+  <si>
+    <t>Santa Monica</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ee/SA%26R_%28Palermo%29_15_07_2019_01.jpg/500px-SA%26R_%28Palermo%29_15_07_2019_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>Iphigénie</t>
+  </si>
+  <si>
+    <t>Chryses</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8f/Michel-ange_slodtz%2C_chrys%C3%A9s_in_terracotta_1740_circa.JPG/960px-Michel-ange_slodtz%2C_chrys%C3%A9s_in_terracotta_1740_circa.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronde-bosse </t>
   </si>
 </sst>
 </file>
@@ -2798,7 +2990,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2810,7 +3002,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2820,12 +3011,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3138,75 +3329,72 @@
   <dimension ref="A1:Y205"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="18" style="5" customWidth="1"/>
-    <col min="4" max="11" width="9.140625" style="5"/>
-    <col min="12" max="12" width="9.140625" style="8" customWidth="1"/>
-    <col min="13" max="17" width="9.140625" style="5"/>
-    <col min="18" max="18" width="28.85546875" style="5" customWidth="1"/>
-    <col min="19" max="19" width="9.140625" style="5"/>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="7" customWidth="1"/>
+    <col min="18" max="18" width="28.85546875" customWidth="1"/>
     <col min="20" max="23" width="9.140625" style="1"/>
     <col min="24" max="24" width="15.140625" style="1" customWidth="1"/>
     <col min="25" max="25" width="14.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
@@ -3229,61 +3417,61 @@
       </c>
     </row>
     <row r="2" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="S2" s="5" t="s">
         <v>18</v>
       </c>
       <c r="T2" s="2" t="s">
@@ -3306,34 +3494,34 @@
       </c>
     </row>
     <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" t="s">
         <v>372</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" t="s">
         <v>30</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" s="5" t="s">
+      <c r="R3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S3" t="s">
         <v>25</v>
       </c>
       <c r="T3" s="1" t="s">
@@ -3356,34 +3544,34 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" t="s">
         <v>372</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" t="s">
         <v>377</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" t="s">
         <v>34</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="R4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S4" s="5" t="s">
+      <c r="R4" t="s">
+        <v>24</v>
+      </c>
+      <c r="S4" t="s">
         <v>36</v>
       </c>
       <c r="T4" s="1" t="s">
@@ -3406,34 +3594,34 @@
       </c>
     </row>
     <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" t="s">
         <v>372</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5">
         <v>1749</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" t="s">
         <v>381</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" t="s">
         <v>382</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" t="s">
         <v>384</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="R5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S5" s="5" t="s">
+      <c r="R5" t="s">
+        <v>24</v>
+      </c>
+      <c r="S5" t="s">
         <v>25</v>
       </c>
       <c r="T5" s="1">
@@ -3456,34 +3644,34 @@
       </c>
     </row>
     <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" t="s">
         <v>372</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" t="s">
         <v>387</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" t="s">
         <v>381</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" t="s">
         <v>382</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" t="s">
         <v>388</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="R6" s="5" t="s">
+      <c r="R6" t="s">
         <v>393</v>
       </c>
-      <c r="S6" s="5" t="s">
+      <c r="S6" t="s">
         <v>25</v>
       </c>
       <c r="T6" s="1" t="s">
@@ -3506,34 +3694,34 @@
       </c>
     </row>
     <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" t="s">
         <v>372</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7">
         <v>1752</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" t="s">
         <v>29</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" t="s">
         <v>391</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="R7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S7" s="5" t="s">
+      <c r="R7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S7" t="s">
         <v>25</v>
       </c>
       <c r="T7" s="1">
@@ -3556,34 +3744,34 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" t="s">
         <v>372</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8">
         <v>1749</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" t="s">
         <v>399</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" t="s">
         <v>412</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" t="s">
         <v>413</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="R8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S8" s="5" t="s">
+      <c r="R8" t="s">
+        <v>24</v>
+      </c>
+      <c r="S8" t="s">
         <v>101</v>
       </c>
       <c r="T8" s="1">
@@ -3606,31 +3794,31 @@
       </c>
     </row>
     <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9">
         <v>1762</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S9" s="5" t="s">
+      <c r="R9" t="s">
+        <v>24</v>
+      </c>
+      <c r="S9" t="s">
         <v>25</v>
       </c>
       <c r="T9" s="1">
@@ -3653,31 +3841,31 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10">
         <v>1737</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" t="s">
         <v>394</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" t="s">
         <v>395</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" t="s">
         <v>396</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="R10" s="5" t="s">
+      <c r="R10" t="s">
         <v>398</v>
       </c>
-      <c r="S10" s="5" t="s">
+      <c r="S10" t="s">
         <v>58</v>
       </c>
       <c r="T10" s="1">
@@ -3697,31 +3885,31 @@
       </c>
     </row>
     <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11">
         <v>1749</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" t="s">
         <v>399</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" t="s">
         <v>400</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" t="s">
         <v>401</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="R11" s="5" t="s">
+      <c r="R11" t="s">
         <v>403</v>
       </c>
-      <c r="S11" s="5" t="s">
+      <c r="S11" t="s">
         <v>25</v>
       </c>
       <c r="T11" s="1">
@@ -3744,31 +3932,31 @@
       </c>
     </row>
     <row r="12" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12">
         <v>1753</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" t="s">
         <v>404</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" t="s">
         <v>405</v>
       </c>
       <c r="L12" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="R12" s="5" t="s">
+      <c r="R12" t="s">
         <v>407</v>
       </c>
-      <c r="S12" s="5" t="s">
+      <c r="S12" t="s">
         <v>212</v>
       </c>
       <c r="T12" s="1">
@@ -3791,31 +3979,31 @@
       </c>
     </row>
     <row r="13" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13">
         <v>1753</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" t="s">
         <v>404</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" t="s">
         <v>408</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="R13" s="5" t="s">
+      <c r="R13" t="s">
         <v>407</v>
       </c>
-      <c r="S13" s="5" t="s">
+      <c r="S13" t="s">
         <v>212</v>
       </c>
       <c r="T13" s="1">
@@ -3838,31 +4026,31 @@
       </c>
     </row>
     <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14">
         <v>1753</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" t="s">
         <v>404</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" t="s">
         <v>410</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="R14" s="5" t="s">
+      <c r="R14" t="s">
         <v>407</v>
       </c>
-      <c r="S14" s="5" t="s">
+      <c r="S14" t="s">
         <v>212</v>
       </c>
       <c r="T14" s="1">
@@ -3885,31 +4073,31 @@
       </c>
     </row>
     <row r="15" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" t="s">
         <v>29</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" t="s">
         <v>415</v>
       </c>
-      <c r="L15" s="10" t="s">
+      <c r="L15" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="R15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S15" s="5" t="s">
+      <c r="R15" t="s">
+        <v>24</v>
+      </c>
+      <c r="S15" t="s">
         <v>25</v>
       </c>
       <c r="T15" s="1" t="s">
@@ -3932,31 +4120,31 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" t="s">
         <v>419</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" t="s">
         <v>29</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" t="s">
         <v>420</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="R16" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S16" s="5" t="s">
+      <c r="R16" t="s">
+        <v>24</v>
+      </c>
+      <c r="S16" t="s">
         <v>25</v>
       </c>
       <c r="T16" s="1">
@@ -3979,46 +4167,46 @@
       </c>
     </row>
     <row r="17" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L17" s="11"/>
+      <c r="L17" s="10"/>
     </row>
     <row r="18" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L18" s="11"/>
+      <c r="L18" s="10"/>
     </row>
     <row r="19" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L19" s="11"/>
+      <c r="L19" s="10"/>
     </row>
     <row r="20" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L20" s="11"/>
+      <c r="L20" s="10"/>
     </row>
     <row r="21" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="A21" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" t="s">
         <v>422</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" t="s">
         <v>48</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" t="s">
         <v>49</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" t="s">
         <v>50</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K21" t="s">
         <v>51</v>
       </c>
       <c r="L21" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="R21" s="5" t="s">
+      <c r="R21" t="s">
         <v>53</v>
       </c>
-      <c r="S21" s="5" t="s">
+      <c r="S21" t="s">
         <v>25</v>
       </c>
       <c r="T21" s="1" t="s">
@@ -4041,34 +4229,34 @@
       </c>
     </row>
     <row r="22" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="A22" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" t="s">
         <v>425</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" t="s">
         <v>54</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" t="s">
         <v>55</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="K22" t="s">
         <v>56</v>
       </c>
       <c r="L22" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R22" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S22" s="5" t="s">
+      <c r="R22" t="s">
+        <v>24</v>
+      </c>
+      <c r="S22" t="s">
         <v>58</v>
       </c>
       <c r="T22" s="1" t="s">
@@ -4091,34 +4279,34 @@
       </c>
     </row>
     <row r="23" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="A23" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" t="s">
         <v>428</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" t="s">
         <v>59</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="J23" t="s">
         <v>60</v>
       </c>
-      <c r="K23" s="5" t="s">
+      <c r="K23" t="s">
         <v>61</v>
       </c>
       <c r="L23" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="R23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S23" s="5" t="s">
+      <c r="R23" t="s">
+        <v>24</v>
+      </c>
+      <c r="S23" t="s">
         <v>25</v>
       </c>
       <c r="T23" s="1" t="s">
@@ -4141,34 +4329,34 @@
       </c>
     </row>
     <row r="24" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="A24" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" t="s">
         <v>430</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" t="s">
         <v>48</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" t="s">
         <v>431</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="J24" t="s">
         <v>432</v>
       </c>
-      <c r="K24" s="5" t="s">
+      <c r="K24" t="s">
         <v>433</v>
       </c>
       <c r="L24" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="R24" s="5" t="s">
+      <c r="R24" t="s">
         <v>435</v>
       </c>
-      <c r="S24" s="5" t="s">
+      <c r="S24" t="s">
         <v>25</v>
       </c>
       <c r="T24" s="1">
@@ -4191,34 +4379,34 @@
       </c>
     </row>
     <row r="25" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+      <c r="A25" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25">
         <v>1790</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" t="s">
         <v>65</v>
       </c>
-      <c r="J25" s="5" t="s">
+      <c r="J25" t="s">
         <v>66</v>
       </c>
-      <c r="K25" s="5" t="s">
+      <c r="K25" t="s">
         <v>67</v>
       </c>
       <c r="L25" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="R25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S25" s="5" t="s">
+      <c r="R25" t="s">
+        <v>24</v>
+      </c>
+      <c r="S25" t="s">
         <v>25</v>
       </c>
       <c r="T25" s="1">
@@ -4241,34 +4429,34 @@
       </c>
     </row>
     <row r="26" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="A26" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26">
         <v>1789</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" t="s">
         <v>49</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="J26" t="s">
         <v>436</v>
       </c>
-      <c r="K26" s="5" t="s">
+      <c r="K26" t="s">
         <v>437</v>
       </c>
       <c r="L26" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="R26" s="5" t="s">
+      <c r="R26" t="s">
         <v>439</v>
       </c>
-      <c r="S26" s="5" t="s">
+      <c r="S26" t="s">
         <v>25</v>
       </c>
       <c r="T26" s="1">
@@ -4291,37 +4479,37 @@
       </c>
     </row>
     <row r="27" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="A27" t="s">
         <v>63</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" t="s">
         <v>64</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27">
         <v>1789</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" t="s">
         <v>440</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" t="s">
         <v>441</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" t="s">
         <v>383</v>
       </c>
-      <c r="J27" s="5" t="s">
+      <c r="J27" t="s">
         <v>442</v>
       </c>
-      <c r="K27" s="5" t="s">
+      <c r="K27" t="s">
         <v>443</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="R27" s="5" t="s">
+      <c r="R27" t="s">
         <v>445</v>
       </c>
-      <c r="S27" s="5" t="s">
+      <c r="S27" t="s">
         <v>446</v>
       </c>
       <c r="T27" s="1">
@@ -4344,34 +4532,34 @@
       </c>
     </row>
     <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+      <c r="A28" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28">
         <v>1794</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" t="s">
         <v>48</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" t="s">
         <v>266</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="J28" t="s">
         <v>447</v>
       </c>
-      <c r="K28" s="5" t="s">
+      <c r="K28" t="s">
         <v>448</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="R28" s="5" t="s">
+      <c r="R28" t="s">
         <v>450</v>
       </c>
-      <c r="S28" s="5" t="s">
+      <c r="S28" t="s">
         <v>25</v>
       </c>
       <c r="T28" s="1">
@@ -4397,37 +4585,37 @@
       <c r="L29" s="4"/>
     </row>
     <row r="30" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L30" s="11"/>
+      <c r="L30" s="10"/>
     </row>
     <row r="31" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="A31" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" t="s">
         <v>70</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" t="s">
         <v>71</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" t="s">
         <v>28</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" t="s">
         <v>72</v>
       </c>
-      <c r="J31" s="5" t="s">
+      <c r="J31" t="s">
         <v>73</v>
       </c>
-      <c r="K31" s="5" t="s">
+      <c r="K31" t="s">
         <v>74</v>
       </c>
-      <c r="L31" s="9" t="s">
+      <c r="L31" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="R31" s="5" t="s">
+      <c r="R31" t="s">
         <v>76</v>
       </c>
-      <c r="S31" s="5" t="s">
+      <c r="S31" t="s">
         <v>77</v>
       </c>
       <c r="T31" s="1">
@@ -4450,34 +4638,34 @@
       </c>
     </row>
     <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+      <c r="A32" t="s">
         <v>69</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" t="s">
         <v>451</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" t="s">
         <v>28</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" t="s">
         <v>29</v>
       </c>
-      <c r="J32" s="5" t="s">
+      <c r="J32" t="s">
         <v>78</v>
       </c>
-      <c r="K32" s="5" t="s">
+      <c r="K32" t="s">
         <v>79</v>
       </c>
-      <c r="L32" s="9" t="s">
+      <c r="L32" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="R32" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S32" s="5" t="s">
+      <c r="R32" t="s">
+        <v>24</v>
+      </c>
+      <c r="S32" t="s">
         <v>25</v>
       </c>
       <c r="T32" s="1">
@@ -4500,34 +4688,34 @@
       </c>
     </row>
     <row r="33" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+      <c r="A33" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" t="s">
         <v>387</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" t="s">
         <v>28</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" t="s">
         <v>29</v>
       </c>
-      <c r="J33" s="5" t="s">
+      <c r="J33" t="s">
         <v>81</v>
       </c>
-      <c r="K33" s="5" t="s">
+      <c r="K33" t="s">
         <v>82</v>
       </c>
-      <c r="L33" s="9" t="s">
+      <c r="L33" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="R33" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S33" s="5" t="s">
+      <c r="R33" t="s">
+        <v>24</v>
+      </c>
+      <c r="S33" t="s">
         <v>25</v>
       </c>
       <c r="T33" s="1">
@@ -4550,37 +4738,37 @@
       </c>
     </row>
     <row r="34" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="A34" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" t="s">
         <v>452</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" t="s">
         <v>86</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" t="s">
         <v>173</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H34" t="s">
         <v>174</v>
       </c>
-      <c r="J34" s="5" t="s">
+      <c r="J34" t="s">
         <v>453</v>
       </c>
-      <c r="K34" s="5" t="s">
+      <c r="K34" t="s">
         <v>454</v>
       </c>
       <c r="L34" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="R34" s="5" t="s">
+      <c r="R34" t="s">
         <v>450</v>
       </c>
-      <c r="S34" s="5" t="s">
+      <c r="S34" t="s">
         <v>25</v>
       </c>
       <c r="T34" s="1">
@@ -4603,34 +4791,34 @@
       </c>
     </row>
     <row r="35" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+      <c r="A35" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" t="s">
         <v>70</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35">
         <v>1745</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" t="s">
         <v>28</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="F35" t="s">
         <v>29</v>
       </c>
-      <c r="J35" s="5" t="s">
+      <c r="J35" t="s">
         <v>456</v>
       </c>
-      <c r="K35" s="5" t="s">
+      <c r="K35" t="s">
         <v>457</v>
       </c>
       <c r="L35" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="R35" s="5" t="s">
+      <c r="R35" t="s">
         <v>459</v>
       </c>
-      <c r="S35" s="5" t="s">
+      <c r="S35" t="s">
         <v>25</v>
       </c>
       <c r="T35" s="1">
@@ -4653,34 +4841,34 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
+      <c r="A36" t="s">
         <v>69</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" t="s">
         <v>70</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" t="s">
         <v>460</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" t="s">
         <v>342</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" t="s">
         <v>461</v>
       </c>
-      <c r="J36" s="5" t="s">
+      <c r="J36" t="s">
         <v>462</v>
       </c>
-      <c r="K36" s="5" t="s">
+      <c r="K36" t="s">
         <v>462</v>
       </c>
       <c r="L36" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="R36" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S36" s="5" t="s">
+      <c r="R36" t="s">
+        <v>24</v>
+      </c>
+      <c r="S36" t="s">
         <v>101</v>
       </c>
       <c r="T36" s="1">
@@ -4703,40 +4891,40 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
+      <c r="A37" t="s">
         <v>69</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" t="s">
         <v>70</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" t="s">
         <v>71</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" t="s">
         <v>28</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" t="s">
         <v>72</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H37" t="s">
         <v>73</v>
       </c>
-      <c r="I37" s="9" t="s">
+      <c r="I37" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="J37" s="5" t="s">
+      <c r="J37" t="s">
         <v>464</v>
       </c>
-      <c r="K37" s="5" t="s">
+      <c r="K37" t="s">
         <v>465</v>
       </c>
       <c r="L37" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="R37" s="5" t="s">
+      <c r="R37" t="s">
         <v>467</v>
       </c>
-      <c r="S37" s="5" t="s">
+      <c r="S37" t="s">
         <v>77</v>
       </c>
       <c r="T37" s="1">
@@ -4759,40 +4947,40 @@
       </c>
     </row>
     <row r="38" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
+      <c r="A38" t="s">
         <v>69</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" t="s">
         <v>70</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" t="s">
         <v>71</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" t="s">
         <v>28</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" t="s">
         <v>72</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H38" t="s">
         <v>73</v>
       </c>
-      <c r="I38" s="9" t="s">
+      <c r="I38" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="J38" s="5" t="s">
+      <c r="J38" t="s">
         <v>464</v>
       </c>
-      <c r="K38" s="5" t="s">
+      <c r="K38" t="s">
         <v>468</v>
       </c>
       <c r="L38" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="R38" s="5" t="s">
+      <c r="R38" t="s">
         <v>467</v>
       </c>
-      <c r="S38" s="5" t="s">
+      <c r="S38" t="s">
         <v>77</v>
       </c>
       <c r="T38" s="1">
@@ -4815,43 +5003,43 @@
       </c>
     </row>
     <row r="39" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+      <c r="A39" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" t="s">
         <v>38</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" t="s">
         <v>86</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" t="s">
         <v>87</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H39" t="s">
         <v>88</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="J39" s="5" t="s">
+      <c r="J39" t="s">
         <v>89</v>
       </c>
-      <c r="K39" s="5" t="s">
+      <c r="K39" t="s">
         <v>90</v>
       </c>
       <c r="L39" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="R39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S39" s="5" t="s">
+      <c r="R39" t="s">
+        <v>24</v>
+      </c>
+      <c r="S39" t="s">
         <v>25</v>
       </c>
       <c r="T39" s="1" t="s">
@@ -4874,37 +5062,37 @@
       </c>
     </row>
     <row r="40" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" t="s">
         <v>84</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" t="s">
         <v>474</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" t="s">
         <v>86</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" t="s">
         <v>105</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="H40" t="s">
         <v>475</v>
       </c>
-      <c r="J40" s="5" t="s">
+      <c r="J40" t="s">
         <v>476</v>
       </c>
-      <c r="K40" s="5" t="s">
+      <c r="K40" t="s">
         <v>477</v>
       </c>
       <c r="L40" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="R40" s="5" t="s">
+      <c r="R40" t="s">
         <v>479</v>
       </c>
-      <c r="S40" s="5" t="s">
+      <c r="S40" t="s">
         <v>480</v>
       </c>
       <c r="T40" s="1" t="s">
@@ -4927,40 +5115,40 @@
       </c>
     </row>
     <row r="41" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+      <c r="A41" t="s">
         <v>84</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" t="s">
         <v>85</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" t="s">
         <v>474</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" t="s">
         <v>135</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" t="s">
         <v>483</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="H41" t="s">
         <v>484</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="J41" s="5" t="s">
+      <c r="J41" t="s">
         <v>486</v>
       </c>
-      <c r="K41" s="5" t="s">
+      <c r="K41" t="s">
         <v>487</v>
       </c>
       <c r="L41" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="R41" s="5" t="s">
+      <c r="R41" t="s">
         <v>407</v>
       </c>
-      <c r="S41" s="5" t="s">
+      <c r="S41" t="s">
         <v>289</v>
       </c>
       <c r="T41" s="1">
@@ -4983,34 +5171,34 @@
       </c>
     </row>
     <row r="42" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+      <c r="A42" t="s">
         <v>84</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" t="s">
         <v>85</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" t="s">
         <v>489</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" t="s">
         <v>86</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" t="s">
         <v>490</v>
       </c>
-      <c r="J42" s="5" t="s">
+      <c r="J42" t="s">
         <v>491</v>
       </c>
-      <c r="K42" s="5" t="s">
+      <c r="K42" t="s">
         <v>492</v>
       </c>
       <c r="L42" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="R42" s="5" t="s">
+      <c r="R42" t="s">
         <v>53</v>
       </c>
-      <c r="S42" s="5" t="s">
+      <c r="S42" t="s">
         <v>25</v>
       </c>
       <c r="T42" s="1" t="s">
@@ -5033,31 +5221,31 @@
       </c>
     </row>
     <row r="43" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
+      <c r="A43" t="s">
         <v>94</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" t="s">
         <v>95</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" t="s">
         <v>96</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" t="s">
         <v>97</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" t="s">
         <v>98</v>
       </c>
-      <c r="J43" s="5" t="s">
+      <c r="J43" t="s">
         <v>99</v>
       </c>
       <c r="L43" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="R43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S43" s="5" t="s">
+      <c r="R43" t="s">
+        <v>24</v>
+      </c>
+      <c r="S43" t="s">
         <v>101</v>
       </c>
       <c r="T43" s="1" t="s">
@@ -5080,31 +5268,31 @@
       </c>
     </row>
     <row r="44" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
+      <c r="A44" t="s">
         <v>94</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" t="s">
         <v>95</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" t="s">
         <v>498</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" t="s">
         <v>499</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="F44" t="s">
         <v>98</v>
       </c>
-      <c r="J44" s="5" t="s">
+      <c r="J44" t="s">
         <v>500</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="R44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S44" s="5" t="s">
+      <c r="R44" t="s">
+        <v>24</v>
+      </c>
+      <c r="S44" t="s">
         <v>101</v>
       </c>
       <c r="T44" s="1">
@@ -5127,31 +5315,31 @@
       </c>
     </row>
     <row r="45" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
+      <c r="A45" t="s">
         <v>94</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" t="s">
         <v>95</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45">
         <v>1762</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" t="s">
         <v>97</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="F45" t="s">
         <v>98</v>
       </c>
-      <c r="J45" s="5" t="s">
+      <c r="J45" t="s">
         <v>502</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="R45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S45" s="5" t="s">
+      <c r="R45" t="s">
+        <v>24</v>
+      </c>
+      <c r="S45" t="s">
         <v>101</v>
       </c>
       <c r="T45" s="1">
@@ -5174,31 +5362,31 @@
       </c>
     </row>
     <row r="46" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
+      <c r="A46" t="s">
         <v>94</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" t="s">
         <v>95</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46">
         <v>1781</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" t="s">
         <v>28</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="F46" t="s">
         <v>29</v>
       </c>
-      <c r="J46" s="5" t="s">
+      <c r="J46" t="s">
         <v>504</v>
       </c>
       <c r="L46" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="R46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S46" s="5" t="s">
+      <c r="R46" t="s">
+        <v>24</v>
+      </c>
+      <c r="S46" t="s">
         <v>25</v>
       </c>
       <c r="T46" s="1">
@@ -5221,31 +5409,31 @@
       </c>
     </row>
     <row r="47" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+      <c r="A47" t="s">
         <v>94</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" t="s">
         <v>95</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47">
         <v>1769</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E47" t="s">
         <v>506</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="F47" t="s">
         <v>507</v>
       </c>
-      <c r="J47" s="5" t="s">
+      <c r="J47" t="s">
         <v>508</v>
       </c>
       <c r="L47" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="R47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S47" s="5" t="s">
+      <c r="R47" t="s">
+        <v>24</v>
+      </c>
+      <c r="S47" t="s">
         <v>25</v>
       </c>
       <c r="T47" s="1">
@@ -5268,31 +5456,31 @@
       </c>
     </row>
     <row r="48" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
+      <c r="A48" t="s">
         <v>94</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" t="s">
         <v>95</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48">
         <v>1785</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E48" t="s">
         <v>510</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F48" t="s">
         <v>511</v>
       </c>
-      <c r="J48" s="5" t="s">
+      <c r="J48" t="s">
         <v>512</v>
       </c>
       <c r="L48" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="R48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S48" s="5" t="s">
+      <c r="R48" t="s">
+        <v>24</v>
+      </c>
+      <c r="S48" t="s">
         <v>101</v>
       </c>
       <c r="T48" s="1">
@@ -5315,34 +5503,34 @@
       </c>
     </row>
     <row r="49" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
+      <c r="A49" t="s">
         <v>102</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" t="s">
         <v>103</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" t="s">
         <v>104</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E49" t="s">
         <v>86</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="F49" t="s">
         <v>105</v>
       </c>
-      <c r="J49" s="5" t="s">
+      <c r="J49" t="s">
         <v>106</v>
       </c>
-      <c r="K49" s="5" t="s">
+      <c r="K49" t="s">
         <v>107</v>
       </c>
-      <c r="L49" s="11" t="s">
+      <c r="L49" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="R49" s="5" t="s">
+      <c r="R49" t="s">
         <v>53</v>
       </c>
-      <c r="S49" s="5" t="s">
+      <c r="S49" t="s">
         <v>25</v>
       </c>
       <c r="T49" s="1">
@@ -5365,34 +5553,34 @@
       </c>
     </row>
     <row r="50" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
+      <c r="A50" t="s">
         <v>102</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" t="s">
         <v>103</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" t="s">
         <v>109</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E50" t="s">
         <v>28</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="F50" t="s">
         <v>29</v>
       </c>
-      <c r="J50" s="5" t="s">
+      <c r="J50" t="s">
         <v>110</v>
       </c>
-      <c r="K50" s="5" t="s">
+      <c r="K50" t="s">
         <v>111</v>
       </c>
-      <c r="L50" s="11" t="s">
+      <c r="L50" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="R50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S50" s="5" t="s">
+      <c r="R50" t="s">
+        <v>24</v>
+      </c>
+      <c r="S50" t="s">
         <v>25</v>
       </c>
       <c r="T50" s="1">
@@ -5415,34 +5603,34 @@
       </c>
     </row>
     <row r="51" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
+      <c r="A51" t="s">
         <v>102</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" t="s">
         <v>103</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51">
         <v>1790</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="E51" t="s">
         <v>86</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="F51" t="s">
         <v>113</v>
       </c>
-      <c r="J51" s="5" t="s">
+      <c r="J51" t="s">
         <v>114</v>
       </c>
-      <c r="K51" s="5" t="s">
+      <c r="K51" t="s">
         <v>115</v>
       </c>
-      <c r="L51" s="11" t="s">
+      <c r="L51" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="R51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S51" s="5" t="s">
+      <c r="R51" t="s">
+        <v>24</v>
+      </c>
+      <c r="S51" t="s">
         <v>25</v>
       </c>
       <c r="T51" s="1">
@@ -5465,34 +5653,34 @@
       </c>
     </row>
     <row r="52" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
+      <c r="A52" t="s">
         <v>102</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" t="s">
         <v>103</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D52" t="s">
         <v>117</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="E52" t="s">
         <v>118</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="F52" t="s">
         <v>119</v>
       </c>
-      <c r="J52" s="5" t="s">
+      <c r="J52" t="s">
         <v>120</v>
       </c>
-      <c r="K52" s="5" t="s">
+      <c r="K52" t="s">
         <v>121</v>
       </c>
-      <c r="L52" s="11" t="s">
+      <c r="L52" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="R52" s="5" t="s">
+      <c r="R52" t="s">
         <v>53</v>
       </c>
-      <c r="S52" s="5" t="s">
+      <c r="S52" t="s">
         <v>25</v>
       </c>
       <c r="T52" s="1">
@@ -5515,37 +5703,37 @@
       </c>
     </row>
     <row r="53" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+      <c r="A53" t="s">
         <v>102</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" t="s">
         <v>103</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D53" t="s">
         <v>123</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" t="s">
         <v>48</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="F53" t="s">
         <v>124</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="H53" t="s">
         <v>125</v>
       </c>
-      <c r="J53" s="5" t="s">
+      <c r="J53" t="s">
         <v>126</v>
       </c>
-      <c r="K53" s="5" t="s">
+      <c r="K53" t="s">
         <v>127</v>
       </c>
-      <c r="L53" s="11" t="s">
+      <c r="L53" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="R53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S53" s="5" t="s">
+      <c r="R53" t="s">
+        <v>24</v>
+      </c>
+      <c r="S53" t="s">
         <v>25</v>
       </c>
       <c r="T53" s="1">
@@ -5568,34 +5756,34 @@
       </c>
     </row>
     <row r="54" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
+      <c r="A54" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" t="s">
         <v>103</v>
       </c>
-      <c r="D54" s="5">
+      <c r="D54">
         <v>1796</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" t="s">
         <v>129</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="F54" t="s">
         <v>130</v>
       </c>
-      <c r="J54" s="5" t="s">
+      <c r="J54" t="s">
         <v>131</v>
       </c>
-      <c r="K54" s="5" t="s">
+      <c r="K54" t="s">
         <v>132</v>
       </c>
-      <c r="L54" s="11" t="s">
+      <c r="L54" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="R54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S54" s="5" t="s">
+      <c r="R54" t="s">
+        <v>24</v>
+      </c>
+      <c r="S54" t="s">
         <v>25</v>
       </c>
       <c r="T54" s="1">
@@ -5618,34 +5806,34 @@
       </c>
     </row>
     <row r="55" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
+      <c r="A55" t="s">
         <v>102</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" t="s">
         <v>103</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="D55" t="s">
         <v>134</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E55" t="s">
         <v>135</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="F55" t="s">
         <v>136</v>
       </c>
-      <c r="J55" s="5" t="s">
+      <c r="J55" t="s">
         <v>137</v>
       </c>
-      <c r="K55" s="5" t="s">
+      <c r="K55" t="s">
         <v>138</v>
       </c>
-      <c r="L55" s="11" t="s">
+      <c r="L55" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="R55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S55" s="5" t="s">
+      <c r="R55" t="s">
+        <v>24</v>
+      </c>
+      <c r="S55" t="s">
         <v>25</v>
       </c>
       <c r="T55" s="1">
@@ -5668,34 +5856,34 @@
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
+      <c r="A56" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" t="s">
         <v>103</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" t="s">
         <v>514</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="E56" t="s">
         <v>48</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" t="s">
         <v>65</v>
       </c>
-      <c r="J56" s="5" t="s">
+      <c r="J56" t="s">
         <v>515</v>
       </c>
-      <c r="K56" s="5" t="s">
+      <c r="K56" t="s">
         <v>516</v>
       </c>
       <c r="L56" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="R56" s="5" t="s">
+      <c r="R56" t="s">
         <v>518</v>
       </c>
-      <c r="S56" s="5" t="s">
+      <c r="S56" t="s">
         <v>25</v>
       </c>
       <c r="T56" s="1">
@@ -5718,31 +5906,31 @@
       </c>
     </row>
     <row r="57" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
+      <c r="A57" t="s">
         <v>140</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" t="s">
         <v>141</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D57" t="s">
         <v>142</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="E57" t="s">
         <v>143</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="F57" t="s">
         <v>569</v>
       </c>
-      <c r="J57" s="5" t="s">
+      <c r="J57" t="s">
         <v>144</v>
       </c>
       <c r="L57" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="R57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S57" s="5" t="s">
+      <c r="R57" t="s">
+        <v>24</v>
+      </c>
+      <c r="S57" t="s">
         <v>146</v>
       </c>
       <c r="T57" s="1" t="s">
@@ -5765,34 +5953,34 @@
       </c>
     </row>
     <row r="58" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
+      <c r="A58" t="s">
         <v>140</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" t="s">
         <v>141</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D58" t="s">
         <v>522</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" t="s">
         <v>143</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="F58" t="s">
         <v>569</v>
       </c>
-      <c r="J58" s="5" t="s">
+      <c r="J58" t="s">
         <v>523</v>
       </c>
-      <c r="K58" s="5" t="s">
+      <c r="K58" t="s">
         <v>524</v>
       </c>
       <c r="L58" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="R58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S58" s="5" t="s">
+      <c r="R58" t="s">
+        <v>24</v>
+      </c>
+      <c r="S58" t="s">
         <v>146</v>
       </c>
       <c r="W58" s="1" t="s">
@@ -5806,37 +5994,37 @@
       </c>
     </row>
     <row r="59" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
+      <c r="A59" t="s">
         <v>140</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" t="s">
         <v>141</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D59" t="s">
         <v>96</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="E59" t="s">
         <v>526</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="F59" t="s">
         <v>527</v>
       </c>
-      <c r="H59" s="5" t="s">
+      <c r="H59" t="s">
         <v>528</v>
       </c>
-      <c r="J59" s="5" t="s">
+      <c r="J59" t="s">
         <v>529</v>
       </c>
-      <c r="K59" s="5" t="s">
+      <c r="K59" t="s">
         <v>530</v>
       </c>
       <c r="L59" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="R59" s="5" t="s">
+      <c r="R59" t="s">
         <v>532</v>
       </c>
-      <c r="S59" s="5" t="s">
+      <c r="S59" t="s">
         <v>146</v>
       </c>
       <c r="W59" s="1" t="s">
@@ -5850,37 +6038,37 @@
       </c>
     </row>
     <row r="60" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L60" s="11"/>
+      <c r="L60" s="10"/>
     </row>
     <row r="61" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
+      <c r="A61" t="s">
         <v>102</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" t="s">
         <v>149</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="D61" t="s">
         <v>150</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="E61" t="s">
         <v>135</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="F61" t="s">
         <v>151</v>
       </c>
-      <c r="J61" s="5" t="s">
+      <c r="J61" t="s">
         <v>152</v>
       </c>
-      <c r="K61" s="5" t="s">
+      <c r="K61" t="s">
         <v>533</v>
       </c>
       <c r="L61" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="R61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S61" s="5" t="s">
+      <c r="R61" t="s">
+        <v>24</v>
+      </c>
+      <c r="S61" t="s">
         <v>25</v>
       </c>
       <c r="T61" s="1">
@@ -5900,34 +6088,34 @@
       </c>
     </row>
     <row r="62" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
+      <c r="A62" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" t="s">
         <v>149</v>
       </c>
-      <c r="D62" s="5">
+      <c r="D62">
         <v>1722</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="E62" t="s">
         <v>534</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="F62" t="s">
         <v>535</v>
       </c>
-      <c r="J62" s="5" t="s">
+      <c r="J62" t="s">
         <v>536</v>
       </c>
-      <c r="K62" s="5" t="s">
+      <c r="K62" t="s">
         <v>537</v>
       </c>
       <c r="L62" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="R62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S62" s="5" t="s">
+      <c r="R62" t="s">
+        <v>24</v>
+      </c>
+      <c r="S62" t="s">
         <v>25</v>
       </c>
       <c r="T62" s="1">
@@ -5950,34 +6138,34 @@
       </c>
     </row>
     <row r="63" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
+      <c r="A63" t="s">
         <v>102</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" t="s">
         <v>149</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D63" t="s">
         <v>539</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="E63" t="s">
         <v>28</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="F63" t="s">
         <v>29</v>
       </c>
-      <c r="J63" s="5" t="s">
+      <c r="J63" t="s">
         <v>540</v>
       </c>
-      <c r="K63" s="5" t="s">
+      <c r="K63" t="s">
         <v>541</v>
       </c>
       <c r="L63" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="R63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S63" s="5" t="s">
+      <c r="R63" t="s">
+        <v>24</v>
+      </c>
+      <c r="S63" t="s">
         <v>25</v>
       </c>
       <c r="T63" s="1">
@@ -6000,34 +6188,34 @@
       </c>
     </row>
     <row r="64" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="s">
+      <c r="A64" t="s">
         <v>102</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B64" t="s">
         <v>149</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" t="s">
         <v>543</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="E64" t="s">
         <v>544</v>
       </c>
-      <c r="F64" s="5" t="s">
+      <c r="F64" t="s">
         <v>568</v>
       </c>
-      <c r="J64" s="5" t="s">
+      <c r="J64" t="s">
         <v>545</v>
       </c>
-      <c r="K64" s="5" t="s">
+      <c r="K64" t="s">
         <v>546</v>
       </c>
       <c r="L64" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="R64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S64" s="5" t="s">
+      <c r="R64" t="s">
+        <v>24</v>
+      </c>
+      <c r="S64" t="s">
         <v>25</v>
       </c>
       <c r="W64" s="1">
@@ -6041,31 +6229,31 @@
       </c>
     </row>
     <row r="65" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="s">
+      <c r="A65" t="s">
         <v>154</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B65" t="s">
         <v>155</v>
       </c>
-      <c r="D65" s="5">
+      <c r="D65">
         <v>1712</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="E65" t="s">
         <v>28</v>
       </c>
-      <c r="F65" s="5" t="s">
+      <c r="F65" t="s">
         <v>29</v>
       </c>
-      <c r="J65" s="5" t="s">
+      <c r="J65" t="s">
         <v>156</v>
       </c>
-      <c r="L65" s="12" t="s">
+      <c r="L65" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="R65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S65" s="5" t="s">
+      <c r="R65" t="s">
+        <v>24</v>
+      </c>
+      <c r="S65" t="s">
         <v>25</v>
       </c>
       <c r="T65" s="1">
@@ -6088,37 +6276,37 @@
       </c>
     </row>
     <row r="66" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
+      <c r="A66" t="s">
         <v>154</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" t="s">
         <v>155</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="D66" t="s">
         <v>548</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="E66" t="s">
         <v>28</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="F66" t="s">
         <v>549</v>
       </c>
-      <c r="H66" s="5" t="s">
+      <c r="H66" t="s">
         <v>484</v>
       </c>
-      <c r="J66" s="5" t="s">
+      <c r="J66" t="s">
         <v>550</v>
       </c>
-      <c r="K66" s="5" t="s">
+      <c r="K66" t="s">
         <v>551</v>
       </c>
       <c r="L66" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="R66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S66" s="5" t="s">
+      <c r="R66" t="s">
+        <v>24</v>
+      </c>
+      <c r="S66" t="s">
         <v>25</v>
       </c>
       <c r="T66" s="1">
@@ -6135,34 +6323,34 @@
       </c>
     </row>
     <row r="67" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="5" t="s">
+      <c r="A67" t="s">
         <v>154</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B67" t="s">
         <v>155</v>
       </c>
-      <c r="D67" s="5">
+      <c r="D67">
         <v>1710</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="E67" t="s">
         <v>28</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="F67" t="s">
         <v>29</v>
       </c>
-      <c r="J67" s="5" t="s">
+      <c r="J67" t="s">
         <v>553</v>
       </c>
-      <c r="K67" s="5" t="s">
+      <c r="K67" t="s">
         <v>554</v>
       </c>
       <c r="L67" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="R67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S67" s="5" t="s">
+      <c r="R67" t="s">
+        <v>24</v>
+      </c>
+      <c r="S67" t="s">
         <v>25</v>
       </c>
       <c r="T67" s="1">
@@ -6185,34 +6373,34 @@
       </c>
     </row>
     <row r="68" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
+      <c r="A68" t="s">
         <v>154</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" t="s">
         <v>155</v>
       </c>
-      <c r="D68" s="5">
+      <c r="D68">
         <v>1731</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="E68" t="s">
         <v>28</v>
       </c>
-      <c r="F68" s="5" t="s">
+      <c r="F68" t="s">
         <v>29</v>
       </c>
-      <c r="J68" s="5" t="s">
+      <c r="J68" t="s">
         <v>556</v>
       </c>
-      <c r="K68" s="5" t="s">
+      <c r="K68" t="s">
         <v>556</v>
       </c>
       <c r="L68" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="R68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S68" s="5" t="s">
+      <c r="R68" t="s">
+        <v>24</v>
+      </c>
+      <c r="S68" t="s">
         <v>25</v>
       </c>
       <c r="T68" s="1">
@@ -6235,31 +6423,31 @@
       </c>
     </row>
     <row r="69" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="s">
+      <c r="A69" t="s">
         <v>158</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B69" t="s">
         <v>159</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="D69" t="s">
         <v>160</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="E69" t="s">
         <v>28</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="F69" t="s">
         <v>29</v>
       </c>
-      <c r="J69" s="5" t="s">
+      <c r="J69" t="s">
         <v>161</v>
       </c>
       <c r="L69" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="R69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S69" s="5" t="s">
+      <c r="R69" t="s">
+        <v>24</v>
+      </c>
+      <c r="S69" t="s">
         <v>25</v>
       </c>
       <c r="T69" s="1">
@@ -6282,34 +6470,34 @@
       </c>
     </row>
     <row r="70" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="5" t="s">
+      <c r="A70" t="s">
         <v>158</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B70" t="s">
         <v>159</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="D70" t="s">
         <v>558</v>
       </c>
-      <c r="E70" s="5" t="s">
+      <c r="E70" t="s">
         <v>28</v>
       </c>
-      <c r="F70" s="5" t="s">
+      <c r="F70" t="s">
         <v>29</v>
       </c>
-      <c r="J70" s="5" t="s">
+      <c r="J70" t="s">
         <v>559</v>
       </c>
-      <c r="K70" s="5" t="s">
+      <c r="K70" t="s">
         <v>559</v>
       </c>
       <c r="L70" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="R70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S70" s="5" t="s">
+      <c r="R70" t="s">
+        <v>24</v>
+      </c>
+      <c r="S70" t="s">
         <v>25</v>
       </c>
       <c r="T70" s="1">
@@ -6332,34 +6520,34 @@
       </c>
     </row>
     <row r="71" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
+      <c r="A71" t="s">
         <v>158</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B71" t="s">
         <v>159</v>
       </c>
-      <c r="D71" s="5" t="s">
+      <c r="D71" t="s">
         <v>561</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="E71" t="s">
         <v>28</v>
       </c>
-      <c r="F71" s="5" t="s">
+      <c r="F71" t="s">
         <v>29</v>
       </c>
-      <c r="J71" s="5" t="s">
+      <c r="J71" t="s">
         <v>562</v>
       </c>
-      <c r="K71" s="5" t="s">
+      <c r="K71" t="s">
         <v>562</v>
       </c>
       <c r="L71" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="R71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S71" s="5" t="s">
+      <c r="R71" t="s">
+        <v>24</v>
+      </c>
+      <c r="S71" t="s">
         <v>25</v>
       </c>
       <c r="T71" s="1">
@@ -6382,31 +6570,31 @@
       </c>
     </row>
     <row r="72" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
+      <c r="A72" t="s">
         <v>158</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" t="s">
         <v>159</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D72">
         <v>1704</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="E72" t="s">
         <v>28</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="F72" t="s">
         <v>29</v>
       </c>
-      <c r="J72" s="5" t="s">
+      <c r="J72" t="s">
         <v>564</v>
       </c>
       <c r="L72" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="R72" s="5" t="s">
+      <c r="R72" t="s">
         <v>393</v>
       </c>
-      <c r="S72" s="5" t="s">
+      <c r="S72" t="s">
         <v>25</v>
       </c>
       <c r="T72" s="1">
@@ -6429,28 +6617,28 @@
       </c>
     </row>
     <row r="73" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="s">
+      <c r="A73" t="s">
         <v>158</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B73" t="s">
         <v>159</v>
       </c>
-      <c r="D73" s="5">
+      <c r="D73">
         <v>1714</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="E73" t="s">
         <v>28</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="F73" t="s">
         <v>29</v>
       </c>
-      <c r="J73" s="5" t="s">
+      <c r="J73" t="s">
         <v>566</v>
       </c>
       <c r="L73" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="S73" s="5" t="s">
+      <c r="S73" t="s">
         <v>25</v>
       </c>
       <c r="T73" s="1">
@@ -6467,31 +6655,31 @@
       </c>
     </row>
     <row r="74" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
+      <c r="A74" t="s">
         <v>158</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" t="s">
         <v>163</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="D74" t="s">
         <v>164</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="E74" t="s">
         <v>28</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="F74" t="s">
         <v>29</v>
       </c>
-      <c r="J74" s="5" t="s">
+      <c r="J74" t="s">
         <v>165</v>
       </c>
       <c r="L74" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="R74" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S74" s="5" t="s">
+      <c r="R74" t="s">
+        <v>24</v>
+      </c>
+      <c r="S74" t="s">
         <v>25</v>
       </c>
       <c r="T74" s="1" t="s">
@@ -6514,28 +6702,28 @@
       </c>
     </row>
     <row r="75" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="s">
+      <c r="A75" t="s">
         <v>158</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="B75" t="s">
         <v>163</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="D75" t="s">
         <v>574</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="E75" t="s">
         <v>394</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="F75" t="s">
         <v>32</v>
       </c>
-      <c r="J75" s="5" t="s">
+      <c r="J75" t="s">
         <v>575</v>
       </c>
       <c r="L75" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="S75" s="5" t="s">
+      <c r="S75" t="s">
         <v>25</v>
       </c>
       <c r="T75" s="1" t="s">
@@ -6558,28 +6746,28 @@
       </c>
     </row>
     <row r="76" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+      <c r="A76" t="s">
         <v>158</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" t="s">
         <v>163</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="D76" t="s">
         <v>578</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="E76" t="s">
         <v>48</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F76" t="s">
         <v>65</v>
       </c>
-      <c r="J76" s="5" t="s">
+      <c r="J76" t="s">
         <v>579</v>
       </c>
       <c r="L76" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="S76" s="5" t="s">
+      <c r="S76" t="s">
         <v>25</v>
       </c>
       <c r="T76" s="1" t="s">
@@ -6602,28 +6790,28 @@
       </c>
     </row>
     <row r="77" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="5" t="s">
+      <c r="A77" t="s">
         <v>158</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B77" t="s">
         <v>163</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="D77" t="s">
         <v>498</v>
       </c>
-      <c r="E77" s="5" t="s">
+      <c r="E77" t="s">
         <v>583</v>
       </c>
-      <c r="F77" s="5" t="s">
+      <c r="F77" t="s">
         <v>584</v>
       </c>
-      <c r="J77" s="5" t="s">
+      <c r="J77" t="s">
         <v>585</v>
       </c>
       <c r="L77" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="S77" s="5" t="s">
+      <c r="S77" t="s">
         <v>289</v>
       </c>
       <c r="T77" s="1" t="s">
@@ -6646,46 +6834,46 @@
       </c>
     </row>
     <row r="78" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L78" s="11"/>
+      <c r="L78" s="10"/>
     </row>
     <row r="79" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L79" s="11"/>
+      <c r="L79" s="10"/>
     </row>
     <row r="80" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L80" s="11"/>
+      <c r="L80" s="10"/>
     </row>
     <row r="81" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L81" s="11"/>
+      <c r="L81" s="10"/>
     </row>
     <row r="82" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L82" s="11"/>
+      <c r="L82" s="10"/>
     </row>
     <row r="83" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="5" t="s">
+      <c r="A83" t="s">
         <v>167</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="B83" t="s">
         <v>168</v>
       </c>
-      <c r="D83" s="5" t="s">
+      <c r="D83" t="s">
         <v>169</v>
       </c>
-      <c r="E83" s="5" t="s">
+      <c r="E83" t="s">
         <v>86</v>
       </c>
-      <c r="F83" s="5" t="s">
+      <c r="F83" t="s">
         <v>87</v>
       </c>
-      <c r="J83" s="5" t="s">
+      <c r="J83" t="s">
         <v>170</v>
       </c>
       <c r="L83" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="R83" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S83" s="5" t="s">
+      <c r="R83" t="s">
+        <v>24</v>
+      </c>
+      <c r="S83" t="s">
         <v>25</v>
       </c>
       <c r="T83" s="1" t="s">
@@ -6702,37 +6890,37 @@
       </c>
     </row>
     <row r="84" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="5" t="s">
+      <c r="A84" t="s">
         <v>167</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="B84" t="s">
         <v>168</v>
       </c>
-      <c r="D84" s="5" t="s">
+      <c r="D84" t="s">
         <v>460</v>
       </c>
-      <c r="E84" s="5" t="s">
+      <c r="E84" t="s">
         <v>86</v>
       </c>
-      <c r="F84" s="5" t="s">
+      <c r="F84" t="s">
         <v>173</v>
       </c>
-      <c r="H84" s="5" t="s">
+      <c r="H84" t="s">
         <v>174</v>
       </c>
-      <c r="J84" s="5" t="s">
+      <c r="J84" t="s">
         <v>175</v>
       </c>
-      <c r="K84" s="5" t="s">
+      <c r="K84" t="s">
         <v>176</v>
       </c>
       <c r="L84" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="R84" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S84" s="5" t="s">
+      <c r="R84" t="s">
+        <v>24</v>
+      </c>
+      <c r="S84" t="s">
         <v>25</v>
       </c>
       <c r="T84" s="1" t="s">
@@ -6755,37 +6943,37 @@
       </c>
     </row>
     <row r="85" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="5" t="s">
+      <c r="A85" t="s">
         <v>167</v>
       </c>
-      <c r="B85" s="5" t="s">
+      <c r="B85" t="s">
         <v>168</v>
       </c>
-      <c r="D85" s="5" t="s">
+      <c r="D85" t="s">
         <v>38</v>
       </c>
-      <c r="E85" s="5" t="s">
+      <c r="E85" t="s">
         <v>86</v>
       </c>
-      <c r="F85" s="5" t="s">
+      <c r="F85" t="s">
         <v>87</v>
       </c>
-      <c r="H85" s="5" t="s">
+      <c r="H85" t="s">
         <v>590</v>
       </c>
-      <c r="J85" s="5" t="s">
+      <c r="J85" t="s">
         <v>591</v>
       </c>
-      <c r="K85" s="5" t="s">
+      <c r="K85" t="s">
         <v>592</v>
       </c>
       <c r="L85" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="R85" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S85" s="5" t="s">
+      <c r="R85" t="s">
+        <v>24</v>
+      </c>
+      <c r="S85" t="s">
         <v>25</v>
       </c>
       <c r="T85" s="1" t="s">
@@ -6802,37 +6990,37 @@
       </c>
     </row>
     <row r="86" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="5" t="s">
+      <c r="A86" t="s">
         <v>167</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="B86" t="s">
         <v>168</v>
       </c>
-      <c r="D86" s="5" t="s">
+      <c r="D86" t="s">
         <v>325</v>
       </c>
-      <c r="E86" s="5" t="s">
+      <c r="E86" t="s">
         <v>595</v>
       </c>
-      <c r="F86" s="5" t="s">
+      <c r="F86" t="s">
         <v>105</v>
       </c>
-      <c r="H86" s="5" t="s">
+      <c r="H86" t="s">
         <v>596</v>
       </c>
-      <c r="J86" s="5" t="s">
+      <c r="J86" t="s">
         <v>597</v>
       </c>
-      <c r="K86" s="5" t="s">
+      <c r="K86" t="s">
         <v>598</v>
       </c>
       <c r="L86" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="R86" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S86" s="5" t="s">
+      <c r="R86" t="s">
+        <v>24</v>
+      </c>
+      <c r="S86" t="s">
         <v>25</v>
       </c>
       <c r="T86" s="1" t="s">
@@ -6849,34 +7037,34 @@
       </c>
     </row>
     <row r="87" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="5" t="s">
+      <c r="A87" t="s">
         <v>178</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B87" t="s">
         <v>179</v>
       </c>
-      <c r="D87" s="5" t="s">
+      <c r="D87" t="s">
         <v>150</v>
       </c>
-      <c r="E87" s="5" t="s">
+      <c r="E87" t="s">
         <v>180</v>
       </c>
-      <c r="F87" s="5" t="s">
+      <c r="F87" t="s">
         <v>368</v>
       </c>
-      <c r="H87" s="5" t="s">
+      <c r="H87" t="s">
         <v>181</v>
       </c>
-      <c r="J87" s="5" t="s">
+      <c r="J87" t="s">
         <v>182</v>
       </c>
       <c r="L87" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="R87" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S87" s="5" t="s">
+      <c r="R87" t="s">
+        <v>24</v>
+      </c>
+      <c r="S87" t="s">
         <v>25</v>
       </c>
       <c r="T87" s="1">
@@ -6899,37 +7087,37 @@
       </c>
     </row>
     <row r="88" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="5" t="s">
+      <c r="A88" t="s">
         <v>178</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" t="s">
         <v>179</v>
       </c>
-      <c r="D88" s="5" t="s">
+      <c r="D88" t="s">
         <v>601</v>
       </c>
-      <c r="E88" s="5" t="s">
+      <c r="E88" t="s">
         <v>602</v>
       </c>
-      <c r="F88" s="5" t="s">
+      <c r="F88" t="s">
         <v>603</v>
       </c>
-      <c r="H88" s="5" t="s">
+      <c r="H88" t="s">
         <v>604</v>
       </c>
-      <c r="J88" s="5" t="s">
+      <c r="J88" t="s">
         <v>605</v>
       </c>
-      <c r="K88" s="5" t="s">
+      <c r="K88" t="s">
         <v>606</v>
       </c>
       <c r="L88" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="R88" s="5" t="s">
+      <c r="R88" t="s">
         <v>608</v>
       </c>
-      <c r="S88" s="5" t="s">
+      <c r="S88" t="s">
         <v>609</v>
       </c>
       <c r="W88" s="1">
@@ -6943,31 +7131,31 @@
       </c>
     </row>
     <row r="89" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="5" t="s">
+      <c r="A89" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="B89" t="s">
         <v>179</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="D89" t="s">
         <v>610</v>
       </c>
-      <c r="E89" s="5" t="s">
+      <c r="E89" t="s">
         <v>611</v>
       </c>
-      <c r="F89" s="5" t="s">
+      <c r="F89" t="s">
         <v>29</v>
       </c>
-      <c r="J89" s="5" t="s">
+      <c r="J89" t="s">
         <v>612</v>
       </c>
       <c r="L89" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="R89" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S89" s="5" t="s">
+      <c r="R89" t="s">
+        <v>24</v>
+      </c>
+      <c r="S89" t="s">
         <v>25</v>
       </c>
       <c r="T89" s="1">
@@ -6990,34 +7178,34 @@
       </c>
     </row>
     <row r="90" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="5" t="s">
+      <c r="A90" t="s">
         <v>178</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B90" t="s">
         <v>179</v>
       </c>
-      <c r="D90" s="5" t="s">
+      <c r="D90" t="s">
         <v>614</v>
       </c>
-      <c r="E90" s="5" t="s">
+      <c r="E90" t="s">
         <v>48</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="F90" t="s">
         <v>65</v>
       </c>
-      <c r="J90" s="5" t="s">
+      <c r="J90" t="s">
         <v>615</v>
       </c>
-      <c r="K90" s="5" t="s">
+      <c r="K90" t="s">
         <v>616</v>
       </c>
       <c r="L90" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="R90" s="5" t="s">
+      <c r="R90" t="s">
         <v>532</v>
       </c>
-      <c r="S90" s="5" t="s">
+      <c r="S90" t="s">
         <v>25</v>
       </c>
       <c r="T90" s="1">
@@ -7034,43 +7222,43 @@
       </c>
     </row>
     <row r="91" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B91" s="7" t="s">
+      <c r="B91" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7" t="s">
+      <c r="C91" s="6"/>
+      <c r="D91" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="E91" s="7" t="s">
+      <c r="E91" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="F91" s="7" t="s">
+      <c r="F91" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="G91" s="7"/>
-      <c r="H91" s="7"/>
-      <c r="I91" s="7"/>
-      <c r="J91" s="7" t="s">
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="6"/>
+      <c r="J91" s="6" t="s">
         <v>618</v>
       </c>
-      <c r="K91" s="7" t="s">
+      <c r="K91" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="L91" s="13" t="s">
+      <c r="L91" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="M91" s="7"/>
-      <c r="N91" s="7"/>
-      <c r="O91" s="7"/>
-      <c r="P91" s="7"/>
-      <c r="Q91" s="7"/>
-      <c r="R91" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S91" s="7" t="s">
+      <c r="M91" s="6"/>
+      <c r="N91" s="6"/>
+      <c r="O91" s="6"/>
+      <c r="P91" s="6"/>
+      <c r="Q91" s="6"/>
+      <c r="R91" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S91" s="6" t="s">
         <v>189</v>
       </c>
       <c r="T91" s="3" t="s">
@@ -7093,45 +7281,45 @@
       </c>
     </row>
     <row r="92" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="7" t="s">
+      <c r="A92" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="7" t="s">
+      <c r="B92" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="7"/>
-      <c r="D92" s="7" t="s">
+      <c r="C92" s="6"/>
+      <c r="D92" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="E92" s="7" t="s">
+      <c r="E92" s="6" t="s">
         <v>620</v>
       </c>
-      <c r="F92" s="7" t="s">
+      <c r="F92" s="6" t="s">
         <v>621</v>
       </c>
-      <c r="G92" s="7"/>
-      <c r="H92" s="7" t="s">
+      <c r="G92" s="6"/>
+      <c r="H92" s="6" t="s">
         <v>622</v>
       </c>
-      <c r="I92" s="7"/>
-      <c r="J92" s="7" t="s">
+      <c r="I92" s="6"/>
+      <c r="J92" s="6" t="s">
         <v>623</v>
       </c>
-      <c r="K92" s="7" t="s">
+      <c r="K92" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="L92" s="14" t="s">
+      <c r="L92" s="13" t="s">
         <v>625</v>
       </c>
-      <c r="M92" s="7"/>
-      <c r="N92" s="7"/>
-      <c r="O92" s="7"/>
-      <c r="P92" s="7"/>
-      <c r="Q92" s="7"/>
-      <c r="R92" s="7" t="s">
+      <c r="M92" s="6"/>
+      <c r="N92" s="6"/>
+      <c r="O92" s="6"/>
+      <c r="P92" s="6"/>
+      <c r="Q92" s="6"/>
+      <c r="R92" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="S92" s="7" t="s">
+      <c r="S92" s="6" t="s">
         <v>627</v>
       </c>
       <c r="T92" s="3" t="s">
@@ -7150,45 +7338,45 @@
       </c>
     </row>
     <row r="93" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="7" t="s">
+      <c r="A93" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B93" s="7" t="s">
+      <c r="B93" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C93" s="7"/>
-      <c r="D93" s="7" t="s">
+      <c r="C93" s="6"/>
+      <c r="D93" s="6" t="s">
         <v>629</v>
       </c>
-      <c r="E93" s="7" t="s">
+      <c r="E93" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="F93" s="7" t="s">
+      <c r="F93" s="6" t="s">
         <v>631</v>
       </c>
-      <c r="G93" s="7"/>
-      <c r="H93" s="7" t="s">
+      <c r="G93" s="6"/>
+      <c r="H93" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I93" s="7"/>
-      <c r="J93" s="7" t="s">
+      <c r="I93" s="6"/>
+      <c r="J93" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="K93" s="7" t="s">
+      <c r="K93" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="L93" s="14" t="s">
+      <c r="L93" s="13" t="s">
         <v>633</v>
       </c>
-      <c r="M93" s="7"/>
-      <c r="N93" s="7"/>
-      <c r="O93" s="7"/>
-      <c r="P93" s="7"/>
-      <c r="Q93" s="7"/>
-      <c r="R93" s="7" t="s">
+      <c r="M93" s="6"/>
+      <c r="N93" s="6"/>
+      <c r="O93" s="6"/>
+      <c r="P93" s="6"/>
+      <c r="Q93" s="6"/>
+      <c r="R93" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="S93" s="7" t="s">
+      <c r="S93" s="6" t="s">
         <v>189</v>
       </c>
       <c r="T93" s="3" t="s">
@@ -7209,45 +7397,45 @@
       </c>
     </row>
     <row r="94" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="7" t="s">
+      <c r="A94" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B94" s="7" t="s">
+      <c r="B94" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="7" t="s">
+      <c r="C94" s="6"/>
+      <c r="D94" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="E94" s="7" t="s">
+      <c r="E94" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="F94" s="7" t="s">
+      <c r="F94" s="6" t="s">
         <v>635</v>
       </c>
-      <c r="G94" s="7"/>
-      <c r="H94" s="7" t="s">
+      <c r="G94" s="6"/>
+      <c r="H94" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="I94" s="7"/>
-      <c r="J94" s="7" t="s">
+      <c r="I94" s="6"/>
+      <c r="J94" s="6" t="s">
         <v>637</v>
       </c>
-      <c r="K94" s="7" t="s">
+      <c r="K94" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="L94" s="14" t="s">
+      <c r="L94" s="13" t="s">
         <v>639</v>
       </c>
-      <c r="M94" s="7"/>
-      <c r="N94" s="7"/>
-      <c r="O94" s="7"/>
-      <c r="P94" s="7"/>
-      <c r="Q94" s="7"/>
-      <c r="R94" s="7" t="s">
+      <c r="M94" s="6"/>
+      <c r="N94" s="6"/>
+      <c r="O94" s="6"/>
+      <c r="P94" s="6"/>
+      <c r="Q94" s="6"/>
+      <c r="R94" s="6" t="s">
         <v>640</v>
       </c>
-      <c r="S94" s="7" t="s">
+      <c r="S94" s="6" t="s">
         <v>189</v>
       </c>
       <c r="T94" s="3" t="s">
@@ -7268,31 +7456,31 @@
       </c>
     </row>
     <row r="95" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="5" t="s">
+      <c r="A95" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="5" t="s">
+      <c r="B95" t="s">
         <v>191</v>
       </c>
-      <c r="D95" s="5" t="s">
+      <c r="D95" t="s">
         <v>643</v>
       </c>
-      <c r="E95" s="5" t="s">
+      <c r="E95" t="s">
         <v>28</v>
       </c>
-      <c r="F95" s="5" t="s">
+      <c r="F95" t="s">
         <v>29</v>
       </c>
-      <c r="J95" s="5" t="s">
+      <c r="J95" t="s">
         <v>192</v>
       </c>
       <c r="L95" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="R95" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S95" s="5" t="s">
+      <c r="R95" t="s">
+        <v>24</v>
+      </c>
+      <c r="S95" t="s">
         <v>25</v>
       </c>
       <c r="T95" s="1">
@@ -7315,31 +7503,31 @@
       </c>
     </row>
     <row r="96" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="5" t="s">
+      <c r="A96" t="s">
         <v>190</v>
       </c>
-      <c r="B96" s="5" t="s">
+      <c r="B96" t="s">
         <v>191</v>
       </c>
-      <c r="D96" s="5" t="s">
+      <c r="D96" t="s">
         <v>643</v>
       </c>
-      <c r="E96" s="5" t="s">
+      <c r="E96" t="s">
         <v>28</v>
       </c>
-      <c r="F96" s="5" t="s">
+      <c r="F96" t="s">
         <v>29</v>
       </c>
-      <c r="J96" s="5" t="s">
+      <c r="J96" t="s">
         <v>194</v>
       </c>
       <c r="L96" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="R96" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S96" s="5" t="s">
+      <c r="R96" t="s">
+        <v>24</v>
+      </c>
+      <c r="S96" t="s">
         <v>25</v>
       </c>
       <c r="T96" s="1">
@@ -7362,37 +7550,37 @@
       </c>
     </row>
     <row r="97" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="5" t="s">
+      <c r="A97" t="s">
         <v>190</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B97" t="s">
         <v>191</v>
       </c>
-      <c r="D97" s="5" t="s">
+      <c r="D97" t="s">
         <v>644</v>
       </c>
-      <c r="E97" s="5" t="s">
+      <c r="E97" t="s">
         <v>196</v>
       </c>
-      <c r="F97" s="5" t="s">
+      <c r="F97" t="s">
         <v>197</v>
       </c>
       <c r="G97" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="J97" s="5" t="s">
+      <c r="J97" t="s">
         <v>198</v>
       </c>
-      <c r="K97" s="5" t="s">
+      <c r="K97" t="s">
         <v>199</v>
       </c>
       <c r="L97" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="R97" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S97" s="5" t="s">
+      <c r="R97" t="s">
+        <v>24</v>
+      </c>
+      <c r="S97" t="s">
         <v>58</v>
       </c>
       <c r="T97" s="1">
@@ -7415,31 +7603,31 @@
       </c>
     </row>
     <row r="98" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="5" t="s">
+      <c r="A98" t="s">
         <v>190</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B98" t="s">
         <v>191</v>
       </c>
-      <c r="D98" s="5" t="s">
+      <c r="D98" t="s">
         <v>646</v>
       </c>
-      <c r="E98" s="5" t="s">
+      <c r="E98" t="s">
         <v>28</v>
       </c>
-      <c r="F98" s="5" t="s">
+      <c r="F98" t="s">
         <v>29</v>
       </c>
-      <c r="J98" s="5" t="s">
+      <c r="J98" t="s">
         <v>647</v>
       </c>
       <c r="L98" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="R98" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S98" s="5" t="s">
+      <c r="R98" t="s">
+        <v>24</v>
+      </c>
+      <c r="S98" t="s">
         <v>25</v>
       </c>
       <c r="T98" s="1">
@@ -7462,31 +7650,31 @@
       </c>
     </row>
     <row r="99" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="5" t="s">
+      <c r="A99" t="s">
         <v>190</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" t="s">
         <v>191</v>
       </c>
-      <c r="D99" s="5" t="s">
+      <c r="D99" t="s">
         <v>649</v>
       </c>
-      <c r="E99" s="5" t="s">
+      <c r="E99" t="s">
         <v>196</v>
       </c>
-      <c r="F99" s="5" t="s">
+      <c r="F99" t="s">
         <v>312</v>
       </c>
-      <c r="J99" s="5" t="s">
+      <c r="J99" t="s">
         <v>650</v>
       </c>
       <c r="L99" s="4" t="s">
         <v>651</v>
       </c>
-      <c r="R99" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S99" s="5" t="s">
+      <c r="R99" t="s">
+        <v>24</v>
+      </c>
+      <c r="S99" t="s">
         <v>25</v>
       </c>
       <c r="T99" s="1">
@@ -7509,31 +7697,31 @@
       </c>
     </row>
     <row r="100" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="5" t="s">
+      <c r="A100" t="s">
         <v>190</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="B100" t="s">
         <v>191</v>
       </c>
-      <c r="D100" s="5" t="s">
+      <c r="D100" t="s">
         <v>652</v>
       </c>
-      <c r="E100" s="5" t="s">
+      <c r="E100" t="s">
         <v>28</v>
       </c>
-      <c r="F100" s="5" t="s">
+      <c r="F100" t="s">
         <v>29</v>
       </c>
-      <c r="J100" s="5" t="s">
+      <c r="J100" t="s">
         <v>653</v>
       </c>
       <c r="L100" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="R100" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S100" s="5" t="s">
+      <c r="R100" t="s">
+        <v>24</v>
+      </c>
+      <c r="S100" t="s">
         <v>25</v>
       </c>
       <c r="T100" s="1">
@@ -7556,31 +7744,31 @@
       </c>
     </row>
     <row r="101" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="5" t="s">
+      <c r="A101" t="s">
         <v>190</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B101" t="s">
         <v>191</v>
       </c>
-      <c r="D101" s="5" t="s">
+      <c r="D101" t="s">
         <v>96</v>
       </c>
-      <c r="E101" s="5" t="s">
+      <c r="E101" t="s">
         <v>655</v>
       </c>
-      <c r="F101" s="5" t="s">
+      <c r="F101" t="s">
         <v>656</v>
       </c>
-      <c r="J101" s="5" t="s">
+      <c r="J101" t="s">
         <v>657</v>
       </c>
       <c r="L101" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="R101" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S101" s="5" t="s">
+      <c r="R101" t="s">
+        <v>24</v>
+      </c>
+      <c r="S101" t="s">
         <v>25</v>
       </c>
       <c r="T101" s="1">
@@ -7603,31 +7791,31 @@
       </c>
     </row>
     <row r="102" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="5" t="s">
+      <c r="A102" t="s">
         <v>190</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B102" t="s">
         <v>191</v>
       </c>
-      <c r="D102" s="5" t="s">
+      <c r="D102" t="s">
         <v>38</v>
       </c>
-      <c r="E102" s="5" t="s">
+      <c r="E102" t="s">
         <v>28</v>
       </c>
-      <c r="F102" s="5" t="s">
+      <c r="F102" t="s">
         <v>29</v>
       </c>
-      <c r="J102" s="5" t="s">
+      <c r="J102" t="s">
         <v>465</v>
       </c>
       <c r="L102" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="R102" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S102" s="5" t="s">
+      <c r="R102" t="s">
+        <v>24</v>
+      </c>
+      <c r="S102" t="s">
         <v>25</v>
       </c>
       <c r="T102" s="1">
@@ -7650,31 +7838,31 @@
       </c>
     </row>
     <row r="103" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="5" t="s">
+      <c r="A103" t="s">
         <v>46</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="B103" t="s">
         <v>201</v>
       </c>
-      <c r="D103" s="5" t="s">
+      <c r="D103" t="s">
         <v>202</v>
       </c>
-      <c r="E103" s="5" t="s">
+      <c r="E103" t="s">
         <v>203</v>
       </c>
-      <c r="F103" s="5" t="s">
+      <c r="F103" t="s">
         <v>204</v>
       </c>
-      <c r="J103" s="5" t="s">
+      <c r="J103" t="s">
         <v>205</v>
       </c>
       <c r="L103" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="R103" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S103" s="5" t="s">
+      <c r="R103" t="s">
+        <v>24</v>
+      </c>
+      <c r="S103" t="s">
         <v>207</v>
       </c>
       <c r="T103" s="1" t="s">
@@ -7697,34 +7885,34 @@
       </c>
     </row>
     <row r="104" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="5" t="s">
+      <c r="A104" t="s">
         <v>46</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" t="s">
         <v>201</v>
       </c>
-      <c r="D104" s="5" t="s">
+      <c r="D104" t="s">
         <v>662</v>
       </c>
-      <c r="E104" s="5" t="s">
+      <c r="E104" t="s">
         <v>48</v>
       </c>
-      <c r="F104" s="5" t="s">
+      <c r="F104" t="s">
         <v>208</v>
       </c>
-      <c r="J104" s="5" t="s">
+      <c r="J104" t="s">
         <v>209</v>
       </c>
-      <c r="K104" s="5" t="s">
+      <c r="K104" t="s">
         <v>210</v>
       </c>
       <c r="L104" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="R104" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S104" s="5" t="s">
+      <c r="R104" t="s">
+        <v>24</v>
+      </c>
+      <c r="S104" t="s">
         <v>25</v>
       </c>
       <c r="T104" s="1" t="s">
@@ -7747,34 +7935,34 @@
       </c>
     </row>
     <row r="105" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="5" t="s">
+      <c r="A105" t="s">
         <v>46</v>
       </c>
-      <c r="B105" s="5" t="s">
+      <c r="B105" t="s">
         <v>201</v>
       </c>
-      <c r="D105" s="5" t="s">
+      <c r="D105" t="s">
         <v>428</v>
       </c>
-      <c r="E105" s="5" t="s">
+      <c r="E105" t="s">
         <v>665</v>
       </c>
-      <c r="F105" s="5" t="s">
+      <c r="F105" t="s">
         <v>666</v>
       </c>
-      <c r="J105" s="5" t="s">
+      <c r="J105" t="s">
         <v>667</v>
       </c>
-      <c r="K105" s="5" t="s">
+      <c r="K105" t="s">
         <v>668</v>
       </c>
       <c r="L105" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="R105" s="5" t="s">
+      <c r="R105" t="s">
         <v>670</v>
       </c>
-      <c r="S105" s="5" t="s">
+      <c r="S105" t="s">
         <v>25</v>
       </c>
       <c r="T105" s="1" t="s">
@@ -7797,34 +7985,34 @@
       </c>
     </row>
     <row r="106" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="5" t="s">
+      <c r="A106" t="s">
         <v>46</v>
       </c>
-      <c r="B106" s="5" t="s">
+      <c r="B106" t="s">
         <v>201</v>
       </c>
-      <c r="D106" s="5" t="s">
+      <c r="D106" t="s">
         <v>673</v>
       </c>
-      <c r="E106" s="5" t="s">
+      <c r="E106" t="s">
         <v>48</v>
       </c>
-      <c r="F106" s="5" t="s">
+      <c r="F106" t="s">
         <v>49</v>
       </c>
-      <c r="J106" s="5" t="s">
+      <c r="J106" t="s">
         <v>674</v>
       </c>
-      <c r="K106" s="5" t="s">
+      <c r="K106" t="s">
         <v>675</v>
       </c>
       <c r="L106" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="R106" s="5" t="s">
+      <c r="R106" t="s">
         <v>626</v>
       </c>
-      <c r="S106" s="5" t="s">
+      <c r="S106" t="s">
         <v>25</v>
       </c>
       <c r="T106" s="1" t="s">
@@ -7847,34 +8035,34 @@
       </c>
     </row>
     <row r="107" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="5" t="s">
+      <c r="A107" t="s">
         <v>46</v>
       </c>
-      <c r="B107" s="5" t="s">
+      <c r="B107" t="s">
         <v>201</v>
       </c>
-      <c r="D107" s="5" t="s">
+      <c r="D107" t="s">
         <v>419</v>
       </c>
-      <c r="E107" s="5" t="s">
+      <c r="E107" t="s">
         <v>48</v>
       </c>
-      <c r="F107" s="5" t="s">
+      <c r="F107" t="s">
         <v>679</v>
       </c>
-      <c r="J107" s="5" t="s">
+      <c r="J107" t="s">
         <v>680</v>
       </c>
-      <c r="K107" s="5" t="s">
+      <c r="K107" t="s">
         <v>681</v>
       </c>
       <c r="L107" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="R107" s="5" t="s">
+      <c r="R107" t="s">
         <v>467</v>
       </c>
-      <c r="S107" s="5" t="s">
+      <c r="S107" t="s">
         <v>207</v>
       </c>
       <c r="T107" s="1" t="s">
@@ -7897,31 +8085,31 @@
       </c>
     </row>
     <row r="108" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="5" t="s">
+      <c r="A108" t="s">
         <v>46</v>
       </c>
-      <c r="B108" s="5" t="s">
+      <c r="B108" t="s">
         <v>201</v>
       </c>
-      <c r="D108" s="5" t="s">
+      <c r="D108" t="s">
         <v>684</v>
       </c>
-      <c r="E108" s="5" t="s">
+      <c r="E108" t="s">
         <v>665</v>
       </c>
-      <c r="F108" s="5" t="s">
+      <c r="F108" t="s">
         <v>666</v>
       </c>
-      <c r="J108" s="5" t="s">
+      <c r="J108" t="s">
         <v>685</v>
       </c>
       <c r="L108" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="R108" s="5" t="s">
+      <c r="R108" t="s">
         <v>670</v>
       </c>
-      <c r="S108" s="5" t="s">
+      <c r="S108" t="s">
         <v>25</v>
       </c>
       <c r="T108" s="1" t="s">
@@ -7944,34 +8132,34 @@
       </c>
     </row>
     <row r="109" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="5" t="s">
+      <c r="A109" t="s">
         <v>46</v>
       </c>
-      <c r="B109" s="5" t="s">
+      <c r="B109" t="s">
         <v>201</v>
       </c>
-      <c r="D109" s="5" t="s">
+      <c r="D109" t="s">
         <v>688</v>
       </c>
-      <c r="E109" s="5" t="s">
+      <c r="E109" t="s">
         <v>689</v>
       </c>
-      <c r="F109" s="5" t="s">
+      <c r="F109" t="s">
         <v>690</v>
       </c>
-      <c r="J109" s="5" t="s">
+      <c r="J109" t="s">
         <v>691</v>
       </c>
-      <c r="K109" s="5" t="s">
+      <c r="K109" t="s">
         <v>692</v>
       </c>
       <c r="L109" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="R109" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S109" s="5" t="s">
+      <c r="R109" t="s">
+        <v>24</v>
+      </c>
+      <c r="S109" t="s">
         <v>25</v>
       </c>
       <c r="T109" s="1" t="s">
@@ -7994,34 +8182,34 @@
       </c>
     </row>
     <row r="110" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="5" t="s">
+      <c r="A110" t="s">
         <v>213</v>
       </c>
-      <c r="B110" s="5" t="s">
+      <c r="B110" t="s">
         <v>214</v>
       </c>
-      <c r="D110" s="5" t="s">
+      <c r="D110" t="s">
         <v>215</v>
       </c>
-      <c r="E110" s="5" t="s">
+      <c r="E110" t="s">
         <v>92</v>
       </c>
-      <c r="F110" s="5" t="s">
+      <c r="F110" t="s">
         <v>93</v>
       </c>
-      <c r="J110" s="5" t="s">
+      <c r="J110" t="s">
         <v>216</v>
       </c>
-      <c r="K110" s="5" t="s">
+      <c r="K110" t="s">
         <v>217</v>
       </c>
       <c r="L110" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="R110" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S110" s="5" t="s">
+      <c r="R110" t="s">
+        <v>24</v>
+      </c>
+      <c r="S110" t="s">
         <v>219</v>
       </c>
       <c r="T110" s="1">
@@ -8044,37 +8232,37 @@
       </c>
     </row>
     <row r="111" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="5" t="s">
+      <c r="A111" t="s">
         <v>213</v>
       </c>
-      <c r="B111" s="5" t="s">
+      <c r="B111" t="s">
         <v>214</v>
       </c>
-      <c r="D111" s="5" t="s">
+      <c r="D111" t="s">
         <v>649</v>
       </c>
-      <c r="E111" s="5" t="s">
+      <c r="E111" t="s">
         <v>220</v>
       </c>
-      <c r="F111" s="5" t="s">
+      <c r="F111" t="s">
         <v>221</v>
       </c>
-      <c r="H111" s="5" t="s">
+      <c r="H111" t="s">
         <v>45</v>
       </c>
-      <c r="J111" s="5" t="s">
+      <c r="J111" t="s">
         <v>222</v>
       </c>
-      <c r="K111" s="5" t="s">
+      <c r="K111" t="s">
         <v>223</v>
       </c>
       <c r="L111" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="R111" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S111" s="5" t="s">
+      <c r="R111" t="s">
+        <v>24</v>
+      </c>
+      <c r="S111" t="s">
         <v>219</v>
       </c>
       <c r="T111" s="1">
@@ -8097,40 +8285,40 @@
       </c>
     </row>
     <row r="112" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="5" t="s">
+      <c r="A112" t="s">
         <v>213</v>
       </c>
-      <c r="B112" s="5" t="s">
+      <c r="B112" t="s">
         <v>214</v>
       </c>
-      <c r="D112" s="5" t="s">
+      <c r="D112" t="s">
         <v>696</v>
       </c>
-      <c r="E112" s="5" t="s">
+      <c r="E112" t="s">
         <v>697</v>
       </c>
-      <c r="F112" s="5" t="s">
+      <c r="F112" t="s">
         <v>698</v>
       </c>
-      <c r="H112" s="5" t="s">
+      <c r="H112" t="s">
         <v>45</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="J112" s="5" t="s">
+      <c r="J112" t="s">
         <v>700</v>
       </c>
-      <c r="K112" s="5" t="s">
+      <c r="K112" t="s">
         <v>701</v>
       </c>
       <c r="L112" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="R112" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S112" s="5" t="s">
+      <c r="R112" t="s">
+        <v>24</v>
+      </c>
+      <c r="S112" t="s">
         <v>703</v>
       </c>
       <c r="T112" s="1">
@@ -8147,40 +8335,40 @@
       </c>
     </row>
     <row r="113" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="5" t="s">
+      <c r="A113" t="s">
         <v>213</v>
       </c>
-      <c r="B113" s="5" t="s">
+      <c r="B113" t="s">
         <v>214</v>
       </c>
-      <c r="D113" s="5" t="s">
+      <c r="D113" t="s">
         <v>696</v>
       </c>
-      <c r="E113" s="5" t="s">
+      <c r="E113" t="s">
         <v>697</v>
       </c>
-      <c r="F113" s="5" t="s">
+      <c r="F113" t="s">
         <v>698</v>
       </c>
-      <c r="H113" s="5" t="s">
+      <c r="H113" t="s">
         <v>45</v>
       </c>
       <c r="I113" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="J113" s="5" t="s">
+      <c r="J113" t="s">
         <v>704</v>
       </c>
-      <c r="K113" s="5" t="s">
+      <c r="K113" t="s">
         <v>705</v>
       </c>
       <c r="L113" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="R113" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S113" s="5" t="s">
+      <c r="R113" t="s">
+        <v>24</v>
+      </c>
+      <c r="S113" t="s">
         <v>703</v>
       </c>
       <c r="T113" s="1">
@@ -8197,34 +8385,34 @@
       </c>
     </row>
     <row r="114" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="5" t="s">
+      <c r="A114" t="s">
         <v>225</v>
       </c>
-      <c r="B114" s="5" t="s">
+      <c r="B114" t="s">
         <v>226</v>
       </c>
-      <c r="D114" s="5" t="s">
+      <c r="D114" t="s">
         <v>419</v>
       </c>
-      <c r="E114" s="5" t="s">
+      <c r="E114" t="s">
         <v>28</v>
       </c>
-      <c r="F114" s="5" t="s">
+      <c r="F114" t="s">
         <v>227</v>
       </c>
-      <c r="H114" s="5" t="s">
+      <c r="H114" t="s">
         <v>228</v>
       </c>
-      <c r="J114" s="5" t="s">
+      <c r="J114" t="s">
         <v>229</v>
       </c>
       <c r="L114" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="R114" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S114" s="5" t="s">
+      <c r="R114" t="s">
+        <v>24</v>
+      </c>
+      <c r="S114" t="s">
         <v>25</v>
       </c>
       <c r="T114" s="1" t="s">
@@ -8247,31 +8435,31 @@
       </c>
     </row>
     <row r="115" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="5" t="s">
+      <c r="A115" t="s">
         <v>225</v>
       </c>
-      <c r="B115" s="5" t="s">
+      <c r="B115" t="s">
         <v>226</v>
       </c>
-      <c r="D115" s="5" t="s">
+      <c r="D115" t="s">
         <v>419</v>
       </c>
-      <c r="E115" s="5" t="s">
+      <c r="E115" t="s">
         <v>28</v>
       </c>
-      <c r="F115" s="5" t="s">
+      <c r="F115" t="s">
         <v>29</v>
       </c>
-      <c r="J115" s="5" t="s">
+      <c r="J115" t="s">
         <v>231</v>
       </c>
       <c r="L115" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="R115" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S115" s="5" t="s">
+      <c r="R115" t="s">
+        <v>24</v>
+      </c>
+      <c r="S115" t="s">
         <v>101</v>
       </c>
       <c r="T115" s="1" t="s">
@@ -8294,31 +8482,31 @@
       </c>
     </row>
     <row r="116" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="5" t="s">
+      <c r="A116" t="s">
         <v>225</v>
       </c>
-      <c r="B116" s="5" t="s">
+      <c r="B116" t="s">
         <v>226</v>
       </c>
-      <c r="D116" s="5" t="s">
+      <c r="D116" t="s">
         <v>711</v>
       </c>
-      <c r="E116" s="5" t="s">
+      <c r="E116" t="s">
         <v>28</v>
       </c>
-      <c r="F116" s="5" t="s">
+      <c r="F116" t="s">
         <v>29</v>
       </c>
-      <c r="J116" s="5" t="s">
+      <c r="J116" t="s">
         <v>233</v>
       </c>
       <c r="L116" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="R116" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S116" s="5" t="s">
+      <c r="R116" t="s">
+        <v>24</v>
+      </c>
+      <c r="S116" t="s">
         <v>235</v>
       </c>
       <c r="T116" s="1" t="s">
@@ -8341,31 +8529,31 @@
       </c>
     </row>
     <row r="117" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="5" t="s">
+      <c r="A117" t="s">
         <v>225</v>
       </c>
-      <c r="B117" s="5" t="s">
+      <c r="B117" t="s">
         <v>226</v>
       </c>
-      <c r="D117" s="5" t="s">
+      <c r="D117" t="s">
         <v>714</v>
       </c>
-      <c r="E117" s="5" t="s">
+      <c r="E117" t="s">
         <v>236</v>
       </c>
-      <c r="F117" s="5" t="s">
+      <c r="F117" t="s">
         <v>237</v>
       </c>
-      <c r="J117" s="5" t="s">
+      <c r="J117" t="s">
         <v>238</v>
       </c>
       <c r="L117" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="R117" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S117" s="5" t="s">
+      <c r="R117" t="s">
+        <v>24</v>
+      </c>
+      <c r="S117" t="s">
         <v>25</v>
       </c>
       <c r="T117" s="1" t="s">
@@ -8388,31 +8576,31 @@
       </c>
     </row>
     <row r="118" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="5" t="s">
+      <c r="A118" t="s">
         <v>225</v>
       </c>
-      <c r="B118" s="5" t="s">
+      <c r="B118" t="s">
         <v>226</v>
       </c>
-      <c r="D118" s="5">
+      <c r="D118">
         <v>1767</v>
       </c>
-      <c r="E118" s="5" t="s">
+      <c r="E118" t="s">
         <v>717</v>
       </c>
-      <c r="F118" s="5" t="s">
+      <c r="F118" t="s">
         <v>718</v>
       </c>
-      <c r="J118" s="5" t="s">
+      <c r="J118" t="s">
         <v>719</v>
       </c>
       <c r="L118" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="R118" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S118" s="5" t="s">
+      <c r="R118" t="s">
+        <v>24</v>
+      </c>
+      <c r="S118" t="s">
         <v>721</v>
       </c>
       <c r="T118" s="1">
@@ -8432,31 +8620,31 @@
       </c>
     </row>
     <row r="119" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="5" t="s">
+      <c r="A119" t="s">
         <v>225</v>
       </c>
-      <c r="B119" s="5" t="s">
+      <c r="B119" t="s">
         <v>226</v>
       </c>
-      <c r="D119" s="5">
+      <c r="D119">
         <v>1776</v>
       </c>
-      <c r="E119" s="5" t="s">
+      <c r="E119" t="s">
         <v>722</v>
       </c>
-      <c r="F119" s="5" t="s">
+      <c r="F119" t="s">
         <v>98</v>
       </c>
-      <c r="J119" s="5" t="s">
+      <c r="J119" t="s">
         <v>723</v>
       </c>
       <c r="L119" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="R119" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S119" s="5" t="s">
+      <c r="R119" t="s">
+        <v>24</v>
+      </c>
+      <c r="S119" t="s">
         <v>58</v>
       </c>
       <c r="T119" s="1">
@@ -8479,31 +8667,31 @@
       </c>
     </row>
     <row r="120" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="5" t="s">
+      <c r="A120" t="s">
         <v>225</v>
       </c>
-      <c r="B120" s="5" t="s">
+      <c r="B120" t="s">
         <v>226</v>
       </c>
-      <c r="D120" s="5" t="s">
+      <c r="D120" t="s">
         <v>726</v>
       </c>
-      <c r="E120" s="5" t="s">
+      <c r="E120" t="s">
         <v>28</v>
       </c>
-      <c r="F120" s="5" t="s">
+      <c r="F120" t="s">
         <v>29</v>
       </c>
-      <c r="J120" s="5" t="s">
+      <c r="J120" t="s">
         <v>727</v>
       </c>
       <c r="L120" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="R120" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S120" s="5" t="s">
+      <c r="R120" t="s">
+        <v>24</v>
+      </c>
+      <c r="S120" t="s">
         <v>25</v>
       </c>
       <c r="T120" s="1" t="s">
@@ -8520,31 +8708,31 @@
       </c>
     </row>
     <row r="121" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="5" t="s">
+      <c r="A121" t="s">
         <v>225</v>
       </c>
-      <c r="B121" s="5" t="s">
+      <c r="B121" t="s">
         <v>226</v>
       </c>
-      <c r="D121" s="5">
+      <c r="D121">
         <v>1783</v>
       </c>
-      <c r="E121" s="5" t="s">
+      <c r="E121" t="s">
         <v>717</v>
       </c>
-      <c r="F121" s="5" t="s">
+      <c r="F121" t="s">
         <v>718</v>
       </c>
-      <c r="J121" s="5" t="s">
+      <c r="J121" t="s">
         <v>730</v>
       </c>
       <c r="L121" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="R121" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S121" s="5" t="s">
+      <c r="R121" t="s">
+        <v>24</v>
+      </c>
+      <c r="S121" t="s">
         <v>25</v>
       </c>
       <c r="T121" s="1" t="s">
@@ -8567,31 +8755,31 @@
       </c>
     </row>
     <row r="122" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="5" t="s">
+      <c r="A122" t="s">
         <v>240</v>
       </c>
-      <c r="B122" s="5" t="s">
+      <c r="B122" t="s">
         <v>241</v>
       </c>
-      <c r="D122" s="5" t="s">
+      <c r="D122" t="s">
         <v>242</v>
       </c>
-      <c r="E122" s="5" t="s">
+      <c r="E122" t="s">
         <v>28</v>
       </c>
-      <c r="F122" s="5" t="s">
+      <c r="F122" t="s">
         <v>243</v>
       </c>
-      <c r="J122" s="5" t="s">
+      <c r="J122" t="s">
         <v>244</v>
       </c>
       <c r="L122" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="R122" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S122" s="5" t="s">
+      <c r="R122" t="s">
+        <v>24</v>
+      </c>
+      <c r="S122" t="s">
         <v>212</v>
       </c>
       <c r="T122" s="1" t="s">
@@ -8614,37 +8802,37 @@
       </c>
     </row>
     <row r="123" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="5" t="s">
+      <c r="A123" t="s">
         <v>240</v>
       </c>
-      <c r="B123" s="5" t="s">
+      <c r="B123" t="s">
         <v>241</v>
       </c>
-      <c r="D123" s="5" t="s">
+      <c r="D123" t="s">
         <v>741</v>
       </c>
-      <c r="E123" s="5" t="s">
+      <c r="E123" t="s">
         <v>655</v>
       </c>
-      <c r="F123" s="5" t="s">
+      <c r="F123" t="s">
         <v>656</v>
       </c>
-      <c r="H123" s="5" t="s">
+      <c r="H123" t="s">
         <v>742</v>
       </c>
-      <c r="J123" s="5" t="s">
+      <c r="J123" t="s">
         <v>743</v>
       </c>
-      <c r="K123" s="5" t="s">
+      <c r="K123" t="s">
         <v>744</v>
       </c>
       <c r="L123" s="4" t="s">
         <v>745</v>
       </c>
-      <c r="R123" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S123" s="5" t="s">
+      <c r="R123" t="s">
+        <v>24</v>
+      </c>
+      <c r="S123" t="s">
         <v>25</v>
       </c>
       <c r="T123" s="1" t="s">
@@ -8667,34 +8855,34 @@
       </c>
     </row>
     <row r="124" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="5" t="s">
+      <c r="A124" t="s">
         <v>240</v>
       </c>
-      <c r="B124" s="5" t="s">
+      <c r="B124" t="s">
         <v>241</v>
       </c>
-      <c r="D124" s="5" t="s">
+      <c r="D124" t="s">
         <v>747</v>
       </c>
-      <c r="E124" s="5" t="s">
+      <c r="E124" t="s">
         <v>28</v>
       </c>
-      <c r="F124" s="5" t="s">
+      <c r="F124" t="s">
         <v>748</v>
       </c>
-      <c r="H124" s="5" t="s">
+      <c r="H124" t="s">
         <v>749</v>
       </c>
-      <c r="J124" s="5" t="s">
+      <c r="J124" t="s">
         <v>750</v>
       </c>
       <c r="L124" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="R124" s="5" t="s">
+      <c r="R124" t="s">
         <v>407</v>
       </c>
-      <c r="S124" s="5" t="s">
+      <c r="S124" t="s">
         <v>212</v>
       </c>
       <c r="W124" s="1" t="s">
@@ -8708,34 +8896,34 @@
       </c>
     </row>
     <row r="125" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="5" t="s">
+      <c r="A125" t="s">
         <v>240</v>
       </c>
-      <c r="B125" s="5" t="s">
+      <c r="B125" t="s">
         <v>241</v>
       </c>
-      <c r="D125" s="5" t="s">
+      <c r="D125" t="s">
         <v>752</v>
       </c>
-      <c r="E125" s="5" t="s">
+      <c r="E125" t="s">
         <v>394</v>
       </c>
-      <c r="F125" s="5" t="s">
+      <c r="F125" t="s">
         <v>32</v>
       </c>
-      <c r="H125" s="5" t="s">
+      <c r="H125" t="s">
         <v>753</v>
       </c>
-      <c r="J125" s="5" t="s">
+      <c r="J125" t="s">
         <v>754</v>
       </c>
       <c r="L125" s="4" t="s">
         <v>755</v>
       </c>
-      <c r="R125" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S125" s="5" t="s">
+      <c r="R125" t="s">
+        <v>24</v>
+      </c>
+      <c r="S125" t="s">
         <v>25</v>
       </c>
       <c r="T125" s="1" t="s">
@@ -8752,34 +8940,34 @@
       </c>
     </row>
     <row r="126" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="5" t="s">
+      <c r="A126" t="s">
         <v>240</v>
       </c>
-      <c r="B126" s="5" t="s">
+      <c r="B126" t="s">
         <v>241</v>
       </c>
-      <c r="D126" s="5" t="s">
+      <c r="D126" t="s">
         <v>614</v>
       </c>
-      <c r="E126" s="5" t="s">
+      <c r="E126" t="s">
         <v>28</v>
       </c>
-      <c r="F126" s="5" t="s">
+      <c r="F126" t="s">
         <v>29</v>
       </c>
-      <c r="H126" s="5" t="s">
+      <c r="H126" t="s">
         <v>756</v>
       </c>
-      <c r="J126" s="5" t="s">
+      <c r="J126" t="s">
         <v>757</v>
       </c>
       <c r="L126" s="4" t="s">
         <v>758</v>
       </c>
-      <c r="R126" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S126" s="5" t="s">
+      <c r="R126" t="s">
+        <v>24</v>
+      </c>
+      <c r="S126" t="s">
         <v>58</v>
       </c>
       <c r="T126" s="1" t="s">
@@ -8802,34 +8990,34 @@
       </c>
     </row>
     <row r="127" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="5" t="s">
+      <c r="A127" t="s">
         <v>240</v>
       </c>
-      <c r="B127" s="5" t="s">
+      <c r="B127" t="s">
         <v>241</v>
       </c>
-      <c r="D127" s="5" t="s">
+      <c r="D127" t="s">
         <v>760</v>
       </c>
-      <c r="E127" s="5" t="s">
+      <c r="E127" t="s">
         <v>285</v>
       </c>
-      <c r="F127" s="5" t="s">
+      <c r="F127" t="s">
         <v>761</v>
       </c>
-      <c r="H127" s="5" t="s">
+      <c r="H127" t="s">
         <v>762</v>
       </c>
-      <c r="J127" s="5" t="s">
+      <c r="J127" t="s">
         <v>763</v>
       </c>
       <c r="L127" s="4" t="s">
         <v>764</v>
       </c>
-      <c r="R127" s="5" t="s">
+      <c r="R127" t="s">
         <v>407</v>
       </c>
-      <c r="S127" s="5" t="s">
+      <c r="S127" t="s">
         <v>212</v>
       </c>
       <c r="W127" s="1" t="s">
@@ -8849,7 +9037,6 @@
       <c r="B128" t="s">
         <v>247</v>
       </c>
-      <c r="C128"/>
       <c r="D128" t="s">
         <v>248</v>
       </c>
@@ -8859,21 +9046,12 @@
       <c r="F128" t="s">
         <v>32</v>
       </c>
-      <c r="G128"/>
-      <c r="H128"/>
-      <c r="I128"/>
       <c r="J128" t="s">
         <v>249</v>
       </c>
-      <c r="K128"/>
       <c r="L128" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="M128"/>
-      <c r="N128"/>
-      <c r="O128"/>
-      <c r="P128"/>
-      <c r="Q128"/>
       <c r="R128" t="s">
         <v>24</v>
       </c>
@@ -8906,7 +9084,6 @@
       <c r="B129" t="s">
         <v>247</v>
       </c>
-      <c r="C129"/>
       <c r="D129" t="s">
         <v>96</v>
       </c>
@@ -8916,23 +9093,15 @@
       <c r="F129" t="s">
         <v>29</v>
       </c>
-      <c r="G129"/>
       <c r="H129" t="s">
         <v>767</v>
       </c>
-      <c r="I129"/>
       <c r="J129" t="s">
         <v>615</v>
       </c>
-      <c r="K129"/>
       <c r="L129" s="4" t="s">
         <v>768</v>
       </c>
-      <c r="M129"/>
-      <c r="N129"/>
-      <c r="O129"/>
-      <c r="P129"/>
-      <c r="Q129"/>
       <c r="R129" t="s">
         <v>769</v>
       </c>
@@ -8965,7 +9134,6 @@
       <c r="B130" t="s">
         <v>247</v>
       </c>
-      <c r="C130"/>
       <c r="D130" t="s">
         <v>771</v>
       </c>
@@ -8975,21 +9143,12 @@
       <c r="F130" t="s">
         <v>772</v>
       </c>
-      <c r="G130"/>
-      <c r="H130"/>
-      <c r="I130"/>
       <c r="J130" t="s">
         <v>773</v>
       </c>
-      <c r="K130"/>
       <c r="L130" s="4" t="s">
         <v>774</v>
       </c>
-      <c r="M130"/>
-      <c r="N130"/>
-      <c r="O130"/>
-      <c r="P130"/>
-      <c r="Q130"/>
       <c r="R130" t="s">
         <v>24</v>
       </c>
@@ -9022,7 +9181,6 @@
       <c r="B131" t="s">
         <v>247</v>
       </c>
-      <c r="C131"/>
       <c r="D131" t="s">
         <v>474</v>
       </c>
@@ -9032,21 +9190,12 @@
       <c r="F131" t="s">
         <v>262</v>
       </c>
-      <c r="G131"/>
-      <c r="H131"/>
-      <c r="I131"/>
       <c r="J131" t="s">
         <v>775</v>
       </c>
-      <c r="K131"/>
       <c r="L131" s="4" t="s">
         <v>776</v>
       </c>
-      <c r="M131"/>
-      <c r="N131"/>
-      <c r="O131"/>
-      <c r="P131"/>
-      <c r="Q131"/>
       <c r="R131" t="s">
         <v>769</v>
       </c>
@@ -9079,7 +9228,6 @@
       <c r="B132" t="s">
         <v>247</v>
       </c>
-      <c r="C132"/>
       <c r="D132" t="s">
         <v>649</v>
       </c>
@@ -9089,21 +9237,12 @@
       <c r="F132" t="s">
         <v>779</v>
       </c>
-      <c r="G132"/>
-      <c r="H132"/>
-      <c r="I132"/>
       <c r="J132" t="s">
         <v>780</v>
       </c>
-      <c r="K132"/>
       <c r="L132" s="4" t="s">
         <v>781</v>
       </c>
-      <c r="M132"/>
-      <c r="N132"/>
-      <c r="O132"/>
-      <c r="P132"/>
-      <c r="Q132"/>
       <c r="R132" t="s">
         <v>24</v>
       </c>
@@ -9136,7 +9275,6 @@
       <c r="B133" t="s">
         <v>247</v>
       </c>
-      <c r="C133"/>
       <c r="D133" t="s">
         <v>377</v>
       </c>
@@ -9146,21 +9284,12 @@
       <c r="F133" t="s">
         <v>461</v>
       </c>
-      <c r="G133"/>
-      <c r="H133"/>
-      <c r="I133"/>
       <c r="J133" t="s">
         <v>784</v>
       </c>
-      <c r="K133"/>
       <c r="L133" s="4" t="s">
         <v>785</v>
       </c>
-      <c r="M133"/>
-      <c r="N133"/>
-      <c r="O133"/>
-      <c r="P133"/>
-      <c r="Q133"/>
       <c r="R133" t="s">
         <v>24</v>
       </c>
@@ -9193,7 +9322,6 @@
       <c r="B134" t="s">
         <v>252</v>
       </c>
-      <c r="C134"/>
       <c r="D134" t="s">
         <v>253</v>
       </c>
@@ -9203,23 +9331,15 @@
       <c r="F134" t="s">
         <v>255</v>
       </c>
-      <c r="G134"/>
-      <c r="H134"/>
-      <c r="I134"/>
       <c r="J134" t="s">
         <v>256</v>
       </c>
-      <c r="K134"/>
       <c r="L134" s="4" t="s">
         <v>257</v>
       </c>
       <c r="M134" t="s">
         <v>787</v>
       </c>
-      <c r="N134"/>
-      <c r="O134"/>
-      <c r="P134"/>
-      <c r="Q134"/>
       <c r="R134" t="s">
         <v>24</v>
       </c>
@@ -9252,7 +9372,6 @@
       <c r="B135" t="s">
         <v>252</v>
       </c>
-      <c r="C135"/>
       <c r="D135" t="s">
         <v>253</v>
       </c>
@@ -9262,9 +9381,6 @@
       <c r="F135" t="s">
         <v>788</v>
       </c>
-      <c r="G135"/>
-      <c r="H135"/>
-      <c r="I135"/>
       <c r="J135" t="s">
         <v>789</v>
       </c>
@@ -9277,10 +9393,6 @@
       <c r="M135" t="s">
         <v>787</v>
       </c>
-      <c r="N135"/>
-      <c r="O135"/>
-      <c r="P135"/>
-      <c r="Q135"/>
       <c r="R135" t="s">
         <v>24</v>
       </c>
@@ -9313,7 +9425,6 @@
       <c r="B136" t="s">
         <v>252</v>
       </c>
-      <c r="C136"/>
       <c r="D136" t="s">
         <v>253</v>
       </c>
@@ -9323,9 +9434,6 @@
       <c r="F136" t="s">
         <v>793</v>
       </c>
-      <c r="G136"/>
-      <c r="H136"/>
-      <c r="I136"/>
       <c r="J136" t="s">
         <v>794</v>
       </c>
@@ -9338,10 +9446,6 @@
       <c r="M136" t="s">
         <v>787</v>
       </c>
-      <c r="N136"/>
-      <c r="O136"/>
-      <c r="P136"/>
-      <c r="Q136"/>
       <c r="R136" t="s">
         <v>24</v>
       </c>
@@ -9374,7 +9478,6 @@
       <c r="B137" t="s">
         <v>252</v>
       </c>
-      <c r="C137"/>
       <c r="D137" t="s">
         <v>253</v>
       </c>
@@ -9384,9 +9487,6 @@
       <c r="F137" t="s">
         <v>798</v>
       </c>
-      <c r="G137"/>
-      <c r="H137"/>
-      <c r="I137"/>
       <c r="J137" t="s">
         <v>799</v>
       </c>
@@ -9399,10 +9499,6 @@
       <c r="M137" t="s">
         <v>787</v>
       </c>
-      <c r="N137"/>
-      <c r="O137"/>
-      <c r="P137"/>
-      <c r="Q137"/>
       <c r="R137" t="s">
         <v>24</v>
       </c>
@@ -9429,34 +9525,34 @@
       </c>
     </row>
     <row r="138" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="5" t="s">
+      <c r="A138" t="s">
         <v>259</v>
       </c>
-      <c r="B138" s="5" t="s">
+      <c r="B138" t="s">
         <v>260</v>
       </c>
-      <c r="C138" s="5" t="s">
+      <c r="C138" t="s">
         <v>802</v>
       </c>
-      <c r="D138" s="5">
+      <c r="D138">
         <v>1780</v>
       </c>
-      <c r="E138" s="5" t="s">
+      <c r="E138" t="s">
         <v>261</v>
       </c>
-      <c r="F138" s="5" t="s">
+      <c r="F138" t="s">
         <v>262</v>
       </c>
-      <c r="J138" s="5" t="s">
+      <c r="J138" t="s">
         <v>263</v>
       </c>
-      <c r="L138" s="11" t="s">
+      <c r="L138" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="R138" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S138" s="5" t="s">
+      <c r="R138" t="s">
+        <v>24</v>
+      </c>
+      <c r="S138" t="s">
         <v>101</v>
       </c>
       <c r="T138" s="1">
@@ -9479,34 +9575,34 @@
       </c>
     </row>
     <row r="139" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="5" t="s">
+      <c r="A139" t="s">
         <v>259</v>
       </c>
-      <c r="B139" s="5" t="s">
+      <c r="B139" t="s">
         <v>260</v>
       </c>
-      <c r="C139" s="5" t="s">
+      <c r="C139" t="s">
         <v>802</v>
       </c>
-      <c r="D139" s="5">
+      <c r="D139">
         <v>1782</v>
       </c>
-      <c r="E139" s="5" t="s">
+      <c r="E139" t="s">
         <v>499</v>
       </c>
-      <c r="F139" s="5" t="s">
+      <c r="F139" t="s">
         <v>483</v>
       </c>
-      <c r="J139" s="5" t="s">
+      <c r="J139" t="s">
         <v>803</v>
       </c>
-      <c r="L139" s="11" t="s">
+      <c r="L139" s="10" t="s">
         <v>804</v>
       </c>
-      <c r="R139" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S139" s="5" t="s">
+      <c r="R139" t="s">
+        <v>24</v>
+      </c>
+      <c r="S139" t="s">
         <v>25</v>
       </c>
       <c r="T139" s="1">
@@ -9529,34 +9625,34 @@
       </c>
     </row>
     <row r="140" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="5" t="s">
+      <c r="A140" t="s">
         <v>259</v>
       </c>
-      <c r="B140" s="5" t="s">
+      <c r="B140" t="s">
         <v>260</v>
       </c>
-      <c r="C140" s="5" t="s">
+      <c r="C140" t="s">
         <v>802</v>
       </c>
-      <c r="D140" s="5">
+      <c r="D140">
         <v>1783</v>
       </c>
-      <c r="E140" s="5" t="s">
+      <c r="E140" t="s">
         <v>28</v>
       </c>
-      <c r="F140" s="5" t="s">
+      <c r="F140" t="s">
         <v>29</v>
       </c>
-      <c r="J140" s="5" t="s">
+      <c r="J140" t="s">
         <v>805</v>
       </c>
-      <c r="L140" s="11" t="s">
+      <c r="L140" s="10" t="s">
         <v>806</v>
       </c>
-      <c r="R140" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S140" s="5" t="s">
+      <c r="R140" t="s">
+        <v>24</v>
+      </c>
+      <c r="S140" t="s">
         <v>25</v>
       </c>
       <c r="T140" s="1">
@@ -9579,34 +9675,34 @@
       </c>
     </row>
     <row r="141" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="5" t="s">
+      <c r="A141" t="s">
         <v>259</v>
       </c>
-      <c r="B141" s="5" t="s">
+      <c r="B141" t="s">
         <v>260</v>
       </c>
-      <c r="C141" s="5" t="s">
+      <c r="C141" t="s">
         <v>802</v>
       </c>
-      <c r="D141" s="5">
+      <c r="D141">
         <v>1795</v>
       </c>
-      <c r="E141" s="5" t="s">
+      <c r="E141" t="s">
         <v>506</v>
       </c>
-      <c r="F141" s="5" t="s">
+      <c r="F141" t="s">
         <v>807</v>
       </c>
-      <c r="J141" s="5" t="s">
+      <c r="J141" t="s">
         <v>808</v>
       </c>
-      <c r="L141" s="11" t="s">
+      <c r="L141" s="10" t="s">
         <v>809</v>
       </c>
-      <c r="R141" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S141" s="5" t="s">
+      <c r="R141" t="s">
+        <v>24</v>
+      </c>
+      <c r="S141" t="s">
         <v>101</v>
       </c>
       <c r="T141" s="1">
@@ -9623,34 +9719,34 @@
       </c>
     </row>
     <row r="142" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="5" t="s">
+      <c r="A142" t="s">
         <v>259</v>
       </c>
-      <c r="B142" s="5" t="s">
+      <c r="B142" t="s">
         <v>260</v>
       </c>
-      <c r="C142" s="5" t="s">
+      <c r="C142" t="s">
         <v>802</v>
       </c>
-      <c r="D142" s="5">
+      <c r="D142">
         <v>1780</v>
       </c>
-      <c r="E142" s="5" t="s">
+      <c r="E142" t="s">
         <v>261</v>
       </c>
-      <c r="F142" s="5" t="s">
+      <c r="F142" t="s">
         <v>262</v>
       </c>
-      <c r="J142" s="5" t="s">
+      <c r="J142" t="s">
         <v>810</v>
       </c>
-      <c r="L142" s="11" t="s">
+      <c r="L142" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="R142" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S142" s="5" t="s">
+      <c r="R142" t="s">
+        <v>24</v>
+      </c>
+      <c r="S142" t="s">
         <v>101</v>
       </c>
       <c r="T142" s="1">
@@ -9673,34 +9769,34 @@
       </c>
     </row>
     <row r="143" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="5" t="s">
+      <c r="A143" t="s">
         <v>259</v>
       </c>
-      <c r="B143" s="5" t="s">
+      <c r="B143" t="s">
         <v>260</v>
       </c>
-      <c r="C143" s="5" t="s">
+      <c r="C143" t="s">
         <v>802</v>
       </c>
-      <c r="D143" s="5">
+      <c r="D143">
         <v>1770</v>
       </c>
-      <c r="E143" s="5" t="s">
+      <c r="E143" t="s">
         <v>655</v>
       </c>
-      <c r="F143" s="5" t="s">
+      <c r="F143" t="s">
         <v>656</v>
       </c>
-      <c r="J143" s="5" t="s">
+      <c r="J143" t="s">
         <v>812</v>
       </c>
-      <c r="L143" s="11" t="s">
+      <c r="L143" s="10" t="s">
         <v>813</v>
       </c>
-      <c r="R143" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S143" s="5" t="s">
+      <c r="R143" t="s">
+        <v>24</v>
+      </c>
+      <c r="S143" t="s">
         <v>25</v>
       </c>
       <c r="T143" s="1">
@@ -9723,34 +9819,34 @@
       </c>
     </row>
     <row r="144" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="5" t="s">
+      <c r="A144" t="s">
         <v>259</v>
       </c>
-      <c r="B144" s="5" t="s">
+      <c r="B144" t="s">
         <v>260</v>
       </c>
-      <c r="C144" s="5" t="s">
+      <c r="C144" t="s">
         <v>802</v>
       </c>
-      <c r="D144" s="5">
+      <c r="D144">
         <v>1781</v>
       </c>
-      <c r="E144" s="5" t="s">
+      <c r="E144" t="s">
         <v>261</v>
       </c>
-      <c r="F144" s="5" t="s">
+      <c r="F144" t="s">
         <v>262</v>
       </c>
-      <c r="J144" s="5" t="s">
+      <c r="J144" t="s">
         <v>814</v>
       </c>
-      <c r="L144" s="11" t="s">
+      <c r="L144" s="10" t="s">
         <v>815</v>
       </c>
-      <c r="R144" s="5" t="s">
+      <c r="R144" t="s">
         <v>467</v>
       </c>
-      <c r="S144" s="5" t="s">
+      <c r="S144" t="s">
         <v>101</v>
       </c>
       <c r="T144" s="1">
@@ -9770,34 +9866,34 @@
       </c>
     </row>
     <row r="145" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="5" t="s">
+      <c r="A145" t="s">
         <v>259</v>
       </c>
-      <c r="B145" s="5" t="s">
+      <c r="B145" t="s">
         <v>260</v>
       </c>
-      <c r="C145" s="5" t="s">
+      <c r="C145" t="s">
         <v>802</v>
       </c>
-      <c r="D145" s="5" t="s">
+      <c r="D145" t="s">
         <v>816</v>
       </c>
-      <c r="E145" s="5" t="s">
+      <c r="E145" t="s">
         <v>817</v>
       </c>
-      <c r="F145" s="5" t="s">
+      <c r="F145" t="s">
         <v>204</v>
       </c>
-      <c r="J145" s="5" t="s">
+      <c r="J145" t="s">
         <v>818</v>
       </c>
-      <c r="L145" s="11" t="s">
+      <c r="L145" s="10" t="s">
         <v>819</v>
       </c>
-      <c r="R145" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S145" s="5" t="s">
+      <c r="R145" t="s">
+        <v>24</v>
+      </c>
+      <c r="S145" t="s">
         <v>721</v>
       </c>
       <c r="W145" s="1">
@@ -9817,7 +9913,6 @@
       <c r="B146" t="s">
         <v>265</v>
       </c>
-      <c r="C146"/>
       <c r="D146" t="s">
         <v>148</v>
       </c>
@@ -9827,21 +9922,12 @@
       <c r="F146" t="s">
         <v>266</v>
       </c>
-      <c r="G146"/>
-      <c r="H146"/>
-      <c r="I146"/>
       <c r="J146" t="s">
         <v>267</v>
       </c>
-      <c r="K146"/>
       <c r="L146" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="M146"/>
-      <c r="N146"/>
-      <c r="O146"/>
-      <c r="P146"/>
-      <c r="Q146"/>
       <c r="R146" t="s">
         <v>24</v>
       </c>
@@ -9874,7 +9960,6 @@
       <c r="B147" t="s">
         <v>265</v>
       </c>
-      <c r="C147"/>
       <c r="D147" t="s">
         <v>820</v>
       </c>
@@ -9884,9 +9969,6 @@
       <c r="F147" t="s">
         <v>65</v>
       </c>
-      <c r="G147"/>
-      <c r="H147"/>
-      <c r="I147"/>
       <c r="J147" t="s">
         <v>821</v>
       </c>
@@ -9896,11 +9978,6 @@
       <c r="L147" s="4" t="s">
         <v>823</v>
       </c>
-      <c r="M147"/>
-      <c r="N147"/>
-      <c r="O147"/>
-      <c r="P147"/>
-      <c r="Q147"/>
       <c r="R147" t="s">
         <v>24</v>
       </c>
@@ -9933,7 +10010,6 @@
       <c r="B148" t="s">
         <v>265</v>
       </c>
-      <c r="C148"/>
       <c r="D148" t="s">
         <v>824</v>
       </c>
@@ -9943,21 +10019,12 @@
       <c r="F148" t="s">
         <v>262</v>
       </c>
-      <c r="G148"/>
-      <c r="H148"/>
-      <c r="I148"/>
       <c r="J148" t="s">
         <v>825</v>
       </c>
-      <c r="K148"/>
       <c r="L148" s="4" t="s">
         <v>826</v>
       </c>
-      <c r="M148"/>
-      <c r="N148"/>
-      <c r="O148"/>
-      <c r="P148"/>
-      <c r="Q148"/>
       <c r="R148" t="s">
         <v>24</v>
       </c>
@@ -9990,7 +10057,6 @@
       <c r="B149" t="s">
         <v>265</v>
       </c>
-      <c r="C149"/>
       <c r="D149">
         <v>1777</v>
       </c>
@@ -10000,21 +10066,12 @@
       <c r="F149" t="s">
         <v>828</v>
       </c>
-      <c r="G149"/>
-      <c r="H149"/>
-      <c r="I149"/>
       <c r="J149" t="s">
         <v>829</v>
       </c>
-      <c r="K149"/>
       <c r="L149" s="4" t="s">
         <v>830</v>
       </c>
-      <c r="M149"/>
-      <c r="N149"/>
-      <c r="O149"/>
-      <c r="P149"/>
-      <c r="Q149"/>
       <c r="R149" t="s">
         <v>24</v>
       </c>
@@ -10041,31 +10098,31 @@
       </c>
     </row>
     <row r="150" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="5" t="s">
+      <c r="A150" t="s">
         <v>269</v>
       </c>
-      <c r="B150" s="5" t="s">
+      <c r="B150" t="s">
         <v>270</v>
       </c>
-      <c r="D150" s="5">
+      <c r="D150">
         <v>1769</v>
       </c>
-      <c r="E150" s="5" t="s">
+      <c r="E150" t="s">
         <v>28</v>
       </c>
-      <c r="F150" s="5" t="s">
+      <c r="F150" t="s">
         <v>29</v>
       </c>
-      <c r="J150" s="5" t="s">
+      <c r="J150" t="s">
         <v>271</v>
       </c>
-      <c r="L150" s="11" t="s">
+      <c r="L150" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="R150" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S150" s="5" t="s">
+      <c r="R150" t="s">
+        <v>24</v>
+      </c>
+      <c r="S150" t="s">
         <v>25</v>
       </c>
       <c r="T150" s="1">
@@ -10088,31 +10145,31 @@
       </c>
     </row>
     <row r="151" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="5" t="s">
+      <c r="A151" t="s">
         <v>269</v>
       </c>
-      <c r="B151" s="5" t="s">
+      <c r="B151" t="s">
         <v>270</v>
       </c>
-      <c r="D151" s="5">
+      <c r="D151">
         <v>1773</v>
       </c>
-      <c r="E151" s="5" t="s">
+      <c r="E151" t="s">
         <v>273</v>
       </c>
-      <c r="F151" s="5" t="s">
+      <c r="F151" t="s">
         <v>274</v>
       </c>
-      <c r="J151" s="5" t="s">
+      <c r="J151" t="s">
         <v>275</v>
       </c>
-      <c r="L151" s="11" t="s">
+      <c r="L151" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="R151" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S151" s="5" t="s">
+      <c r="R151" t="s">
+        <v>24</v>
+      </c>
+      <c r="S151" t="s">
         <v>25</v>
       </c>
       <c r="T151" s="1">
@@ -10135,31 +10192,31 @@
       </c>
     </row>
     <row r="152" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="5" t="s">
+      <c r="A152" t="s">
         <v>269</v>
       </c>
-      <c r="B152" s="5" t="s">
+      <c r="B152" t="s">
         <v>270</v>
       </c>
-      <c r="D152" s="5">
+      <c r="D152">
         <v>1775</v>
       </c>
-      <c r="E152" s="5" t="s">
+      <c r="E152" t="s">
         <v>28</v>
       </c>
-      <c r="F152" s="5" t="s">
+      <c r="F152" t="s">
         <v>29</v>
       </c>
-      <c r="J152" s="5" t="s">
+      <c r="J152" t="s">
         <v>277</v>
       </c>
-      <c r="L152" s="11" t="s">
+      <c r="L152" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="R152" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S152" s="5" t="s">
+      <c r="R152" t="s">
+        <v>24</v>
+      </c>
+      <c r="S152" t="s">
         <v>25</v>
       </c>
       <c r="T152" s="1">
@@ -10182,31 +10239,31 @@
       </c>
     </row>
     <row r="153" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="5" t="s">
+      <c r="A153" t="s">
         <v>269</v>
       </c>
-      <c r="B153" s="5" t="s">
+      <c r="B153" t="s">
         <v>270</v>
       </c>
-      <c r="D153" s="5">
+      <c r="D153">
         <v>1783</v>
       </c>
-      <c r="E153" s="5" t="s">
+      <c r="E153" t="s">
         <v>28</v>
       </c>
-      <c r="F153" s="5" t="s">
+      <c r="F153" t="s">
         <v>29</v>
       </c>
-      <c r="J153" s="5" t="s">
+      <c r="J153" t="s">
         <v>279</v>
       </c>
-      <c r="L153" s="11" t="s">
+      <c r="L153" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="R153" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S153" s="5" t="s">
+      <c r="R153" t="s">
+        <v>24</v>
+      </c>
+      <c r="S153" t="s">
         <v>25</v>
       </c>
       <c r="T153" s="1">
@@ -10229,31 +10286,31 @@
       </c>
     </row>
     <row r="154" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="5" t="s">
+      <c r="A154" t="s">
         <v>269</v>
       </c>
-      <c r="B154" s="5" t="s">
+      <c r="B154" t="s">
         <v>270</v>
       </c>
-      <c r="D154" s="5">
+      <c r="D154">
         <v>1760</v>
       </c>
-      <c r="E154" s="5" t="s">
+      <c r="E154" t="s">
         <v>28</v>
       </c>
-      <c r="F154" s="5" t="s">
+      <c r="F154" t="s">
         <v>29</v>
       </c>
-      <c r="J154" s="5" t="s">
+      <c r="J154" t="s">
         <v>733</v>
       </c>
       <c r="L154" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="R154" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S154" s="5" t="s">
+      <c r="R154" t="s">
+        <v>24</v>
+      </c>
+      <c r="S154" t="s">
         <v>25</v>
       </c>
       <c r="T154" s="1">
@@ -10276,31 +10333,31 @@
       </c>
     </row>
     <row r="155" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="5" t="s">
+      <c r="A155" t="s">
         <v>269</v>
       </c>
-      <c r="B155" s="5" t="s">
+      <c r="B155" t="s">
         <v>270</v>
       </c>
-      <c r="D155" s="5" t="s">
+      <c r="D155" t="s">
         <v>202</v>
       </c>
-      <c r="E155" s="5" t="s">
+      <c r="E155" t="s">
         <v>28</v>
       </c>
-      <c r="F155" s="5" t="s">
+      <c r="F155" t="s">
         <v>29</v>
       </c>
-      <c r="J155" s="5" t="s">
+      <c r="J155" t="s">
         <v>735</v>
       </c>
       <c r="L155" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="R155" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S155" s="5" t="s">
+      <c r="R155" t="s">
+        <v>24</v>
+      </c>
+      <c r="S155" t="s">
         <v>101</v>
       </c>
       <c r="T155" s="1" t="s">
@@ -10329,7 +10386,6 @@
       <c r="B156" t="s">
         <v>281</v>
       </c>
-      <c r="C156"/>
       <c r="D156" t="s">
         <v>451</v>
       </c>
@@ -10339,21 +10395,12 @@
       <c r="F156" t="s">
         <v>29</v>
       </c>
-      <c r="G156"/>
-      <c r="H156"/>
-      <c r="I156"/>
       <c r="J156" t="s">
         <v>282</v>
       </c>
-      <c r="K156"/>
       <c r="L156" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="M156"/>
-      <c r="N156"/>
-      <c r="O156"/>
-      <c r="P156"/>
-      <c r="Q156"/>
       <c r="R156" t="s">
         <v>24</v>
       </c>
@@ -10386,7 +10433,6 @@
       <c r="B157" t="s">
         <v>281</v>
       </c>
-      <c r="C157"/>
       <c r="D157" t="s">
         <v>284</v>
       </c>
@@ -10396,21 +10442,12 @@
       <c r="F157" t="s">
         <v>286</v>
       </c>
-      <c r="G157"/>
-      <c r="H157"/>
-      <c r="I157"/>
       <c r="J157" t="s">
         <v>287</v>
       </c>
-      <c r="K157"/>
       <c r="L157" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="M157"/>
-      <c r="N157"/>
-      <c r="O157"/>
-      <c r="P157"/>
-      <c r="Q157"/>
       <c r="R157" t="s">
         <v>53</v>
       </c>
@@ -10443,7 +10480,6 @@
       <c r="B158" t="s">
         <v>281</v>
       </c>
-      <c r="C158"/>
       <c r="D158" t="s">
         <v>831</v>
       </c>
@@ -10453,21 +10489,12 @@
       <c r="F158" t="s">
         <v>29</v>
       </c>
-      <c r="G158"/>
-      <c r="H158"/>
-      <c r="I158"/>
       <c r="J158" t="s">
         <v>290</v>
       </c>
-      <c r="K158"/>
       <c r="L158" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="M158"/>
-      <c r="N158"/>
-      <c r="O158"/>
-      <c r="P158"/>
-      <c r="Q158"/>
       <c r="R158" t="s">
         <v>24</v>
       </c>
@@ -10500,7 +10527,6 @@
       <c r="B159" t="s">
         <v>281</v>
       </c>
-      <c r="C159"/>
       <c r="D159" t="s">
         <v>832</v>
       </c>
@@ -10510,21 +10536,12 @@
       <c r="F159" t="s">
         <v>293</v>
       </c>
-      <c r="G159"/>
-      <c r="H159"/>
-      <c r="I159"/>
       <c r="J159" t="s">
         <v>833</v>
       </c>
-      <c r="K159"/>
       <c r="L159" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="M159"/>
-      <c r="N159"/>
-      <c r="O159"/>
-      <c r="P159"/>
-      <c r="Q159"/>
       <c r="R159" t="s">
         <v>24</v>
       </c>
@@ -10557,7 +10574,6 @@
       <c r="B160" t="s">
         <v>281</v>
       </c>
-      <c r="C160"/>
       <c r="D160" t="s">
         <v>820</v>
       </c>
@@ -10567,21 +10583,12 @@
       <c r="F160" t="s">
         <v>29</v>
       </c>
-      <c r="G160"/>
-      <c r="H160"/>
-      <c r="I160"/>
       <c r="J160" t="s">
         <v>295</v>
       </c>
-      <c r="K160"/>
       <c r="L160" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="M160"/>
-      <c r="N160"/>
-      <c r="O160"/>
-      <c r="P160"/>
-      <c r="Q160"/>
       <c r="R160" t="s">
         <v>24</v>
       </c>
@@ -10614,7 +10621,6 @@
       <c r="B161" t="s">
         <v>281</v>
       </c>
-      <c r="C161"/>
       <c r="D161" t="s">
         <v>460</v>
       </c>
@@ -10624,21 +10630,12 @@
       <c r="F161" t="s">
         <v>29</v>
       </c>
-      <c r="G161"/>
-      <c r="H161"/>
-      <c r="I161"/>
       <c r="J161" t="s">
         <v>834</v>
       </c>
-      <c r="K161"/>
       <c r="L161" s="4" t="s">
         <v>835</v>
       </c>
-      <c r="M161"/>
-      <c r="N161"/>
-      <c r="O161"/>
-      <c r="P161"/>
-      <c r="Q161"/>
       <c r="R161" t="s">
         <v>24</v>
       </c>
@@ -10671,7 +10668,6 @@
       <c r="B162" t="s">
         <v>281</v>
       </c>
-      <c r="C162"/>
       <c r="D162" t="s">
         <v>202</v>
       </c>
@@ -10681,21 +10677,12 @@
       <c r="F162" t="s">
         <v>836</v>
       </c>
-      <c r="G162"/>
-      <c r="H162"/>
-      <c r="I162"/>
       <c r="J162" t="s">
         <v>837</v>
       </c>
-      <c r="K162"/>
       <c r="L162" s="4" t="s">
         <v>838</v>
       </c>
-      <c r="M162"/>
-      <c r="N162"/>
-      <c r="O162"/>
-      <c r="P162"/>
-      <c r="Q162"/>
       <c r="R162" t="s">
         <v>24</v>
       </c>
@@ -10728,7 +10715,6 @@
       <c r="B163" t="s">
         <v>281</v>
       </c>
-      <c r="C163"/>
       <c r="D163">
         <v>1777</v>
       </c>
@@ -10738,21 +10724,12 @@
       <c r="F163" t="s">
         <v>839</v>
       </c>
-      <c r="G163"/>
-      <c r="H163"/>
-      <c r="I163"/>
       <c r="J163" t="s">
         <v>840</v>
       </c>
-      <c r="K163"/>
       <c r="L163" s="4" t="s">
         <v>841</v>
       </c>
-      <c r="M163"/>
-      <c r="N163"/>
-      <c r="O163"/>
-      <c r="P163"/>
-      <c r="Q163"/>
       <c r="R163" t="s">
         <v>53</v>
       </c>
@@ -10779,34 +10756,34 @@
       </c>
     </row>
     <row r="164" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="5" t="s">
+      <c r="A164" t="s">
         <v>297</v>
       </c>
-      <c r="B164" s="5" t="s">
+      <c r="B164" t="s">
         <v>298</v>
       </c>
-      <c r="D164" s="5" t="s">
+      <c r="D164" t="s">
         <v>299</v>
       </c>
-      <c r="E164" s="5" t="s">
+      <c r="E164" t="s">
         <v>135</v>
       </c>
-      <c r="F164" s="5" t="s">
+      <c r="F164" t="s">
         <v>151</v>
       </c>
-      <c r="J164" s="5" t="s">
+      <c r="J164" t="s">
         <v>300</v>
       </c>
-      <c r="K164" s="5" t="s">
+      <c r="K164" t="s">
         <v>301</v>
       </c>
-      <c r="L164" s="11" t="s">
+      <c r="L164" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="R164" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S164" s="5" t="s">
+      <c r="R164" t="s">
+        <v>24</v>
+      </c>
+      <c r="S164" t="s">
         <v>303</v>
       </c>
       <c r="T164" s="1">
@@ -10829,37 +10806,37 @@
       </c>
     </row>
     <row r="165" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="5" t="s">
+      <c r="A165" t="s">
         <v>297</v>
       </c>
-      <c r="B165" s="5" t="s">
+      <c r="B165" t="s">
         <v>298</v>
       </c>
-      <c r="D165" s="5" t="s">
+      <c r="D165" t="s">
         <v>248</v>
       </c>
-      <c r="E165" s="5" t="s">
+      <c r="E165" t="s">
         <v>86</v>
       </c>
-      <c r="F165" s="5" t="s">
+      <c r="F165" t="s">
         <v>87</v>
       </c>
-      <c r="H165" s="5" t="s">
+      <c r="H165" t="s">
         <v>842</v>
       </c>
-      <c r="J165" s="5" t="s">
+      <c r="J165" t="s">
         <v>843</v>
       </c>
-      <c r="K165" s="5" t="s">
+      <c r="K165" t="s">
         <v>844</v>
       </c>
-      <c r="L165" s="11" t="s">
+      <c r="L165" s="10" t="s">
         <v>845</v>
       </c>
-      <c r="R165" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S165" s="5" t="s">
+      <c r="R165" t="s">
+        <v>24</v>
+      </c>
+      <c r="S165" t="s">
         <v>25</v>
       </c>
       <c r="T165" s="1">
@@ -10882,10 +10859,10 @@
       </c>
     </row>
     <row r="166" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L166" s="11"/>
+      <c r="L166" s="10"/>
     </row>
     <row r="167" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L167" s="11"/>
+      <c r="L167" s="10"/>
     </row>
     <row r="168" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
@@ -10894,7 +10871,6 @@
       <c r="B168" t="s">
         <v>305</v>
       </c>
-      <c r="C168"/>
       <c r="D168" t="s">
         <v>578</v>
       </c>
@@ -10904,9 +10880,6 @@
       <c r="F168" t="s">
         <v>49</v>
       </c>
-      <c r="G168"/>
-      <c r="H168"/>
-      <c r="I168"/>
       <c r="J168" t="s">
         <v>306</v>
       </c>
@@ -10916,11 +10889,6 @@
       <c r="L168" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="M168"/>
-      <c r="N168"/>
-      <c r="O168"/>
-      <c r="P168"/>
-      <c r="Q168"/>
       <c r="R168" t="s">
         <v>53</v>
       </c>
@@ -10953,7 +10921,6 @@
       <c r="B169" t="s">
         <v>305</v>
       </c>
-      <c r="C169"/>
       <c r="D169" t="s">
         <v>652</v>
       </c>
@@ -10963,11 +10930,9 @@
       <c r="F169" t="s">
         <v>847</v>
       </c>
-      <c r="G169"/>
       <c r="H169" t="s">
         <v>848</v>
       </c>
-      <c r="I169"/>
       <c r="J169" t="s">
         <v>849</v>
       </c>
@@ -10977,11 +10942,6 @@
       <c r="L169" s="4" t="s">
         <v>851</v>
       </c>
-      <c r="M169"/>
-      <c r="N169"/>
-      <c r="O169"/>
-      <c r="P169"/>
-      <c r="Q169"/>
       <c r="R169" t="s">
         <v>24</v>
       </c>
@@ -11014,7 +10974,6 @@
       <c r="B170" t="s">
         <v>305</v>
       </c>
-      <c r="C170"/>
       <c r="D170" t="s">
         <v>629</v>
       </c>
@@ -11024,9 +10983,6 @@
       <c r="F170" t="s">
         <v>266</v>
       </c>
-      <c r="G170"/>
-      <c r="H170"/>
-      <c r="I170"/>
       <c r="J170" t="s">
         <v>852</v>
       </c>
@@ -11036,11 +10992,6 @@
       <c r="L170" s="4" t="s">
         <v>854</v>
       </c>
-      <c r="M170"/>
-      <c r="N170"/>
-      <c r="O170"/>
-      <c r="P170"/>
-      <c r="Q170"/>
       <c r="R170" t="s">
         <v>24</v>
       </c>
@@ -11073,7 +11024,6 @@
       <c r="B171" t="s">
         <v>305</v>
       </c>
-      <c r="C171"/>
       <c r="D171" t="s">
         <v>855</v>
       </c>
@@ -11083,9 +11033,6 @@
       <c r="F171" t="s">
         <v>65</v>
       </c>
-      <c r="G171"/>
-      <c r="H171"/>
-      <c r="I171"/>
       <c r="J171" t="s">
         <v>856</v>
       </c>
@@ -11095,11 +11042,6 @@
       <c r="L171" s="4" t="s">
         <v>858</v>
       </c>
-      <c r="M171"/>
-      <c r="N171"/>
-      <c r="O171"/>
-      <c r="P171"/>
-      <c r="Q171"/>
       <c r="R171" t="s">
         <v>24</v>
       </c>
@@ -11132,7 +11074,6 @@
       <c r="B172" t="s">
         <v>305</v>
       </c>
-      <c r="C172"/>
       <c r="D172" t="s">
         <v>387</v>
       </c>
@@ -11142,9 +11083,6 @@
       <c r="F172" t="s">
         <v>860</v>
       </c>
-      <c r="G172"/>
-      <c r="H172"/>
-      <c r="I172"/>
       <c r="J172" t="s">
         <v>861</v>
       </c>
@@ -11154,11 +11092,6 @@
       <c r="L172" s="4" t="s">
         <v>863</v>
       </c>
-      <c r="M172"/>
-      <c r="N172"/>
-      <c r="O172"/>
-      <c r="P172"/>
-      <c r="Q172"/>
       <c r="R172" t="s">
         <v>24</v>
       </c>
@@ -11185,40 +11118,40 @@
       </c>
     </row>
     <row r="173" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L173" s="11"/>
+      <c r="L173" s="10"/>
     </row>
     <row r="174" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L174" s="11"/>
+      <c r="L174" s="10"/>
     </row>
     <row r="175" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L175" s="11"/>
+      <c r="L175" s="10"/>
     </row>
     <row r="176" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="5" t="s">
+      <c r="A176" t="s">
         <v>309</v>
       </c>
-      <c r="B176" s="5" t="s">
+      <c r="B176" t="s">
         <v>310</v>
       </c>
-      <c r="D176" s="5" t="s">
+      <c r="D176" t="s">
         <v>311</v>
       </c>
-      <c r="E176" s="5" t="s">
+      <c r="E176" t="s">
         <v>196</v>
       </c>
-      <c r="F176" s="5" t="s">
+      <c r="F176" t="s">
         <v>312</v>
       </c>
-      <c r="J176" s="5" t="s">
+      <c r="J176" t="s">
         <v>313</v>
       </c>
-      <c r="L176" s="11" t="s">
+      <c r="L176" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="R176" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S176" s="5" t="s">
+      <c r="R176" t="s">
+        <v>24</v>
+      </c>
+      <c r="S176" t="s">
         <v>101</v>
       </c>
       <c r="T176" s="1" t="s">
@@ -11235,37 +11168,37 @@
       </c>
     </row>
     <row r="177" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="5" t="s">
+      <c r="A177" t="s">
         <v>309</v>
       </c>
-      <c r="B177" s="5" t="s">
+      <c r="B177" t="s">
         <v>310</v>
       </c>
-      <c r="D177" s="5" t="s">
+      <c r="D177" t="s">
         <v>311</v>
       </c>
-      <c r="E177" s="5" t="s">
+      <c r="E177" t="s">
         <v>86</v>
       </c>
-      <c r="F177" s="5" t="s">
+      <c r="F177" t="s">
         <v>173</v>
       </c>
-      <c r="J177" s="5" t="s">
+      <c r="J177" t="s">
         <v>315</v>
       </c>
-      <c r="K177" s="5" t="s">
+      <c r="K177" t="s">
         <v>316</v>
       </c>
-      <c r="L177" s="11" t="s">
+      <c r="L177" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="M177" s="5" t="s">
+      <c r="M177" t="s">
         <v>318</v>
       </c>
-      <c r="R177" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S177" s="5" t="s">
+      <c r="R177" t="s">
+        <v>24</v>
+      </c>
+      <c r="S177" t="s">
         <v>25</v>
       </c>
       <c r="T177" s="1" t="s">
@@ -11288,35 +11221,35 @@
       </c>
     </row>
     <row r="178" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="5" t="s">
+      <c r="A178" t="s">
         <v>309</v>
       </c>
-      <c r="B178" s="5" t="s">
+      <c r="B178" t="s">
         <v>310</v>
       </c>
-      <c r="D178" s="5" t="s">
+      <c r="D178" t="s">
         <v>866</v>
       </c>
-      <c r="E178" s="5" t="s">
+      <c r="E178" t="s">
         <v>86</v>
       </c>
-      <c r="F178" s="5" t="s">
+      <c r="F178" t="s">
         <v>173</v>
       </c>
-      <c r="J178" s="5" t="s">
+      <c r="J178" t="s">
         <v>867</v>
       </c>
-      <c r="K178" s="5" t="s">
+      <c r="K178" t="s">
         <v>868</v>
       </c>
-      <c r="L178" s="11"/>
-      <c r="M178" s="5" t="s">
+      <c r="L178" s="10"/>
+      <c r="M178" t="s">
         <v>869</v>
       </c>
-      <c r="R178" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S178" s="5" t="s">
+      <c r="R178" t="s">
+        <v>24</v>
+      </c>
+      <c r="S178" t="s">
         <v>25</v>
       </c>
       <c r="T178" s="1" t="s">
@@ -11339,37 +11272,37 @@
       </c>
     </row>
     <row r="179" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="5" t="s">
+      <c r="A179" t="s">
         <v>309</v>
       </c>
-      <c r="B179" s="5" t="s">
+      <c r="B179" t="s">
         <v>310</v>
       </c>
-      <c r="D179" s="5" t="s">
+      <c r="D179" t="s">
         <v>871</v>
       </c>
-      <c r="E179" s="5" t="s">
+      <c r="E179" t="s">
         <v>86</v>
       </c>
-      <c r="F179" s="5" t="s">
+      <c r="F179" t="s">
         <v>173</v>
       </c>
-      <c r="J179" s="5" t="s">
+      <c r="J179" t="s">
         <v>872</v>
       </c>
-      <c r="K179" s="5" t="s">
+      <c r="K179" t="s">
         <v>873</v>
       </c>
-      <c r="L179" s="11" t="s">
+      <c r="L179" s="10" t="s">
         <v>874</v>
       </c>
-      <c r="M179" s="5" t="s">
+      <c r="M179" t="s">
         <v>869</v>
       </c>
-      <c r="R179" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S179" s="5" t="s">
+      <c r="R179" t="s">
+        <v>24</v>
+      </c>
+      <c r="S179" t="s">
         <v>25</v>
       </c>
       <c r="T179" s="1" t="s">
@@ -11392,31 +11325,31 @@
       </c>
     </row>
     <row r="180" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="5" t="s">
+      <c r="A180" t="s">
         <v>319</v>
       </c>
-      <c r="B180" s="5" t="s">
+      <c r="B180" t="s">
         <v>320</v>
       </c>
-      <c r="D180" s="5">
+      <c r="D180">
         <v>1731</v>
       </c>
-      <c r="E180" s="5" t="s">
+      <c r="E180" t="s">
         <v>48</v>
       </c>
-      <c r="F180" s="5" t="s">
+      <c r="F180" t="s">
         <v>49</v>
       </c>
-      <c r="J180" s="5" t="s">
+      <c r="J180" t="s">
         <v>321</v>
       </c>
-      <c r="L180" s="11" t="s">
+      <c r="L180" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="R180" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S180" s="5" t="s">
+      <c r="R180" t="s">
+        <v>24</v>
+      </c>
+      <c r="S180" t="s">
         <v>25</v>
       </c>
       <c r="T180" s="1">
@@ -11433,34 +11366,34 @@
       </c>
     </row>
     <row r="181" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="5" t="s">
+      <c r="A181" t="s">
         <v>319</v>
       </c>
-      <c r="B181" s="5" t="s">
+      <c r="B181" t="s">
         <v>320</v>
       </c>
-      <c r="D181" s="5">
+      <c r="D181">
         <v>1733</v>
       </c>
-      <c r="E181" s="5" t="s">
+      <c r="E181" t="s">
         <v>875</v>
       </c>
-      <c r="F181" s="5" t="s">
+      <c r="F181" t="s">
         <v>876</v>
       </c>
-      <c r="J181" s="5" t="s">
+      <c r="J181" t="s">
         <v>877</v>
       </c>
-      <c r="K181" s="5" t="s">
+      <c r="K181" t="s">
         <v>878</v>
       </c>
-      <c r="L181" s="11" t="s">
+      <c r="L181" s="10" t="s">
         <v>879</v>
       </c>
-      <c r="R181" s="5" t="s">
+      <c r="R181" t="s">
         <v>880</v>
       </c>
-      <c r="S181" s="5" t="s">
+      <c r="S181" t="s">
         <v>58</v>
       </c>
       <c r="W181" s="1">
@@ -11474,34 +11407,34 @@
       </c>
     </row>
     <row r="182" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="5" t="s">
+      <c r="A182" t="s">
         <v>319</v>
       </c>
-      <c r="B182" s="5" t="s">
+      <c r="B182" t="s">
         <v>320</v>
       </c>
-      <c r="D182" s="5">
+      <c r="D182">
         <v>1737</v>
       </c>
-      <c r="E182" s="5" t="s">
+      <c r="E182" t="s">
         <v>48</v>
       </c>
-      <c r="F182" s="5" t="s">
+      <c r="F182" t="s">
         <v>49</v>
       </c>
-      <c r="J182" s="5" t="s">
+      <c r="J182" t="s">
         <v>881</v>
       </c>
-      <c r="K182" s="5" t="s">
+      <c r="K182" t="s">
         <v>882</v>
       </c>
-      <c r="L182" s="11" t="s">
+      <c r="L182" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="R182" s="5" t="s">
+      <c r="R182" t="s">
         <v>626</v>
       </c>
-      <c r="S182" s="5" t="s">
+      <c r="S182" t="s">
         <v>25</v>
       </c>
       <c r="W182" s="1">
@@ -11515,34 +11448,34 @@
       </c>
     </row>
     <row r="183" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="5" t="s">
+      <c r="A183" t="s">
         <v>319</v>
       </c>
-      <c r="B183" s="5" t="s">
+      <c r="B183" t="s">
         <v>320</v>
       </c>
-      <c r="D183" s="5">
+      <c r="D183">
         <v>1756</v>
       </c>
-      <c r="E183" s="5" t="s">
+      <c r="E183" t="s">
         <v>48</v>
       </c>
-      <c r="F183" s="5" t="s">
+      <c r="F183" t="s">
         <v>679</v>
       </c>
-      <c r="J183" s="5" t="s">
+      <c r="J183" t="s">
         <v>884</v>
       </c>
-      <c r="K183" s="5" t="s">
+      <c r="K183" t="s">
         <v>885</v>
       </c>
-      <c r="L183" s="11" t="s">
+      <c r="L183" s="10" t="s">
         <v>886</v>
       </c>
-      <c r="R183" s="5" t="s">
+      <c r="R183" t="s">
         <v>887</v>
       </c>
-      <c r="S183" s="5" t="s">
+      <c r="S183" t="s">
         <v>25</v>
       </c>
       <c r="W183" s="1">
@@ -11556,44 +11489,40 @@
       </c>
     </row>
     <row r="184" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="5" t="s">
+      <c r="A184" t="s">
         <v>323</v>
       </c>
-      <c r="B184" s="5" t="s">
+      <c r="B184" t="s">
         <v>324</v>
       </c>
-      <c r="D184" s="5" t="s">
+      <c r="D184" t="s">
         <v>325</v>
       </c>
-      <c r="E184" s="5" t="s">
+      <c r="E184" t="s">
         <v>326</v>
       </c>
-      <c r="F184" s="5" t="s">
+      <c r="F184" t="s">
         <v>327</v>
       </c>
-      <c r="J184" s="5" t="s">
+      <c r="J184" t="s">
         <v>328</v>
       </c>
-      <c r="L184" s="11" t="s">
+      <c r="L184" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="R184" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S184" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="T184" s="1">
-        <v>246</v>
-      </c>
-      <c r="U184" s="1">
-        <v>442</v>
-      </c>
-      <c r="V184" s="1">
-        <v>247</v>
-      </c>
-      <c r="W184" s="1">
-        <v>3</v>
+      <c r="R184" t="s">
+        <v>24</v>
+      </c>
+      <c r="S184" t="s">
+        <v>25</v>
+      </c>
+      <c r="T184" t="s">
+        <v>739</v>
+      </c>
+      <c r="U184"/>
+      <c r="V184"/>
+      <c r="W184" t="s">
+        <v>386</v>
       </c>
       <c r="X184" s="1" t="s">
         <v>323</v>
@@ -11603,384 +11532,964 @@
       </c>
     </row>
     <row r="185" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L185" s="11"/>
+      <c r="A185" t="s">
+        <v>323</v>
+      </c>
+      <c r="B185" t="s">
+        <v>324</v>
+      </c>
+      <c r="D185" t="s">
+        <v>888</v>
+      </c>
+      <c r="E185" t="s">
+        <v>326</v>
+      </c>
+      <c r="F185" t="s">
+        <v>327</v>
+      </c>
+      <c r="J185" t="s">
+        <v>889</v>
+      </c>
+      <c r="K185" t="s">
+        <v>890</v>
+      </c>
+      <c r="L185" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="R185" t="s">
+        <v>24</v>
+      </c>
+      <c r="S185" t="s">
+        <v>146</v>
+      </c>
+      <c r="T185"/>
+      <c r="U185"/>
+      <c r="V185"/>
+      <c r="W185" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="186" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L186" s="11"/>
+      <c r="A186" t="s">
+        <v>323</v>
+      </c>
+      <c r="B186" t="s">
+        <v>324</v>
+      </c>
+      <c r="D186" t="s">
+        <v>649</v>
+      </c>
+      <c r="E186" t="s">
+        <v>326</v>
+      </c>
+      <c r="F186" t="s">
+        <v>327</v>
+      </c>
+      <c r="J186" t="s">
+        <v>892</v>
+      </c>
+      <c r="K186" t="s">
+        <v>893</v>
+      </c>
+      <c r="L186" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="R186" t="s">
+        <v>24</v>
+      </c>
+      <c r="S186" t="s">
+        <v>146</v>
+      </c>
+      <c r="T186"/>
+      <c r="U186"/>
+      <c r="V186"/>
+      <c r="W186" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="187" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L187" s="11"/>
+      <c r="A187" t="s">
+        <v>323</v>
+      </c>
+      <c r="B187" t="s">
+        <v>324</v>
+      </c>
+      <c r="D187" t="s">
+        <v>652</v>
+      </c>
+      <c r="E187" t="s">
+        <v>326</v>
+      </c>
+      <c r="F187" t="s">
+        <v>327</v>
+      </c>
+      <c r="J187" t="s">
+        <v>895</v>
+      </c>
+      <c r="K187" t="s">
+        <v>896</v>
+      </c>
+      <c r="L187" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="R187" t="s">
+        <v>24</v>
+      </c>
+      <c r="S187" t="s">
+        <v>146</v>
+      </c>
+      <c r="T187"/>
+      <c r="U187"/>
+      <c r="V187"/>
+      <c r="W187" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="188" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="5" t="s">
+      <c r="A188" t="s">
         <v>330</v>
       </c>
-      <c r="B188" s="5" t="s">
+      <c r="B188" t="s">
         <v>331</v>
       </c>
-      <c r="D188" s="5">
-        <v>1753</v>
-      </c>
-      <c r="E188" s="5" t="s">
+      <c r="D188" t="s">
+        <v>574</v>
+      </c>
+      <c r="E188" t="s">
         <v>135</v>
       </c>
-      <c r="F188" s="5" t="s">
+      <c r="F188" t="s">
         <v>151</v>
       </c>
-      <c r="J188" s="5" t="s">
+      <c r="J188" t="s">
         <v>332</v>
       </c>
-      <c r="K188" s="5" t="s">
+      <c r="K188" t="s">
         <v>333</v>
       </c>
-      <c r="L188" s="11" t="s">
+      <c r="L188" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="R188" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S188" s="5" t="s">
+      <c r="R188" t="s">
+        <v>24</v>
+      </c>
+      <c r="S188" t="s">
         <v>25</v>
       </c>
-      <c r="T188" s="1">
-        <v>50</v>
-      </c>
-      <c r="U188" s="1">
-        <v>180</v>
-      </c>
-      <c r="V188" s="1">
-        <v>80</v>
-      </c>
-      <c r="W188" s="1">
-        <v>3</v>
-      </c>
-      <c r="X188" s="1" t="s">
+      <c r="T188" t="s">
+        <v>571</v>
+      </c>
+      <c r="U188" t="s">
+        <v>482</v>
+      </c>
+      <c r="V188" t="s">
+        <v>898</v>
+      </c>
+      <c r="W188" t="s">
+        <v>386</v>
+      </c>
+      <c r="X188" t="s">
         <v>330</v>
       </c>
-      <c r="Y188" s="1" t="s">
+      <c r="Y188" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="189" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="5" t="s">
+      <c r="A189" t="s">
         <v>330</v>
       </c>
-      <c r="B189" s="5" t="s">
+      <c r="B189" t="s">
         <v>331</v>
       </c>
-      <c r="D189" s="5">
-        <v>1760</v>
-      </c>
-      <c r="E189" s="5" t="s">
+      <c r="D189" t="s">
+        <v>96</v>
+      </c>
+      <c r="E189" t="s">
         <v>135</v>
       </c>
-      <c r="F189" s="5" t="s">
+      <c r="F189" t="s">
         <v>335</v>
       </c>
-      <c r="J189" s="5" t="s">
+      <c r="J189" t="s">
         <v>336</v>
       </c>
-      <c r="K189" s="5" t="s">
+      <c r="K189" t="s">
         <v>337</v>
       </c>
-      <c r="L189" s="11" t="s">
+      <c r="L189" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="R189" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S189" s="5" t="s">
+      <c r="R189" t="s">
+        <v>24</v>
+      </c>
+      <c r="S189" t="s">
         <v>25</v>
       </c>
-      <c r="T189" s="1">
-        <v>196</v>
-      </c>
-      <c r="U189" s="1">
-        <v>110</v>
-      </c>
-      <c r="V189" s="1">
-        <v>85</v>
-      </c>
-      <c r="W189" s="1">
-        <v>3</v>
-      </c>
-      <c r="X189" s="1" t="s">
+      <c r="T189" t="s">
+        <v>899</v>
+      </c>
+      <c r="U189" t="s">
+        <v>664</v>
+      </c>
+      <c r="V189" t="s">
+        <v>373</v>
+      </c>
+      <c r="W189" t="s">
+        <v>386</v>
+      </c>
+      <c r="X189" t="s">
         <v>330</v>
       </c>
-      <c r="Y189" s="1" t="s">
+      <c r="Y189" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="190" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L190" s="11"/>
+      <c r="A190" t="s">
+        <v>330</v>
+      </c>
+      <c r="B190" t="s">
+        <v>331</v>
+      </c>
+      <c r="D190" t="s">
+        <v>900</v>
+      </c>
+      <c r="E190" t="s">
+        <v>135</v>
+      </c>
+      <c r="F190" t="s">
+        <v>335</v>
+      </c>
+      <c r="J190" t="s">
+        <v>901</v>
+      </c>
+      <c r="L190" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="R190" t="s">
+        <v>24</v>
+      </c>
+      <c r="S190" t="s">
+        <v>25</v>
+      </c>
+      <c r="T190">
+        <v>173</v>
+      </c>
+      <c r="U190"/>
+      <c r="V190"/>
+      <c r="W190" t="s">
+        <v>386</v>
+      </c>
+      <c r="X190" t="s">
+        <v>330</v>
+      </c>
+      <c r="Y190" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="191" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L191" s="11"/>
+      <c r="A191" t="s">
+        <v>330</v>
+      </c>
+      <c r="B191" t="s">
+        <v>331</v>
+      </c>
+      <c r="D191" t="s">
+        <v>498</v>
+      </c>
+      <c r="E191" t="s">
+        <v>135</v>
+      </c>
+      <c r="F191" t="s">
+        <v>903</v>
+      </c>
+      <c r="J191" t="s">
+        <v>904</v>
+      </c>
+      <c r="K191" t="s">
+        <v>905</v>
+      </c>
+      <c r="L191" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="R191" t="s">
+        <v>24</v>
+      </c>
+      <c r="S191" t="s">
+        <v>25</v>
+      </c>
+      <c r="T191" t="s">
+        <v>587</v>
+      </c>
+      <c r="U191"/>
+      <c r="V191"/>
+      <c r="W191" t="s">
+        <v>386</v>
+      </c>
+      <c r="X191" t="s">
+        <v>330</v>
+      </c>
+      <c r="Y191" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="192" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="5" t="s">
+      <c r="A192" t="s">
         <v>339</v>
       </c>
-      <c r="B192" s="5" t="s">
+      <c r="B192" t="s">
         <v>340</v>
       </c>
-      <c r="D192" s="5" t="s">
+      <c r="D192" t="s">
         <v>341</v>
       </c>
-      <c r="E192" s="5" t="s">
+      <c r="E192" t="s">
         <v>342</v>
       </c>
-      <c r="F192" s="5" t="s">
+      <c r="F192" t="s">
         <v>343</v>
       </c>
-      <c r="J192" s="5" t="s">
+      <c r="J192" t="s">
         <v>344</v>
       </c>
-      <c r="L192" s="11" t="s">
+      <c r="K192" t="s">
+        <v>907</v>
+      </c>
+      <c r="L192" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="R192" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S192" s="5" t="s">
+      <c r="R192" t="s">
+        <v>24</v>
+      </c>
+      <c r="S192" t="s">
         <v>25</v>
       </c>
-      <c r="T192" s="1">
-        <v>172</v>
-      </c>
-      <c r="W192" s="1">
-        <v>3</v>
-      </c>
-      <c r="X192" s="1" t="s">
+      <c r="T192" t="s">
+        <v>908</v>
+      </c>
+      <c r="U192"/>
+      <c r="V192"/>
+      <c r="W192" t="s">
+        <v>386</v>
+      </c>
+      <c r="X192" t="s">
         <v>339</v>
       </c>
-      <c r="Y192" s="1" t="s">
+      <c r="Y192" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="193" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L193" s="11"/>
+      <c r="A193" t="s">
+        <v>339</v>
+      </c>
+      <c r="B193" t="s">
+        <v>340</v>
+      </c>
+      <c r="D193" t="s">
+        <v>662</v>
+      </c>
+      <c r="E193" t="s">
+        <v>342</v>
+      </c>
+      <c r="F193" t="s">
+        <v>909</v>
+      </c>
+      <c r="J193" t="s">
+        <v>910</v>
+      </c>
+      <c r="K193" t="s">
+        <v>911</v>
+      </c>
+      <c r="L193" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="R193" t="s">
+        <v>913</v>
+      </c>
+      <c r="S193" t="s">
+        <v>914</v>
+      </c>
+      <c r="T193" t="s">
+        <v>481</v>
+      </c>
+      <c r="U193"/>
+      <c r="V193"/>
+      <c r="W193" t="s">
+        <v>386</v>
+      </c>
+      <c r="X193" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y193" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="194" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L194" s="11"/>
+      <c r="A194" t="s">
+        <v>339</v>
+      </c>
+      <c r="B194" t="s">
+        <v>340</v>
+      </c>
+      <c r="D194" t="s">
+        <v>688</v>
+      </c>
+      <c r="E194" t="s">
+        <v>342</v>
+      </c>
+      <c r="F194" t="s">
+        <v>343</v>
+      </c>
+      <c r="J194" t="s">
+        <v>915</v>
+      </c>
+      <c r="K194" t="s">
+        <v>916</v>
+      </c>
+      <c r="L194" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="R194" t="s">
+        <v>626</v>
+      </c>
+      <c r="S194" t="s">
+        <v>25</v>
+      </c>
+      <c r="T194"/>
+      <c r="U194"/>
+      <c r="V194"/>
+      <c r="W194" t="s">
+        <v>386</v>
+      </c>
+      <c r="X194" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y194" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="195" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L195" s="11"/>
+      <c r="A195" t="s">
+        <v>339</v>
+      </c>
+      <c r="B195" t="s">
+        <v>340</v>
+      </c>
+      <c r="D195" t="s">
+        <v>918</v>
+      </c>
+      <c r="E195" t="s">
+        <v>919</v>
+      </c>
+      <c r="F195" t="s">
+        <v>920</v>
+      </c>
+      <c r="J195" t="s">
+        <v>921</v>
+      </c>
+      <c r="K195" t="s">
+        <v>922</v>
+      </c>
+      <c r="L195" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="R195" t="s">
+        <v>24</v>
+      </c>
+      <c r="S195" t="s">
+        <v>58</v>
+      </c>
+      <c r="T195"/>
+      <c r="U195"/>
+      <c r="V195"/>
+      <c r="W195" t="s">
+        <v>386</v>
+      </c>
+      <c r="X195" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y195" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="196" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="5" t="s">
+      <c r="A196" t="s">
         <v>346</v>
       </c>
-      <c r="B196" s="5" t="s">
+      <c r="B196" t="s">
         <v>347</v>
       </c>
-      <c r="D196" s="5">
-        <v>1702</v>
-      </c>
-      <c r="E196" s="5" t="s">
+      <c r="D196" t="s">
+        <v>924</v>
+      </c>
+      <c r="E196" t="s">
         <v>348</v>
       </c>
-      <c r="F196" s="5" t="s">
+      <c r="F196" t="s">
         <v>349</v>
       </c>
-      <c r="J196" s="5" t="s">
+      <c r="J196" t="s">
         <v>350</v>
       </c>
-      <c r="K196" s="5" t="s">
+      <c r="K196" t="s">
         <v>351</v>
       </c>
-      <c r="L196" s="11" t="s">
+      <c r="L196" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="R196" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S196" s="5" t="s">
+      <c r="R196" t="s">
+        <v>24</v>
+      </c>
+      <c r="S196" t="s">
         <v>353</v>
       </c>
-      <c r="T196" s="1">
-        <v>185</v>
-      </c>
-      <c r="U196" s="1">
-        <v>72</v>
-      </c>
-      <c r="V196" s="1">
-        <v>50</v>
-      </c>
-      <c r="W196" s="1">
-        <v>2</v>
-      </c>
-      <c r="X196" s="1" t="s">
+      <c r="T196" t="s">
+        <v>925</v>
+      </c>
+      <c r="U196" t="s">
+        <v>926</v>
+      </c>
+      <c r="V196" t="s">
+        <v>571</v>
+      </c>
+      <c r="W196" t="s">
+        <v>376</v>
+      </c>
+      <c r="X196" t="s">
         <v>346</v>
       </c>
-      <c r="Y196" s="1" t="s">
+      <c r="Y196" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="197" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="5" t="s">
+      <c r="A197" t="s">
         <v>346</v>
       </c>
-      <c r="B197" s="5" t="s">
+      <c r="B197" t="s">
         <v>347</v>
       </c>
-      <c r="D197" s="5" t="s">
+      <c r="D197" t="s">
         <v>354</v>
       </c>
-      <c r="E197" s="5" t="s">
+      <c r="E197" t="s">
         <v>348</v>
       </c>
-      <c r="F197" s="5" t="s">
+      <c r="F197" t="s">
         <v>355</v>
       </c>
-      <c r="J197" s="5" t="s">
+      <c r="J197" t="s">
         <v>356</v>
       </c>
-      <c r="K197" s="5" t="s">
+      <c r="K197" t="s">
         <v>357</v>
       </c>
-      <c r="L197" s="11" t="s">
+      <c r="L197" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="R197" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S197" s="5" t="s">
+      <c r="R197" t="s">
+        <v>24</v>
+      </c>
+      <c r="S197" t="s">
         <v>359</v>
       </c>
-      <c r="T197" s="1">
-        <v>180</v>
-      </c>
-      <c r="U197" s="1">
-        <v>70</v>
-      </c>
-      <c r="V197" s="1">
-        <v>50</v>
-      </c>
-      <c r="W197" s="1">
-        <v>2</v>
-      </c>
-      <c r="X197" s="1" t="s">
+      <c r="T197" t="s">
+        <v>482</v>
+      </c>
+      <c r="U197" t="s">
+        <v>582</v>
+      </c>
+      <c r="V197" t="s">
+        <v>571</v>
+      </c>
+      <c r="W197" t="s">
+        <v>376</v>
+      </c>
+      <c r="X197" t="s">
         <v>346</v>
       </c>
-      <c r="Y197" s="1" t="s">
+      <c r="Y197" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="198" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L198" s="11"/>
+      <c r="A198" t="s">
+        <v>346</v>
+      </c>
+      <c r="B198" t="s">
+        <v>347</v>
+      </c>
+      <c r="D198" t="s">
+        <v>927</v>
+      </c>
+      <c r="E198" t="s">
+        <v>348</v>
+      </c>
+      <c r="F198" t="s">
+        <v>928</v>
+      </c>
+      <c r="J198" t="s">
+        <v>929</v>
+      </c>
+      <c r="K198" t="s">
+        <v>930</v>
+      </c>
+      <c r="L198" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="R198" t="s">
+        <v>24</v>
+      </c>
+      <c r="S198" t="s">
+        <v>353</v>
+      </c>
+      <c r="T198" t="s">
+        <v>482</v>
+      </c>
+      <c r="U198"/>
+      <c r="V198"/>
+      <c r="W198" t="s">
+        <v>376</v>
+      </c>
+      <c r="X198" t="s">
+        <v>346</v>
+      </c>
+      <c r="Y198" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="199" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L199" s="11"/>
+      <c r="A199" t="s">
+        <v>346</v>
+      </c>
+      <c r="B199" t="s">
+        <v>347</v>
+      </c>
+      <c r="D199" t="s">
+        <v>932</v>
+      </c>
+      <c r="E199" t="s">
+        <v>933</v>
+      </c>
+      <c r="F199" t="s">
+        <v>934</v>
+      </c>
+      <c r="J199" t="s">
+        <v>935</v>
+      </c>
+      <c r="K199" t="s">
+        <v>936</v>
+      </c>
+      <c r="L199" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="R199" t="s">
+        <v>24</v>
+      </c>
+      <c r="S199" t="s">
+        <v>353</v>
+      </c>
+      <c r="T199" t="s">
+        <v>938</v>
+      </c>
+      <c r="U199"/>
+      <c r="V199"/>
+      <c r="W199" t="s">
+        <v>376</v>
+      </c>
+      <c r="X199" t="s">
+        <v>346</v>
+      </c>
+      <c r="Y199" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="200" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L200" s="11"/>
+      <c r="A200" t="s">
+        <v>346</v>
+      </c>
+      <c r="B200" t="s">
+        <v>347</v>
+      </c>
+      <c r="D200" t="s">
+        <v>939</v>
+      </c>
+      <c r="E200" t="s">
+        <v>348</v>
+      </c>
+      <c r="F200" t="s">
+        <v>940</v>
+      </c>
+      <c r="J200" t="s">
+        <v>941</v>
+      </c>
+      <c r="K200" t="s">
+        <v>942</v>
+      </c>
+      <c r="L200" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="R200" t="s">
+        <v>24</v>
+      </c>
+      <c r="S200" t="s">
+        <v>353</v>
+      </c>
+      <c r="T200" t="s">
+        <v>427</v>
+      </c>
+      <c r="U200"/>
+      <c r="V200"/>
+      <c r="W200" t="s">
+        <v>376</v>
+      </c>
+      <c r="X200" t="s">
+        <v>346</v>
+      </c>
+      <c r="Y200" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="201" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L201" s="11"/>
+      <c r="A201" t="s">
+        <v>346</v>
+      </c>
+      <c r="B201" t="s">
+        <v>347</v>
+      </c>
+      <c r="D201" t="s">
+        <v>939</v>
+      </c>
+      <c r="E201" t="s">
+        <v>348</v>
+      </c>
+      <c r="F201" t="s">
+        <v>940</v>
+      </c>
+      <c r="J201" t="s">
+        <v>944</v>
+      </c>
+      <c r="K201" t="s">
+        <v>945</v>
+      </c>
+      <c r="L201" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="R201" t="s">
+        <v>24</v>
+      </c>
+      <c r="S201" t="s">
+        <v>353</v>
+      </c>
+      <c r="T201" t="s">
+        <v>482</v>
+      </c>
+      <c r="U201"/>
+      <c r="V201"/>
+      <c r="W201" t="s">
+        <v>376</v>
+      </c>
+      <c r="X201" t="s">
+        <v>346</v>
+      </c>
+      <c r="Y201" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="202" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="5" t="s">
+      <c r="A202" t="s">
         <v>360</v>
       </c>
-      <c r="B202" s="5" t="s">
+      <c r="B202" t="s">
         <v>361</v>
       </c>
-      <c r="D202" s="5">
-        <v>1750</v>
-      </c>
-      <c r="E202" s="5" t="s">
+      <c r="D202" t="s">
+        <v>460</v>
+      </c>
+      <c r="E202" t="s">
         <v>86</v>
       </c>
-      <c r="F202" s="5" t="s">
+      <c r="F202" t="s">
         <v>105</v>
       </c>
-      <c r="J202" s="5" t="s">
+      <c r="J202" t="s">
         <v>362</v>
       </c>
-      <c r="K202" s="5" t="s">
+      <c r="K202" t="s">
         <v>363</v>
       </c>
-      <c r="L202" s="11" t="s">
+      <c r="L202" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="R202" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S202" s="5" t="s">
+      <c r="R202" t="s">
+        <v>24</v>
+      </c>
+      <c r="S202" t="s">
         <v>25</v>
       </c>
-      <c r="T202" s="1">
-        <v>450</v>
-      </c>
-      <c r="U202" s="1">
-        <v>190</v>
-      </c>
-      <c r="V202" s="1">
-        <v>170</v>
-      </c>
-      <c r="W202" s="1">
-        <v>3</v>
-      </c>
-      <c r="X202" s="1" t="s">
+      <c r="T202" t="s">
+        <v>677</v>
+      </c>
+      <c r="U202" t="s">
+        <v>938</v>
+      </c>
+      <c r="V202" t="s">
+        <v>947</v>
+      </c>
+      <c r="W202" t="s">
+        <v>386</v>
+      </c>
+      <c r="X202" t="s">
         <v>360</v>
       </c>
-      <c r="Y202" s="1" t="s">
+      <c r="Y202" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="203" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="5" t="s">
+      <c r="A203" t="s">
         <v>360</v>
       </c>
-      <c r="B203" s="5" t="s">
+      <c r="B203" t="s">
         <v>361</v>
       </c>
-      <c r="D203" s="5">
-        <v>1755</v>
-      </c>
-      <c r="E203" s="5" t="s">
+      <c r="D203" t="s">
+        <v>652</v>
+      </c>
+      <c r="E203" t="s">
         <v>28</v>
       </c>
-      <c r="F203" s="5" t="s">
+      <c r="F203" t="s">
         <v>365</v>
       </c>
-      <c r="J203" s="5" t="s">
+      <c r="J203" t="s">
         <v>366</v>
       </c>
-      <c r="L203" s="11" t="s">
+      <c r="L203" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="R203" s="5" t="s">
+      <c r="R203" t="s">
         <v>53</v>
       </c>
-      <c r="S203" s="5" t="s">
+      <c r="S203" t="s">
         <v>289</v>
       </c>
-      <c r="T203" s="1">
-        <v>320</v>
-      </c>
-      <c r="U203" s="1">
-        <v>210</v>
-      </c>
-      <c r="V203" s="1">
-        <v>140</v>
-      </c>
-      <c r="W203" s="1">
-        <v>3</v>
-      </c>
-      <c r="X203" s="1" t="s">
+      <c r="T203" t="s">
+        <v>378</v>
+      </c>
+      <c r="U203" t="s">
+        <v>427</v>
+      </c>
+      <c r="V203" t="s">
+        <v>694</v>
+      </c>
+      <c r="W203" t="s">
+        <v>386</v>
+      </c>
+      <c r="X203" t="s">
         <v>360</v>
       </c>
-      <c r="Y203" s="1" t="s">
+      <c r="Y203" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="204" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L204" s="11"/>
+      <c r="A204" t="s">
+        <v>360</v>
+      </c>
+      <c r="B204" t="s">
+        <v>361</v>
+      </c>
+      <c r="D204" t="s">
+        <v>377</v>
+      </c>
+      <c r="E204" t="s">
+        <v>28</v>
+      </c>
+      <c r="F204" t="s">
+        <v>29</v>
+      </c>
+      <c r="J204" t="s">
+        <v>948</v>
+      </c>
+      <c r="K204" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="L204"/>
+      <c r="R204" t="s">
+        <v>951</v>
+      </c>
+      <c r="S204" t="s">
+        <v>101</v>
+      </c>
+      <c r="T204">
+        <v>67</v>
+      </c>
+      <c r="U204">
+        <v>40</v>
+      </c>
+      <c r="V204">
+        <v>20</v>
+      </c>
+      <c r="W204" t="s">
+        <v>386</v>
+      </c>
+      <c r="X204" t="s">
+        <v>360</v>
+      </c>
+      <c r="Y204" t="s">
+        <v>361</v>
+      </c>
     </row>
     <row r="205" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L205" s="11"/>
+      <c r="A205" t="s">
+        <v>360</v>
+      </c>
+      <c r="B205" t="s">
+        <v>361</v>
+      </c>
+      <c r="D205" t="s">
+        <v>377</v>
+      </c>
+      <c r="E205" t="s">
+        <v>28</v>
+      </c>
+      <c r="F205" t="s">
+        <v>29</v>
+      </c>
+      <c r="J205" t="s">
+        <v>949</v>
+      </c>
+      <c r="K205" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="L205"/>
+      <c r="R205" t="s">
+        <v>951</v>
+      </c>
+      <c r="S205" t="s">
+        <v>101</v>
+      </c>
+      <c r="T205">
+        <v>53</v>
+      </c>
+      <c r="U205">
+        <v>35</v>
+      </c>
+      <c r="V205">
+        <v>38</v>
+      </c>
+      <c r="W205" t="s">
+        <v>386</v>
+      </c>
+      <c r="X205" t="s">
+        <v>360</v>
+      </c>
+      <c r="Y205" t="s">
+        <v>361</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -12000,158 +12509,172 @@
     <hyperlink ref="L164" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
     <hyperlink ref="L176" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
     <hyperlink ref="L177" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="L184" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="L188" r:id="rId17" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="L189" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="L192" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="L196" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="L197" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="L202" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="L203" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="L3" r:id="rId24" xr:uid="{C93FFFB4-311C-431D-A81A-5ED783E7D10D}"/>
-    <hyperlink ref="L4" r:id="rId25" xr:uid="{BEE53EB8-5420-4E5B-9125-9EFAF078A599}"/>
-    <hyperlink ref="L7" r:id="rId26" xr:uid="{D9870754-541D-47FC-8A89-370E50BA9055}"/>
-    <hyperlink ref="L6" r:id="rId27" xr:uid="{7D3D2B05-56E6-4E6D-B145-2A3A5AC87887}"/>
-    <hyperlink ref="L5" r:id="rId28" xr:uid="{8DE15AD6-1CFB-408F-8AF9-ED3B39CAC211}"/>
-    <hyperlink ref="L9" r:id="rId29" xr:uid="{410F5B7C-2B6E-4021-AD10-EA3E2911C15B}"/>
-    <hyperlink ref="L12" r:id="rId30" xr:uid="{368E8181-4037-4114-9A18-812E5C911AAE}"/>
-    <hyperlink ref="L13" r:id="rId31" xr:uid="{64060F1C-BE13-4D25-B541-1FD39F322381}"/>
-    <hyperlink ref="L14" r:id="rId32" xr:uid="{98D49299-AAAB-4950-9AAF-B7D85CE54D79}"/>
-    <hyperlink ref="L11" r:id="rId33" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Nancy%2C_%C3%A9glise_baroque_Notre_Dame_de_Bonsecours%2C_mausol%C3%A9e_de_Catherine_Opalinska_1.jpg/960px-Nancy%2C_%C3%A9glise_baroque_Notre_Dame_de_Bonsecours%2C_mausol%C3%A9e_de_Catherine_Opalinska_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C6F5C490-5299-4E39-9A5C-BC39322DEB9D}"/>
-    <hyperlink ref="L10" r:id="rId34" xr:uid="{7D86CCCE-86BB-44CF-878C-EC63C89717B3}"/>
-    <hyperlink ref="L8" r:id="rId35" xr:uid="{CFC1415A-C7E0-46F3-B2F3-16F8EE0787A9}"/>
-    <hyperlink ref="L15" r:id="rId36" xr:uid="{C2A95D2E-EE39-4A59-88F2-AD2A139A9566}"/>
-    <hyperlink ref="L16" r:id="rId37" xr:uid="{9E05E86C-37E4-4FDB-BFF2-1D98FD31D2DA}"/>
-    <hyperlink ref="L21" r:id="rId38" xr:uid="{EEA3D149-41D6-461B-9972-761A5FB77D1C}"/>
-    <hyperlink ref="L22" r:id="rId39" xr:uid="{DA958F5E-84DB-48F0-95EC-1CF07515DCE9}"/>
-    <hyperlink ref="L23" r:id="rId40" xr:uid="{B2981A04-5715-4061-97AC-A9003B0B4825}"/>
-    <hyperlink ref="L24" r:id="rId41" xr:uid="{DB5CBEE9-42A1-4648-91FE-361D772D1E1E}"/>
-    <hyperlink ref="L25" r:id="rId42" xr:uid="{86A56036-B9FE-4287-82FD-EAD58725A247}"/>
-    <hyperlink ref="L27" r:id="rId43" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Sculpture_of_Shakespeare_in_the_garden_of_New_Place%2C_Stratford-upon-Avon.jpg/960px-Sculpture_of_Shakespeare_in_the_garden_of_New_Place%2C_Stratford-upon-Avon.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B79B2EAA-7972-4EAC-B81F-1D2B558C1EFD}"/>
-    <hyperlink ref="L26" r:id="rId44" xr:uid="{9DEBED11-29C7-47D7-87B2-7BCA972527B4}"/>
-    <hyperlink ref="L28" r:id="rId45" xr:uid="{5E23B361-79FD-47DB-81A8-552B4A92CBF3}"/>
-    <hyperlink ref="L31" r:id="rId46" xr:uid="{EF5F1708-9F84-4150-BB3E-BCB789F37744}"/>
-    <hyperlink ref="L32" r:id="rId47" xr:uid="{C7755D7F-D07E-4747-8FCF-ED7A5756464B}"/>
-    <hyperlink ref="L33" r:id="rId48" xr:uid="{AC2A0C7C-27D4-4067-BD1F-904E5A45511A}"/>
-    <hyperlink ref="L35" r:id="rId49" xr:uid="{C0651B9D-9098-4FFD-82EE-1BACEC606B7F}"/>
-    <hyperlink ref="L34" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Portrait_of_Pope_Clemente_XII_%28Lorenzo_Corsini%29_by_Edme_Bouchardon%2C_French%2C_after_1730%2C_tinted_plaster_and_terracotta_-_California_Palace_of_the_Legion_of_Honor_-_DSC07739.JPG/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8B86DBCE-0A72-4760-A47C-0E8B681B3570}"/>
-    <hyperlink ref="L36" r:id="rId51" xr:uid="{8A084969-8958-49B4-853C-3AE75082A12B}"/>
-    <hyperlink ref="L38" r:id="rId52" xr:uid="{CF536289-4EEE-45F1-8084-B0371B565C41}"/>
-    <hyperlink ref="L37" r:id="rId53" xr:uid="{8A257BF5-79FF-4BF8-A978-DF4AA2821305}"/>
-    <hyperlink ref="I38" r:id="rId54" xr:uid="{B4207168-3FEC-425F-A795-F5784DF13615}"/>
-    <hyperlink ref="I37" r:id="rId55" xr:uid="{78A5F208-39F1-4E0D-8845-26F0E123BACC}"/>
-    <hyperlink ref="L39" r:id="rId56" xr:uid="{CCBD85D5-3F49-4572-824C-CA8F88DB5FDC}"/>
-    <hyperlink ref="L40" r:id="rId57" xr:uid="{7DBEBA58-DBE8-4168-8217-CD887A3BCE97}"/>
-    <hyperlink ref="G39" r:id="rId58" xr:uid="{26E871FC-575D-43D6-9F77-54326016822C}"/>
-    <hyperlink ref="I39" r:id="rId59" xr:uid="{99DED6AB-344A-4740-A203-89BBD0FE2617}"/>
-    <hyperlink ref="I41" r:id="rId60" xr:uid="{9FD53BA3-BFCA-4144-BDFF-649BBC5B3558}"/>
-    <hyperlink ref="L41" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9d/05_2023_Napoli_ITA_Duomo_%28Chiesa%29_-_Altare_maggiore%2C_scultura_l%27Assunta_di_Pietro_Bracci_1739_Tardo_Barocco_-_photo_Paolo_Villa_FO231710_correction_with_gimp.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F3102698-B78C-4C21-9039-4341BB078473}"/>
-    <hyperlink ref="L42" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/94/Pietro_bracci%2C_monumento_del_cardinale_carlo_leopoldo_calcagnini%2C_1746_ca._01.jpg/960px-Pietro_bracci%2C_monumento_del_cardinale_carlo_leopoldo_calcagnini%2C_1746_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4D7419BA-CC4A-4779-9436-FB1EA35A4AAD}"/>
-    <hyperlink ref="L43" r:id="rId63" xr:uid="{6433C034-4867-4ED5-87FB-FB4304FA60D4}"/>
-    <hyperlink ref="L45" r:id="rId64" xr:uid="{F2AF0062-C78E-46E8-B793-FB34A67B76CB}"/>
-    <hyperlink ref="L46" r:id="rId65" xr:uid="{3E3EC00B-8ACF-42AB-A745-A4201CABFE7E}"/>
-    <hyperlink ref="L44" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/57/Pierre_Corneille%2C_Jean-Jacques_Caffieri%2C_Paris_1723_1792.JPG/960px-Pierre_Corneille%2C_Jean-Jacques_Caffieri%2C_Paris_1723_1792.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E2469EC-8642-4E81-A446-2CC2FAE8B43E}"/>
-    <hyperlink ref="L47" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Hope_Nourishes_Love%2C_by_Jean-Jacques_Caffieri_%28Getty_103RR5%29.jpg/960px-Hope_Nourishes_Love%2C_by_Jean-Jacques_Caffieri_%28Getty_103RR5%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{8F832910-E656-4EFB-AC57-3D74592E6676}"/>
-    <hyperlink ref="L48" r:id="rId68" xr:uid="{07CA4426-387E-4AF5-ABAB-4128909EC254}"/>
-    <hyperlink ref="L56" r:id="rId69" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Antonio_Canova-Theseus_and_the_Minotaur-Victoria_and_Albert_Museum.jpg/960px-Antonio_Canova-Theseus_and_the_Minotaur-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2E9A1016-E90D-4659-8209-31B74E3F24C7}"/>
-    <hyperlink ref="L59" r:id="rId70" xr:uid="{6C84B94A-43B1-4D8A-9BF9-CDFE564415F5}"/>
-    <hyperlink ref="L57" r:id="rId71" xr:uid="{B3640A00-3EC5-4C99-82B5-B36103E6C177}"/>
-    <hyperlink ref="L58" r:id="rId72" xr:uid="{A1A250C1-22B8-444E-8FE4-18FD5FB58CF3}"/>
-    <hyperlink ref="L61" r:id="rId73" xr:uid="{5ECC010C-30BE-43F0-A7CA-0260E3CE130D}"/>
-    <hyperlink ref="L62" r:id="rId74" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Antonio_Corradini_-_Dama_Velata_%28Puritas%29_-_Museo_del_Settecento_Veneziano_-_Ca%27_Rezzonico%2C_Venice.jpg/1920px-Antonio_Corradini_-_Dama_Velata_%28Puritas%29_-_Museo_del_Settecento_Veneziano_-_Ca%27_Rezzonico%2C_Venice.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E067AB51-1DFF-4081-BF9C-2160687A1817}"/>
-    <hyperlink ref="L63" r:id="rId75" xr:uid="{40249E18-E873-4187-A04E-BC43AA5870BF}"/>
-    <hyperlink ref="L64" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/12/Die_Zeit_enthuellt_die_Wahrheit_Grosser_Garten_Dresden-2.jpg/960px-Die_Zeit_enthuellt_die_Wahrheit_Grosser_Garten_Dresden-2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A3A6C43D-6262-4AB8-8B6D-156B47AA3737}"/>
-    <hyperlink ref="L65" r:id="rId77" xr:uid="{302541C8-469A-4C1B-901B-23B0A5F49E25}"/>
-    <hyperlink ref="L66" r:id="rId78" xr:uid="{63E34BC2-58C7-4CFF-BD2E-20022C208234}"/>
-    <hyperlink ref="L67" r:id="rId79" xr:uid="{8CC71EB9-3199-49EF-A7A9-510A7755A425}"/>
-    <hyperlink ref="L68" r:id="rId80" xr:uid="{DAE8B983-E503-400A-BAF0-FACE83FED6E4}"/>
-    <hyperlink ref="L69" r:id="rId81" xr:uid="{FE11C8C7-7233-40B4-BA5F-1A8528A9B5B6}"/>
-    <hyperlink ref="L71" r:id="rId82" xr:uid="{C60C02F6-E3DE-459C-ABD4-F5D2850BFBFD}"/>
-    <hyperlink ref="L70" r:id="rId83" xr:uid="{C8B23DFB-0783-41B8-ABC2-49EF1E8F4E4C}"/>
-    <hyperlink ref="L72" r:id="rId84" xr:uid="{F6E29A87-A4DE-4D36-A3F6-1EF40D094D20}"/>
-    <hyperlink ref="L73" r:id="rId85" xr:uid="{9C249EE3-FBC9-42B3-ADF3-45DA8444C250}"/>
-    <hyperlink ref="L74" r:id="rId86" xr:uid="{736CB61F-DB8D-4D34-831C-03D972612AD4}"/>
-    <hyperlink ref="L77" r:id="rId87" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/2012--DSC_0253-C%C3%A9notaphe-du-grand-Dauphin-par-Coustou-dans-la-cathedrale-de-Sens.jpg/960px-2012--DSC_0253-C%C3%A9notaphe-du-grand-Dauphin-par-Coustou-dans-la-cathedrale-de-Sens.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8B3A1AC7-EC23-47AE-952E-EBEB844B3107}"/>
-    <hyperlink ref="L75" r:id="rId88" xr:uid="{BAE1A9D4-896A-4274-B7A4-D7851AAFF3E4}"/>
-    <hyperlink ref="L76" r:id="rId89" xr:uid="{0876674F-89FF-491E-A710-E8D816C42436}"/>
-    <hyperlink ref="L83" r:id="rId90" xr:uid="{93422A34-E47F-4EC0-B9B6-C9390AF2A5A4}"/>
-    <hyperlink ref="L84" r:id="rId91" xr:uid="{239D762E-78B0-4394-89DF-444F8993C868}"/>
-    <hyperlink ref="L85" r:id="rId92" xr:uid="{C601465F-6588-4CFC-A32C-1D37F5CFF0E1}"/>
-    <hyperlink ref="L86" r:id="rId93" xr:uid="{0B562E20-DF22-47B8-B6FB-AD1E07393A01}"/>
-    <hyperlink ref="L87" r:id="rId94" xr:uid="{BE4D15ED-CB7B-4449-A950-1A890376BCA4}"/>
-    <hyperlink ref="L90" r:id="rId95" xr:uid="{6AB13AFE-2406-4E93-ADA6-46FDCD31365A}"/>
-    <hyperlink ref="L88" r:id="rId96" xr:uid="{C83A0152-012B-483B-9231-2A1E78BBD9C0}"/>
-    <hyperlink ref="L89" r:id="rId97" xr:uid="{47B42195-9EC3-40B8-9B46-BD6E6B84E07C}"/>
-    <hyperlink ref="L91" r:id="rId98" xr:uid="{FC084A53-72A5-46D6-BA8B-9EDF408325E8}"/>
-    <hyperlink ref="L93" r:id="rId99" xr:uid="{A0209D99-D2A7-4D01-9D4A-1D01BE96F274}"/>
-    <hyperlink ref="L94" r:id="rId100" xr:uid="{87800057-0E6E-4997-AE5C-8E9E992038EC}"/>
-    <hyperlink ref="L92" r:id="rId101" xr:uid="{219B437E-3E02-401E-B8DD-54C18AE1422E}"/>
-    <hyperlink ref="L95" r:id="rId102" xr:uid="{E4D15D0F-4493-49C9-82EC-921ADE7F7649}"/>
-    <hyperlink ref="L96" r:id="rId103" xr:uid="{08D0AD74-167F-460E-9E0D-87B452D8FCDA}"/>
-    <hyperlink ref="L97" r:id="rId104" xr:uid="{79C25996-0268-4345-9482-E6D0D91FBCDB}"/>
-    <hyperlink ref="L98" r:id="rId105" xr:uid="{6A6598FD-AB7A-4377-A28E-D84A11EE770B}"/>
-    <hyperlink ref="G97" r:id="rId106" xr:uid="{4968AB49-790D-4B21-834D-BD88FF405AF0}"/>
-    <hyperlink ref="L99" r:id="rId107" xr:uid="{6F6F2D1A-8AC2-4E8F-AD62-5895107640F4}"/>
-    <hyperlink ref="L102" r:id="rId108" xr:uid="{1A778003-D53A-46C7-9C4F-0866ED4A1FBF}"/>
-    <hyperlink ref="L100" r:id="rId109" xr:uid="{CEBDE0C6-0B4A-4C8F-BAEC-6CA4771D91A9}"/>
-    <hyperlink ref="L101" r:id="rId110" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/07/Venus_of_the_Doves_by_Etienne-Maurice_Falconet%2C_undated_mid_1700s%2C_marble_-_National_Gallery_of_Art%2C_Washington_-_DSC09976.JPG/1280px-Venus_of_the_Doves_by_Etienne-Maurice_Falconet%2C_undated_mid_1700s%2C_marble_-_National_Gallery_of_Art%2C_Washington_-_DSC09976.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{207012E8-F898-42AB-A943-D36FADE8F355}"/>
-    <hyperlink ref="L103" r:id="rId111" xr:uid="{BBF98FE5-4DFE-4FDD-A544-E80BC7A25126}"/>
-    <hyperlink ref="L104" r:id="rId112" xr:uid="{FF151DBC-7144-4288-A673-8F481A2C101A}"/>
-    <hyperlink ref="L106" r:id="rId113" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Monument_to_Lord_Mansfield%2C_Westminster_Abbey_01.jpg/960px-Monument_to_Lord_Mansfield%2C_Westminster_Abbey_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{C11B2C6E-208E-4A71-B269-E34EAE7C6083}"/>
-    <hyperlink ref="L107" r:id="rId114" xr:uid="{6ED28258-66B6-4B49-B8D7-3C03B0C1DC7C}"/>
-    <hyperlink ref="L108" r:id="rId115" xr:uid="{88433733-48D0-4D92-93C2-565748FFE72C}"/>
-    <hyperlink ref="L105" r:id="rId116" xr:uid="{DC64D51C-9988-44E8-A744-459093BA68A0}"/>
-    <hyperlink ref="L109" r:id="rId117" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/10/John_Flaxman_%281755-1826%29_-_Cephalus_and_Aurora_%281789-90%29_front%2C_Lady_Lever_Art_Gallery%2C_Port_Sunlight%2C_Cheshire%2C_June_2013_%289103113142%29.png/500px-John_Flaxman_%281755-1826%29_-_Cephalus_and_Aurora_%281789-90%29_front%2C_Lady_Lever_Art_Gallery%2C_Port_Sunlight%2C_Cheshire%2C_June_2013_%289103113142%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B7B496B9-90D1-4969-9870-7B7656D9A169}"/>
-    <hyperlink ref="L110" r:id="rId118" xr:uid="{28CC63AD-0682-4A87-A9F4-B621624C9015}"/>
-    <hyperlink ref="L111" r:id="rId119" xr:uid="{16C08E16-E991-4783-8EF3-C3F1417EEEA6}"/>
-    <hyperlink ref="L112" r:id="rId120" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg/960px-St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FF930F9C-A9AC-4607-A859-3ABD807649A4}"/>
-    <hyperlink ref="L113" r:id="rId121" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/St._Paulus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg/960px-St._Paulus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A801BD6C-0A7D-46EC-AA6B-F1137861AA28}"/>
-    <hyperlink ref="I112" r:id="rId122" xr:uid="{D76F3B05-FA60-432A-A109-15C083FC3E09}"/>
-    <hyperlink ref="I113" r:id="rId123" xr:uid="{82CED098-B306-46C4-9441-0AD55B76FFC2}"/>
-    <hyperlink ref="L114" r:id="rId124" xr:uid="{3B0D8049-B520-4810-B239-50AA43905165}"/>
-    <hyperlink ref="L115" r:id="rId125" xr:uid="{B1606A58-EDCF-48FA-BB29-771BF06A9515}"/>
-    <hyperlink ref="L116" r:id="rId126" xr:uid="{8FD76DC7-7F79-4F5A-83E7-5E8D60AA822D}"/>
-    <hyperlink ref="L117" r:id="rId127" xr:uid="{FA268604-165F-41CF-83A0-B2CBF8A0F863}"/>
-    <hyperlink ref="L120" r:id="rId128" xr:uid="{E764FD93-AA66-476B-ADC0-DCB38775F84F}"/>
-    <hyperlink ref="L118" r:id="rId129" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/06/Houdon_Jean_Antoine%2C_L%27%C3%A9corch%C3%A9_bras_lev%C3%A9%2C_Mus%C3%A9e_Fabre%2C_Montpellier.jpg/960px-Houdon_Jean_Antoine%2C_L%27%C3%A9corch%C3%A9_bras_lev%C3%A9%2C_Mus%C3%A9e_Fabre%2C_Montpellier.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CE4949A3-9DCD-4051-B144-545B5D6AE5FB}"/>
-    <hyperlink ref="L121" r:id="rId130" xr:uid="{D7E3DDA7-E4FC-4310-898E-48047F7A5160}"/>
-    <hyperlink ref="L119" r:id="rId131" xr:uid="{8FB74D72-A77F-4B4B-AE35-582003521528}"/>
-    <hyperlink ref="L154" r:id="rId132" xr:uid="{881AB544-C00A-4F17-BA6D-032A002C02EE}"/>
-    <hyperlink ref="L155" r:id="rId133" xr:uid="{85549018-4524-417C-8A3F-737C6216056C}"/>
-    <hyperlink ref="L122" r:id="rId134" xr:uid="{59D2448C-30F1-4EC0-B5EB-C506997C1927}"/>
-    <hyperlink ref="L125" r:id="rId135" xr:uid="{7AAF307B-3089-439D-9AB6-72FB4643435E}"/>
-    <hyperlink ref="L123" r:id="rId136" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/Galatea_by_Robert_Le_Lorrain%2C_1701%2C_marble_-_National_Gallery_of_Art%2C_Washington_-_DSC09966.JPG/960px-Galatea_by_Robert_Le_Lorrain%2C_1701%2C_marble_-_National_Gallery_of_Art%2C_Washington_-_DSC09966.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A2868C28-65B0-4F27-9DC1-D42AB35AAFC9}"/>
-    <hyperlink ref="L126" r:id="rId137" xr:uid="{CEE4BF6F-373A-4CAF-8057-D8C6CED562F1}"/>
-    <hyperlink ref="L127" r:id="rId138" xr:uid="{98158628-3FD0-43F9-B857-7013B4920514}"/>
-    <hyperlink ref="L124" r:id="rId139" xr:uid="{C5F3FFD6-AAED-4994-8C63-008E6F593707}"/>
-    <hyperlink ref="L128" r:id="rId140" xr:uid="{5C971F2A-99C4-4D45-A1C0-41660A874517}"/>
-    <hyperlink ref="L132" r:id="rId141" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0f/Buste_de_Maurice-Quentin_de_La_Tour_par_Jean-Baptiste_Lemoyne_-_Mus%C3%A9e_Antoine_L%C3%A9cuyer_Saint-Quentin.jpg/960px-Buste_de_Maurice-Quentin_de_La_Tour_par_Jean-Baptiste_Lemoyne_-_Mus%C3%A9e_Antoine_L%C3%A9cuyer_Saint-Quentin.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C583F16E-844A-4E26-AD66-BDF41E63BAB6}"/>
-    <hyperlink ref="L133" r:id="rId142" xr:uid="{14BBAE43-D799-4E87-B9ED-17E67F57D50C}"/>
-    <hyperlink ref="L129" r:id="rId143" xr:uid="{46584188-597F-4B8B-939B-F847C3E32BEE}"/>
-    <hyperlink ref="L131" r:id="rId144" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/11/WLA_metmuseum_La_Crainte_des_Traits_de_lAmour_by_Jean_Louis_Lemoyne.jpg/500px-WLA_metmuseum_La_Crainte_des_Traits_de_lAmour_by_Jean_Louis_Lemoyne.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{21150A3D-EE25-493D-8678-ECF98A81B21D}"/>
-    <hyperlink ref="L130" r:id="rId145" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7c/Buste_de_Marie-Antoinette_par_Jean_Baptiste_Lemoyne_-_1771.jpg/960px-Buste_de_Marie-Antoinette_par_Jean_Baptiste_Lemoyne_-_1771.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B398DE66-0DF2-445D-AC92-B6D871BF8C07}"/>
-    <hyperlink ref="L134" r:id="rId146" xr:uid="{B32DAEAF-CBB2-4B19-AE14-68256494C36B}"/>
-    <hyperlink ref="L136" r:id="rId147" xr:uid="{8039580C-466B-426C-920D-C43EE4192481}"/>
-    <hyperlink ref="L135" r:id="rId148" xr:uid="{8BD35C45-6C65-4F6B-BD3A-6522CC4929EC}"/>
-    <hyperlink ref="L137" r:id="rId149" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/56/The_Vexed_Man_%28Franz_Xaver_Messerschmidt%29%2C_Getty_Center.jpg/960px-The_Vexed_Man_%28Franz_Xaver_Messerschmidt%29%2C_Getty_Center.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{B7A5A066-179E-4D8B-BEE0-3683D11676E3}"/>
-    <hyperlink ref="L146" r:id="rId150" xr:uid="{7249162A-30B4-44C7-8EE0-081E5B3364A3}"/>
-    <hyperlink ref="L149" r:id="rId151" xr:uid="{68BF51D4-9BED-49CB-8DDB-50B9B2BD239B}"/>
-    <hyperlink ref="L147" r:id="rId152" xr:uid="{12EA42D0-C645-4657-805F-04515A86DDDF}"/>
-    <hyperlink ref="L148" r:id="rId153" xr:uid="{18E06423-54F7-45A2-B9B8-4CF6B73C873C}"/>
-    <hyperlink ref="L156" r:id="rId154" xr:uid="{2E169D95-96E0-493D-9728-13E61505FCB5}"/>
-    <hyperlink ref="L157" r:id="rId155" xr:uid="{CF8FD038-AD3C-46D0-9A82-51E15E47F02B}"/>
-    <hyperlink ref="L158" r:id="rId156" xr:uid="{C787A27C-45F7-43A3-8E5C-E46C5635382F}"/>
-    <hyperlink ref="L159" r:id="rId157" xr:uid="{DEBB429E-B33E-40EB-A760-A57487AF75E3}"/>
-    <hyperlink ref="L160" r:id="rId158" xr:uid="{1F01F486-638B-4803-96BD-163CCAAFC3AB}"/>
-    <hyperlink ref="L162" r:id="rId159" xr:uid="{239474DD-C3B8-46EE-B090-9EEF5E730499}"/>
-    <hyperlink ref="L161" r:id="rId160" xr:uid="{C21AD739-3C24-4EA2-8EB2-2F9F7C05837C}"/>
-    <hyperlink ref="L163" r:id="rId161" xr:uid="{1B12F134-C44F-479B-B2B4-89A0B8434F4D}"/>
-    <hyperlink ref="L168" r:id="rId162" xr:uid="{08DEE694-8FBB-4B47-9597-55263EBBC0B4}"/>
-    <hyperlink ref="L171" r:id="rId163" xr:uid="{200DA680-A0D2-4E22-8551-6EFA4CB091A6}"/>
-    <hyperlink ref="L169" r:id="rId164" xr:uid="{BDADEABC-9943-4795-AC79-BD5AB51E7DB6}"/>
-    <hyperlink ref="L172" r:id="rId165" xr:uid="{172E871D-6586-4D3B-A001-F45D6400E014}"/>
-    <hyperlink ref="L170" r:id="rId166" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Louis-Fran%C3%A7ois_Roubiliac_-_Alexander_Pope_-_B1993.27_-_Yale_Center_for_British_Art.jpg/960px-Louis-Fran%C3%A7ois_Roubiliac_-_Alexander_Pope_-_B1993.27_-_Yale_Center_for_British_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E6CB38CC-6BFB-4EB8-B269-7E2C880E9E08}"/>
-    <hyperlink ref="L180" r:id="rId167" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="L3" r:id="rId16" xr:uid="{C93FFFB4-311C-431D-A81A-5ED783E7D10D}"/>
+    <hyperlink ref="L4" r:id="rId17" xr:uid="{BEE53EB8-5420-4E5B-9125-9EFAF078A599}"/>
+    <hyperlink ref="L7" r:id="rId18" xr:uid="{D9870754-541D-47FC-8A89-370E50BA9055}"/>
+    <hyperlink ref="L6" r:id="rId19" xr:uid="{7D3D2B05-56E6-4E6D-B145-2A3A5AC87887}"/>
+    <hyperlink ref="L5" r:id="rId20" xr:uid="{8DE15AD6-1CFB-408F-8AF9-ED3B39CAC211}"/>
+    <hyperlink ref="L9" r:id="rId21" xr:uid="{410F5B7C-2B6E-4021-AD10-EA3E2911C15B}"/>
+    <hyperlink ref="L12" r:id="rId22" xr:uid="{368E8181-4037-4114-9A18-812E5C911AAE}"/>
+    <hyperlink ref="L13" r:id="rId23" xr:uid="{64060F1C-BE13-4D25-B541-1FD39F322381}"/>
+    <hyperlink ref="L14" r:id="rId24" xr:uid="{98D49299-AAAB-4950-9AAF-B7D85CE54D79}"/>
+    <hyperlink ref="L11" r:id="rId25" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Nancy%2C_%C3%A9glise_baroque_Notre_Dame_de_Bonsecours%2C_mausol%C3%A9e_de_Catherine_Opalinska_1.jpg/960px-Nancy%2C_%C3%A9glise_baroque_Notre_Dame_de_Bonsecours%2C_mausol%C3%A9e_de_Catherine_Opalinska_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C6F5C490-5299-4E39-9A5C-BC39322DEB9D}"/>
+    <hyperlink ref="L10" r:id="rId26" xr:uid="{7D86CCCE-86BB-44CF-878C-EC63C89717B3}"/>
+    <hyperlink ref="L8" r:id="rId27" xr:uid="{CFC1415A-C7E0-46F3-B2F3-16F8EE0787A9}"/>
+    <hyperlink ref="L15" r:id="rId28" xr:uid="{C2A95D2E-EE39-4A59-88F2-AD2A139A9566}"/>
+    <hyperlink ref="L16" r:id="rId29" xr:uid="{9E05E86C-37E4-4FDB-BFF2-1D98FD31D2DA}"/>
+    <hyperlink ref="L21" r:id="rId30" xr:uid="{EEA3D149-41D6-461B-9972-761A5FB77D1C}"/>
+    <hyperlink ref="L22" r:id="rId31" xr:uid="{DA958F5E-84DB-48F0-95EC-1CF07515DCE9}"/>
+    <hyperlink ref="L23" r:id="rId32" xr:uid="{B2981A04-5715-4061-97AC-A9003B0B4825}"/>
+    <hyperlink ref="L24" r:id="rId33" xr:uid="{DB5CBEE9-42A1-4648-91FE-361D772D1E1E}"/>
+    <hyperlink ref="L25" r:id="rId34" xr:uid="{86A56036-B9FE-4287-82FD-EAD58725A247}"/>
+    <hyperlink ref="L27" r:id="rId35" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Sculpture_of_Shakespeare_in_the_garden_of_New_Place%2C_Stratford-upon-Avon.jpg/960px-Sculpture_of_Shakespeare_in_the_garden_of_New_Place%2C_Stratford-upon-Avon.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B79B2EAA-7972-4EAC-B81F-1D2B558C1EFD}"/>
+    <hyperlink ref="L26" r:id="rId36" xr:uid="{9DEBED11-29C7-47D7-87B2-7BCA972527B4}"/>
+    <hyperlink ref="L28" r:id="rId37" xr:uid="{5E23B361-79FD-47DB-81A8-552B4A92CBF3}"/>
+    <hyperlink ref="L31" r:id="rId38" xr:uid="{EF5F1708-9F84-4150-BB3E-BCB789F37744}"/>
+    <hyperlink ref="L32" r:id="rId39" xr:uid="{C7755D7F-D07E-4747-8FCF-ED7A5756464B}"/>
+    <hyperlink ref="L33" r:id="rId40" xr:uid="{AC2A0C7C-27D4-4067-BD1F-904E5A45511A}"/>
+    <hyperlink ref="L35" r:id="rId41" xr:uid="{C0651B9D-9098-4FFD-82EE-1BACEC606B7F}"/>
+    <hyperlink ref="L34" r:id="rId42" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Portrait_of_Pope_Clemente_XII_%28Lorenzo_Corsini%29_by_Edme_Bouchardon%2C_French%2C_after_1730%2C_tinted_plaster_and_terracotta_-_California_Palace_of_the_Legion_of_Honor_-_DSC07739.JPG/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8B86DBCE-0A72-4760-A47C-0E8B681B3570}"/>
+    <hyperlink ref="L36" r:id="rId43" xr:uid="{8A084969-8958-49B4-853C-3AE75082A12B}"/>
+    <hyperlink ref="L38" r:id="rId44" xr:uid="{CF536289-4EEE-45F1-8084-B0371B565C41}"/>
+    <hyperlink ref="L37" r:id="rId45" xr:uid="{8A257BF5-79FF-4BF8-A978-DF4AA2821305}"/>
+    <hyperlink ref="I38" r:id="rId46" xr:uid="{B4207168-3FEC-425F-A795-F5784DF13615}"/>
+    <hyperlink ref="I37" r:id="rId47" xr:uid="{78A5F208-39F1-4E0D-8845-26F0E123BACC}"/>
+    <hyperlink ref="L39" r:id="rId48" xr:uid="{CCBD85D5-3F49-4572-824C-CA8F88DB5FDC}"/>
+    <hyperlink ref="L40" r:id="rId49" xr:uid="{7DBEBA58-DBE8-4168-8217-CD887A3BCE97}"/>
+    <hyperlink ref="G39" r:id="rId50" xr:uid="{26E871FC-575D-43D6-9F77-54326016822C}"/>
+    <hyperlink ref="I39" r:id="rId51" xr:uid="{99DED6AB-344A-4740-A203-89BBD0FE2617}"/>
+    <hyperlink ref="I41" r:id="rId52" xr:uid="{9FD53BA3-BFCA-4144-BDFF-649BBC5B3558}"/>
+    <hyperlink ref="L41" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9d/05_2023_Napoli_ITA_Duomo_%28Chiesa%29_-_Altare_maggiore%2C_scultura_l%27Assunta_di_Pietro_Bracci_1739_Tardo_Barocco_-_photo_Paolo_Villa_FO231710_correction_with_gimp.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F3102698-B78C-4C21-9039-4341BB078473}"/>
+    <hyperlink ref="L42" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/94/Pietro_bracci%2C_monumento_del_cardinale_carlo_leopoldo_calcagnini%2C_1746_ca._01.jpg/960px-Pietro_bracci%2C_monumento_del_cardinale_carlo_leopoldo_calcagnini%2C_1746_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4D7419BA-CC4A-4779-9436-FB1EA35A4AAD}"/>
+    <hyperlink ref="L43" r:id="rId55" xr:uid="{6433C034-4867-4ED5-87FB-FB4304FA60D4}"/>
+    <hyperlink ref="L45" r:id="rId56" xr:uid="{F2AF0062-C78E-46E8-B793-FB34A67B76CB}"/>
+    <hyperlink ref="L46" r:id="rId57" xr:uid="{3E3EC00B-8ACF-42AB-A745-A4201CABFE7E}"/>
+    <hyperlink ref="L44" r:id="rId58" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/57/Pierre_Corneille%2C_Jean-Jacques_Caffieri%2C_Paris_1723_1792.JPG/960px-Pierre_Corneille%2C_Jean-Jacques_Caffieri%2C_Paris_1723_1792.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E2469EC-8642-4E81-A446-2CC2FAE8B43E}"/>
+    <hyperlink ref="L47" r:id="rId59" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Hope_Nourishes_Love%2C_by_Jean-Jacques_Caffieri_%28Getty_103RR5%29.jpg/960px-Hope_Nourishes_Love%2C_by_Jean-Jacques_Caffieri_%28Getty_103RR5%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{8F832910-E656-4EFB-AC57-3D74592E6676}"/>
+    <hyperlink ref="L48" r:id="rId60" xr:uid="{07CA4426-387E-4AF5-ABAB-4128909EC254}"/>
+    <hyperlink ref="L56" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Antonio_Canova-Theseus_and_the_Minotaur-Victoria_and_Albert_Museum.jpg/960px-Antonio_Canova-Theseus_and_the_Minotaur-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2E9A1016-E90D-4659-8209-31B74E3F24C7}"/>
+    <hyperlink ref="L59" r:id="rId62" xr:uid="{6C84B94A-43B1-4D8A-9BF9-CDFE564415F5}"/>
+    <hyperlink ref="L57" r:id="rId63" xr:uid="{B3640A00-3EC5-4C99-82B5-B36103E6C177}"/>
+    <hyperlink ref="L58" r:id="rId64" xr:uid="{A1A250C1-22B8-444E-8FE4-18FD5FB58CF3}"/>
+    <hyperlink ref="L61" r:id="rId65" xr:uid="{5ECC010C-30BE-43F0-A7CA-0260E3CE130D}"/>
+    <hyperlink ref="L62" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Antonio_Corradini_-_Dama_Velata_%28Puritas%29_-_Museo_del_Settecento_Veneziano_-_Ca%27_Rezzonico%2C_Venice.jpg/1920px-Antonio_Corradini_-_Dama_Velata_%28Puritas%29_-_Museo_del_Settecento_Veneziano_-_Ca%27_Rezzonico%2C_Venice.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E067AB51-1DFF-4081-BF9C-2160687A1817}"/>
+    <hyperlink ref="L63" r:id="rId67" xr:uid="{40249E18-E873-4187-A04E-BC43AA5870BF}"/>
+    <hyperlink ref="L64" r:id="rId68" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/12/Die_Zeit_enthuellt_die_Wahrheit_Grosser_Garten_Dresden-2.jpg/960px-Die_Zeit_enthuellt_die_Wahrheit_Grosser_Garten_Dresden-2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A3A6C43D-6262-4AB8-8B6D-156B47AA3737}"/>
+    <hyperlink ref="L65" r:id="rId69" xr:uid="{302541C8-469A-4C1B-901B-23B0A5F49E25}"/>
+    <hyperlink ref="L66" r:id="rId70" xr:uid="{63E34BC2-58C7-4CFF-BD2E-20022C208234}"/>
+    <hyperlink ref="L67" r:id="rId71" xr:uid="{8CC71EB9-3199-49EF-A7A9-510A7755A425}"/>
+    <hyperlink ref="L68" r:id="rId72" xr:uid="{DAE8B983-E503-400A-BAF0-FACE83FED6E4}"/>
+    <hyperlink ref="L69" r:id="rId73" xr:uid="{FE11C8C7-7233-40B4-BA5F-1A8528A9B5B6}"/>
+    <hyperlink ref="L71" r:id="rId74" xr:uid="{C60C02F6-E3DE-459C-ABD4-F5D2850BFBFD}"/>
+    <hyperlink ref="L70" r:id="rId75" xr:uid="{C8B23DFB-0783-41B8-ABC2-49EF1E8F4E4C}"/>
+    <hyperlink ref="L72" r:id="rId76" xr:uid="{F6E29A87-A4DE-4D36-A3F6-1EF40D094D20}"/>
+    <hyperlink ref="L73" r:id="rId77" xr:uid="{9C249EE3-FBC9-42B3-ADF3-45DA8444C250}"/>
+    <hyperlink ref="L74" r:id="rId78" xr:uid="{736CB61F-DB8D-4D34-831C-03D972612AD4}"/>
+    <hyperlink ref="L77" r:id="rId79" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/2012--DSC_0253-C%C3%A9notaphe-du-grand-Dauphin-par-Coustou-dans-la-cathedrale-de-Sens.jpg/960px-2012--DSC_0253-C%C3%A9notaphe-du-grand-Dauphin-par-Coustou-dans-la-cathedrale-de-Sens.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8B3A1AC7-EC23-47AE-952E-EBEB844B3107}"/>
+    <hyperlink ref="L75" r:id="rId80" xr:uid="{BAE1A9D4-896A-4274-B7A4-D7851AAFF3E4}"/>
+    <hyperlink ref="L76" r:id="rId81" xr:uid="{0876674F-89FF-491E-A710-E8D816C42436}"/>
+    <hyperlink ref="L83" r:id="rId82" xr:uid="{93422A34-E47F-4EC0-B9B6-C9390AF2A5A4}"/>
+    <hyperlink ref="L84" r:id="rId83" xr:uid="{239D762E-78B0-4394-89DF-444F8993C868}"/>
+    <hyperlink ref="L85" r:id="rId84" xr:uid="{C601465F-6588-4CFC-A32C-1D37F5CFF0E1}"/>
+    <hyperlink ref="L86" r:id="rId85" xr:uid="{0B562E20-DF22-47B8-B6FB-AD1E07393A01}"/>
+    <hyperlink ref="L87" r:id="rId86" xr:uid="{BE4D15ED-CB7B-4449-A950-1A890376BCA4}"/>
+    <hyperlink ref="L90" r:id="rId87" xr:uid="{6AB13AFE-2406-4E93-ADA6-46FDCD31365A}"/>
+    <hyperlink ref="L88" r:id="rId88" xr:uid="{C83A0152-012B-483B-9231-2A1E78BBD9C0}"/>
+    <hyperlink ref="L89" r:id="rId89" xr:uid="{47B42195-9EC3-40B8-9B46-BD6E6B84E07C}"/>
+    <hyperlink ref="L91" r:id="rId90" xr:uid="{FC084A53-72A5-46D6-BA8B-9EDF408325E8}"/>
+    <hyperlink ref="L93" r:id="rId91" xr:uid="{A0209D99-D2A7-4D01-9D4A-1D01BE96F274}"/>
+    <hyperlink ref="L94" r:id="rId92" xr:uid="{87800057-0E6E-4997-AE5C-8E9E992038EC}"/>
+    <hyperlink ref="L92" r:id="rId93" xr:uid="{219B437E-3E02-401E-B8DD-54C18AE1422E}"/>
+    <hyperlink ref="L95" r:id="rId94" xr:uid="{E4D15D0F-4493-49C9-82EC-921ADE7F7649}"/>
+    <hyperlink ref="L96" r:id="rId95" xr:uid="{08D0AD74-167F-460E-9E0D-87B452D8FCDA}"/>
+    <hyperlink ref="L97" r:id="rId96" xr:uid="{79C25996-0268-4345-9482-E6D0D91FBCDB}"/>
+    <hyperlink ref="L98" r:id="rId97" xr:uid="{6A6598FD-AB7A-4377-A28E-D84A11EE770B}"/>
+    <hyperlink ref="G97" r:id="rId98" xr:uid="{4968AB49-790D-4B21-834D-BD88FF405AF0}"/>
+    <hyperlink ref="L99" r:id="rId99" xr:uid="{6F6F2D1A-8AC2-4E8F-AD62-5895107640F4}"/>
+    <hyperlink ref="L102" r:id="rId100" xr:uid="{1A778003-D53A-46C7-9C4F-0866ED4A1FBF}"/>
+    <hyperlink ref="L100" r:id="rId101" xr:uid="{CEBDE0C6-0B4A-4C8F-BAEC-6CA4771D91A9}"/>
+    <hyperlink ref="L101" r:id="rId102" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/07/Venus_of_the_Doves_by_Etienne-Maurice_Falconet%2C_undated_mid_1700s%2C_marble_-_National_Gallery_of_Art%2C_Washington_-_DSC09976.JPG/1280px-Venus_of_the_Doves_by_Etienne-Maurice_Falconet%2C_undated_mid_1700s%2C_marble_-_National_Gallery_of_Art%2C_Washington_-_DSC09976.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{207012E8-F898-42AB-A943-D36FADE8F355}"/>
+    <hyperlink ref="L103" r:id="rId103" xr:uid="{BBF98FE5-4DFE-4FDD-A544-E80BC7A25126}"/>
+    <hyperlink ref="L104" r:id="rId104" xr:uid="{FF151DBC-7144-4288-A673-8F481A2C101A}"/>
+    <hyperlink ref="L106" r:id="rId105" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Monument_to_Lord_Mansfield%2C_Westminster_Abbey_01.jpg/960px-Monument_to_Lord_Mansfield%2C_Westminster_Abbey_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{C11B2C6E-208E-4A71-B269-E34EAE7C6083}"/>
+    <hyperlink ref="L107" r:id="rId106" xr:uid="{6ED28258-66B6-4B49-B8D7-3C03B0C1DC7C}"/>
+    <hyperlink ref="L108" r:id="rId107" xr:uid="{88433733-48D0-4D92-93C2-565748FFE72C}"/>
+    <hyperlink ref="L105" r:id="rId108" xr:uid="{DC64D51C-9988-44E8-A744-459093BA68A0}"/>
+    <hyperlink ref="L109" r:id="rId109" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/10/John_Flaxman_%281755-1826%29_-_Cephalus_and_Aurora_%281789-90%29_front%2C_Lady_Lever_Art_Gallery%2C_Port_Sunlight%2C_Cheshire%2C_June_2013_%289103113142%29.png/500px-John_Flaxman_%281755-1826%29_-_Cephalus_and_Aurora_%281789-90%29_front%2C_Lady_Lever_Art_Gallery%2C_Port_Sunlight%2C_Cheshire%2C_June_2013_%289103113142%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B7B496B9-90D1-4969-9870-7B7656D9A169}"/>
+    <hyperlink ref="L110" r:id="rId110" xr:uid="{28CC63AD-0682-4A87-A9F4-B621624C9015}"/>
+    <hyperlink ref="L111" r:id="rId111" xr:uid="{16C08E16-E991-4783-8EF3-C3F1417EEEA6}"/>
+    <hyperlink ref="L112" r:id="rId112" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg/960px-St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FF930F9C-A9AC-4607-A859-3ABD807649A4}"/>
+    <hyperlink ref="L113" r:id="rId113" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/St._Paulus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg/960px-St._Paulus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A801BD6C-0A7D-46EC-AA6B-F1137861AA28}"/>
+    <hyperlink ref="I112" r:id="rId114" xr:uid="{D76F3B05-FA60-432A-A109-15C083FC3E09}"/>
+    <hyperlink ref="I113" r:id="rId115" xr:uid="{82CED098-B306-46C4-9441-0AD55B76FFC2}"/>
+    <hyperlink ref="L114" r:id="rId116" xr:uid="{3B0D8049-B520-4810-B239-50AA43905165}"/>
+    <hyperlink ref="L115" r:id="rId117" xr:uid="{B1606A58-EDCF-48FA-BB29-771BF06A9515}"/>
+    <hyperlink ref="L116" r:id="rId118" xr:uid="{8FD76DC7-7F79-4F5A-83E7-5E8D60AA822D}"/>
+    <hyperlink ref="L117" r:id="rId119" xr:uid="{FA268604-165F-41CF-83A0-B2CBF8A0F863}"/>
+    <hyperlink ref="L120" r:id="rId120" xr:uid="{E764FD93-AA66-476B-ADC0-DCB38775F84F}"/>
+    <hyperlink ref="L118" r:id="rId121" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/06/Houdon_Jean_Antoine%2C_L%27%C3%A9corch%C3%A9_bras_lev%C3%A9%2C_Mus%C3%A9e_Fabre%2C_Montpellier.jpg/960px-Houdon_Jean_Antoine%2C_L%27%C3%A9corch%C3%A9_bras_lev%C3%A9%2C_Mus%C3%A9e_Fabre%2C_Montpellier.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CE4949A3-9DCD-4051-B144-545B5D6AE5FB}"/>
+    <hyperlink ref="L121" r:id="rId122" xr:uid="{D7E3DDA7-E4FC-4310-898E-48047F7A5160}"/>
+    <hyperlink ref="L119" r:id="rId123" xr:uid="{8FB74D72-A77F-4B4B-AE35-582003521528}"/>
+    <hyperlink ref="L154" r:id="rId124" xr:uid="{881AB544-C00A-4F17-BA6D-032A002C02EE}"/>
+    <hyperlink ref="L155" r:id="rId125" xr:uid="{85549018-4524-417C-8A3F-737C6216056C}"/>
+    <hyperlink ref="L122" r:id="rId126" xr:uid="{59D2448C-30F1-4EC0-B5EB-C506997C1927}"/>
+    <hyperlink ref="L125" r:id="rId127" xr:uid="{7AAF307B-3089-439D-9AB6-72FB4643435E}"/>
+    <hyperlink ref="L123" r:id="rId128" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/Galatea_by_Robert_Le_Lorrain%2C_1701%2C_marble_-_National_Gallery_of_Art%2C_Washington_-_DSC09966.JPG/960px-Galatea_by_Robert_Le_Lorrain%2C_1701%2C_marble_-_National_Gallery_of_Art%2C_Washington_-_DSC09966.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A2868C28-65B0-4F27-9DC1-D42AB35AAFC9}"/>
+    <hyperlink ref="L126" r:id="rId129" xr:uid="{CEE4BF6F-373A-4CAF-8057-D8C6CED562F1}"/>
+    <hyperlink ref="L127" r:id="rId130" xr:uid="{98158628-3FD0-43F9-B857-7013B4920514}"/>
+    <hyperlink ref="L124" r:id="rId131" xr:uid="{C5F3FFD6-AAED-4994-8C63-008E6F593707}"/>
+    <hyperlink ref="L128" r:id="rId132" xr:uid="{5C971F2A-99C4-4D45-A1C0-41660A874517}"/>
+    <hyperlink ref="L132" r:id="rId133" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0f/Buste_de_Maurice-Quentin_de_La_Tour_par_Jean-Baptiste_Lemoyne_-_Mus%C3%A9e_Antoine_L%C3%A9cuyer_Saint-Quentin.jpg/960px-Buste_de_Maurice-Quentin_de_La_Tour_par_Jean-Baptiste_Lemoyne_-_Mus%C3%A9e_Antoine_L%C3%A9cuyer_Saint-Quentin.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C583F16E-844A-4E26-AD66-BDF41E63BAB6}"/>
+    <hyperlink ref="L133" r:id="rId134" xr:uid="{14BBAE43-D799-4E87-B9ED-17E67F57D50C}"/>
+    <hyperlink ref="L129" r:id="rId135" xr:uid="{46584188-597F-4B8B-939B-F847C3E32BEE}"/>
+    <hyperlink ref="L131" r:id="rId136" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/11/WLA_metmuseum_La_Crainte_des_Traits_de_lAmour_by_Jean_Louis_Lemoyne.jpg/500px-WLA_metmuseum_La_Crainte_des_Traits_de_lAmour_by_Jean_Louis_Lemoyne.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{21150A3D-EE25-493D-8678-ECF98A81B21D}"/>
+    <hyperlink ref="L130" r:id="rId137" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7c/Buste_de_Marie-Antoinette_par_Jean_Baptiste_Lemoyne_-_1771.jpg/960px-Buste_de_Marie-Antoinette_par_Jean_Baptiste_Lemoyne_-_1771.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B398DE66-0DF2-445D-AC92-B6D871BF8C07}"/>
+    <hyperlink ref="L134" r:id="rId138" xr:uid="{B32DAEAF-CBB2-4B19-AE14-68256494C36B}"/>
+    <hyperlink ref="L136" r:id="rId139" xr:uid="{8039580C-466B-426C-920D-C43EE4192481}"/>
+    <hyperlink ref="L135" r:id="rId140" xr:uid="{8BD35C45-6C65-4F6B-BD3A-6522CC4929EC}"/>
+    <hyperlink ref="L137" r:id="rId141" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/56/The_Vexed_Man_%28Franz_Xaver_Messerschmidt%29%2C_Getty_Center.jpg/960px-The_Vexed_Man_%28Franz_Xaver_Messerschmidt%29%2C_Getty_Center.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{B7A5A066-179E-4D8B-BEE0-3683D11676E3}"/>
+    <hyperlink ref="L146" r:id="rId142" xr:uid="{7249162A-30B4-44C7-8EE0-081E5B3364A3}"/>
+    <hyperlink ref="L149" r:id="rId143" xr:uid="{68BF51D4-9BED-49CB-8DDB-50B9B2BD239B}"/>
+    <hyperlink ref="L147" r:id="rId144" xr:uid="{12EA42D0-C645-4657-805F-04515A86DDDF}"/>
+    <hyperlink ref="L148" r:id="rId145" xr:uid="{18E06423-54F7-45A2-B9B8-4CF6B73C873C}"/>
+    <hyperlink ref="L156" r:id="rId146" xr:uid="{2E169D95-96E0-493D-9728-13E61505FCB5}"/>
+    <hyperlink ref="L157" r:id="rId147" xr:uid="{CF8FD038-AD3C-46D0-9A82-51E15E47F02B}"/>
+    <hyperlink ref="L158" r:id="rId148" xr:uid="{C787A27C-45F7-43A3-8E5C-E46C5635382F}"/>
+    <hyperlink ref="L159" r:id="rId149" xr:uid="{DEBB429E-B33E-40EB-A760-A57487AF75E3}"/>
+    <hyperlink ref="L160" r:id="rId150" xr:uid="{1F01F486-638B-4803-96BD-163CCAAFC3AB}"/>
+    <hyperlink ref="L162" r:id="rId151" xr:uid="{239474DD-C3B8-46EE-B090-9EEF5E730499}"/>
+    <hyperlink ref="L161" r:id="rId152" xr:uid="{C21AD739-3C24-4EA2-8EB2-2F9F7C05837C}"/>
+    <hyperlink ref="L163" r:id="rId153" xr:uid="{1B12F134-C44F-479B-B2B4-89A0B8434F4D}"/>
+    <hyperlink ref="L168" r:id="rId154" xr:uid="{08DEE694-8FBB-4B47-9597-55263EBBC0B4}"/>
+    <hyperlink ref="L171" r:id="rId155" xr:uid="{200DA680-A0D2-4E22-8551-6EFA4CB091A6}"/>
+    <hyperlink ref="L169" r:id="rId156" xr:uid="{BDADEABC-9943-4795-AC79-BD5AB51E7DB6}"/>
+    <hyperlink ref="L172" r:id="rId157" xr:uid="{172E871D-6586-4D3B-A001-F45D6400E014}"/>
+    <hyperlink ref="L170" r:id="rId158" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Louis-Fran%C3%A7ois_Roubiliac_-_Alexander_Pope_-_B1993.27_-_Yale_Center_for_British_Art.jpg/960px-Louis-Fran%C3%A7ois_Roubiliac_-_Alexander_Pope_-_B1993.27_-_Yale_Center_for_British_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E6CB38CC-6BFB-4EB8-B269-7E2C880E9E08}"/>
+    <hyperlink ref="L180" r:id="rId159" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="L184" r:id="rId160" xr:uid="{4358A1D0-89BE-471E-BA57-F84F4C571F76}"/>
+    <hyperlink ref="L187" r:id="rId161" xr:uid="{C2DA4C69-7E2C-4B67-AC56-18105BC3E9C7}"/>
+    <hyperlink ref="L186" r:id="rId162" xr:uid="{F14BAA17-0CB0-4E27-AE63-3AD83FCD7B80}"/>
+    <hyperlink ref="L185" r:id="rId163" xr:uid="{EB54CAA1-4876-4617-B352-D3205DD1C5B2}"/>
+    <hyperlink ref="L188" r:id="rId164" xr:uid="{05CFA97D-37DA-46B5-AB7D-67BD08CA89D0}"/>
+    <hyperlink ref="L189" r:id="rId165" xr:uid="{E093538F-3696-4B3D-8D0F-C91FB54175CC}"/>
+    <hyperlink ref="L191" r:id="rId166" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Tomb_of_Philip_Bourbon_-_Cappella_dei_Borbone_-_Santa_Chiara_-_Naples.jpg/500px-Tomb_of_Philip_Bourbon_-_Cappella_dei_Borbone_-_Santa_Chiara_-_Naples.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D573DB3B-A16B-4FC9-9275-F3ABBA9FD4AA}"/>
+    <hyperlink ref="L190" r:id="rId167" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/91/Giuseppe_sanmartino%2C_san_francesco_in_estasi%2C_da_sant%27eframo_nuovo%2C_inv._427.JPG/960px-Giuseppe_sanmartino%2C_san_francesco_in_estasi%2C_da_sant%27eframo_nuovo%2C_inv._427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF3EA868-2419-4A6B-8E31-DB15568CDCB0}"/>
+    <hyperlink ref="L192" r:id="rId168" xr:uid="{6DE105E5-B19B-46CD-9AC3-6B0FA2C4640E}"/>
+    <hyperlink ref="L193" r:id="rId169" xr:uid="{08A6C5C5-05D3-4134-B12E-2916E88C4FA5}"/>
+    <hyperlink ref="L194" r:id="rId170" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/Johann_gottfried_schadow%2C_monumento_funebre_per_il_conte_alexander_von_der_mark%2C_1788-90%2C_01.jpg/960px-Johann_gottfried_schadow%2C_monumento_funebre_per_il_conte_alexander_von_der_mark%2C_1788-90%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C47CED85-B63A-466E-9984-B4A5146F90DC}"/>
+    <hyperlink ref="L195" r:id="rId171" xr:uid="{D76E3946-18FA-4BC6-BAC1-AF89F0A8514C}"/>
+    <hyperlink ref="L196" r:id="rId172" xr:uid="{56793C3D-E192-4A04-BB57-15A39E917646}"/>
+    <hyperlink ref="L197" r:id="rId173" xr:uid="{EF543571-EA5E-482E-B40B-E9ED54530277}"/>
+    <hyperlink ref="L198" r:id="rId174" xr:uid="{70DBA15C-5256-432A-8B1D-386B0F72090D}"/>
+    <hyperlink ref="L199" r:id="rId175" xr:uid="{D1D4D8C9-3F4D-4DBE-81AC-2CB15EEE593A}"/>
+    <hyperlink ref="L200" r:id="rId176" xr:uid="{0BF119AF-2474-485A-8385-4B94543AE7E9}"/>
+    <hyperlink ref="L201" r:id="rId177" xr:uid="{8F1627A4-1430-4DDC-8F4C-6D25B3C6305A}"/>
+    <hyperlink ref="L202" r:id="rId178" xr:uid="{7DF06C24-00A8-4B94-A167-80D2D767B547}"/>
+    <hyperlink ref="L203" r:id="rId179" xr:uid="{EAD52D1B-7ACB-4A08-849E-A72F62DC43BB}"/>
+    <hyperlink ref="K204" r:id="rId180" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Nancy%2C_%C3%A9glise_baroque_Notre_Dame_de_Bonsecours%2C_mausol%C3%A9e_de_Catherine_Opalinska_1.jpg/960px-Nancy%2C_%C3%A9glise_baroque_Notre_Dame_de_Bonsecours%2C_mausol%C3%A9e_de_Catherine_Opalinska_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{30250A7D-8DE5-446D-BEDF-8C7D1696BDBD}"/>
+    <hyperlink ref="K205" r:id="rId181" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8f/Michel-ange_slodtz%2C_chrys%C3%A9s_in_terracotta_1740_circa.JPG/960px-Michel-ange_slodtz%2C_chrys%C3%A9s_in_terracotta_1740_circa.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1C6422D5-1705-49AD-9231-CC8B4E521A9B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EA0DC1-C0F2-444E-8F71-BCFBE0529FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54508CE-8903-4FD9-8317-F1EB8B3BC268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2450" uniqueCount="952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2429" uniqueCount="933">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -404,15 +404,9 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e9/Wien_Augustinerkirche_Kenotaph_Maria_Christina_1.jpg/1280px-Wien_Augustinerkirche_Kenotaph_Maria_Christina_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>1795-1805</t>
-  </si>
-  <si>
     <t>Apsley House</t>
   </si>
   <si>
-    <t>Hall d'honneur</t>
-  </si>
-  <si>
     <t>Napoléon en Mars désarmé et pacificateur</t>
   </si>
   <si>
@@ -473,9 +467,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d4/Cristo_Crucificado%2C_Luis_Salvador_Carmona.jpg/960px-Cristo_Crucificado%2C_Luis_Salvador_Carmona.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Bois polychrome</t>
-  </si>
-  <si>
     <t>Joseph</t>
   </si>
   <si>
@@ -545,9 +536,6 @@
     <t>1732-1760</t>
   </si>
   <si>
-    <t>Abondance</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/%22Abundance%22_by_Filippo_della_Valle_%28Florence_1698-Rome_1768%29_-_Fountain_of_Trevi_%281732-1762%29_in_Rome_%2823235744623%29.jpg/960px-%22Abundance%22_by_Filippo_della_Valle_%28Florence_1698-Rome_1768%29_-_Fountain_of_Trevi_%281732-1762%29_in_Rome_%2823235744623%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -557,9 +545,6 @@
     <t>Basilique Saint-Jean-de-Latran</t>
   </si>
   <si>
-    <t>Chapelle Corsini</t>
-  </si>
-  <si>
     <t xml:space="preserve">L'Annonciation </t>
   </si>
   <si>
@@ -578,9 +563,6 @@
     <t>Bruxelles</t>
   </si>
   <si>
-    <t>Section 18e</t>
-  </si>
-  <si>
     <t>Hercule assis</t>
   </si>
   <si>
@@ -989,9 +971,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c8/Saint_Jean_l%27%C3%A9vang%C3%A9liste_statue_Latran.jpg/960px-Saint_Jean_l%27%C3%A9vang%C3%A9liste_statue_Latran.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Les Quatre Évangélistes</t>
-  </si>
-  <si>
     <t>John Michael</t>
   </si>
   <si>
@@ -1085,9 +1064,6 @@
     <t>Oratoire de San Domenico</t>
   </si>
   <si>
-    <t>L'Allégorie de la Simplicité</t>
-  </si>
-  <si>
     <t>La Prudenza</t>
   </si>
   <si>
@@ -1103,18 +1079,12 @@
     <t>Oratoire de San Lorenzo</t>
   </si>
   <si>
-    <t xml:space="preserve">Les Vertus </t>
-  </si>
-  <si>
     <t>Le Virtù</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/c/ce/OSL_%28Palermo%29_16_07_2019_13.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>Stuc (Gesso)</t>
-  </si>
-  <si>
     <t>René-Michel</t>
   </si>
   <si>
@@ -1214,9 +1184,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7f/LouvreAdamPoesie2.jpg/960px-LouvreAdamPoesie2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Groupe de deux rondes-bosses</t>
-  </si>
-  <si>
     <t>Versailles</t>
   </si>
   <si>
@@ -1244,9 +1211,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Nancy%2C_%C3%A9glise_baroque_Notre_Dame_de_Bonsecours%2C_mausol%C3%A9e_de_Catherine_Opalinska_1.jpg/960px-Nancy%2C_%C3%A9glise_baroque_Notre_Dame_de_Bonsecours%2C_mausol%C3%A9e_de_Catherine_Opalinska_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Monument funéraire composé de deux rondes-bosses et deux médaillons en bas-relief</t>
-  </si>
-  <si>
     <t>Musée Carnavalet</t>
   </si>
   <si>
@@ -1385,9 +1349,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Hastings_bust.jpg/960px-Hastings_bust.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
   </si>
   <si>
-    <t>Buste</t>
-  </si>
-  <si>
     <t>1744</t>
   </si>
   <si>
@@ -1412,9 +1373,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/LouvreBouchardonChrist.jpg/960px-LouvreBouchardonChrist.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Statue monumentale</t>
-  </si>
-  <si>
     <t>1750</t>
   </si>
   <si>
@@ -1427,9 +1385,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e4/Bouchardon_Genius_des_%C3%9Cberflusses.jpg/960px-Bouchardon_Genius_des_%C3%9Cberflusses.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>L'Hiver (Bassin de Versailles - modèle)</t>
-  </si>
-  <si>
     <t>L'Hiver</t>
   </si>
   <si>
@@ -1460,9 +1415,6 @@
     <t>1739</t>
   </si>
   <si>
-    <t>Navette latérale</t>
-  </si>
-  <si>
     <t>Tombeau de Maria Clementina Sobieska</t>
   </si>
   <si>
@@ -1472,9 +1424,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Pietro_Bracci.jpg/960px-Pietro_Bracci.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Monument funéraire avec quatre rondes-bosses</t>
-  </si>
-  <si>
     <t>Marbre et mosaïque</t>
   </si>
   <si>
@@ -1556,9 +1505,6 @@
     <t>Los Angeles</t>
   </si>
   <si>
-    <t>Getty Center</t>
-  </si>
-  <si>
     <t>L'Amour nourri par l'Espérance</t>
   </si>
   <si>
@@ -1589,9 +1535,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Antonio_Canova-Theseus_and_the_Minotaur-Victoria_and_Albert_Museum.jpg/960px-Antonio_Canova-Theseus_and_the_Minotaur-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Groupe sculpté en ronde-bosse</t>
-  </si>
-  <si>
     <t>322</t>
   </si>
   <si>
@@ -1655,9 +1598,6 @@
     <t>1716</t>
   </si>
   <si>
-    <t>La Foi (Femme voilée)</t>
-  </si>
-  <si>
     <t>La Fede</t>
   </si>
   <si>
@@ -1685,9 +1625,6 @@
     <t>Cathédrale Notre-Dame de Paris</t>
   </si>
   <si>
-    <t>Pietà (Descente de croix / Vœu de Louis XIII)</t>
-  </si>
-  <si>
     <t>Pietà</t>
   </si>
   <si>
@@ -1790,9 +1727,6 @@
     <t>Cathédrale Saint-Étienne</t>
   </si>
   <si>
-    <t>Monument funéraire du Dauphin Louis de France</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/2012--DSC_0253-C%C3%A9notaphe-du-grand-Dauphin-par-Coustou-dans-la-cathedrale-de-Sens.jpg/960px-2012--DSC_0253-C%C3%A9notaphe-du-grand-Dauphin-par-Coustou-dans-la-cathedrale-de-Sens.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -1805,9 +1739,6 @@
     <t>40</t>
   </si>
   <si>
-    <t>Niche de droite</t>
-  </si>
-  <si>
     <t>La Salubrité</t>
   </si>
   <si>
@@ -1823,9 +1754,6 @@
     <t>Vatican</t>
   </si>
   <si>
-    <t>Niche de la nef</t>
-  </si>
-  <si>
     <t>Sainte Thérèse d'Avila</t>
   </si>
   <si>
@@ -1859,9 +1787,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/8/84/Gent%2C_Sint-Baafskathedraal_Preekstoel_B_STB_122_07.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>Chaire à prêcher</t>
-  </si>
-  <si>
     <t>Marbre et bois de chêne</t>
   </si>
   <si>
@@ -1889,9 +1814,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9f/Delvaux%27s_Vertumnus_and_Pomona.JPG/960px-Delvaux%27s_Vertumnus_and_Pomona.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>La Providence</t>
-  </si>
-  <si>
     <t>150</t>
   </si>
   <si>
@@ -1955,9 +1877,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/32/Georg_Raphael_Donner_-_Christus_am_Jakobsbrunnen.JPG/960px-Georg_Raphael_Donner_-_Christus_am_Jakobsbrunnen.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Bas-relief / Lavabo</t>
-  </si>
-  <si>
     <t>102</t>
   </si>
   <si>
@@ -2045,9 +1964,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/78/Tribute_to_William_Collins_at_Chichester_Cathedral.jpg/960px-Tribute_to_William_Collins_at_Chichester_Cathedral.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Bas-relief / Monument funéraire</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -2222,12 +2138,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/50/Houdon_Sophie_Arnould_Iphig%C3%A9nie.jpg/960px-Houdon_Sophie_Arnould_Iphig%C3%A9nie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>La Frileuse</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/67/Jean-Antoine_Houdon-La_frileuse.JPG/960px-Jean-Antoine_Houdon-La_frileuse.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -2261,9 +2171,6 @@
     <t>1701</t>
   </si>
   <si>
-    <t>West Building, Galerie M54</t>
-  </si>
-  <si>
     <t>Galatée</t>
   </si>
   <si>
@@ -2282,9 +2189,6 @@
     <t>Hôtel de Soubise</t>
   </si>
   <si>
-    <t>Façade principale</t>
-  </si>
-  <si>
     <t>Allégories des Quatre Saisons</t>
   </si>
   <si>
@@ -2294,18 +2198,12 @@
     <t>1710</t>
   </si>
   <si>
-    <t>Allée méridionale / Bosquet des Dômes</t>
-  </si>
-  <si>
     <t>Bacchus</t>
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3c/Versailles_Demi-Lune_Bacchus_Le_Lorrain.jpg/960px-Versailles_Demi-Lune_Bacchus_Le_Lorrain.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Département des Sculptures</t>
-  </si>
-  <si>
     <t>Andromède enchaînée au rocher</t>
   </si>
   <si>
@@ -2321,9 +2219,6 @@
     <t>Palais des Rohan</t>
   </si>
   <si>
-    <t>Façade et intérieurs</t>
-  </si>
-  <si>
     <t>Décors sculptés du Palais des Rohan</t>
   </si>
   <si>
@@ -2336,9 +2231,6 @@
     <t>58</t>
   </si>
   <si>
-    <t>Aile Richelieu - Cour Puget</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a9/Vertumne_et_pomone.JPG/1280px-Vertumne_et_pomone.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -2396,9 +2288,6 @@
     <t>82</t>
   </si>
   <si>
-    <t>SérieTêtes de caractère</t>
-  </si>
-  <si>
     <t>Palais du Belvedere</t>
   </si>
   <si>
@@ -2429,9 +2318,6 @@
     <t>Alliage de plomb</t>
   </si>
   <si>
-    <t>J. Paul Getty Museum</t>
-  </si>
-  <si>
     <t>L'Homme piqué par une mouche</t>
   </si>
   <si>
@@ -2465,9 +2351,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Clodion_-_Bacchante_Supported_by_Bacchus_and_a_Faun_-_Norton_Simon_Museum_-_01.jpg/960px-Clodion_-_Bacchante_Supported_by_Bacchus_and_a_Faun_-_Norton_Simon_Museum_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=eo</t>
   </si>
   <si>
-    <t>L'Intoxication au vin</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/39/The_Intoxication_of_Wine_MET_DP218007.jpg/960px-The_Intoxication_of_Wine_MET_DP218007.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=eo</t>
   </si>
   <si>
@@ -2543,9 +2426,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/0/01/L%27Amiti%C3%A9_sous_les_traits_de_Mme_de_Pompadour_Pigalle_Louvre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>Église de Saint-Sulpice</t>
-  </si>
-  <si>
     <t>Vierge à l'Enfant</t>
   </si>
   <si>
@@ -2579,9 +2459,6 @@
     <t>Trinity College</t>
   </si>
   <si>
-    <t>Antechapel</t>
-  </si>
-  <si>
     <t>Statue d'Isaac Newton</t>
   </si>
   <si>
@@ -2642,9 +2519,6 @@
     <t>Sant'Andrea</t>
   </si>
   <si>
-    <t>Les Apôtres</t>
-  </si>
-  <si>
     <t>425</t>
   </si>
   <si>
@@ -2687,24 +2561,12 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Monument_to_John_Milton%2C_Westminster_Abbey_01.jpg/960px-Monument_to_John_Milton%2C_Westminster_Abbey_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Statue de Sir Hans Sloane</t>
-  </si>
-  <si>
     <t>Statue of Sir Hans Sloane</t>
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/10/Hans_Sloane_bust.jpg/1280px-Hans_Sloane_bust.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Statue</t>
-  </si>
-  <si>
-    <t>1756</t>
-  </si>
-  <si>
-    <t>Le Baiser de Judas (L'Arrestation)</t>
-  </si>
-  <si>
     <t>El Prendimiento</t>
   </si>
   <si>
@@ -2720,9 +2582,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/26/Jes%C3%BAs_en_la_columna_20231222_195757_01.jpg/960px-Jes%C3%BAs_en_la_columna_20231222_195757_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>La Chute (Le Christ sur le chemin du Calvaire)</t>
-  </si>
-  <si>
     <t>La Caída</t>
   </si>
   <si>
@@ -2774,9 +2633,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/5/57/Brandenburg_gate_sunset_quadriga.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>Ronde-bosse (groupe monumental)</t>
-  </si>
-  <si>
     <t>Cuivre repoussé</t>
   </si>
   <si>
@@ -2889,6 +2745,93 @@
   </si>
   <si>
     <t xml:space="preserve">Ronde-bosse </t>
+  </si>
+  <si>
+    <t>La Constance</t>
+  </si>
+  <si>
+    <t>La Prudence</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/Iphig%C3%A9nie_-_Michel-Ange_Slodtz_-_Mus%C3%A9e_du_Louvre_Sculptures_ENT_1984.23.jpg/960px-Iphig%C3%A9nie_-_Michel-Ange_Slodtz_-_Mus%C3%A9e_du_Louvre_Sculptures_ENT_1984.23.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Michel-Ange SLODTZ</t>
+  </si>
+  <si>
+    <t>Fontaine de la Providence</t>
+  </si>
+  <si>
+    <t>Centre Getty</t>
+  </si>
+  <si>
+    <t>Groupe en ronde-bosse</t>
+  </si>
+  <si>
+    <t>Haut-relief de façade sur pierre de bossage</t>
+  </si>
+  <si>
+    <t>1780 environ</t>
+  </si>
+  <si>
+    <t>L'Ivresse</t>
+  </si>
+  <si>
+    <t>Copie de 1790 d'après l'original de 1761</t>
+  </si>
+  <si>
+    <t>1748 (l'installation date de 1777)</t>
+  </si>
+  <si>
+    <t>Le Baiser de Judas</t>
+  </si>
+  <si>
+    <t>1802-1806</t>
+  </si>
+  <si>
+    <t>La Frileuse (version originale)</t>
+  </si>
+  <si>
+    <t>Bois polychromé</t>
+  </si>
+  <si>
+    <t>Monument liturgique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bas-relief </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Monument funéraire</t>
+  </si>
+  <si>
+    <t>Tombeau du Dauphin Louis de France</t>
+  </si>
+  <si>
+    <t>Monument avec  rondes-bosses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Chute </t>
+  </si>
+  <si>
+    <t>400 (statue) 400 (socle)</t>
+  </si>
+  <si>
+    <t>285 (statue) 320 (socle)</t>
+  </si>
+  <si>
+    <t>Buste de Sir Hans Sloane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groupe en ronde-bosse </t>
+  </si>
+  <si>
+    <t>L'Abondance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Foi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pietà </t>
   </si>
 </sst>
 </file>
@@ -2951,12 +2894,30 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -2990,7 +2951,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3022,6 +2983,19 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3326,13 +3300,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y205"/>
+  <dimension ref="A1:Y209"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="4.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" customWidth="1"/>
+    <col min="11" max="11" width="40.7109375" customWidth="1"/>
     <col min="12" max="12" width="9.140625" style="7" customWidth="1"/>
+    <col min="15" max="15" width="6.140625" customWidth="1"/>
+    <col min="16" max="17" width="9.140625" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="28.85546875" customWidth="1"/>
     <col min="20" max="23" width="9.140625" style="1"/>
     <col min="24" max="24" width="15.140625" style="1" customWidth="1"/>
@@ -3424,7 +3403,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>3</v>
@@ -3487,10 +3466,10 @@
         <v>22</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3501,7 +3480,7 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D3" t="s">
         <v>27</v>
@@ -3519,22 +3498,22 @@
         <v>31</v>
       </c>
       <c r="R3" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S3" t="s">
         <v>25</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X3" s="1" t="s">
         <v>26</v>
@@ -3551,10 +3530,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D4" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="F4" t="s">
         <v>32</v>
@@ -3569,22 +3548,22 @@
         <v>35</v>
       </c>
       <c r="R4" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S4" t="s">
         <v>36</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X4" s="1" t="s">
         <v>26</v>
@@ -3601,25 +3580,25 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D5">
         <v>1749</v>
       </c>
       <c r="E5" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="F5" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="J5" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="R5" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S5" t="s">
         <v>25</v>
@@ -3634,7 +3613,7 @@
         <v>155</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X5" s="1" t="s">
         <v>26</v>
@@ -3651,31 +3630,31 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
+        <v>362</v>
+      </c>
+      <c r="D6" t="s">
+        <v>377</v>
+      </c>
+      <c r="E6" t="s">
+        <v>371</v>
+      </c>
+      <c r="F6" t="s">
         <v>372</v>
       </c>
-      <c r="D6" t="s">
-        <v>387</v>
-      </c>
-      <c r="E6" t="s">
-        <v>381</v>
-      </c>
-      <c r="F6" t="s">
-        <v>382</v>
-      </c>
       <c r="J6" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="R6" t="s">
-        <v>393</v>
+        <v>910</v>
       </c>
       <c r="S6" t="s">
         <v>25</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="U6" s="1">
         <v>185</v>
@@ -3684,7 +3663,7 @@
         <v>150</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X6" s="1" t="s">
         <v>26</v>
@@ -3701,7 +3680,7 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D7">
         <v>1752</v>
@@ -3713,10 +3692,10 @@
         <v>29</v>
       </c>
       <c r="J7" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="R7" t="s">
         <v>24</v>
@@ -3734,7 +3713,7 @@
         <v>80</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X7" s="1" t="s">
         <v>26</v>
@@ -3751,22 +3730,22 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D8">
         <v>1749</v>
       </c>
       <c r="E8" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="F8" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="J8" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="R8" t="s">
         <v>24</v>
@@ -3784,7 +3763,7 @@
         <v>46</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X8" s="1" t="s">
         <v>26</v>
@@ -3816,7 +3795,7 @@
         <v>40</v>
       </c>
       <c r="R9" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S9" t="s">
         <v>25</v>
@@ -3831,7 +3810,7 @@
         <v>48</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X9" s="1" t="s">
         <v>37</v>
@@ -3851,19 +3830,19 @@
         <v>1737</v>
       </c>
       <c r="E10" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="F10" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="J10" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="R10" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="S10" t="s">
         <v>58</v>
@@ -3875,7 +3854,7 @@
         <v>137</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X10" s="1" t="s">
         <v>37</v>
@@ -3895,19 +3874,19 @@
         <v>1749</v>
       </c>
       <c r="E11" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="F11" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="J11" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="R11" t="s">
-        <v>403</v>
+        <v>53</v>
       </c>
       <c r="S11" t="s">
         <v>25</v>
@@ -3922,7 +3901,7 @@
         <v>120</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X11" s="1" t="s">
         <v>37</v>
@@ -3945,19 +3924,19 @@
         <v>28</v>
       </c>
       <c r="F12" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="J12" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="R12" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="S12" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="T12" s="1">
         <v>110</v>
@@ -3969,7 +3948,7 @@
         <v>26</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X12" s="1" t="s">
         <v>37</v>
@@ -3992,19 +3971,19 @@
         <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="J13" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="R13" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="S13" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="T13" s="1">
         <v>113</v>
@@ -4016,7 +3995,7 @@
         <v>22</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X13" s="1" t="s">
         <v>37</v>
@@ -4039,19 +4018,19 @@
         <v>28</v>
       </c>
       <c r="F14" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="J14" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="R14" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="S14" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="T14" s="1">
         <v>101</v>
@@ -4063,7 +4042,7 @@
         <v>18.5</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X14" s="1" t="s">
         <v>37</v>
@@ -4089,7 +4068,7 @@
         <v>29</v>
       </c>
       <c r="J15" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="L15" s="9" t="s">
         <v>44</v>
@@ -4101,16 +4080,16 @@
         <v>25</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X15" s="1" t="s">
         <v>41</v>
@@ -4127,7 +4106,7 @@
         <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
@@ -4136,10 +4115,10 @@
         <v>29</v>
       </c>
       <c r="J16" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="R16" t="s">
         <v>24</v>
@@ -4157,7 +4136,7 @@
         <v>100</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X16" s="1" t="s">
         <v>41</v>
@@ -4186,7 +4165,7 @@
         <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="E21" t="s">
         <v>48</v>
@@ -4210,16 +4189,16 @@
         <v>25</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X21" s="1" t="s">
         <v>46</v>
@@ -4236,7 +4215,7 @@
         <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="E22" t="s">
         <v>48</v>
@@ -4254,19 +4233,19 @@
         <v>57</v>
       </c>
       <c r="R22" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S22" t="s">
         <v>58</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="W22" s="1">
         <v>3</v>
@@ -4286,7 +4265,7 @@
         <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="E23" t="s">
         <v>48</v>
@@ -4310,16 +4289,16 @@
         <v>25</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X23" s="1" t="s">
         <v>46</v>
@@ -4336,25 +4315,25 @@
         <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E24" t="s">
         <v>48</v>
       </c>
       <c r="F24" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="J24" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="K24" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="R24" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="S24" t="s">
         <v>25</v>
@@ -4369,7 +4348,7 @@
         <v>60</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X24" s="1" t="s">
         <v>46</v>
@@ -4404,7 +4383,7 @@
         <v>68</v>
       </c>
       <c r="R25" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S25" t="s">
         <v>25</v>
@@ -4445,16 +4424,16 @@
         <v>49</v>
       </c>
       <c r="J26" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="K26" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="R26" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="S26" t="s">
         <v>25</v>
@@ -4489,28 +4468,28 @@
         <v>1789</v>
       </c>
       <c r="E27" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="F27" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="H27" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="J27" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="K27" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="R27" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="S27" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="T27" s="1">
         <v>250</v>
@@ -4545,19 +4524,19 @@
         <v>48</v>
       </c>
       <c r="F28" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="J28" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="K28" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="R28" t="s">
-        <v>450</v>
+        <v>24</v>
       </c>
       <c r="S28" t="s">
         <v>25</v>
@@ -4645,7 +4624,7 @@
         <v>70</v>
       </c>
       <c r="D32" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
@@ -4695,7 +4674,7 @@
         <v>70</v>
       </c>
       <c r="D33" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E33" t="s">
         <v>28</v>
@@ -4745,28 +4724,25 @@
         <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="E34" t="s">
         <v>86</v>
       </c>
       <c r="F34" t="s">
-        <v>173</v>
-      </c>
-      <c r="H34" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J34" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="K34" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="R34" t="s">
-        <v>450</v>
+        <v>24</v>
       </c>
       <c r="S34" t="s">
         <v>25</v>
@@ -4807,16 +4783,16 @@
         <v>29</v>
       </c>
       <c r="J35" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="K35" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="R35" t="s">
-        <v>459</v>
+        <v>24</v>
       </c>
       <c r="S35" t="s">
         <v>25</v>
@@ -4848,22 +4824,22 @@
         <v>70</v>
       </c>
       <c r="D36" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="E36" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="F36" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="J36" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="K36" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="R36" t="s">
         <v>24</v>
@@ -4913,16 +4889,16 @@
         <v>75</v>
       </c>
       <c r="J37" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="K37" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="R37" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="S37" t="s">
         <v>77</v>
@@ -4969,16 +4945,16 @@
         <v>75</v>
       </c>
       <c r="J38" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="K38" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="R38" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="S38" t="s">
         <v>77</v>
@@ -5019,13 +4995,13 @@
         <v>87</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="H39" t="s">
         <v>88</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="J39" t="s">
         <v>89</v>
@@ -5043,16 +5019,16 @@
         <v>25</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="U39" s="1" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X39" s="1" t="s">
         <v>84</v>
@@ -5069,7 +5045,7 @@
         <v>85</v>
       </c>
       <c r="D40" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="E40" t="s">
         <v>86</v>
@@ -5077,35 +5053,32 @@
       <c r="F40" t="s">
         <v>105</v>
       </c>
-      <c r="H40" t="s">
-        <v>475</v>
-      </c>
       <c r="J40" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="K40" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="R40" t="s">
-        <v>479</v>
+        <v>53</v>
       </c>
       <c r="S40" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="V40" s="1" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X40" s="1" t="s">
         <v>84</v>
@@ -5115,41 +5088,35 @@
       </c>
     </row>
     <row r="41" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>84</v>
-      </c>
       <c r="B41" t="s">
         <v>85</v>
       </c>
       <c r="D41" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="E41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F41" t="s">
-        <v>483</v>
-      </c>
-      <c r="H41" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="J41" t="s">
-        <v>486</v>
+        <v>469</v>
       </c>
       <c r="K41" t="s">
-        <v>487</v>
+        <v>470</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="R41" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="S41" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="T41" s="1">
         <v>800</v>
@@ -5161,7 +5128,7 @@
         <v>200</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X41" s="1" t="s">
         <v>84</v>
@@ -5178,22 +5145,22 @@
         <v>85</v>
       </c>
       <c r="D42" t="s">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="E42" t="s">
         <v>86</v>
       </c>
       <c r="F42" t="s">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="J42" t="s">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="K42" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="R42" t="s">
         <v>53</v>
@@ -5202,16 +5169,16 @@
         <v>25</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X42" s="1" t="s">
         <v>84</v>
@@ -5249,16 +5216,16 @@
         <v>101</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X43" s="1" t="s">
         <v>94</v>
@@ -5275,19 +5242,19 @@
         <v>95</v>
       </c>
       <c r="D44" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="E44" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="F44" t="s">
         <v>98</v>
       </c>
       <c r="J44" t="s">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
       <c r="R44" t="s">
         <v>24</v>
@@ -5305,7 +5272,7 @@
         <v>125</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X44" s="1" t="s">
         <v>94</v>
@@ -5331,10 +5298,10 @@
         <v>98</v>
       </c>
       <c r="J45" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="R45" t="s">
         <v>24</v>
@@ -5352,7 +5319,7 @@
         <v>29</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X45" s="1" t="s">
         <v>94</v>
@@ -5378,10 +5345,10 @@
         <v>29</v>
       </c>
       <c r="J46" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="R46" t="s">
         <v>24</v>
@@ -5399,7 +5366,7 @@
         <v>128</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X46" s="1" t="s">
         <v>94</v>
@@ -5419,19 +5386,19 @@
         <v>1769</v>
       </c>
       <c r="E47" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
       <c r="F47" t="s">
-        <v>507</v>
+        <v>909</v>
       </c>
       <c r="J47" t="s">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>509</v>
+        <v>491</v>
       </c>
       <c r="R47" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S47" t="s">
         <v>25</v>
@@ -5446,7 +5413,7 @@
         <v>34</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X47" s="1" t="s">
         <v>94</v>
@@ -5466,16 +5433,16 @@
         <v>1785</v>
       </c>
       <c r="E48" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="F48" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="J48" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>513</v>
+        <v>495</v>
       </c>
       <c r="R48" t="s">
         <v>24</v>
@@ -5493,7 +5460,7 @@
         <v>30</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X48" s="1" t="s">
         <v>94</v>
@@ -5578,7 +5545,7 @@
         <v>112</v>
       </c>
       <c r="R50" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S50" t="s">
         <v>25</v>
@@ -5710,25 +5677,22 @@
         <v>103</v>
       </c>
       <c r="D53" t="s">
-        <v>123</v>
+        <v>917</v>
       </c>
       <c r="E53" t="s">
         <v>48</v>
       </c>
       <c r="F53" t="s">
+        <v>123</v>
+      </c>
+      <c r="J53" t="s">
         <v>124</v>
       </c>
-      <c r="H53" t="s">
+      <c r="K53" t="s">
         <v>125</v>
       </c>
-      <c r="J53" t="s">
+      <c r="L53" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="K53" t="s">
-        <v>127</v>
-      </c>
-      <c r="L53" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="R53" t="s">
         <v>24</v>
@@ -5766,19 +5730,19 @@
         <v>1796</v>
       </c>
       <c r="E54" t="s">
+        <v>127</v>
+      </c>
+      <c r="F54" t="s">
+        <v>128</v>
+      </c>
+      <c r="J54" t="s">
         <v>129</v>
       </c>
-      <c r="F54" t="s">
+      <c r="K54" t="s">
         <v>130</v>
       </c>
-      <c r="J54" t="s">
+      <c r="L54" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="K54" t="s">
-        <v>132</v>
-      </c>
-      <c r="L54" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="R54" t="s">
         <v>24</v>
@@ -5813,22 +5777,22 @@
         <v>103</v>
       </c>
       <c r="D55" t="s">
+        <v>132</v>
+      </c>
+      <c r="E55" t="s">
+        <v>133</v>
+      </c>
+      <c r="F55" t="s">
         <v>134</v>
       </c>
-      <c r="E55" t="s">
+      <c r="J55" t="s">
         <v>135</v>
       </c>
-      <c r="F55" t="s">
+      <c r="K55" t="s">
         <v>136</v>
       </c>
-      <c r="J55" t="s">
+      <c r="L55" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="K55" t="s">
-        <v>138</v>
-      </c>
-      <c r="L55" s="10" t="s">
-        <v>139</v>
       </c>
       <c r="R55" t="s">
         <v>24</v>
@@ -5863,7 +5827,7 @@
         <v>103</v>
       </c>
       <c r="D56" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="E56" t="s">
         <v>48</v>
@@ -5872,16 +5836,16 @@
         <v>65</v>
       </c>
       <c r="J56" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="K56" t="s">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="R56" t="s">
-        <v>518</v>
+        <v>910</v>
       </c>
       <c r="S56" t="s">
         <v>25</v>
@@ -5907,134 +5871,134 @@
     </row>
     <row r="57" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>138</v>
+      </c>
+      <c r="B57" t="s">
+        <v>139</v>
+      </c>
+      <c r="D57" t="s">
         <v>140</v>
       </c>
-      <c r="B57" t="s">
+      <c r="E57" t="s">
         <v>141</v>
       </c>
-      <c r="D57" t="s">
+      <c r="F57" t="s">
+        <v>548</v>
+      </c>
+      <c r="J57" t="s">
         <v>142</v>
       </c>
-      <c r="E57" t="s">
+      <c r="L57" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="F57" t="s">
-        <v>569</v>
-      </c>
-      <c r="J57" t="s">
-        <v>144</v>
-      </c>
-      <c r="L57" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="R57" t="s">
         <v>24</v>
       </c>
       <c r="S57" t="s">
-        <v>146</v>
+        <v>919</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="U57" s="1" t="s">
-        <v>520</v>
+        <v>501</v>
       </c>
       <c r="V57" s="1" t="s">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="W57" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X57" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Y57" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B58" t="s">
+        <v>139</v>
+      </c>
+      <c r="D58" t="s">
+        <v>503</v>
+      </c>
+      <c r="E58" t="s">
         <v>141</v>
       </c>
-      <c r="D58" t="s">
-        <v>522</v>
-      </c>
-      <c r="E58" t="s">
-        <v>143</v>
-      </c>
       <c r="F58" t="s">
-        <v>569</v>
+        <v>548</v>
       </c>
       <c r="J58" t="s">
-        <v>523</v>
+        <v>504</v>
       </c>
       <c r="K58" t="s">
-        <v>524</v>
+        <v>505</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>525</v>
+        <v>506</v>
       </c>
       <c r="R58" t="s">
         <v>24</v>
       </c>
       <c r="S58" t="s">
-        <v>146</v>
+        <v>919</v>
       </c>
       <c r="W58" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X58" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Y58" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B59" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D59" t="s">
         <v>96</v>
       </c>
       <c r="E59" t="s">
-        <v>526</v>
+        <v>507</v>
       </c>
       <c r="F59" t="s">
-        <v>527</v>
+        <v>508</v>
       </c>
       <c r="H59" t="s">
-        <v>528</v>
+        <v>509</v>
       </c>
       <c r="J59" t="s">
-        <v>529</v>
+        <v>510</v>
       </c>
       <c r="K59" t="s">
-        <v>530</v>
+        <v>511</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>531</v>
+        <v>512</v>
       </c>
       <c r="R59" t="s">
-        <v>532</v>
+        <v>910</v>
       </c>
       <c r="S59" t="s">
-        <v>146</v>
+        <v>919</v>
       </c>
       <c r="W59" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X59" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Y59" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="60" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6045,25 +6009,25 @@
         <v>102</v>
       </c>
       <c r="B61" t="s">
+        <v>146</v>
+      </c>
+      <c r="D61" t="s">
+        <v>147</v>
+      </c>
+      <c r="E61" t="s">
+        <v>133</v>
+      </c>
+      <c r="F61" t="s">
+        <v>148</v>
+      </c>
+      <c r="J61" t="s">
         <v>149</v>
       </c>
-      <c r="D61" t="s">
+      <c r="K61" t="s">
+        <v>514</v>
+      </c>
+      <c r="L61" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="E61" t="s">
-        <v>135</v>
-      </c>
-      <c r="F61" t="s">
-        <v>151</v>
-      </c>
-      <c r="J61" t="s">
-        <v>152</v>
-      </c>
-      <c r="K61" t="s">
-        <v>533</v>
-      </c>
-      <c r="L61" s="4" t="s">
-        <v>153</v>
       </c>
       <c r="R61" t="s">
         <v>24</v>
@@ -6084,7 +6048,7 @@
         <v>102</v>
       </c>
       <c r="Y61" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6092,25 +6056,25 @@
         <v>102</v>
       </c>
       <c r="B62" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D62">
         <v>1722</v>
       </c>
       <c r="E62" t="s">
-        <v>534</v>
+        <v>515</v>
       </c>
       <c r="F62" t="s">
-        <v>535</v>
+        <v>516</v>
       </c>
       <c r="J62" t="s">
-        <v>536</v>
+        <v>517</v>
       </c>
       <c r="K62" t="s">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="R62" t="s">
         <v>24</v>
@@ -6134,7 +6098,7 @@
         <v>102</v>
       </c>
       <c r="Y62" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6142,10 +6106,10 @@
         <v>102</v>
       </c>
       <c r="B63" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D63" t="s">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="E63" t="s">
         <v>28</v>
@@ -6154,13 +6118,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="s">
-        <v>540</v>
+        <v>931</v>
       </c>
       <c r="K63" t="s">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>542</v>
+        <v>522</v>
       </c>
       <c r="R63" t="s">
         <v>24</v>
@@ -6184,7 +6148,7 @@
         <v>102</v>
       </c>
       <c r="Y63" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6192,25 +6156,25 @@
         <v>102</v>
       </c>
       <c r="B64" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D64" t="s">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="E64" t="s">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="F64" t="s">
-        <v>568</v>
+        <v>547</v>
       </c>
       <c r="J64" t="s">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="K64" t="s">
-        <v>546</v>
+        <v>526</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>547</v>
+        <v>527</v>
       </c>
       <c r="R64" t="s">
         <v>24</v>
@@ -6225,15 +6189,15 @@
         <v>102</v>
       </c>
       <c r="Y64" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B65" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D65">
         <v>1712</v>
@@ -6245,10 +6209,10 @@
         <v>29</v>
       </c>
       <c r="J65" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L65" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="R65" t="s">
         <v>24</v>
@@ -6269,39 +6233,39 @@
         <v>2</v>
       </c>
       <c r="X65" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Y65" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="66" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B66" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D66" t="s">
-        <v>548</v>
+        <v>528</v>
       </c>
       <c r="E66" t="s">
         <v>28</v>
       </c>
       <c r="F66" t="s">
-        <v>549</v>
+        <v>529</v>
       </c>
       <c r="H66" t="s">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="J66" t="s">
-        <v>550</v>
+        <v>932</v>
       </c>
       <c r="K66" t="s">
-        <v>551</v>
+        <v>530</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>552</v>
+        <v>531</v>
       </c>
       <c r="R66" t="s">
         <v>24</v>
@@ -6316,18 +6280,18 @@
         <v>2</v>
       </c>
       <c r="X66" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Y66" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="67" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B67" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D67">
         <v>1710</v>
@@ -6339,13 +6303,13 @@
         <v>29</v>
       </c>
       <c r="J67" t="s">
-        <v>553</v>
+        <v>532</v>
       </c>
       <c r="K67" t="s">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>555</v>
+        <v>534</v>
       </c>
       <c r="R67" t="s">
         <v>24</v>
@@ -6366,18 +6330,18 @@
         <v>2</v>
       </c>
       <c r="X67" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Y67" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="68" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B68" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D68">
         <v>1731</v>
@@ -6389,13 +6353,13 @@
         <v>29</v>
       </c>
       <c r="J68" t="s">
-        <v>556</v>
+        <v>535</v>
       </c>
       <c r="K68" t="s">
-        <v>556</v>
+        <v>535</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>557</v>
+        <v>536</v>
       </c>
       <c r="R68" t="s">
         <v>24</v>
@@ -6416,21 +6380,21 @@
         <v>2</v>
       </c>
       <c r="X68" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Y68" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="69" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E69" t="s">
         <v>28</v>
@@ -6439,10 +6403,10 @@
         <v>29</v>
       </c>
       <c r="J69" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="R69" t="s">
         <v>24</v>
@@ -6463,21 +6427,21 @@
         <v>2</v>
       </c>
       <c r="X69" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y69" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="70" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B70" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D70" t="s">
-        <v>558</v>
+        <v>537</v>
       </c>
       <c r="E70" t="s">
         <v>28</v>
@@ -6486,13 +6450,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="s">
-        <v>559</v>
+        <v>538</v>
       </c>
       <c r="K70" t="s">
-        <v>559</v>
+        <v>538</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>560</v>
+        <v>539</v>
       </c>
       <c r="R70" t="s">
         <v>24</v>
@@ -6513,21 +6477,21 @@
         <v>2</v>
       </c>
       <c r="X70" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y70" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="71" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B71" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D71" t="s">
-        <v>561</v>
+        <v>540</v>
       </c>
       <c r="E71" t="s">
         <v>28</v>
@@ -6536,16 +6500,16 @@
         <v>29</v>
       </c>
       <c r="J71" t="s">
-        <v>562</v>
+        <v>541</v>
       </c>
       <c r="K71" t="s">
-        <v>562</v>
+        <v>541</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>563</v>
+        <v>542</v>
       </c>
       <c r="R71" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S71" t="s">
         <v>25</v>
@@ -6563,18 +6527,18 @@
         <v>2</v>
       </c>
       <c r="X71" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y71" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="72" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B72" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D72">
         <v>1704</v>
@@ -6586,13 +6550,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>565</v>
+        <v>544</v>
       </c>
       <c r="R72" t="s">
-        <v>393</v>
+        <v>910</v>
       </c>
       <c r="S72" t="s">
         <v>25</v>
@@ -6610,18 +6574,18 @@
         <v>2</v>
       </c>
       <c r="X72" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y72" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="73" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B73" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D73">
         <v>1714</v>
@@ -6633,10 +6597,13 @@
         <v>29</v>
       </c>
       <c r="J73" t="s">
-        <v>566</v>
+        <v>545</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>567</v>
+        <v>546</v>
+      </c>
+      <c r="R73" t="s">
+        <v>910</v>
       </c>
       <c r="S73" t="s">
         <v>25</v>
@@ -6648,21 +6615,21 @@
         <v>2</v>
       </c>
       <c r="X73" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y73" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="74" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B74" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D74" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E74" t="s">
         <v>28</v>
@@ -6671,10 +6638,10 @@
         <v>29</v>
       </c>
       <c r="J74" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="R74" t="s">
         <v>24</v>
@@ -6683,77 +6650,80 @@
         <v>25</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>570</v>
+        <v>549</v>
       </c>
       <c r="U74" s="1" t="s">
-        <v>571</v>
+        <v>550</v>
       </c>
       <c r="V74" s="1" t="s">
-        <v>572</v>
+        <v>551</v>
       </c>
       <c r="W74" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X74" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y74" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="75" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B75" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D75" t="s">
-        <v>574</v>
+        <v>553</v>
       </c>
       <c r="E75" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="F75" t="s">
         <v>32</v>
       </c>
       <c r="J75" t="s">
-        <v>575</v>
+        <v>554</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>576</v>
+        <v>555</v>
+      </c>
+      <c r="R75" t="s">
+        <v>24</v>
       </c>
       <c r="S75" t="s">
         <v>25</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>577</v>
+        <v>556</v>
       </c>
       <c r="U75" s="1" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="V75" s="1" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="W75" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X75" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y75" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="76" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B76" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D76" t="s">
-        <v>578</v>
+        <v>557</v>
       </c>
       <c r="E76" t="s">
         <v>48</v>
@@ -6762,75 +6732,81 @@
         <v>65</v>
       </c>
       <c r="J76" t="s">
-        <v>579</v>
+        <v>558</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>580</v>
+        <v>559</v>
+      </c>
+      <c r="R76" t="s">
+        <v>24</v>
       </c>
       <c r="S76" t="s">
         <v>25</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>581</v>
+        <v>560</v>
       </c>
       <c r="U76" s="1" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="V76" s="1" t="s">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="W76" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X76" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y76" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="77" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B77" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D77" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="E77" t="s">
-        <v>583</v>
+        <v>562</v>
       </c>
       <c r="F77" t="s">
-        <v>584</v>
+        <v>563</v>
       </c>
       <c r="J77" t="s">
-        <v>585</v>
+        <v>923</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>586</v>
+        <v>564</v>
+      </c>
+      <c r="R77" t="s">
+        <v>53</v>
       </c>
       <c r="S77" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="U77" s="1" t="s">
-        <v>587</v>
+        <v>565</v>
       </c>
       <c r="V77" s="1" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="W77" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X77" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y77" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="78" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6850,13 +6826,13 @@
     </row>
     <row r="83" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B83" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D83" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E83" t="s">
         <v>86</v>
@@ -6865,10 +6841,10 @@
         <v>87</v>
       </c>
       <c r="J83" t="s">
-        <v>170</v>
+        <v>930</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="R83" t="s">
         <v>24</v>
@@ -6877,45 +6853,42 @@
         <v>25</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="W83" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X83" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Y83" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="84" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B84" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D84" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="E84" t="s">
         <v>86</v>
       </c>
       <c r="F84" t="s">
-        <v>173</v>
-      </c>
-      <c r="H84" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J84" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="K84" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="R84" t="s">
         <v>24</v>
@@ -6924,30 +6897,30 @@
         <v>25</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>588</v>
+        <v>566</v>
       </c>
       <c r="U84" s="1" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="V84" s="1" t="s">
-        <v>589</v>
+        <v>567</v>
       </c>
       <c r="W84" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X84" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Y84" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="85" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B85" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D85" t="s">
         <v>38</v>
@@ -6958,17 +6931,14 @@
       <c r="F85" t="s">
         <v>87</v>
       </c>
-      <c r="H85" t="s">
-        <v>590</v>
-      </c>
       <c r="J85" t="s">
-        <v>591</v>
+        <v>568</v>
       </c>
       <c r="K85" t="s">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>593</v>
+        <v>570</v>
       </c>
       <c r="R85" t="s">
         <v>24</v>
@@ -6977,45 +6947,42 @@
         <v>25</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>594</v>
+        <v>571</v>
       </c>
       <c r="W85" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X85" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Y85" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="86" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B86" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D86" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E86" t="s">
-        <v>595</v>
+        <v>572</v>
       </c>
       <c r="F86" t="s">
         <v>105</v>
       </c>
-      <c r="H86" t="s">
-        <v>596</v>
-      </c>
       <c r="J86" t="s">
-        <v>597</v>
+        <v>573</v>
       </c>
       <c r="K86" t="s">
-        <v>598</v>
+        <v>574</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>599</v>
+        <v>575</v>
       </c>
       <c r="R86" t="s">
         <v>24</v>
@@ -7024,42 +6991,39 @@
         <v>25</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>600</v>
+        <v>576</v>
       </c>
       <c r="W86" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X86" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Y86" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B87" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D87" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E87" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F87" t="s">
-        <v>368</v>
-      </c>
-      <c r="H87" t="s">
-        <v>181</v>
+        <v>358</v>
       </c>
       <c r="J87" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="R87" t="s">
         <v>24</v>
@@ -7067,90 +7031,90 @@
       <c r="S87" t="s">
         <v>25</v>
       </c>
-      <c r="T87" s="1">
+      <c r="T87" s="19">
         <v>168</v>
       </c>
-      <c r="U87" s="1">
+      <c r="U87" s="19">
         <v>95</v>
       </c>
-      <c r="V87" s="1">
+      <c r="V87" s="19">
         <v>90</v>
       </c>
       <c r="W87" s="1">
         <v>3</v>
       </c>
       <c r="X87" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="Y87" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="88" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B88" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D88" t="s">
-        <v>601</v>
+        <v>577</v>
       </c>
       <c r="E88" t="s">
-        <v>602</v>
+        <v>578</v>
       </c>
       <c r="F88" t="s">
-        <v>603</v>
+        <v>579</v>
       </c>
       <c r="H88" t="s">
-        <v>604</v>
+        <v>580</v>
       </c>
       <c r="J88" t="s">
-        <v>605</v>
+        <v>581</v>
       </c>
       <c r="K88" t="s">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>607</v>
+        <v>583</v>
       </c>
       <c r="R88" t="s">
-        <v>608</v>
+        <v>920</v>
       </c>
       <c r="S88" t="s">
-        <v>609</v>
+        <v>584</v>
       </c>
       <c r="W88" s="1">
         <v>3</v>
       </c>
       <c r="X88" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="Y88" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="89" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B89" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D89" t="s">
-        <v>610</v>
+        <v>585</v>
       </c>
       <c r="E89" t="s">
-        <v>611</v>
+        <v>586</v>
       </c>
       <c r="F89" t="s">
         <v>29</v>
       </c>
       <c r="J89" t="s">
-        <v>612</v>
+        <v>587</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>613</v>
+        <v>588</v>
       </c>
       <c r="R89" t="s">
         <v>24</v>
@@ -7171,21 +7135,21 @@
         <v>3</v>
       </c>
       <c r="X89" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="Y89" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="90" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B90" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D90" t="s">
-        <v>614</v>
+        <v>589</v>
       </c>
       <c r="E90" t="s">
         <v>48</v>
@@ -7194,16 +7158,16 @@
         <v>65</v>
       </c>
       <c r="J90" t="s">
-        <v>615</v>
+        <v>590</v>
       </c>
       <c r="K90" t="s">
-        <v>616</v>
+        <v>591</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>617</v>
+        <v>592</v>
       </c>
       <c r="R90" t="s">
-        <v>532</v>
+        <v>513</v>
       </c>
       <c r="S90" t="s">
         <v>25</v>
@@ -7215,40 +7179,40 @@
         <v>3</v>
       </c>
       <c r="X90" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="Y90" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="91" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C91" s="6"/>
       <c r="D91" s="6" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>118</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G91" s="6"/>
       <c r="H91" s="6"/>
       <c r="I91" s="6"/>
       <c r="J91" s="6" t="s">
-        <v>618</v>
+        <v>908</v>
       </c>
       <c r="K91" s="6" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="L91" s="12" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="M91" s="6"/>
       <c r="N91" s="6"/>
@@ -7256,60 +7220,60 @@
       <c r="P91" s="6"/>
       <c r="Q91" s="6"/>
       <c r="R91" s="6" t="s">
-        <v>24</v>
+        <v>924</v>
       </c>
       <c r="S91" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>619</v>
+        <v>58</v>
+      </c>
+      <c r="T91" s="3">
+        <v>500</v>
+      </c>
+      <c r="U91" s="3">
+        <v>1300</v>
+      </c>
+      <c r="V91" s="3">
+        <v>840</v>
       </c>
       <c r="W91" s="3" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X91" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="Y91" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="92" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="6" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>620</v>
+        <v>594</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>621</v>
+        <v>595</v>
       </c>
       <c r="G92" s="6"/>
       <c r="H92" s="6" t="s">
-        <v>622</v>
+        <v>596</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="6" t="s">
-        <v>623</v>
+        <v>597</v>
       </c>
       <c r="K92" s="6" t="s">
-        <v>624</v>
+        <v>598</v>
       </c>
       <c r="L92" s="13" t="s">
-        <v>625</v>
+        <v>599</v>
       </c>
       <c r="M92" s="6"/>
       <c r="N92" s="6"/>
@@ -7317,42 +7281,42 @@
       <c r="P92" s="6"/>
       <c r="Q92" s="6"/>
       <c r="R92" s="6" t="s">
-        <v>626</v>
+        <v>600</v>
       </c>
       <c r="S92" s="6" t="s">
-        <v>627</v>
+        <v>601</v>
       </c>
       <c r="T92" s="3" t="s">
-        <v>628</v>
+        <v>602</v>
       </c>
       <c r="U92" s="3"/>
       <c r="V92" s="3"/>
       <c r="W92" s="3" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X92" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="Y92" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="93" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C93" s="6"/>
       <c r="D93" s="6" t="s">
-        <v>629</v>
+        <v>603</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>630</v>
+        <v>604</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>631</v>
+        <v>605</v>
       </c>
       <c r="G93" s="6"/>
       <c r="H93" s="6" t="s">
@@ -7360,13 +7324,13 @@
       </c>
       <c r="I93" s="6"/>
       <c r="J93" s="6" t="s">
-        <v>551</v>
+        <v>530</v>
       </c>
       <c r="K93" s="6" t="s">
-        <v>632</v>
+        <v>606</v>
       </c>
       <c r="L93" s="13" t="s">
-        <v>633</v>
+        <v>607</v>
       </c>
       <c r="M93" s="6"/>
       <c r="N93" s="6"/>
@@ -7374,58 +7338,58 @@
       <c r="P93" s="6"/>
       <c r="Q93" s="6"/>
       <c r="R93" s="6" t="s">
-        <v>532</v>
+        <v>513</v>
       </c>
       <c r="S93" s="6" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="T93" s="3" t="s">
-        <v>634</v>
+        <v>608</v>
       </c>
       <c r="U93" s="3" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="V93" s="3"/>
       <c r="W93" s="3" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X93" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="Y93" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="94" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="6" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>118</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>635</v>
+        <v>609</v>
       </c>
       <c r="G94" s="6"/>
       <c r="H94" s="6" t="s">
-        <v>636</v>
+        <v>610</v>
       </c>
       <c r="I94" s="6"/>
       <c r="J94" s="6" t="s">
-        <v>637</v>
+        <v>611</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>638</v>
+        <v>612</v>
       </c>
       <c r="L94" s="13" t="s">
-        <v>639</v>
+        <v>613</v>
       </c>
       <c r="M94" s="6"/>
       <c r="N94" s="6"/>
@@ -7433,37 +7397,37 @@
       <c r="P94" s="6"/>
       <c r="Q94" s="6"/>
       <c r="R94" s="6" t="s">
-        <v>640</v>
+        <v>921</v>
       </c>
       <c r="S94" s="6" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="T94" s="3" t="s">
-        <v>641</v>
+        <v>614</v>
       </c>
       <c r="U94" s="3" t="s">
-        <v>642</v>
+        <v>615</v>
       </c>
       <c r="V94" s="3"/>
       <c r="W94" s="3" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X94" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="Y94" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="95" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B95" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D95" t="s">
-        <v>643</v>
+        <v>616</v>
       </c>
       <c r="E95" t="s">
         <v>28</v>
@@ -7472,10 +7436,10 @@
         <v>29</v>
       </c>
       <c r="J95" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="R95" t="s">
         <v>24</v>
@@ -7496,21 +7460,21 @@
         <v>1</v>
       </c>
       <c r="X95" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="Y95" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="96" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B96" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D96" t="s">
-        <v>643</v>
+        <v>616</v>
       </c>
       <c r="E96" t="s">
         <v>28</v>
@@ -7519,10 +7483,10 @@
         <v>29</v>
       </c>
       <c r="J96" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="R96" t="s">
         <v>24</v>
@@ -7531,51 +7495,51 @@
         <v>25</v>
       </c>
       <c r="T96" s="1">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="U96" s="1">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="V96" s="1">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="W96" s="1">
         <v>1</v>
       </c>
       <c r="X96" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="Y96" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="97" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>184</v>
+      </c>
+      <c r="B97" t="s">
+        <v>185</v>
+      </c>
+      <c r="D97" t="s">
+        <v>617</v>
+      </c>
+      <c r="E97" t="s">
         <v>190</v>
       </c>
-      <c r="B97" t="s">
+      <c r="F97" t="s">
         <v>191</v>
       </c>
-      <c r="D97" t="s">
-        <v>644</v>
-      </c>
-      <c r="E97" t="s">
-        <v>196</v>
-      </c>
-      <c r="F97" t="s">
-        <v>197</v>
-      </c>
       <c r="G97" s="4" t="s">
-        <v>645</v>
+        <v>618</v>
       </c>
       <c r="J97" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="K97" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="R97" t="s">
         <v>24</v>
@@ -7596,21 +7560,21 @@
         <v>1</v>
       </c>
       <c r="X97" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="Y97" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="98" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B98" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D98" t="s">
-        <v>646</v>
+        <v>619</v>
       </c>
       <c r="E98" t="s">
         <v>28</v>
@@ -7619,10 +7583,10 @@
         <v>29</v>
       </c>
       <c r="J98" t="s">
-        <v>647</v>
+        <v>620</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>648</v>
+        <v>621</v>
       </c>
       <c r="R98" t="s">
         <v>24</v>
@@ -7643,36 +7607,36 @@
         <v>1</v>
       </c>
       <c r="X98" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="Y98" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="99" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>184</v>
+      </c>
+      <c r="B99" t="s">
+        <v>185</v>
+      </c>
+      <c r="D99" t="s">
+        <v>914</v>
+      </c>
+      <c r="E99" t="s">
         <v>190</v>
       </c>
-      <c r="B99" t="s">
-        <v>191</v>
-      </c>
-      <c r="D99" t="s">
-        <v>649</v>
-      </c>
-      <c r="E99" t="s">
-        <v>196</v>
-      </c>
       <c r="F99" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J99" t="s">
-        <v>650</v>
+        <v>623</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>651</v>
+        <v>624</v>
       </c>
       <c r="R99" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S99" t="s">
         <v>25</v>
@@ -7690,21 +7654,21 @@
         <v>1</v>
       </c>
       <c r="X99" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="Y99" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="100" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B100" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D100" t="s">
-        <v>652</v>
+        <v>625</v>
       </c>
       <c r="E100" t="s">
         <v>28</v>
@@ -7713,10 +7677,10 @@
         <v>29</v>
       </c>
       <c r="J100" t="s">
-        <v>653</v>
+        <v>626</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="R100" t="s">
         <v>24</v>
@@ -7737,33 +7701,33 @@
         <v>1</v>
       </c>
       <c r="X100" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="Y100" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="101" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B101" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D101" t="s">
         <v>96</v>
       </c>
       <c r="E101" t="s">
-        <v>655</v>
+        <v>628</v>
       </c>
       <c r="F101" t="s">
-        <v>656</v>
+        <v>629</v>
       </c>
       <c r="J101" t="s">
-        <v>657</v>
+        <v>630</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>658</v>
+        <v>631</v>
       </c>
       <c r="R101" t="s">
         <v>24</v>
@@ -7784,18 +7748,18 @@
         <v>1</v>
       </c>
       <c r="X101" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="Y101" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="102" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B102" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D102" t="s">
         <v>38</v>
@@ -7807,10 +7771,10 @@
         <v>29</v>
       </c>
       <c r="J102" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>659</v>
+        <v>632</v>
       </c>
       <c r="R102" t="s">
         <v>24</v>
@@ -7831,10 +7795,10 @@
         <v>1</v>
       </c>
       <c r="X102" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="Y102" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="103" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7842,46 +7806,46 @@
         <v>46</v>
       </c>
       <c r="B103" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D103" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E103" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="F103" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="J103" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="R103" t="s">
         <v>24</v>
       </c>
       <c r="S103" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="T103" s="1" t="s">
-        <v>660</v>
+        <v>633</v>
       </c>
       <c r="U103" s="1" t="s">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="V103" s="1" t="s">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="W103" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X103" s="1" t="s">
         <v>46</v>
       </c>
       <c r="Y103" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="104" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7889,25 +7853,25 @@
         <v>46</v>
       </c>
       <c r="B104" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D104" t="s">
-        <v>662</v>
+        <v>635</v>
       </c>
       <c r="E104" t="s">
         <v>48</v>
       </c>
       <c r="F104" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="J104" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="K104" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="R104" t="s">
         <v>24</v>
@@ -7916,22 +7880,22 @@
         <v>25</v>
       </c>
       <c r="T104" s="1" t="s">
-        <v>663</v>
+        <v>636</v>
       </c>
       <c r="U104" s="1" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="V104" s="1" t="s">
-        <v>664</v>
+        <v>637</v>
       </c>
       <c r="W104" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X104" s="1" t="s">
         <v>46</v>
       </c>
       <c r="Y104" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="105" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7939,49 +7903,49 @@
         <v>46</v>
       </c>
       <c r="B105" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D105" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="E105" t="s">
-        <v>665</v>
+        <v>638</v>
       </c>
       <c r="F105" t="s">
-        <v>666</v>
+        <v>639</v>
       </c>
       <c r="J105" t="s">
-        <v>667</v>
+        <v>640</v>
       </c>
       <c r="K105" t="s">
-        <v>668</v>
+        <v>641</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>669</v>
+        <v>642</v>
       </c>
       <c r="R105" t="s">
-        <v>670</v>
+        <v>922</v>
       </c>
       <c r="S105" t="s">
         <v>25</v>
       </c>
       <c r="T105" s="1" t="s">
-        <v>619</v>
+        <v>593</v>
       </c>
       <c r="U105" s="1" t="s">
-        <v>671</v>
+        <v>643</v>
       </c>
       <c r="V105" s="1" t="s">
-        <v>672</v>
+        <v>644</v>
       </c>
       <c r="W105" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X105" s="1" t="s">
         <v>46</v>
       </c>
       <c r="Y105" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="106" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7989,10 +7953,10 @@
         <v>46</v>
       </c>
       <c r="B106" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D106" t="s">
-        <v>673</v>
+        <v>645</v>
       </c>
       <c r="E106" t="s">
         <v>48</v>
@@ -8001,37 +7965,37 @@
         <v>49</v>
       </c>
       <c r="J106" t="s">
-        <v>674</v>
+        <v>646</v>
       </c>
       <c r="K106" t="s">
-        <v>675</v>
+        <v>647</v>
       </c>
       <c r="L106" s="4" t="s">
-        <v>676</v>
+        <v>648</v>
       </c>
       <c r="R106" t="s">
-        <v>626</v>
+        <v>600</v>
       </c>
       <c r="S106" t="s">
         <v>25</v>
       </c>
       <c r="T106" s="1" t="s">
-        <v>677</v>
+        <v>649</v>
       </c>
       <c r="U106" s="1" t="s">
-        <v>587</v>
+        <v>565</v>
       </c>
       <c r="V106" s="1" t="s">
-        <v>678</v>
+        <v>650</v>
       </c>
       <c r="W106" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X106" s="1" t="s">
         <v>46</v>
       </c>
       <c r="Y106" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="107" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8039,49 +8003,49 @@
         <v>46</v>
       </c>
       <c r="B107" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D107" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="E107" t="s">
         <v>48</v>
       </c>
       <c r="F107" t="s">
-        <v>679</v>
+        <v>651</v>
       </c>
       <c r="J107" t="s">
-        <v>680</v>
+        <v>652</v>
       </c>
       <c r="K107" t="s">
-        <v>681</v>
+        <v>653</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>682</v>
+        <v>654</v>
       </c>
       <c r="R107" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="S107" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="T107" s="1" t="s">
-        <v>672</v>
+        <v>644</v>
       </c>
       <c r="U107" s="1" t="s">
-        <v>683</v>
+        <v>655</v>
       </c>
       <c r="V107" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="W107" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X107" s="1" t="s">
         <v>46</v>
       </c>
       <c r="Y107" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="108" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8089,46 +8053,46 @@
         <v>46</v>
       </c>
       <c r="B108" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D108" t="s">
-        <v>684</v>
+        <v>656</v>
       </c>
       <c r="E108" t="s">
-        <v>665</v>
+        <v>638</v>
       </c>
       <c r="F108" t="s">
-        <v>666</v>
+        <v>639</v>
       </c>
       <c r="J108" t="s">
-        <v>685</v>
+        <v>657</v>
       </c>
       <c r="L108" s="4" t="s">
-        <v>686</v>
+        <v>658</v>
       </c>
       <c r="R108" t="s">
-        <v>670</v>
+        <v>600</v>
       </c>
       <c r="S108" t="s">
         <v>25</v>
       </c>
       <c r="T108" s="1" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="U108" s="1" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="V108" s="1" t="s">
-        <v>687</v>
+        <v>659</v>
       </c>
       <c r="W108" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X108" s="1" t="s">
         <v>46</v>
       </c>
       <c r="Y108" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="109" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8136,25 +8100,25 @@
         <v>46</v>
       </c>
       <c r="B109" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D109" t="s">
-        <v>688</v>
+        <v>660</v>
       </c>
       <c r="E109" t="s">
-        <v>689</v>
+        <v>661</v>
       </c>
       <c r="F109" t="s">
-        <v>690</v>
+        <v>662</v>
       </c>
       <c r="J109" t="s">
-        <v>691</v>
+        <v>663</v>
       </c>
       <c r="K109" t="s">
-        <v>692</v>
+        <v>664</v>
       </c>
       <c r="L109" s="4" t="s">
-        <v>693</v>
+        <v>665</v>
       </c>
       <c r="R109" t="s">
         <v>24</v>
@@ -8163,33 +8127,33 @@
         <v>25</v>
       </c>
       <c r="T109" s="1" t="s">
-        <v>664</v>
+        <v>637</v>
       </c>
       <c r="U109" s="1" t="s">
-        <v>694</v>
+        <v>666</v>
       </c>
       <c r="V109" s="1" t="s">
-        <v>695</v>
+        <v>667</v>
       </c>
       <c r="W109" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X109" s="1" t="s">
         <v>46</v>
       </c>
       <c r="Y109" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="110" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B110" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D110" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E110" t="s">
         <v>92</v>
@@ -8198,19 +8162,19 @@
         <v>93</v>
       </c>
       <c r="J110" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="K110" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="L110" s="4" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="R110" t="s">
         <v>24</v>
       </c>
       <c r="S110" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="T110" s="1">
         <v>182</v>
@@ -8225,45 +8189,45 @@
         <v>3</v>
       </c>
       <c r="X110" s="1" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="Y110" s="1" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="111" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B111" t="s">
+        <v>208</v>
+      </c>
+      <c r="D111" t="s">
+        <v>622</v>
+      </c>
+      <c r="E111" t="s">
         <v>214</v>
       </c>
-      <c r="D111" t="s">
-        <v>649</v>
-      </c>
-      <c r="E111" t="s">
-        <v>220</v>
-      </c>
       <c r="F111" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="H111" t="s">
         <v>45</v>
       </c>
       <c r="J111" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="K111" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="L111" s="4" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="R111" t="s">
         <v>24</v>
       </c>
       <c r="S111" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="T111" s="1">
         <v>165</v>
@@ -8278,48 +8242,48 @@
         <v>3</v>
       </c>
       <c r="X111" s="1" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="Y111" s="1" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="112" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B112" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D112" t="s">
-        <v>696</v>
+        <v>668</v>
       </c>
       <c r="E112" t="s">
-        <v>697</v>
+        <v>669</v>
       </c>
       <c r="F112" t="s">
-        <v>698</v>
+        <v>670</v>
       </c>
       <c r="H112" t="s">
         <v>45</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>699</v>
+        <v>671</v>
       </c>
       <c r="J112" t="s">
-        <v>700</v>
+        <v>672</v>
       </c>
       <c r="K112" t="s">
-        <v>701</v>
+        <v>673</v>
       </c>
       <c r="L112" s="4" t="s">
-        <v>702</v>
+        <v>674</v>
       </c>
       <c r="R112" t="s">
         <v>24</v>
       </c>
       <c r="S112" t="s">
-        <v>703</v>
+        <v>675</v>
       </c>
       <c r="T112" s="1">
         <v>210</v>
@@ -8328,48 +8292,48 @@
         <v>3</v>
       </c>
       <c r="X112" s="1" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="Y112" s="1" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="113" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B113" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D113" t="s">
-        <v>696</v>
+        <v>668</v>
       </c>
       <c r="E113" t="s">
-        <v>697</v>
+        <v>669</v>
       </c>
       <c r="F113" t="s">
-        <v>698</v>
+        <v>670</v>
       </c>
       <c r="H113" t="s">
         <v>45</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>699</v>
+        <v>671</v>
       </c>
       <c r="J113" t="s">
-        <v>704</v>
+        <v>676</v>
       </c>
       <c r="K113" t="s">
-        <v>705</v>
+        <v>677</v>
       </c>
       <c r="L113" s="4" t="s">
-        <v>706</v>
+        <v>678</v>
       </c>
       <c r="R113" t="s">
         <v>24</v>
       </c>
       <c r="S113" t="s">
-        <v>703</v>
+        <v>675</v>
       </c>
       <c r="T113" s="1">
         <v>215</v>
@@ -8378,36 +8342,36 @@
         <v>3</v>
       </c>
       <c r="X113" s="1" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="Y113" s="1" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="114" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B114" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D114" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="E114" t="s">
         <v>28</v>
       </c>
       <c r="F114" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="H114" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="J114" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="L114" s="4" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="R114" t="s">
         <v>24</v>
@@ -8416,33 +8380,33 @@
         <v>25</v>
       </c>
       <c r="T114" s="1" t="s">
-        <v>707</v>
+        <v>679</v>
       </c>
       <c r="U114" s="1" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="V114" s="1" t="s">
-        <v>708</v>
+        <v>680</v>
       </c>
       <c r="W114" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X114" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Y114" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="115" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B115" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D115" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="E115" t="s">
         <v>28</v>
@@ -8451,10 +8415,10 @@
         <v>29</v>
       </c>
       <c r="J115" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="R115" t="s">
         <v>24</v>
@@ -8463,33 +8427,33 @@
         <v>101</v>
       </c>
       <c r="T115" s="1" t="s">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="U115" s="1" t="s">
-        <v>709</v>
+        <v>681</v>
       </c>
       <c r="V115" s="1" t="s">
-        <v>710</v>
+        <v>682</v>
       </c>
       <c r="W115" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X115" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Y115" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="116" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B116" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D116" t="s">
-        <v>711</v>
+        <v>683</v>
       </c>
       <c r="E116" t="s">
         <v>28</v>
@@ -8498,57 +8462,57 @@
         <v>29</v>
       </c>
       <c r="J116" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="R116" t="s">
         <v>24</v>
       </c>
       <c r="S116" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="T116" s="1" t="s">
-        <v>712</v>
+        <v>684</v>
       </c>
       <c r="U116" s="1" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="V116" s="1" t="s">
-        <v>713</v>
+        <v>685</v>
       </c>
       <c r="W116" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X116" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Y116" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="117" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B117" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D117" t="s">
-        <v>714</v>
+        <v>686</v>
       </c>
       <c r="E117" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="F117" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="J117" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L117" s="4" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="R117" t="s">
         <v>24</v>
@@ -8557,51 +8521,51 @@
         <v>25</v>
       </c>
       <c r="T117" s="1" t="s">
-        <v>715</v>
+        <v>687</v>
       </c>
       <c r="U117" s="1" t="s">
-        <v>716</v>
+        <v>688</v>
       </c>
       <c r="V117" s="1" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="W117" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X117" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Y117" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="118" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B118" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D118">
         <v>1767</v>
       </c>
       <c r="E118" t="s">
-        <v>717</v>
+        <v>689</v>
       </c>
       <c r="F118" t="s">
-        <v>718</v>
+        <v>690</v>
       </c>
       <c r="J118" t="s">
-        <v>719</v>
+        <v>691</v>
       </c>
       <c r="L118" s="4" t="s">
-        <v>720</v>
+        <v>692</v>
       </c>
       <c r="R118" t="s">
         <v>24</v>
       </c>
       <c r="S118" t="s">
-        <v>721</v>
+        <v>693</v>
       </c>
       <c r="T118" s="1">
         <v>185</v>
@@ -8609,37 +8573,40 @@
       <c r="U118" s="1">
         <v>80</v>
       </c>
+      <c r="V118" s="1">
+        <v>80</v>
+      </c>
       <c r="W118" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X118" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Y118" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="119" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B119" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D119">
         <v>1776</v>
       </c>
       <c r="E119" t="s">
-        <v>722</v>
+        <v>694</v>
       </c>
       <c r="F119" t="s">
         <v>98</v>
       </c>
       <c r="J119" t="s">
-        <v>723</v>
+        <v>695</v>
       </c>
       <c r="L119" s="4" t="s">
-        <v>724</v>
+        <v>696</v>
       </c>
       <c r="R119" t="s">
         <v>24</v>
@@ -8654,27 +8621,27 @@
         <v>80</v>
       </c>
       <c r="V119" s="1" t="s">
-        <v>725</v>
+        <v>697</v>
       </c>
       <c r="W119" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X119" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Y119" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="120" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B120" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D120" t="s">
-        <v>726</v>
+        <v>698</v>
       </c>
       <c r="E120" t="s">
         <v>28</v>
@@ -8683,10 +8650,10 @@
         <v>29</v>
       </c>
       <c r="J120" t="s">
-        <v>727</v>
+        <v>699</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>728</v>
+        <v>700</v>
       </c>
       <c r="R120" t="s">
         <v>24</v>
@@ -8694,40 +8661,46 @@
       <c r="S120" t="s">
         <v>25</v>
       </c>
-      <c r="T120" s="1" t="s">
-        <v>729</v>
+      <c r="T120" s="1">
+        <v>67</v>
+      </c>
+      <c r="U120" s="1">
+        <v>51</v>
+      </c>
+      <c r="V120" s="1">
+        <v>29</v>
       </c>
       <c r="W120" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X120" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Y120" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="121" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B121" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D121">
         <v>1783</v>
       </c>
       <c r="E121" t="s">
-        <v>717</v>
+        <v>689</v>
       </c>
       <c r="F121" t="s">
-        <v>718</v>
+        <v>690</v>
       </c>
       <c r="J121" t="s">
-        <v>730</v>
+        <v>918</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>731</v>
+        <v>701</v>
       </c>
       <c r="R121" t="s">
         <v>24</v>
@@ -8736,7 +8709,7 @@
         <v>25</v>
       </c>
       <c r="T121" s="1" t="s">
-        <v>732</v>
+        <v>702</v>
       </c>
       <c r="U121" s="1">
         <v>57</v>
@@ -8745,89 +8718,94 @@
         <v>64</v>
       </c>
       <c r="W121" s="1" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="X121" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Y121" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="122" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>240</v>
-      </c>
-      <c r="B122" t="s">
-        <v>241</v>
-      </c>
-      <c r="D122" t="s">
-        <v>242</v>
-      </c>
-      <c r="E122" t="s">
+      <c r="A122" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B122" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C122" s="15"/>
+      <c r="D122" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="E122" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="F122" t="s">
-        <v>243</v>
-      </c>
-      <c r="J122" t="s">
-        <v>244</v>
-      </c>
-      <c r="L122" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="R122" t="s">
-        <v>24</v>
-      </c>
-      <c r="S122" t="s">
-        <v>212</v>
-      </c>
-      <c r="T122" s="1" t="s">
-        <v>739</v>
-      </c>
-      <c r="U122" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="V122" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="W122" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="X122" t="s">
-        <v>240</v>
-      </c>
-      <c r="Y122" t="s">
-        <v>241</v>
+      <c r="F122" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="G122" s="15"/>
+      <c r="H122" s="15"/>
+      <c r="I122" s="15"/>
+      <c r="J122" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="K122" s="15"/>
+      <c r="L122" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="M122" s="15"/>
+      <c r="N122" s="15"/>
+      <c r="O122" s="15"/>
+      <c r="P122" s="15"/>
+      <c r="Q122" s="15"/>
+      <c r="R122" s="15" t="s">
+        <v>911</v>
+      </c>
+      <c r="S122" s="15"/>
+      <c r="T122" s="17" t="s">
+        <v>709</v>
+      </c>
+      <c r="U122" s="17" t="s">
+        <v>710</v>
+      </c>
+      <c r="V122" s="17" t="s">
+        <v>685</v>
+      </c>
+      <c r="W122" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="X122" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y122" s="15" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="123" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B123" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D123" t="s">
-        <v>741</v>
+        <v>711</v>
       </c>
       <c r="E123" t="s">
-        <v>655</v>
+        <v>628</v>
       </c>
       <c r="F123" t="s">
-        <v>656</v>
-      </c>
-      <c r="H123" t="s">
-        <v>742</v>
+        <v>629</v>
       </c>
       <c r="J123" t="s">
-        <v>743</v>
+        <v>712</v>
       </c>
       <c r="K123" t="s">
-        <v>744</v>
+        <v>713</v>
       </c>
       <c r="L123" s="4" t="s">
-        <v>745</v>
+        <v>714</v>
       </c>
       <c r="R123" t="s">
         <v>24</v>
@@ -8836,89 +8814,80 @@
         <v>25</v>
       </c>
       <c r="T123" s="1" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="U123" s="1" t="s">
-        <v>746</v>
+        <v>715</v>
       </c>
       <c r="V123" s="1" t="s">
-        <v>695</v>
+        <v>667</v>
       </c>
       <c r="W123" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X123" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="Y123" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="124" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B124" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D124" t="s">
-        <v>747</v>
+        <v>716</v>
       </c>
       <c r="E124" t="s">
         <v>28</v>
       </c>
       <c r="F124" t="s">
-        <v>748</v>
-      </c>
-      <c r="H124" t="s">
-        <v>749</v>
+        <v>717</v>
       </c>
       <c r="J124" t="s">
-        <v>750</v>
+        <v>718</v>
       </c>
       <c r="L124" s="4" t="s">
-        <v>751</v>
+        <v>719</v>
       </c>
       <c r="R124" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="S124" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="W124" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X124" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="Y124" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="125" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B125" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D125" t="s">
-        <v>752</v>
-      </c>
-      <c r="E125" t="s">
-        <v>394</v>
+        <v>720</v>
       </c>
       <c r="F125" t="s">
         <v>32</v>
       </c>
-      <c r="H125" t="s">
-        <v>753</v>
-      </c>
       <c r="J125" t="s">
-        <v>754</v>
+        <v>721</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>755</v>
+        <v>722</v>
       </c>
       <c r="R125" t="s">
         <v>24</v>
@@ -8926,28 +8895,34 @@
       <c r="S125" t="s">
         <v>25</v>
       </c>
-      <c r="T125" s="1" t="s">
-        <v>482</v>
+      <c r="T125" s="1">
+        <v>175</v>
+      </c>
+      <c r="U125" s="1">
+        <v>81</v>
+      </c>
+      <c r="V125" s="1">
+        <v>82</v>
       </c>
       <c r="W125" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X125" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="Y125" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="126" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B126" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D126" t="s">
-        <v>614</v>
+        <v>589</v>
       </c>
       <c r="E126" t="s">
         <v>28</v>
@@ -8955,14 +8930,11 @@
       <c r="F126" t="s">
         <v>29</v>
       </c>
-      <c r="H126" t="s">
-        <v>756</v>
-      </c>
       <c r="J126" t="s">
-        <v>757</v>
+        <v>723</v>
       </c>
       <c r="L126" s="4" t="s">
-        <v>758</v>
+        <v>724</v>
       </c>
       <c r="R126" t="s">
         <v>24</v>
@@ -8971,86 +8943,83 @@
         <v>58</v>
       </c>
       <c r="T126" s="1" t="s">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="U126" s="1" t="s">
-        <v>759</v>
+        <v>725</v>
       </c>
       <c r="V126" s="1" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="W126" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X126" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="Y126" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="127" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B127" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D127" t="s">
-        <v>760</v>
+        <v>726</v>
       </c>
       <c r="E127" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="F127" t="s">
-        <v>761</v>
-      </c>
-      <c r="H127" t="s">
-        <v>762</v>
+        <v>727</v>
       </c>
       <c r="J127" t="s">
-        <v>763</v>
+        <v>728</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>764</v>
+        <v>729</v>
       </c>
       <c r="R127" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="S127" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="W127" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X127" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="Y127" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="128" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B128" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D128" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E128" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="F128" t="s">
         <v>32</v>
       </c>
       <c r="J128" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="L128" s="4" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="R128" t="s">
         <v>24</v>
@@ -9059,30 +9028,30 @@
         <v>25</v>
       </c>
       <c r="T128" s="1" t="s">
-        <v>765</v>
+        <v>730</v>
       </c>
       <c r="U128" s="1" t="s">
-        <v>766</v>
+        <v>731</v>
       </c>
       <c r="V128" s="1" t="s">
-        <v>746</v>
+        <v>715</v>
       </c>
       <c r="W128" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X128" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Y128" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="129" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B129" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D129" t="s">
         <v>96</v>
@@ -9093,61 +9062,58 @@
       <c r="F129" t="s">
         <v>29</v>
       </c>
-      <c r="H129" t="s">
-        <v>767</v>
-      </c>
       <c r="J129" t="s">
-        <v>615</v>
+        <v>590</v>
       </c>
       <c r="L129" s="4" t="s">
-        <v>768</v>
+        <v>732</v>
       </c>
       <c r="R129" t="s">
-        <v>769</v>
+        <v>733</v>
       </c>
       <c r="S129" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="T129" s="1" t="s">
-        <v>770</v>
+        <v>734</v>
       </c>
       <c r="U129" s="1" t="s">
-        <v>619</v>
+        <v>593</v>
       </c>
       <c r="V129" s="1" t="s">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="W129" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X129" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Y129" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="130" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B130" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D130" t="s">
-        <v>771</v>
+        <v>735</v>
       </c>
       <c r="E130" t="s">
         <v>118</v>
       </c>
       <c r="F130" t="s">
-        <v>772</v>
+        <v>736</v>
       </c>
       <c r="J130" t="s">
-        <v>773</v>
+        <v>737</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>774</v>
+        <v>738</v>
       </c>
       <c r="R130" t="s">
         <v>24</v>
@@ -9156,92 +9122,92 @@
         <v>25</v>
       </c>
       <c r="T130" s="1" t="s">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="U130" s="1" t="s">
-        <v>571</v>
+        <v>550</v>
       </c>
       <c r="V130" s="1" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="W130" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X130" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Y130" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="131" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B131" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D131" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="E131" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="F131" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J131" t="s">
-        <v>775</v>
+        <v>739</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>776</v>
+        <v>740</v>
       </c>
       <c r="R131" t="s">
-        <v>769</v>
+        <v>733</v>
       </c>
       <c r="S131" t="s">
         <v>25</v>
       </c>
       <c r="T131" s="1" t="s">
-        <v>777</v>
+        <v>741</v>
       </c>
       <c r="U131" s="1" t="s">
-        <v>664</v>
+        <v>637</v>
       </c>
       <c r="V131" s="1" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="W131" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X131" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Y131" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="132" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B132" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D132" t="s">
-        <v>649</v>
+        <v>622</v>
       </c>
       <c r="E132" t="s">
-        <v>778</v>
+        <v>742</v>
       </c>
       <c r="F132" t="s">
-        <v>779</v>
+        <v>743</v>
       </c>
       <c r="J132" t="s">
-        <v>780</v>
+        <v>744</v>
       </c>
       <c r="L132" s="4" t="s">
-        <v>781</v>
+        <v>745</v>
       </c>
       <c r="R132" t="s">
         <v>24</v>
@@ -9250,45 +9216,45 @@
         <v>101</v>
       </c>
       <c r="T132" s="1" t="s">
-        <v>782</v>
+        <v>746</v>
       </c>
       <c r="U132" s="1" t="s">
-        <v>572</v>
+        <v>551</v>
       </c>
       <c r="V132" s="1" t="s">
-        <v>783</v>
+        <v>747</v>
       </c>
       <c r="W132" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X132" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Y132" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="133" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B133" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D133" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="E133" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="F133" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="J133" t="s">
-        <v>784</v>
+        <v>748</v>
       </c>
       <c r="L133" s="4" t="s">
-        <v>785</v>
+        <v>749</v>
       </c>
       <c r="R133" t="s">
         <v>24</v>
@@ -9297,54 +9263,51 @@
         <v>25</v>
       </c>
       <c r="T133" s="1" t="s">
-        <v>786</v>
+        <v>750</v>
       </c>
       <c r="U133" s="1" t="s">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="V133" s="1" t="s">
-        <v>759</v>
+        <v>725</v>
       </c>
       <c r="W133" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X133" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Y133" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="134" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>245</v>
+      </c>
+      <c r="B134" t="s">
+        <v>246</v>
+      </c>
+      <c r="D134" t="s">
+        <v>247</v>
+      </c>
+      <c r="E134" t="s">
+        <v>248</v>
+      </c>
+      <c r="F134" t="s">
+        <v>249</v>
+      </c>
+      <c r="J134" t="s">
+        <v>250</v>
+      </c>
+      <c r="L134" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="B134" t="s">
-        <v>252</v>
-      </c>
-      <c r="D134" t="s">
-        <v>253</v>
-      </c>
-      <c r="E134" t="s">
-        <v>254</v>
-      </c>
-      <c r="F134" t="s">
-        <v>255</v>
-      </c>
-      <c r="J134" t="s">
-        <v>256</v>
-      </c>
-      <c r="L134" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="M134" t="s">
-        <v>787</v>
       </c>
       <c r="R134" t="s">
         <v>24</v>
       </c>
       <c r="S134" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="T134" s="1">
         <v>42</v>
@@ -9359,45 +9322,42 @@
         <v>3</v>
       </c>
       <c r="X134" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="Y134" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="135" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B135" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D135" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E135" t="s">
         <v>118</v>
       </c>
       <c r="F135" t="s">
-        <v>788</v>
+        <v>751</v>
       </c>
       <c r="J135" t="s">
-        <v>789</v>
+        <v>752</v>
       </c>
       <c r="K135" t="s">
-        <v>790</v>
+        <v>753</v>
       </c>
       <c r="L135" s="4" t="s">
-        <v>791</v>
-      </c>
-      <c r="M135" t="s">
-        <v>787</v>
+        <v>754</v>
       </c>
       <c r="R135" t="s">
         <v>24</v>
       </c>
       <c r="S135" t="s">
-        <v>792</v>
+        <v>755</v>
       </c>
       <c r="T135" s="1">
         <v>44</v>
@@ -9412,45 +9372,42 @@
         <v>3</v>
       </c>
       <c r="X135" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="Y135" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B136" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D136" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E136" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="F136" t="s">
-        <v>793</v>
+        <v>756</v>
       </c>
       <c r="J136" t="s">
-        <v>794</v>
+        <v>757</v>
       </c>
       <c r="K136" t="s">
-        <v>795</v>
+        <v>758</v>
       </c>
       <c r="L136" s="4" t="s">
-        <v>796</v>
-      </c>
-      <c r="M136" t="s">
-        <v>787</v>
+        <v>759</v>
       </c>
       <c r="R136" t="s">
         <v>24</v>
       </c>
       <c r="S136" t="s">
-        <v>797</v>
+        <v>760</v>
       </c>
       <c r="T136" s="1">
         <v>42</v>
@@ -9465,45 +9422,42 @@
         <v>3</v>
       </c>
       <c r="X136" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="Y136" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B137" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D137" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E137" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
       <c r="F137" t="s">
-        <v>798</v>
+        <v>909</v>
       </c>
       <c r="J137" t="s">
-        <v>799</v>
+        <v>761</v>
       </c>
       <c r="K137" t="s">
-        <v>800</v>
+        <v>762</v>
       </c>
       <c r="L137" s="4" t="s">
-        <v>801</v>
-      </c>
-      <c r="M137" t="s">
-        <v>787</v>
+        <v>763</v>
       </c>
       <c r="R137" t="s">
         <v>24</v>
       </c>
       <c r="S137" t="s">
-        <v>797</v>
+        <v>760</v>
       </c>
       <c r="T137" s="1">
         <v>45</v>
@@ -9518,36 +9472,36 @@
         <v>3</v>
       </c>
       <c r="X137" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="Y137" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="138" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B138" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C138" t="s">
-        <v>802</v>
+        <v>764</v>
       </c>
       <c r="D138">
         <v>1780</v>
       </c>
       <c r="E138" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="F138" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J138" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="L138" s="10" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="R138" t="s">
         <v>24</v>
@@ -9568,36 +9522,36 @@
         <v>1</v>
       </c>
       <c r="X138" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="Y138" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="139" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B139" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C139" t="s">
-        <v>802</v>
+        <v>764</v>
       </c>
       <c r="D139">
         <v>1782</v>
       </c>
       <c r="E139" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="F139" t="s">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="J139" t="s">
-        <v>803</v>
+        <v>765</v>
       </c>
       <c r="L139" s="10" t="s">
-        <v>804</v>
+        <v>766</v>
       </c>
       <c r="R139" t="s">
         <v>24</v>
@@ -9618,21 +9572,21 @@
         <v>1</v>
       </c>
       <c r="X139" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="Y139" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="140" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B140" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C140" t="s">
-        <v>802</v>
+        <v>764</v>
       </c>
       <c r="D140">
         <v>1783</v>
@@ -9644,10 +9598,10 @@
         <v>29</v>
       </c>
       <c r="J140" t="s">
-        <v>805</v>
+        <v>767</v>
       </c>
       <c r="L140" s="10" t="s">
-        <v>806</v>
+        <v>768</v>
       </c>
       <c r="R140" t="s">
         <v>24</v>
@@ -9668,36 +9622,36 @@
         <v>1</v>
       </c>
       <c r="X140" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="Y140" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="141" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B141" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C141" t="s">
-        <v>802</v>
+        <v>764</v>
       </c>
       <c r="D141">
         <v>1795</v>
       </c>
       <c r="E141" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
       <c r="F141" t="s">
-        <v>807</v>
+        <v>769</v>
       </c>
       <c r="J141" t="s">
-        <v>808</v>
+        <v>770</v>
       </c>
       <c r="L141" s="10" t="s">
-        <v>809</v>
+        <v>771</v>
       </c>
       <c r="R141" t="s">
         <v>24</v>
@@ -9712,39 +9666,39 @@
         <v>1</v>
       </c>
       <c r="X141" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="Y141" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="142" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B142" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C142" t="s">
-        <v>802</v>
-      </c>
-      <c r="D142">
-        <v>1780</v>
+        <v>764</v>
+      </c>
+      <c r="D142" t="s">
+        <v>912</v>
       </c>
       <c r="E142" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="F142" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J142" t="s">
-        <v>810</v>
+        <v>913</v>
       </c>
       <c r="L142" s="10" t="s">
-        <v>811</v>
+        <v>772</v>
       </c>
       <c r="R142" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S142" t="s">
         <v>101</v>
@@ -9762,36 +9716,36 @@
         <v>1</v>
       </c>
       <c r="X142" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="Y142" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="143" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B143" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C143" t="s">
-        <v>802</v>
+        <v>764</v>
       </c>
       <c r="D143">
         <v>1770</v>
       </c>
       <c r="E143" t="s">
-        <v>655</v>
+        <v>628</v>
       </c>
       <c r="F143" t="s">
-        <v>656</v>
+        <v>629</v>
       </c>
       <c r="J143" t="s">
-        <v>812</v>
+        <v>773</v>
       </c>
       <c r="L143" s="10" t="s">
-        <v>813</v>
+        <v>774</v>
       </c>
       <c r="R143" t="s">
         <v>24</v>
@@ -9812,39 +9766,39 @@
         <v>1</v>
       </c>
       <c r="X143" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="Y143" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="144" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B144" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C144" t="s">
-        <v>802</v>
+        <v>764</v>
       </c>
       <c r="D144">
         <v>1781</v>
       </c>
       <c r="E144" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="F144" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J144" t="s">
-        <v>814</v>
+        <v>775</v>
       </c>
       <c r="L144" s="10" t="s">
-        <v>815</v>
+        <v>776</v>
       </c>
       <c r="R144" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="S144" t="s">
         <v>101</v>
@@ -9859,74 +9813,74 @@
         <v>1</v>
       </c>
       <c r="X144" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="Y144" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="145" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B145" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C145" t="s">
-        <v>802</v>
+        <v>764</v>
       </c>
       <c r="D145" t="s">
-        <v>816</v>
+        <v>777</v>
       </c>
       <c r="E145" t="s">
-        <v>817</v>
+        <v>778</v>
       </c>
       <c r="F145" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="J145" t="s">
-        <v>818</v>
+        <v>779</v>
       </c>
       <c r="L145" s="10" t="s">
-        <v>819</v>
+        <v>780</v>
       </c>
       <c r="R145" t="s">
         <v>24</v>
       </c>
       <c r="S145" t="s">
-        <v>721</v>
+        <v>693</v>
       </c>
       <c r="W145" s="1">
         <v>1</v>
       </c>
       <c r="X145" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="Y145" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="146" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D146" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E146" t="s">
         <v>48</v>
       </c>
       <c r="F146" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="J146" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="L146" s="4" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="R146" t="s">
         <v>24</v>
@@ -9947,21 +9901,21 @@
         <v>3</v>
       </c>
       <c r="X146" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="Y146" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="147" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B147" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D147" t="s">
-        <v>820</v>
+        <v>781</v>
       </c>
       <c r="E147" t="s">
         <v>48</v>
@@ -9970,13 +9924,13 @@
         <v>65</v>
       </c>
       <c r="J147" t="s">
-        <v>821</v>
+        <v>782</v>
       </c>
       <c r="K147" t="s">
-        <v>822</v>
+        <v>783</v>
       </c>
       <c r="L147" s="4" t="s">
-        <v>823</v>
+        <v>784</v>
       </c>
       <c r="R147" t="s">
         <v>24</v>
@@ -9997,33 +9951,33 @@
         <v>3</v>
       </c>
       <c r="X147" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="Y147" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="148" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B148" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D148" t="s">
-        <v>824</v>
+        <v>785</v>
       </c>
       <c r="E148" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="F148" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J148" t="s">
-        <v>825</v>
+        <v>786</v>
       </c>
       <c r="L148" s="4" t="s">
-        <v>826</v>
+        <v>787</v>
       </c>
       <c r="R148" t="s">
         <v>24</v>
@@ -10044,39 +9998,39 @@
         <v>3</v>
       </c>
       <c r="X148" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="Y148" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="149" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B149" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D149">
         <v>1777</v>
       </c>
       <c r="E149" t="s">
-        <v>827</v>
+        <v>788</v>
       </c>
       <c r="F149" t="s">
-        <v>828</v>
+        <v>789</v>
       </c>
       <c r="J149" t="s">
-        <v>829</v>
+        <v>790</v>
       </c>
       <c r="L149" s="4" t="s">
-        <v>830</v>
+        <v>791</v>
       </c>
       <c r="R149" t="s">
         <v>24</v>
       </c>
       <c r="S149" t="s">
-        <v>721</v>
+        <v>693</v>
       </c>
       <c r="T149" s="1">
         <v>61</v>
@@ -10091,18 +10045,18 @@
         <v>3</v>
       </c>
       <c r="X149" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="Y149" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="150" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B150" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D150">
         <v>1769</v>
@@ -10114,10 +10068,10 @@
         <v>29</v>
       </c>
       <c r="J150" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="L150" s="10" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="R150" t="s">
         <v>24</v>
@@ -10138,33 +10092,33 @@
         <v>2</v>
       </c>
       <c r="X150" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="Y150" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="151" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B151" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D151">
         <v>1773</v>
       </c>
       <c r="E151" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F151" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="J151" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="L151" s="10" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="R151" t="s">
         <v>24</v>
@@ -10185,18 +10139,18 @@
         <v>2</v>
       </c>
       <c r="X151" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="Y151" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="152" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B152" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D152">
         <v>1775</v>
@@ -10208,10 +10162,10 @@
         <v>29</v>
       </c>
       <c r="J152" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="L152" s="10" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="R152" t="s">
         <v>24</v>
@@ -10232,18 +10186,18 @@
         <v>2</v>
       </c>
       <c r="X152" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="Y152" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="153" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B153" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D153">
         <v>1783</v>
@@ -10255,10 +10209,10 @@
         <v>29</v>
       </c>
       <c r="J153" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="L153" s="10" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="R153" t="s">
         <v>24</v>
@@ -10279,18 +10233,18 @@
         <v>2</v>
       </c>
       <c r="X153" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="Y153" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="154" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B154" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D154">
         <v>1760</v>
@@ -10302,10 +10256,10 @@
         <v>29</v>
       </c>
       <c r="J154" t="s">
-        <v>733</v>
+        <v>703</v>
       </c>
       <c r="L154" s="4" t="s">
-        <v>734</v>
+        <v>704</v>
       </c>
       <c r="R154" t="s">
         <v>24</v>
@@ -10323,24 +10277,24 @@
         <v>50</v>
       </c>
       <c r="W154" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X154" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="Y154" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="155" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B155" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D155" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E155" t="s">
         <v>28</v>
@@ -10349,10 +10303,10 @@
         <v>29</v>
       </c>
       <c r="J155" t="s">
-        <v>735</v>
+        <v>705</v>
       </c>
       <c r="L155" s="4" t="s">
-        <v>736</v>
+        <v>706</v>
       </c>
       <c r="R155" t="s">
         <v>24</v>
@@ -10361,33 +10315,33 @@
         <v>101</v>
       </c>
       <c r="T155" s="1" t="s">
-        <v>737</v>
+        <v>707</v>
       </c>
       <c r="U155" s="1" t="s">
-        <v>683</v>
+        <v>655</v>
       </c>
       <c r="V155" s="1" t="s">
-        <v>738</v>
+        <v>708</v>
       </c>
       <c r="W155" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X155" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="Y155" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="156" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B156" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D156" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="E156" t="s">
         <v>28</v>
@@ -10396,10 +10350,10 @@
         <v>29</v>
       </c>
       <c r="J156" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="L156" s="4" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="R156" t="s">
         <v>24</v>
@@ -10420,39 +10374,39 @@
         <v>1</v>
       </c>
       <c r="X156" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Y156" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="157" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B157" t="s">
+        <v>275</v>
+      </c>
+      <c r="D157" t="s">
+        <v>278</v>
+      </c>
+      <c r="E157" t="s">
+        <v>279</v>
+      </c>
+      <c r="F157" t="s">
+        <v>280</v>
+      </c>
+      <c r="J157" t="s">
         <v>281</v>
       </c>
-      <c r="D157" t="s">
-        <v>284</v>
-      </c>
-      <c r="E157" t="s">
-        <v>285</v>
-      </c>
-      <c r="F157" t="s">
-        <v>286</v>
-      </c>
-      <c r="J157" t="s">
-        <v>287</v>
-      </c>
       <c r="L157" s="4" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="R157" t="s">
         <v>53</v>
       </c>
       <c r="S157" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="T157" s="1">
         <v>610</v>
@@ -10467,21 +10421,21 @@
         <v>1</v>
       </c>
       <c r="X157" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Y157" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="158" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B158" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D158" t="s">
-        <v>831</v>
+        <v>792</v>
       </c>
       <c r="E158" t="s">
         <v>28</v>
@@ -10490,10 +10444,10 @@
         <v>29</v>
       </c>
       <c r="J158" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="L158" s="4" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="R158" t="s">
         <v>24</v>
@@ -10514,33 +10468,33 @@
         <v>1</v>
       </c>
       <c r="X158" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Y158" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="159" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B159" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D159" t="s">
-        <v>832</v>
+        <v>793</v>
       </c>
       <c r="E159" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="F159" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="J159" t="s">
-        <v>833</v>
+        <v>794</v>
       </c>
       <c r="L159" s="4" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="R159" t="s">
         <v>24</v>
@@ -10561,21 +10515,21 @@
         <v>1</v>
       </c>
       <c r="X159" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Y159" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="160" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B160" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D160" t="s">
-        <v>820</v>
+        <v>781</v>
       </c>
       <c r="E160" t="s">
         <v>28</v>
@@ -10584,10 +10538,10 @@
         <v>29</v>
       </c>
       <c r="J160" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="L160" s="4" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="R160" t="s">
         <v>24</v>
@@ -10608,21 +10562,21 @@
         <v>1</v>
       </c>
       <c r="X160" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Y160" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="161" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B161" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D161" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="E161" t="s">
         <v>28</v>
@@ -10631,10 +10585,10 @@
         <v>29</v>
       </c>
       <c r="J161" t="s">
-        <v>834</v>
+        <v>795</v>
       </c>
       <c r="L161" s="4" t="s">
-        <v>835</v>
+        <v>796</v>
       </c>
       <c r="R161" t="s">
         <v>24</v>
@@ -10655,80 +10609,80 @@
         <v>1</v>
       </c>
       <c r="X161" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Y161" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="162" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B162" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D162" t="s">
-        <v>202</v>
+        <v>915</v>
       </c>
       <c r="E162" t="s">
         <v>28</v>
       </c>
       <c r="F162" t="s">
-        <v>836</v>
+        <v>355</v>
       </c>
       <c r="J162" t="s">
-        <v>837</v>
+        <v>797</v>
       </c>
       <c r="L162" s="4" t="s">
-        <v>838</v>
+        <v>798</v>
       </c>
       <c r="R162" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S162" t="s">
         <v>25</v>
       </c>
       <c r="T162" s="1">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="U162" s="1">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="V162" s="1">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W162" s="1">
         <v>1</v>
       </c>
       <c r="X162" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Y162" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="163" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B163" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D163">
         <v>1777</v>
       </c>
       <c r="E163" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="F163" t="s">
-        <v>839</v>
+        <v>799</v>
       </c>
       <c r="J163" t="s">
-        <v>840</v>
+        <v>800</v>
       </c>
       <c r="L163" s="4" t="s">
-        <v>841</v>
+        <v>801</v>
       </c>
       <c r="R163" t="s">
         <v>53</v>
@@ -10749,42 +10703,42 @@
         <v>2</v>
       </c>
       <c r="X163" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Y163" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="164" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B164" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D164" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E164" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F164" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J164" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="K164" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="L164" s="10" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="R164" t="s">
         <v>24</v>
       </c>
       <c r="S164" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="T164" s="1">
         <v>195</v>
@@ -10799,21 +10753,21 @@
         <v>3</v>
       </c>
       <c r="X164" s="1" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Y164" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="165" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B165" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D165" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E165" t="s">
         <v>86</v>
@@ -10822,16 +10776,16 @@
         <v>87</v>
       </c>
       <c r="H165" t="s">
-        <v>842</v>
+        <v>802</v>
       </c>
       <c r="J165" t="s">
-        <v>843</v>
+        <v>803</v>
       </c>
       <c r="K165" t="s">
-        <v>844</v>
+        <v>804</v>
       </c>
       <c r="L165" s="10" t="s">
-        <v>845</v>
+        <v>805</v>
       </c>
       <c r="R165" t="s">
         <v>24</v>
@@ -10852,10 +10806,10 @@
         <v>3</v>
       </c>
       <c r="X165" s="1" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Y165" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="166" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10866,13 +10820,13 @@
     </row>
     <row r="168" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B168" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D168" t="s">
-        <v>578</v>
+        <v>557</v>
       </c>
       <c r="E168" t="s">
         <v>48</v>
@@ -10881,13 +10835,13 @@
         <v>49</v>
       </c>
       <c r="J168" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="K168" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="L168" s="4" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="R168" t="s">
         <v>53</v>
@@ -10895,52 +10849,49 @@
       <c r="S168" t="s">
         <v>25</v>
       </c>
-      <c r="T168">
+      <c r="T168" s="1">
         <v>245</v>
       </c>
-      <c r="U168">
+      <c r="U168" s="1">
         <v>150</v>
       </c>
-      <c r="V168">
+      <c r="V168" s="1">
         <v>95</v>
       </c>
       <c r="W168">
         <v>1</v>
       </c>
       <c r="X168" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="Y168" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="169" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B169" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D169" t="s">
-        <v>652</v>
+        <v>625</v>
       </c>
       <c r="E169" t="s">
-        <v>846</v>
+        <v>806</v>
       </c>
       <c r="F169" t="s">
-        <v>847</v>
-      </c>
-      <c r="H169" t="s">
-        <v>848</v>
+        <v>807</v>
       </c>
       <c r="J169" t="s">
-        <v>849</v>
+        <v>808</v>
       </c>
       <c r="K169" t="s">
-        <v>850</v>
+        <v>809</v>
       </c>
       <c r="L169" s="4" t="s">
-        <v>851</v>
+        <v>810</v>
       </c>
       <c r="R169" t="s">
         <v>24</v>
@@ -10948,49 +10899,49 @@
       <c r="S169" t="s">
         <v>25</v>
       </c>
-      <c r="T169">
+      <c r="T169" s="1">
         <v>195</v>
       </c>
-      <c r="U169">
+      <c r="U169" s="1">
         <v>85</v>
       </c>
-      <c r="V169">
+      <c r="V169" s="1">
         <v>75</v>
       </c>
       <c r="W169">
         <v>1</v>
       </c>
       <c r="X169" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="Y169" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="170" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B170" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D170" t="s">
-        <v>629</v>
+        <v>603</v>
       </c>
       <c r="E170" t="s">
         <v>48</v>
       </c>
       <c r="F170" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="J170" t="s">
-        <v>852</v>
+        <v>811</v>
       </c>
       <c r="K170" t="s">
-        <v>853</v>
+        <v>812</v>
       </c>
       <c r="L170" s="4" t="s">
-        <v>854</v>
+        <v>813</v>
       </c>
       <c r="R170" t="s">
         <v>24</v>
@@ -10998,34 +10949,34 @@
       <c r="S170" t="s">
         <v>25</v>
       </c>
-      <c r="T170">
+      <c r="T170" s="1">
         <v>62</v>
       </c>
-      <c r="U170">
+      <c r="U170" s="1">
         <v>45</v>
       </c>
-      <c r="V170">
+      <c r="V170" s="1">
         <v>28</v>
       </c>
       <c r="W170">
         <v>1</v>
       </c>
       <c r="X170" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="Y170" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="171" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B171" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D171" t="s">
-        <v>855</v>
+        <v>814</v>
       </c>
       <c r="E171" t="s">
         <v>48</v>
@@ -11034,13 +10985,13 @@
         <v>65</v>
       </c>
       <c r="J171" t="s">
-        <v>856</v>
+        <v>815</v>
       </c>
       <c r="K171" t="s">
-        <v>857</v>
+        <v>816</v>
       </c>
       <c r="L171" s="4" t="s">
-        <v>858</v>
+        <v>817</v>
       </c>
       <c r="R171" t="s">
         <v>24</v>
@@ -11048,49 +10999,49 @@
       <c r="S171" t="s">
         <v>25</v>
       </c>
-      <c r="T171">
+      <c r="T171" s="1">
         <v>137</v>
       </c>
-      <c r="U171">
+      <c r="U171" s="1">
         <v>102</v>
       </c>
-      <c r="V171">
+      <c r="V171" s="1">
         <v>84</v>
       </c>
       <c r="W171">
         <v>1</v>
       </c>
       <c r="X171" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="Y171" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="172" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B172" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D172" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E172" t="s">
-        <v>859</v>
+        <v>818</v>
       </c>
       <c r="F172" t="s">
-        <v>860</v>
+        <v>819</v>
       </c>
       <c r="J172" t="s">
-        <v>861</v>
+        <v>820</v>
       </c>
       <c r="K172" t="s">
-        <v>862</v>
+        <v>821</v>
       </c>
       <c r="L172" s="4" t="s">
-        <v>863</v>
+        <v>822</v>
       </c>
       <c r="R172" t="s">
         <v>24</v>
@@ -11098,23 +11049,23 @@
       <c r="S172" t="s">
         <v>25</v>
       </c>
-      <c r="T172">
+      <c r="T172" s="1">
         <v>65</v>
       </c>
-      <c r="U172">
+      <c r="U172" s="1">
         <v>48</v>
       </c>
-      <c r="V172">
+      <c r="V172" s="1">
         <v>30</v>
       </c>
       <c r="W172">
         <v>1</v>
       </c>
       <c r="X172" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="Y172" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="173" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11128,25 +11079,25 @@
     </row>
     <row r="176" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B176" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D176" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E176" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="F176" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J176" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="L176" s="10" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="R176" t="s">
         <v>24</v>
@@ -11155,45 +11106,42 @@
         <v>101</v>
       </c>
       <c r="T176" s="1" t="s">
-        <v>864</v>
+        <v>823</v>
       </c>
       <c r="W176" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X176" s="1" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="Y176" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="177" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B177" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D177" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E177" t="s">
         <v>86</v>
       </c>
       <c r="F177" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J177" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="K177" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="L177" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="M177" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="R177" t="s">
         <v>24</v>
@@ -11202,50 +11150,47 @@
         <v>25</v>
       </c>
       <c r="T177" s="1" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="U177" s="1" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="V177" s="1" t="s">
-        <v>865</v>
+        <v>824</v>
       </c>
       <c r="W177" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X177" s="1" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="Y177" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="178" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B178" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D178" t="s">
-        <v>866</v>
+        <v>825</v>
       </c>
       <c r="E178" t="s">
         <v>86</v>
       </c>
       <c r="F178" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J178" t="s">
-        <v>867</v>
+        <v>826</v>
       </c>
       <c r="K178" t="s">
-        <v>868</v>
+        <v>827</v>
       </c>
       <c r="L178" s="10"/>
-      <c r="M178" t="s">
-        <v>869</v>
-      </c>
       <c r="R178" t="s">
         <v>24</v>
       </c>
@@ -11253,51 +11198,48 @@
         <v>25</v>
       </c>
       <c r="T178" s="1" t="s">
-        <v>870</v>
+        <v>828</v>
       </c>
       <c r="U178" s="1" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="V178" s="1" t="s">
-        <v>865</v>
+        <v>824</v>
       </c>
       <c r="W178" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X178" s="1" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="Y178" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="179" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B179" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D179" t="s">
-        <v>871</v>
+        <v>829</v>
       </c>
       <c r="E179" t="s">
         <v>86</v>
       </c>
       <c r="F179" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J179" t="s">
-        <v>872</v>
+        <v>830</v>
       </c>
       <c r="K179" t="s">
-        <v>873</v>
+        <v>831</v>
       </c>
       <c r="L179" s="10" t="s">
-        <v>874</v>
-      </c>
-      <c r="M179" t="s">
-        <v>869</v>
+        <v>832</v>
       </c>
       <c r="R179" t="s">
         <v>24</v>
@@ -11306,30 +11248,30 @@
         <v>25</v>
       </c>
       <c r="T179" s="1" t="s">
-        <v>870</v>
+        <v>828</v>
       </c>
       <c r="U179" s="1" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="V179" s="1" t="s">
-        <v>865</v>
+        <v>824</v>
       </c>
       <c r="W179" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X179" s="1" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="Y179" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="180" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B180" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D180">
         <v>1731</v>
@@ -11341,13 +11283,13 @@
         <v>49</v>
       </c>
       <c r="J180" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L180" s="10" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="R180" t="s">
-        <v>24</v>
+        <v>600</v>
       </c>
       <c r="S180" t="s">
         <v>25</v>
@@ -11355,63 +11297,78 @@
       <c r="T180" s="1">
         <v>400</v>
       </c>
+      <c r="U180" s="1">
+        <v>240</v>
+      </c>
+      <c r="V180" s="1">
+        <v>120</v>
+      </c>
       <c r="W180" s="1">
         <v>3</v>
       </c>
       <c r="X180" s="1" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="Y180" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
     </row>
     <row r="181" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B181" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D181">
         <v>1733</v>
       </c>
       <c r="E181" t="s">
-        <v>875</v>
+        <v>833</v>
       </c>
       <c r="F181" t="s">
-        <v>876</v>
+        <v>834</v>
       </c>
       <c r="J181" t="s">
-        <v>877</v>
+        <v>835</v>
       </c>
       <c r="K181" t="s">
-        <v>878</v>
+        <v>836</v>
       </c>
       <c r="L181" s="10" t="s">
-        <v>879</v>
+        <v>837</v>
       </c>
       <c r="R181" t="s">
-        <v>880</v>
+        <v>838</v>
       </c>
       <c r="S181" t="s">
         <v>58</v>
       </c>
+      <c r="T181" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="U181" s="1">
+        <v>105</v>
+      </c>
+      <c r="V181" s="1">
+        <v>250</v>
+      </c>
       <c r="W181" s="1">
         <v>3</v>
       </c>
       <c r="X181" s="1" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="Y181" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
     </row>
     <row r="182" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B182" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D182">
         <v>1737</v>
@@ -11423,36 +11380,45 @@
         <v>49</v>
       </c>
       <c r="J182" t="s">
-        <v>881</v>
+        <v>839</v>
       </c>
       <c r="K182" t="s">
-        <v>882</v>
+        <v>840</v>
       </c>
       <c r="L182" s="10" t="s">
-        <v>883</v>
+        <v>841</v>
       </c>
       <c r="R182" t="s">
-        <v>626</v>
+        <v>600</v>
       </c>
       <c r="S182" t="s">
         <v>25</v>
       </c>
+      <c r="T182" s="1">
+        <v>150</v>
+      </c>
+      <c r="U182" s="1">
+        <v>100</v>
+      </c>
+      <c r="V182" s="1">
+        <v>50</v>
+      </c>
       <c r="W182" s="1">
         <v>3</v>
       </c>
       <c r="X182" s="1" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="Y182" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
     </row>
     <row r="183" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B183" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D183">
         <v>1756</v>
@@ -11461,214 +11427,242 @@
         <v>48</v>
       </c>
       <c r="F183" t="s">
-        <v>679</v>
+        <v>651</v>
       </c>
       <c r="J183" t="s">
-        <v>884</v>
+        <v>928</v>
       </c>
       <c r="K183" t="s">
-        <v>885</v>
-      </c>
-      <c r="L183" s="10" t="s">
-        <v>886</v>
+        <v>842</v>
+      </c>
+      <c r="L183" s="14" t="s">
+        <v>843</v>
       </c>
       <c r="R183" t="s">
-        <v>887</v>
+        <v>24</v>
       </c>
       <c r="S183" t="s">
         <v>25</v>
       </c>
+      <c r="T183" s="1">
+        <v>68</v>
+      </c>
+      <c r="U183" s="1">
+        <v>60</v>
+      </c>
       <c r="W183" s="1">
         <v>3</v>
       </c>
       <c r="X183" s="1" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="Y183" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
     </row>
     <row r="184" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B184" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="D184" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E184" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="F184" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="J184" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="L184" s="4" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="R184" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S184" t="s">
-        <v>25</v>
-      </c>
-      <c r="T184" t="s">
-        <v>739</v>
-      </c>
-      <c r="U184"/>
-      <c r="V184"/>
+        <v>919</v>
+      </c>
+      <c r="T184" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="U184" s="1">
+        <v>340</v>
+      </c>
+      <c r="V184" s="1">
+        <v>270</v>
+      </c>
       <c r="W184" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X184" s="1" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="Y184" s="1" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="185" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B185" t="s">
-        <v>324</v>
-      </c>
-      <c r="D185" t="s">
-        <v>888</v>
+        <v>317</v>
+      </c>
+      <c r="D185">
+        <v>1763</v>
       </c>
       <c r="E185" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="F185" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="J185" t="s">
-        <v>889</v>
+        <v>916</v>
       </c>
       <c r="K185" t="s">
-        <v>890</v>
+        <v>844</v>
       </c>
       <c r="L185" s="4" t="s">
-        <v>891</v>
+        <v>845</v>
       </c>
       <c r="R185" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S185" t="s">
-        <v>146</v>
-      </c>
-      <c r="T185"/>
-      <c r="U185"/>
-      <c r="V185"/>
+        <v>919</v>
+      </c>
+      <c r="T185" s="1">
+        <v>210</v>
+      </c>
+      <c r="U185" s="1">
+        <v>300</v>
+      </c>
+      <c r="V185" s="1">
+        <v>250</v>
+      </c>
       <c r="W185" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
     </row>
     <row r="186" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B186" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="D186" t="s">
-        <v>649</v>
+        <v>622</v>
       </c>
       <c r="E186" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="F186" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="J186" t="s">
-        <v>892</v>
+        <v>846</v>
       </c>
       <c r="K186" t="s">
-        <v>893</v>
+        <v>847</v>
       </c>
       <c r="L186" s="4" t="s">
-        <v>894</v>
+        <v>848</v>
       </c>
       <c r="R186" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S186" t="s">
-        <v>146</v>
-      </c>
-      <c r="T186"/>
-      <c r="U186"/>
-      <c r="V186"/>
+        <v>919</v>
+      </c>
+      <c r="T186" s="1">
+        <v>170</v>
+      </c>
+      <c r="U186" s="1">
+        <v>210</v>
+      </c>
+      <c r="V186" s="1">
+        <v>230</v>
+      </c>
       <c r="W186" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B187" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="D187" t="s">
-        <v>652</v>
+        <v>625</v>
       </c>
       <c r="E187" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="F187" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="J187" t="s">
-        <v>895</v>
+        <v>925</v>
       </c>
       <c r="K187" t="s">
-        <v>896</v>
+        <v>849</v>
       </c>
       <c r="L187" s="4" t="s">
-        <v>897</v>
+        <v>850</v>
       </c>
       <c r="R187" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S187" t="s">
-        <v>146</v>
-      </c>
-      <c r="T187"/>
-      <c r="U187"/>
-      <c r="V187"/>
+        <v>919</v>
+      </c>
+      <c r="T187" s="1">
+        <v>170</v>
+      </c>
+      <c r="U187" s="1">
+        <v>210</v>
+      </c>
+      <c r="V187" s="1">
+        <v>240</v>
+      </c>
       <c r="W187" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
     </row>
     <row r="188" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B188" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D188" t="s">
-        <v>574</v>
+        <v>553</v>
       </c>
       <c r="E188" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F188" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J188" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="K188" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="L188" s="4" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="R188" t="s">
         <v>24</v>
@@ -11676,49 +11670,49 @@
       <c r="S188" t="s">
         <v>25</v>
       </c>
-      <c r="T188" t="s">
-        <v>571</v>
-      </c>
-      <c r="U188" t="s">
-        <v>482</v>
-      </c>
-      <c r="V188" t="s">
-        <v>898</v>
+      <c r="T188" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="U188" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="V188" s="1" t="s">
+        <v>851</v>
       </c>
       <c r="W188" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X188" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="Y188" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="189" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B189" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D189" t="s">
         <v>96</v>
       </c>
       <c r="E189" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F189" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="J189" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="K189" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L189" s="4" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="R189" t="s">
         <v>24</v>
@@ -11726,46 +11720,46 @@
       <c r="S189" t="s">
         <v>25</v>
       </c>
-      <c r="T189" t="s">
-        <v>899</v>
-      </c>
-      <c r="U189" t="s">
-        <v>664</v>
-      </c>
-      <c r="V189" t="s">
-        <v>373</v>
+      <c r="T189" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="U189" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="V189" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="W189" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X189" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="Y189" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="190" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B190" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D190" t="s">
-        <v>900</v>
+        <v>853</v>
       </c>
       <c r="E190" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F190" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="J190" t="s">
-        <v>901</v>
+        <v>854</v>
       </c>
       <c r="L190" s="4" t="s">
-        <v>902</v>
+        <v>855</v>
       </c>
       <c r="R190" t="s">
         <v>24</v>
@@ -11773,45 +11767,43 @@
       <c r="S190" t="s">
         <v>25</v>
       </c>
-      <c r="T190">
+      <c r="T190" s="1">
         <v>173</v>
       </c>
-      <c r="U190"/>
-      <c r="V190"/>
       <c r="W190" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X190" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="Y190" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="191" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B191" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D191" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="E191" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F191" t="s">
-        <v>903</v>
+        <v>856</v>
       </c>
       <c r="J191" t="s">
-        <v>904</v>
+        <v>857</v>
       </c>
       <c r="K191" t="s">
-        <v>905</v>
+        <v>858</v>
       </c>
       <c r="L191" s="4" t="s">
-        <v>906</v>
+        <v>859</v>
       </c>
       <c r="R191" t="s">
         <v>24</v>
@@ -11819,494 +11811,507 @@
       <c r="S191" t="s">
         <v>25</v>
       </c>
-      <c r="T191" t="s">
-        <v>587</v>
-      </c>
-      <c r="U191"/>
-      <c r="V191"/>
+      <c r="T191" s="1" t="s">
+        <v>565</v>
+      </c>
       <c r="W191" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X191" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="Y191" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="192" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="B192" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D192" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="E192" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="F192" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="J192" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="K192" t="s">
-        <v>907</v>
+        <v>860</v>
       </c>
       <c r="L192" s="4" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="R192" t="s">
-        <v>24</v>
+        <v>910</v>
       </c>
       <c r="S192" t="s">
         <v>25</v>
       </c>
-      <c r="T192" t="s">
-        <v>908</v>
-      </c>
-      <c r="U192"/>
-      <c r="V192"/>
+      <c r="T192" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="U192" s="1">
+        <v>102</v>
+      </c>
+      <c r="V192" s="1">
+        <v>61</v>
+      </c>
       <c r="W192" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X192" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="Y192" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="193" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="B193" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D193" t="s">
-        <v>662</v>
+        <v>635</v>
       </c>
       <c r="E193" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="F193" t="s">
-        <v>909</v>
+        <v>862</v>
       </c>
       <c r="J193" t="s">
-        <v>910</v>
+        <v>863</v>
       </c>
       <c r="K193" t="s">
-        <v>911</v>
+        <v>864</v>
       </c>
       <c r="L193" s="4" t="s">
-        <v>912</v>
+        <v>865</v>
       </c>
       <c r="R193" t="s">
-        <v>913</v>
+        <v>929</v>
       </c>
       <c r="S193" t="s">
-        <v>914</v>
-      </c>
-      <c r="T193" t="s">
-        <v>481</v>
-      </c>
-      <c r="U193"/>
-      <c r="V193"/>
+        <v>866</v>
+      </c>
+      <c r="T193" s="1">
+        <v>550</v>
+      </c>
+      <c r="U193" s="1">
+        <v>650</v>
+      </c>
+      <c r="V193" s="1">
+        <v>500</v>
+      </c>
       <c r="W193" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X193" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="Y193" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="194" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="B194" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D194" t="s">
-        <v>688</v>
+        <v>660</v>
       </c>
       <c r="E194" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="F194" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="J194" t="s">
-        <v>915</v>
+        <v>867</v>
       </c>
       <c r="K194" t="s">
-        <v>916</v>
+        <v>868</v>
       </c>
       <c r="L194" s="4" t="s">
-        <v>917</v>
+        <v>869</v>
       </c>
       <c r="R194" t="s">
-        <v>626</v>
+        <v>600</v>
       </c>
       <c r="S194" t="s">
         <v>25</v>
       </c>
-      <c r="T194"/>
-      <c r="U194"/>
-      <c r="V194"/>
+      <c r="T194" s="1">
+        <v>623</v>
+      </c>
+      <c r="U194" s="1">
+        <v>370</v>
+      </c>
+      <c r="V194" s="1">
+        <v>277</v>
+      </c>
       <c r="W194" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X194" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="Y194" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="195" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="B195" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D195" t="s">
-        <v>918</v>
+        <v>870</v>
       </c>
       <c r="E195" t="s">
-        <v>919</v>
+        <v>871</v>
       </c>
       <c r="F195" t="s">
-        <v>920</v>
+        <v>872</v>
       </c>
       <c r="J195" t="s">
-        <v>921</v>
+        <v>873</v>
       </c>
       <c r="K195" t="s">
-        <v>922</v>
+        <v>874</v>
       </c>
       <c r="L195" s="4" t="s">
-        <v>923</v>
+        <v>875</v>
       </c>
       <c r="R195" t="s">
         <v>24</v>
       </c>
       <c r="S195" t="s">
-        <v>58</v>
-      </c>
-      <c r="T195"/>
-      <c r="U195"/>
-      <c r="V195"/>
+        <v>866</v>
+      </c>
+      <c r="T195" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="U195" s="1">
+        <v>200</v>
+      </c>
+      <c r="V195" s="1">
+        <v>250</v>
+      </c>
       <c r="W195" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X195" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="Y195" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="196" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B196" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="D196" t="s">
-        <v>924</v>
+        <v>876</v>
       </c>
       <c r="E196" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="F196" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="J196" t="s">
-        <v>350</v>
+        <v>905</v>
       </c>
       <c r="K196" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="L196" s="4" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="R196" t="s">
         <v>24</v>
       </c>
       <c r="S196" t="s">
-        <v>353</v>
-      </c>
-      <c r="T196" t="s">
-        <v>925</v>
-      </c>
-      <c r="U196" t="s">
-        <v>926</v>
-      </c>
-      <c r="V196" t="s">
-        <v>571</v>
+        <v>345</v>
+      </c>
+      <c r="T196" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="U196" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="V196" s="1" t="s">
+        <v>550</v>
       </c>
       <c r="W196" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X196" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="Y196" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="197" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>339</v>
+      </c>
+      <c r="B197" t="s">
+        <v>340</v>
+      </c>
+      <c r="D197" t="s">
         <v>346</v>
       </c>
-      <c r="B197" t="s">
+      <c r="E197" t="s">
+        <v>341</v>
+      </c>
+      <c r="F197" t="s">
         <v>347</v>
       </c>
-      <c r="D197" t="s">
-        <v>354</v>
-      </c>
-      <c r="E197" t="s">
+      <c r="J197" t="s">
+        <v>904</v>
+      </c>
+      <c r="K197" t="s">
         <v>348</v>
       </c>
-      <c r="F197" t="s">
-        <v>355</v>
-      </c>
-      <c r="J197" t="s">
-        <v>356</v>
-      </c>
-      <c r="K197" t="s">
-        <v>357</v>
-      </c>
       <c r="L197" s="4" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="R197" t="s">
         <v>24</v>
       </c>
       <c r="S197" t="s">
-        <v>359</v>
-      </c>
-      <c r="T197" t="s">
-        <v>482</v>
-      </c>
-      <c r="U197" t="s">
-        <v>582</v>
-      </c>
-      <c r="V197" t="s">
-        <v>571</v>
+        <v>345</v>
+      </c>
+      <c r="T197" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="U197" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="V197" s="1" t="s">
+        <v>550</v>
       </c>
       <c r="W197" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X197" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="Y197" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="198" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B198" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="D198" t="s">
-        <v>927</v>
+        <v>879</v>
       </c>
       <c r="E198" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="F198" t="s">
-        <v>928</v>
+        <v>880</v>
       </c>
       <c r="J198" t="s">
-        <v>929</v>
+        <v>881</v>
       </c>
       <c r="K198" t="s">
-        <v>930</v>
+        <v>882</v>
       </c>
       <c r="L198" s="4" t="s">
-        <v>931</v>
+        <v>883</v>
       </c>
       <c r="R198" t="s">
         <v>24</v>
       </c>
       <c r="S198" t="s">
-        <v>353</v>
-      </c>
-      <c r="T198" t="s">
-        <v>482</v>
-      </c>
-      <c r="U198"/>
-      <c r="V198"/>
+        <v>345</v>
+      </c>
+      <c r="T198" s="1" t="s">
+        <v>465</v>
+      </c>
       <c r="W198" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X198" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="Y198" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="199" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B199" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="D199" t="s">
-        <v>932</v>
+        <v>884</v>
       </c>
       <c r="E199" t="s">
-        <v>933</v>
+        <v>885</v>
       </c>
       <c r="F199" t="s">
-        <v>934</v>
+        <v>886</v>
       </c>
       <c r="J199" t="s">
-        <v>935</v>
+        <v>887</v>
       </c>
       <c r="K199" t="s">
-        <v>936</v>
+        <v>888</v>
       </c>
       <c r="L199" s="4" t="s">
-        <v>937</v>
+        <v>889</v>
       </c>
       <c r="R199" t="s">
         <v>24</v>
       </c>
       <c r="S199" t="s">
-        <v>353</v>
-      </c>
-      <c r="T199" t="s">
-        <v>938</v>
-      </c>
-      <c r="U199"/>
-      <c r="V199"/>
+        <v>345</v>
+      </c>
+      <c r="T199" s="1" t="s">
+        <v>890</v>
+      </c>
       <c r="W199" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X199" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="Y199" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="200" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B200" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="D200" t="s">
-        <v>939</v>
+        <v>891</v>
       </c>
       <c r="E200" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="F200" t="s">
-        <v>940</v>
+        <v>892</v>
       </c>
       <c r="J200" t="s">
-        <v>941</v>
+        <v>893</v>
       </c>
       <c r="K200" t="s">
-        <v>942</v>
+        <v>894</v>
       </c>
       <c r="L200" s="4" t="s">
-        <v>943</v>
+        <v>895</v>
       </c>
       <c r="R200" t="s">
         <v>24</v>
       </c>
       <c r="S200" t="s">
-        <v>353</v>
-      </c>
-      <c r="T200" t="s">
-        <v>427</v>
-      </c>
-      <c r="U200"/>
-      <c r="V200"/>
+        <v>345</v>
+      </c>
+      <c r="T200" s="1" t="s">
+        <v>415</v>
+      </c>
       <c r="W200" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X200" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="Y200" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="201" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B201" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="D201" t="s">
-        <v>939</v>
+        <v>891</v>
       </c>
       <c r="E201" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="F201" t="s">
-        <v>940</v>
+        <v>892</v>
       </c>
       <c r="J201" t="s">
-        <v>944</v>
+        <v>896</v>
       </c>
       <c r="K201" t="s">
-        <v>945</v>
+        <v>897</v>
       </c>
       <c r="L201" s="4" t="s">
-        <v>946</v>
+        <v>898</v>
       </c>
       <c r="R201" t="s">
         <v>24</v>
       </c>
       <c r="S201" t="s">
-        <v>353</v>
-      </c>
-      <c r="T201" t="s">
-        <v>482</v>
-      </c>
-      <c r="U201"/>
-      <c r="V201"/>
+        <v>345</v>
+      </c>
+      <c r="T201" s="1" t="s">
+        <v>465</v>
+      </c>
       <c r="W201" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="X201" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="Y201" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="202" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B202" t="s">
-        <v>361</v>
+        <v>351</v>
+      </c>
+      <c r="C202" t="s">
+        <v>907</v>
       </c>
       <c r="D202" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="E202" t="s">
         <v>86</v>
@@ -12315,13 +12320,13 @@
         <v>105</v>
       </c>
       <c r="J202" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="K202" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="L202" s="4" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="R202" t="s">
         <v>24</v>
@@ -12329,81 +12334,87 @@
       <c r="S202" t="s">
         <v>25</v>
       </c>
-      <c r="T202" t="s">
-        <v>677</v>
-      </c>
-      <c r="U202" t="s">
-        <v>938</v>
-      </c>
-      <c r="V202" t="s">
-        <v>947</v>
+      <c r="T202" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="U202" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="V202" s="1" t="s">
+        <v>899</v>
       </c>
       <c r="W202" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X202" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="Y202" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="203" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B203" t="s">
-        <v>361</v>
+        <v>351</v>
+      </c>
+      <c r="C203" t="s">
+        <v>907</v>
       </c>
       <c r="D203" t="s">
-        <v>652</v>
+        <v>625</v>
       </c>
       <c r="E203" t="s">
         <v>28</v>
       </c>
       <c r="F203" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="J203" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="L203" s="4" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="R203" t="s">
         <v>53</v>
       </c>
       <c r="S203" t="s">
-        <v>289</v>
-      </c>
-      <c r="T203" t="s">
-        <v>378</v>
-      </c>
-      <c r="U203" t="s">
-        <v>427</v>
-      </c>
-      <c r="V203" t="s">
-        <v>694</v>
+        <v>283</v>
+      </c>
+      <c r="T203" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="U203" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="V203" s="1" t="s">
+        <v>666</v>
       </c>
       <c r="W203" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X203" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="Y203" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="204" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B204" t="s">
-        <v>361</v>
+        <v>351</v>
+      </c>
+      <c r="C204" t="s">
+        <v>907</v>
       </c>
       <c r="D204" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="E204" t="s">
         <v>28</v>
@@ -12412,46 +12423,49 @@
         <v>29</v>
       </c>
       <c r="J204" t="s">
-        <v>948</v>
-      </c>
-      <c r="K204" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="L204"/>
+        <v>900</v>
+      </c>
+      <c r="K204" s="4"/>
+      <c r="L204" s="14" t="s">
+        <v>906</v>
+      </c>
       <c r="R204" t="s">
-        <v>951</v>
+        <v>903</v>
       </c>
       <c r="S204" t="s">
         <v>101</v>
       </c>
-      <c r="T204">
+      <c r="T204" s="1">
         <v>67</v>
       </c>
-      <c r="U204">
+      <c r="U204" s="1">
         <v>40</v>
       </c>
-      <c r="V204">
+      <c r="V204" s="1">
         <v>20</v>
       </c>
       <c r="W204" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X204" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="Y204" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="205" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B205" t="s">
-        <v>361</v>
+        <v>351</v>
+      </c>
+      <c r="C205" t="s">
+        <v>907</v>
       </c>
       <c r="D205" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="E205" t="s">
         <v>28</v>
@@ -12460,36 +12474,38 @@
         <v>29</v>
       </c>
       <c r="J205" t="s">
-        <v>949</v>
-      </c>
-      <c r="K205" s="4" t="s">
-        <v>950</v>
-      </c>
-      <c r="L205"/>
+        <v>901</v>
+      </c>
+      <c r="L205" s="4" t="s">
+        <v>902</v>
+      </c>
       <c r="R205" t="s">
-        <v>951</v>
+        <v>903</v>
       </c>
       <c r="S205" t="s">
         <v>101</v>
       </c>
-      <c r="T205">
+      <c r="T205" s="1">
         <v>53</v>
       </c>
-      <c r="U205">
+      <c r="U205" s="1">
         <v>35</v>
       </c>
-      <c r="V205">
+      <c r="V205" s="1">
         <v>38</v>
       </c>
       <c r="W205" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="X205" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="Y205" t="s">
-        <v>361</v>
-      </c>
+        <v>351</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -12673,8 +12689,9 @@
     <hyperlink ref="L201" r:id="rId177" xr:uid="{8F1627A4-1430-4DDC-8F4C-6D25B3C6305A}"/>
     <hyperlink ref="L202" r:id="rId178" xr:uid="{7DF06C24-00A8-4B94-A167-80D2D767B547}"/>
     <hyperlink ref="L203" r:id="rId179" xr:uid="{EAD52D1B-7ACB-4A08-849E-A72F62DC43BB}"/>
-    <hyperlink ref="K204" r:id="rId180" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Nancy%2C_%C3%A9glise_baroque_Notre_Dame_de_Bonsecours%2C_mausol%C3%A9e_de_Catherine_Opalinska_1.jpg/960px-Nancy%2C_%C3%A9glise_baroque_Notre_Dame_de_Bonsecours%2C_mausol%C3%A9e_de_Catherine_Opalinska_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{30250A7D-8DE5-446D-BEDF-8C7D1696BDBD}"/>
-    <hyperlink ref="K205" r:id="rId181" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8f/Michel-ange_slodtz%2C_chrys%C3%A9s_in_terracotta_1740_circa.JPG/960px-Michel-ange_slodtz%2C_chrys%C3%A9s_in_terracotta_1740_circa.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1C6422D5-1705-49AD-9231-CC8B4E521A9B}"/>
+    <hyperlink ref="L205" r:id="rId180" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8f/Michel-ange_slodtz%2C_chrys%C3%A9s_in_terracotta_1740_circa.JPG/960px-Michel-ange_slodtz%2C_chrys%C3%A9s_in_terracotta_1740_circa.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1C6422D5-1705-49AD-9231-CC8B4E521A9B}"/>
+    <hyperlink ref="L204" r:id="rId181" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/Iphig%C3%A9nie_-_Michel-Ange_Slodtz_-_Mus%C3%A9e_du_Louvre_Sculptures_ENT_1984.23.jpg/960px-Iphig%C3%A9nie_-_Michel-Ange_Slodtz_-_Mus%C3%A9e_du_Louvre_Sculptures_ENT_1984.23.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{ABC1E8B9-5F90-4977-8C63-4D00875F05C0}"/>
+    <hyperlink ref="L183" r:id="rId182" xr:uid="{35DF3567-290E-42FF-8909-C19B847ADC73}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -8474,7 +8474,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Pasadena</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2425DFA-77D1-4A1E-AFA2-50DECE5AAE70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA654CE-3A15-4A7A-A602-F66D3C2E2332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="915">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2341,9 +2341,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bf/070522_ukbris_qsqs.jpg/1280px-070522_ukbris_qsqs.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>285</t>
-  </si>
-  <si>
     <t>Monument to John Milton</t>
   </si>
   <si>
@@ -2753,6 +2750,21 @@
   </si>
   <si>
     <t>Maître-autel de la Croix</t>
+  </si>
+  <si>
+    <t>Artiste associé</t>
+  </si>
+  <si>
+    <t>Monument équestre avec ronde-bosse intégralement conçu par l'artiste</t>
+  </si>
+  <si>
+    <t>Bronze (statue), marbre (socle)</t>
+  </si>
+  <si>
+    <t>285 pour la statue, 430 pour le socle</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/af/In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg/960px-In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -3198,11 +3210,11 @@
     <col min="21" max="21" width="9.140625" style="15" customWidth="1"/>
     <col min="22" max="22" width="8.7109375" style="15" customWidth="1"/>
     <col min="23" max="23" width="6.28515625" style="15" customWidth="1"/>
-    <col min="24" max="24" width="6.5703125" style="15" customWidth="1"/>
+    <col min="24" max="24" width="24" customWidth="1"/>
     <col min="25" max="25" width="14.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3272,8 +3284,11 @@
       <c r="W1" s="15" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X1" s="15" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -3317,7 +3332,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -3364,7 +3379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -3408,7 +3423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -3452,7 +3467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -3496,7 +3511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -3540,7 +3555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>62</v>
       </c>
@@ -3581,7 +3596,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>62</v>
       </c>
@@ -3622,7 +3637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -3645,7 +3660,7 @@
         <v>72</v>
       </c>
       <c r="R10" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="S10" t="s">
         <v>32</v>
@@ -3663,7 +3678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -3704,7 +3719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -3745,7 +3760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -3786,7 +3801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>83</v>
       </c>
@@ -3827,7 +3842,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>83</v>
       </c>
@@ -3868,7 +3883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -3894,7 +3909,7 @@
         <v>101</v>
       </c>
       <c r="R16" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="S16" t="s">
         <v>32</v>
@@ -3973,7 +3988,7 @@
         <v>112</v>
       </c>
       <c r="J18" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K18" t="s">
         <v>113</v>
@@ -4017,7 +4032,7 @@
         <v>117</v>
       </c>
       <c r="J19" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="K19" t="s">
         <v>118</v>
@@ -4026,7 +4041,7 @@
         <v>119</v>
       </c>
       <c r="R19" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="S19" t="s">
         <v>32</v>
@@ -4105,7 +4120,7 @@
         <v>98</v>
       </c>
       <c r="J21" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="K21" t="s">
         <v>126</v>
@@ -4114,7 +4129,7 @@
         <v>127</v>
       </c>
       <c r="R21" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="S21" t="s">
         <v>32</v>
@@ -4249,7 +4264,7 @@
         <v>146</v>
       </c>
       <c r="R24" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="S24" t="s">
         <v>148</v>
@@ -4666,7 +4681,7 @@
         <v>191</v>
       </c>
       <c r="R33" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="S33" t="s">
         <v>192</v>
@@ -4748,7 +4763,7 @@
         <v>203</v>
       </c>
       <c r="J35" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="K35" t="s">
         <v>204</v>
@@ -4757,7 +4772,7 @@
         <v>205</v>
       </c>
       <c r="R35" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="S35" t="s">
         <v>32</v>
@@ -5047,7 +5062,7 @@
         <v>238</v>
       </c>
       <c r="R42" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="S42" t="s">
         <v>32</v>
@@ -5179,7 +5194,7 @@
         <v>252</v>
       </c>
       <c r="R45" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="S45" t="s">
         <v>32</v>
@@ -6038,7 +6053,7 @@
         <v>347</v>
       </c>
       <c r="R65" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="S65" t="s">
         <v>201</v>
@@ -6299,7 +6314,7 @@
         <v>380</v>
       </c>
       <c r="R71" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="S71" t="s">
         <v>381</v>
@@ -6437,7 +6452,7 @@
       <c r="P74" s="4"/>
       <c r="Q74" s="4"/>
       <c r="R74" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="S74" s="4" t="s">
         <v>69</v>
@@ -6478,7 +6493,7 @@
       </c>
       <c r="I75" s="4"/>
       <c r="J75" s="4" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>399</v>
@@ -6529,7 +6544,7 @@
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="I76" s="4"/>
       <c r="J76" s="4" t="s">
@@ -6547,7 +6562,7 @@
       <c r="P76" s="4"/>
       <c r="Q76" s="4"/>
       <c r="R76" s="4" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="S76" s="4" t="s">
         <v>409</v>
@@ -7052,7 +7067,7 @@
         <v>464</v>
       </c>
       <c r="J88" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="K88" t="s">
         <v>465</v>
@@ -7061,7 +7076,7 @@
         <v>466</v>
       </c>
       <c r="R88" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="S88" t="s">
         <v>32</v>
@@ -7096,7 +7111,7 @@
         <v>98</v>
       </c>
       <c r="J89" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K89" t="s">
         <v>471</v>
@@ -7105,7 +7120,7 @@
         <v>472</v>
       </c>
       <c r="R89" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="S89" t="s">
         <v>32</v>
@@ -7545,7 +7560,7 @@
         <v>533</v>
       </c>
       <c r="J99" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="L99" s="3" t="s">
         <v>534</v>
@@ -9231,10 +9246,10 @@
         <v>596</v>
       </c>
       <c r="J139" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="L139" s="11" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="R139" t="s">
         <v>56</v>
@@ -9483,7 +9498,7 @@
         <v>708</v>
       </c>
       <c r="R145" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="S145" t="s">
         <v>32</v>
@@ -9618,7 +9633,7 @@
         <v>724</v>
       </c>
       <c r="R148" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="S148" t="s">
         <v>32</v>
@@ -10043,13 +10058,13 @@
         <v>98</v>
       </c>
       <c r="J158" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="L158" s="8" t="s">
         <v>767</v>
       </c>
       <c r="R158" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="S158" t="s">
         <v>32</v>
@@ -10083,6 +10098,9 @@
       <c r="F159" t="s">
         <v>769</v>
       </c>
+      <c r="G159" s="11" t="s">
+        <v>914</v>
+      </c>
       <c r="J159" t="s">
         <v>770</v>
       </c>
@@ -10093,13 +10111,13 @@
         <v>772</v>
       </c>
       <c r="R159" t="s">
-        <v>56</v>
+        <v>911</v>
       </c>
       <c r="S159" t="s">
-        <v>69</v>
+        <v>912</v>
       </c>
       <c r="T159" s="15" t="s">
-        <v>773</v>
+        <v>913</v>
       </c>
       <c r="U159" s="15">
         <v>105</v>
@@ -10128,13 +10146,13 @@
         <v>98</v>
       </c>
       <c r="J160" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="K160" t="s">
+        <v>773</v>
+      </c>
+      <c r="L160" s="8" t="s">
         <v>774</v>
-      </c>
-      <c r="L160" s="8" t="s">
-        <v>775</v>
       </c>
       <c r="R160" t="s">
         <v>147</v>
@@ -10172,13 +10190,13 @@
         <v>475</v>
       </c>
       <c r="J161" t="s">
+        <v>775</v>
+      </c>
+      <c r="K161" t="s">
         <v>776</v>
       </c>
-      <c r="K161" t="s">
+      <c r="L161" s="11" t="s">
         <v>777</v>
-      </c>
-      <c r="L161" s="11" t="s">
-        <v>778</v>
       </c>
       <c r="R161" t="s">
         <v>56</v>
@@ -10198,25 +10216,25 @@
     </row>
     <row r="162" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>778</v>
+      </c>
+      <c r="B162" t="s">
         <v>779</v>
-      </c>
-      <c r="B162" t="s">
-        <v>780</v>
       </c>
       <c r="D162" t="s">
         <v>362</v>
       </c>
       <c r="E162" t="s">
+        <v>780</v>
+      </c>
+      <c r="F162" t="s">
         <v>781</v>
       </c>
-      <c r="F162" t="s">
+      <c r="J162" t="s">
         <v>782</v>
       </c>
-      <c r="J162" t="s">
+      <c r="L162" s="3" t="s">
         <v>783</v>
-      </c>
-      <c r="L162" s="3" t="s">
-        <v>784</v>
       </c>
       <c r="R162" t="s">
         <v>31</v>
@@ -10239,28 +10257,28 @@
     </row>
     <row r="163" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>778</v>
+      </c>
+      <c r="B163" t="s">
         <v>779</v>
-      </c>
-      <c r="B163" t="s">
-        <v>780</v>
       </c>
       <c r="D163">
         <v>1763</v>
       </c>
       <c r="E163" t="s">
+        <v>780</v>
+      </c>
+      <c r="F163" t="s">
         <v>781</v>
       </c>
-      <c r="F163" t="s">
-        <v>782</v>
-      </c>
       <c r="J163" t="s">
+        <v>784</v>
+      </c>
+      <c r="K163" t="s">
         <v>785</v>
       </c>
-      <c r="K163" t="s">
+      <c r="L163" s="3" t="s">
         <v>786</v>
-      </c>
-      <c r="L163" s="3" t="s">
-        <v>787</v>
       </c>
       <c r="R163" t="s">
         <v>31</v>
@@ -10283,28 +10301,28 @@
     </row>
     <row r="164" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>778</v>
+      </c>
+      <c r="B164" t="s">
         <v>779</v>
-      </c>
-      <c r="B164" t="s">
-        <v>780</v>
       </c>
       <c r="D164" t="s">
         <v>498</v>
       </c>
       <c r="E164" t="s">
+        <v>780</v>
+      </c>
+      <c r="F164" t="s">
         <v>781</v>
       </c>
-      <c r="F164" t="s">
-        <v>782</v>
-      </c>
       <c r="J164" t="s">
+        <v>787</v>
+      </c>
+      <c r="K164" t="s">
         <v>788</v>
       </c>
-      <c r="K164" t="s">
+      <c r="L164" s="3" t="s">
         <v>789</v>
-      </c>
-      <c r="L164" s="3" t="s">
-        <v>790</v>
       </c>
       <c r="R164" t="s">
         <v>31</v>
@@ -10327,28 +10345,28 @@
     </row>
     <row r="165" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>778</v>
+      </c>
+      <c r="B165" t="s">
         <v>779</v>
-      </c>
-      <c r="B165" t="s">
-        <v>780</v>
       </c>
       <c r="D165" t="s">
         <v>439</v>
       </c>
       <c r="E165" t="s">
+        <v>780</v>
+      </c>
+      <c r="F165" t="s">
         <v>781</v>
       </c>
-      <c r="F165" t="s">
-        <v>782</v>
-      </c>
       <c r="J165" t="s">
+        <v>790</v>
+      </c>
+      <c r="K165" t="s">
         <v>791</v>
       </c>
-      <c r="K165" t="s">
+      <c r="L165" s="3" t="s">
         <v>792</v>
-      </c>
-      <c r="L165" s="3" t="s">
-        <v>793</v>
       </c>
       <c r="R165" t="s">
         <v>31</v>
@@ -10371,10 +10389,10 @@
     </row>
     <row r="166" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>793</v>
+      </c>
+      <c r="B166" t="s">
         <v>794</v>
-      </c>
-      <c r="B166" t="s">
-        <v>795</v>
       </c>
       <c r="D166" t="s">
         <v>335</v>
@@ -10386,13 +10404,13 @@
         <v>285</v>
       </c>
       <c r="J166" t="s">
+        <v>795</v>
+      </c>
+      <c r="K166" t="s">
         <v>796</v>
       </c>
-      <c r="K166" t="s">
+      <c r="L166" s="3" t="s">
         <v>797</v>
-      </c>
-      <c r="L166" s="3" t="s">
-        <v>798</v>
       </c>
       <c r="R166" t="s">
         <v>56</v>
@@ -10407,7 +10425,7 @@
         <v>194</v>
       </c>
       <c r="V166" s="15" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="W166" s="15">
         <v>3</v>
@@ -10415,10 +10433,10 @@
     </row>
     <row r="167" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>793</v>
+      </c>
+      <c r="B167" t="s">
         <v>794</v>
-      </c>
-      <c r="B167" t="s">
-        <v>795</v>
       </c>
       <c r="D167" t="s">
         <v>209</v>
@@ -10427,16 +10445,16 @@
         <v>195</v>
       </c>
       <c r="F167" t="s">
+        <v>799</v>
+      </c>
+      <c r="J167" t="s">
         <v>800</v>
       </c>
-      <c r="J167" t="s">
+      <c r="K167" t="s">
         <v>801</v>
       </c>
-      <c r="K167" t="s">
+      <c r="L167" s="3" t="s">
         <v>802</v>
-      </c>
-      <c r="L167" s="3" t="s">
-        <v>803</v>
       </c>
       <c r="R167" t="s">
         <v>56</v>
@@ -10445,7 +10463,7 @@
         <v>32</v>
       </c>
       <c r="T167" s="15" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="U167" s="15" t="s">
         <v>462</v>
@@ -10459,25 +10477,25 @@
     </row>
     <row r="168" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>793</v>
+      </c>
+      <c r="B168" t="s">
         <v>794</v>
       </c>
-      <c r="B168" t="s">
-        <v>795</v>
-      </c>
       <c r="D168" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E168" t="s">
         <v>195</v>
       </c>
       <c r="F168" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J168" t="s">
+        <v>805</v>
+      </c>
+      <c r="L168" s="3" t="s">
         <v>806</v>
-      </c>
-      <c r="L168" s="3" t="s">
-        <v>807</v>
       </c>
       <c r="R168" t="s">
         <v>56</v>
@@ -10500,10 +10518,10 @@
     </row>
     <row r="169" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
+        <v>793</v>
+      </c>
+      <c r="B169" t="s">
         <v>794</v>
-      </c>
-      <c r="B169" t="s">
-        <v>795</v>
       </c>
       <c r="D169" t="s">
         <v>217</v>
@@ -10512,19 +10530,19 @@
         <v>195</v>
       </c>
       <c r="F169" t="s">
+        <v>807</v>
+      </c>
+      <c r="J169" t="s">
+        <v>891</v>
+      </c>
+      <c r="K169" t="s">
         <v>808</v>
       </c>
-      <c r="J169" t="s">
-        <v>892</v>
-      </c>
-      <c r="K169" t="s">
+      <c r="L169" s="3" t="s">
         <v>809</v>
       </c>
-      <c r="L169" s="3" t="s">
-        <v>810</v>
-      </c>
       <c r="R169" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="S169" t="s">
         <v>32</v>
@@ -10544,28 +10562,28 @@
     </row>
     <row r="170" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>810</v>
+      </c>
+      <c r="B170" t="s">
         <v>811</v>
       </c>
-      <c r="B170" t="s">
+      <c r="D170" t="s">
         <v>812</v>
-      </c>
-      <c r="D170" t="s">
-        <v>813</v>
       </c>
       <c r="E170" t="s">
         <v>166</v>
       </c>
       <c r="F170" t="s">
+        <v>813</v>
+      </c>
+      <c r="J170" t="s">
         <v>814</v>
       </c>
-      <c r="J170" t="s">
+      <c r="K170" t="s">
         <v>815</v>
       </c>
-      <c r="K170" t="s">
+      <c r="L170" s="3" t="s">
         <v>816</v>
-      </c>
-      <c r="L170" s="3" t="s">
-        <v>817</v>
       </c>
       <c r="R170" t="s">
         <v>31</v>
@@ -10574,7 +10592,7 @@
         <v>32</v>
       </c>
       <c r="T170" s="15" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="U170" s="15">
         <v>102</v>
@@ -10588,10 +10606,10 @@
     </row>
     <row r="171" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
+        <v>810</v>
+      </c>
+      <c r="B171" t="s">
         <v>811</v>
-      </c>
-      <c r="B171" t="s">
-        <v>812</v>
       </c>
       <c r="D171" t="s">
         <v>456</v>
@@ -10600,22 +10618,22 @@
         <v>166</v>
       </c>
       <c r="F171" t="s">
+        <v>818</v>
+      </c>
+      <c r="J171" t="s">
         <v>819</v>
       </c>
-      <c r="J171" t="s">
+      <c r="K171" t="s">
         <v>820</v>
       </c>
-      <c r="K171" t="s">
+      <c r="L171" s="3" t="s">
         <v>821</v>
-      </c>
-      <c r="L171" s="3" t="s">
-        <v>822</v>
       </c>
       <c r="R171" t="s">
         <v>31</v>
       </c>
       <c r="S171" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="T171" s="15">
         <v>550</v>
@@ -10632,10 +10650,10 @@
     </row>
     <row r="172" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>810</v>
+      </c>
+      <c r="B172" t="s">
         <v>811</v>
-      </c>
-      <c r="B172" t="s">
-        <v>812</v>
       </c>
       <c r="D172" t="s">
         <v>481</v>
@@ -10644,19 +10662,19 @@
         <v>166</v>
       </c>
       <c r="F172" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="J172" t="s">
+        <v>892</v>
+      </c>
+      <c r="K172" t="s">
+        <v>823</v>
+      </c>
+      <c r="L172" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="R172" t="s">
         <v>893</v>
-      </c>
-      <c r="K172" t="s">
-        <v>824</v>
-      </c>
-      <c r="L172" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="R172" t="s">
-        <v>894</v>
       </c>
       <c r="S172" t="s">
         <v>32</v>
@@ -10676,34 +10694,34 @@
     </row>
     <row r="173" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>810</v>
+      </c>
+      <c r="B173" t="s">
         <v>811</v>
       </c>
-      <c r="B173" t="s">
-        <v>812</v>
-      </c>
       <c r="D173" t="s">
+        <v>825</v>
+      </c>
+      <c r="E173" t="s">
         <v>826</v>
       </c>
-      <c r="E173" t="s">
+      <c r="F173" t="s">
         <v>827</v>
       </c>
-      <c r="F173" t="s">
+      <c r="J173" t="s">
         <v>828</v>
       </c>
-      <c r="J173" t="s">
+      <c r="K173" t="s">
         <v>829</v>
       </c>
-      <c r="K173" t="s">
+      <c r="L173" s="3" t="s">
         <v>830</v>
       </c>
-      <c r="L173" s="3" t="s">
-        <v>831</v>
-      </c>
       <c r="R173" t="s">
         <v>56</v>
       </c>
       <c r="S173" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="T173" s="15" t="s">
         <v>559</v>
@@ -10720,40 +10738,40 @@
     </row>
     <row r="174" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>831</v>
+      </c>
+      <c r="B174" t="s">
         <v>832</v>
       </c>
-      <c r="B174" t="s">
+      <c r="D174" t="s">
         <v>833</v>
       </c>
-      <c r="D174" t="s">
+      <c r="E174" t="s">
         <v>834</v>
       </c>
-      <c r="E174" t="s">
+      <c r="F174" t="s">
         <v>835</v>
       </c>
-      <c r="F174" t="s">
+      <c r="J174" t="s">
         <v>836</v>
       </c>
-      <c r="J174" t="s">
+      <c r="K174" t="s">
         <v>837</v>
       </c>
-      <c r="K174" t="s">
+      <c r="L174" s="3" t="s">
         <v>838</v>
       </c>
-      <c r="L174" s="3" t="s">
+      <c r="R174" t="s">
+        <v>56</v>
+      </c>
+      <c r="S174" t="s">
         <v>839</v>
       </c>
-      <c r="R174" t="s">
-        <v>56</v>
-      </c>
-      <c r="S174" t="s">
+      <c r="T174" s="15" t="s">
         <v>840</v>
       </c>
-      <c r="T174" s="15" t="s">
+      <c r="U174" s="15" t="s">
         <v>841</v>
-      </c>
-      <c r="U174" s="15" t="s">
-        <v>842</v>
       </c>
       <c r="V174" s="15" t="s">
         <v>333</v>
@@ -10764,34 +10782,34 @@
     </row>
     <row r="175" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>831</v>
+      </c>
+      <c r="B175" t="s">
         <v>832</v>
       </c>
-      <c r="B175" t="s">
-        <v>833</v>
-      </c>
       <c r="D175" t="s">
+        <v>842</v>
+      </c>
+      <c r="E175" t="s">
+        <v>834</v>
+      </c>
+      <c r="F175" t="s">
         <v>843</v>
       </c>
-      <c r="E175" t="s">
-        <v>835</v>
-      </c>
-      <c r="F175" t="s">
+      <c r="J175" t="s">
         <v>844</v>
       </c>
-      <c r="J175" t="s">
+      <c r="K175" t="s">
         <v>845</v>
       </c>
-      <c r="K175" t="s">
+      <c r="L175" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="L175" s="3" t="s">
-        <v>847</v>
-      </c>
       <c r="R175" t="s">
         <v>56</v>
       </c>
       <c r="S175" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="T175" s="15" t="s">
         <v>194</v>
@@ -10808,34 +10826,34 @@
     </row>
     <row r="176" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>831</v>
+      </c>
+      <c r="B176" t="s">
         <v>832</v>
       </c>
-      <c r="B176" t="s">
-        <v>833</v>
-      </c>
       <c r="D176" t="s">
+        <v>847</v>
+      </c>
+      <c r="E176" t="s">
+        <v>834</v>
+      </c>
+      <c r="F176" t="s">
         <v>848</v>
       </c>
-      <c r="E176" t="s">
-        <v>835</v>
-      </c>
-      <c r="F176" t="s">
+      <c r="J176" t="s">
         <v>849</v>
       </c>
-      <c r="J176" t="s">
+      <c r="K176" t="s">
         <v>850</v>
       </c>
-      <c r="K176" t="s">
+      <c r="L176" s="3" t="s">
         <v>851</v>
       </c>
-      <c r="L176" s="3" t="s">
-        <v>852</v>
-      </c>
       <c r="R176" t="s">
         <v>56</v>
       </c>
       <c r="S176" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="T176" s="15" t="s">
         <v>194</v>
@@ -10852,37 +10870,37 @@
     </row>
     <row r="177" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>831</v>
+      </c>
+      <c r="B177" t="s">
         <v>832</v>
       </c>
-      <c r="B177" t="s">
-        <v>833</v>
-      </c>
       <c r="D177" t="s">
+        <v>852</v>
+      </c>
+      <c r="E177" t="s">
         <v>853</v>
       </c>
-      <c r="E177" t="s">
+      <c r="F177" t="s">
         <v>854</v>
       </c>
-      <c r="F177" t="s">
+      <c r="J177" t="s">
         <v>855</v>
       </c>
-      <c r="J177" t="s">
+      <c r="K177" t="s">
         <v>856</v>
       </c>
-      <c r="K177" t="s">
+      <c r="L177" s="3" t="s">
         <v>857</v>
       </c>
-      <c r="L177" s="3" t="s">
+      <c r="R177" t="s">
+        <v>56</v>
+      </c>
+      <c r="S177" t="s">
+        <v>839</v>
+      </c>
+      <c r="T177" s="15" t="s">
         <v>858</v>
-      </c>
-      <c r="R177" t="s">
-        <v>56</v>
-      </c>
-      <c r="S177" t="s">
-        <v>840</v>
-      </c>
-      <c r="T177" s="15" t="s">
-        <v>859</v>
       </c>
       <c r="U177" s="15">
         <v>80</v>
@@ -10896,34 +10914,34 @@
     </row>
     <row r="178" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>831</v>
+      </c>
+      <c r="B178" t="s">
         <v>832</v>
       </c>
-      <c r="B178" t="s">
-        <v>833</v>
-      </c>
       <c r="D178" t="s">
+        <v>859</v>
+      </c>
+      <c r="E178" t="s">
+        <v>834</v>
+      </c>
+      <c r="F178" t="s">
         <v>860</v>
       </c>
-      <c r="E178" t="s">
-        <v>835</v>
-      </c>
-      <c r="F178" t="s">
+      <c r="J178" t="s">
         <v>861</v>
       </c>
-      <c r="J178" t="s">
+      <c r="K178" t="s">
         <v>862</v>
       </c>
-      <c r="K178" t="s">
+      <c r="L178" s="3" t="s">
         <v>863</v>
       </c>
-      <c r="L178" s="3" t="s">
-        <v>864</v>
-      </c>
       <c r="R178" t="s">
         <v>56</v>
       </c>
       <c r="S178" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="T178" s="15" t="s">
         <v>110</v>
@@ -10940,34 +10958,34 @@
     </row>
     <row r="179" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>831</v>
+      </c>
+      <c r="B179" t="s">
         <v>832</v>
       </c>
-      <c r="B179" t="s">
-        <v>833</v>
-      </c>
       <c r="D179" t="s">
+        <v>859</v>
+      </c>
+      <c r="E179" t="s">
+        <v>834</v>
+      </c>
+      <c r="F179" t="s">
         <v>860</v>
       </c>
-      <c r="E179" t="s">
-        <v>835</v>
-      </c>
-      <c r="F179" t="s">
-        <v>861</v>
-      </c>
       <c r="J179" t="s">
+        <v>864</v>
+      </c>
+      <c r="K179" t="s">
         <v>865</v>
       </c>
-      <c r="K179" t="s">
+      <c r="L179" s="3" t="s">
         <v>866</v>
       </c>
-      <c r="L179" s="3" t="s">
-        <v>867</v>
-      </c>
       <c r="R179" t="s">
         <v>56</v>
       </c>
       <c r="S179" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="T179" s="15" t="s">
         <v>194</v>
@@ -10984,13 +11002,13 @@
     </row>
     <row r="180" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>867</v>
+      </c>
+      <c r="B180" t="s">
         <v>868</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
         <v>869</v>
-      </c>
-      <c r="C180" t="s">
-        <v>870</v>
       </c>
       <c r="D180" t="s">
         <v>165</v>
@@ -11002,13 +11020,13 @@
         <v>188</v>
       </c>
       <c r="J180" t="s">
+        <v>870</v>
+      </c>
+      <c r="K180" t="s">
         <v>871</v>
       </c>
-      <c r="K180" t="s">
+      <c r="L180" s="3" t="s">
         <v>872</v>
-      </c>
-      <c r="L180" s="3" t="s">
-        <v>873</v>
       </c>
       <c r="R180" t="s">
         <v>56</v>
@@ -11020,10 +11038,10 @@
         <v>473</v>
       </c>
       <c r="U180" s="15" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="V180" s="15" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="W180" s="15">
         <v>3</v>
@@ -11031,13 +11049,13 @@
     </row>
     <row r="181" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>867</v>
+      </c>
+      <c r="B181" t="s">
         <v>868</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
         <v>869</v>
-      </c>
-      <c r="C181" t="s">
-        <v>870</v>
       </c>
       <c r="D181" t="s">
         <v>439</v>
@@ -11049,13 +11067,13 @@
         <v>704</v>
       </c>
       <c r="J181" t="s">
+        <v>874</v>
+      </c>
+      <c r="L181" s="3" t="s">
         <v>875</v>
       </c>
-      <c r="L181" s="3" t="s">
-        <v>876</v>
-      </c>
       <c r="R181" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="S181" t="s">
         <v>201</v>
@@ -11075,13 +11093,13 @@
     </row>
     <row r="182" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>867</v>
+      </c>
+      <c r="B182" t="s">
         <v>868</v>
       </c>
-      <c r="B182" t="s">
+      <c r="C182" t="s">
         <v>869</v>
-      </c>
-      <c r="C182" t="s">
-        <v>870</v>
       </c>
       <c r="D182" t="s">
         <v>36</v>
@@ -11093,11 +11111,11 @@
         <v>28</v>
       </c>
       <c r="J182" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="K182" s="3"/>
       <c r="L182" s="11" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="R182" t="s">
         <v>56</v>
@@ -11120,13 +11138,13 @@
     </row>
     <row r="183" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>867</v>
+      </c>
+      <c r="B183" t="s">
         <v>868</v>
       </c>
-      <c r="B183" t="s">
+      <c r="C183" t="s">
         <v>869</v>
-      </c>
-      <c r="C183" t="s">
-        <v>870</v>
       </c>
       <c r="D183" t="s">
         <v>36</v>
@@ -11138,10 +11156,10 @@
         <v>28</v>
       </c>
       <c r="J183" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L183" s="3" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="R183" t="s">
         <v>56</v>
@@ -11357,6 +11375,7 @@
     <hyperlink ref="L182" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
     <hyperlink ref="L183" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
     <hyperlink ref="L139" r:id="rId190" xr:uid="{3811C8DC-91E3-43F8-A084-D829848E6D05}"/>
+    <hyperlink ref="G159" r:id="rId191" xr:uid="{B30FE0F5-FC00-4890-AF9F-A0038722E4EC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -10113,8 +10113,10 @@
       <c r="R159" t="s">
         <v>911</v>
       </c>
-      <c r="S159" t="s">
-        <v>912</v>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bronze pour la statue, marbre pour le socle</t>
+        </is>
       </c>
       <c r="T159" s="15" t="s">
         <v>913</v>

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -10110,8 +10110,10 @@
       <c r="L159" s="8" t="s">
         <v>772</v>
       </c>
-      <c r="R159" t="s">
-        <v>911</v>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monument équestre avec ronde-bosse en bronze intégralement conçu par l'artiste, sur un socle en marbre.</t>
+        </is>
       </c>
       <c r="S159" t="inlineStr">
         <is>

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA654CE-3A15-4A7A-A602-F66D3C2E2332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9FF031-25F9-4730-973C-C7E6E48F393E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="921">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2719,9 +2719,6 @@
     <t>Buste de Denis Diderot</t>
   </si>
   <si>
-    <t>Monument avec groupe en ronde-bosse</t>
-  </si>
-  <si>
     <t>Monument liturgique avec groupe en ronde-bosse, haut-relief et bas-relief</t>
   </si>
   <si>
@@ -2737,9 +2734,6 @@
     <t>Monument funéraire avec groupe en ronde-bosse et haut-relief</t>
   </si>
   <si>
-    <t>Monument avec groupe en ronde-bosse et bas-relief</t>
-  </si>
-  <si>
     <t>Monument  mural avec groupe en ronde-bosse et haut-relief</t>
   </si>
   <si>
@@ -2755,16 +2749,40 @@
     <t>Artiste associé</t>
   </si>
   <si>
-    <t>Monument équestre avec ronde-bosse intégralement conçu par l'artiste</t>
-  </si>
-  <si>
-    <t>Bronze (statue), marbre (socle)</t>
-  </si>
-  <si>
     <t>285 pour la statue, 430 pour le socle</t>
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/af/In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg/960px-In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Monument équestre avec ronde-bosse en bronze intégralement conçu par l'artiste, sur un socle en marbre.</t>
+  </si>
+  <si>
+    <t>Bronze pour la statue, marbre pour le socle</t>
+  </si>
+  <si>
+    <t>Fontaine monumentale avec groupe en ronde-bosse. Le projet a été intégralement conçu par l'artiste. Les statues d'origine en plomb ont été remplacées en 1873 par des copies en bronze moins fragiles,</t>
+  </si>
+  <si>
+    <t>Bronze et pierre</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b4/Wien_-_Donnerbrunnen%2C_Quellnymphe.JPG/1280px-Wien_-_Donnerbrunnen%2C_Quellnymphe.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Austria_august2010_0228.jpg/1280px-Austria_august2010_0228.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fontaine des Quatre-Saisons </t>
+  </si>
+  <si>
+    <t>Monument avec groupe en ronde-bosse et bas-relief. Le projet a été intégralement conçu par l'artiste.</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Fontaine_des_Quatre-Saisons_Paris_7.jpg/1280px-Fontaine_des_Quatre-Saisons_Paris_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/07/Fontaine_des_Quatre-Saisons_Paris_7_partie_centrale.jpg/1280px-Fontaine_des_Quatre-Saisons_Paris_7_partie_centrale.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -3285,7 +3303,7 @@
         <v>22</v>
       </c>
       <c r="X1" s="15" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3660,7 +3678,7 @@
         <v>72</v>
       </c>
       <c r="R10" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="S10" t="s">
         <v>32</v>
@@ -4041,7 +4059,7 @@
         <v>119</v>
       </c>
       <c r="R19" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="S19" t="s">
         <v>32</v>
@@ -4129,7 +4147,7 @@
         <v>127</v>
       </c>
       <c r="R21" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="S21" t="s">
         <v>32</v>
@@ -4254,17 +4272,23 @@
       <c r="F24" t="s">
         <v>143</v>
       </c>
+      <c r="G24" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>919</v>
+      </c>
       <c r="J24" t="s">
-        <v>144</v>
+        <v>917</v>
       </c>
       <c r="K24" t="s">
         <v>145</v>
       </c>
-      <c r="L24" s="6" t="s">
-        <v>146</v>
+      <c r="L24" s="11" t="s">
+        <v>920</v>
       </c>
       <c r="R24" t="s">
-        <v>905</v>
+        <v>918</v>
       </c>
       <c r="S24" t="s">
         <v>148</v>
@@ -4681,7 +4705,7 @@
         <v>191</v>
       </c>
       <c r="R33" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="S33" t="s">
         <v>192</v>
@@ -4772,7 +4796,7 @@
         <v>205</v>
       </c>
       <c r="R35" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="S35" t="s">
         <v>32</v>
@@ -5062,7 +5086,7 @@
         <v>238</v>
       </c>
       <c r="R42" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="S42" t="s">
         <v>32</v>
@@ -5194,7 +5218,7 @@
         <v>252</v>
       </c>
       <c r="R45" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="S45" t="s">
         <v>32</v>
@@ -6314,7 +6338,7 @@
         <v>380</v>
       </c>
       <c r="R71" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="S71" t="s">
         <v>381</v>
@@ -6434,17 +6458,21 @@
       <c r="F74" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="G74" s="4"/>
+      <c r="G74" s="11" t="s">
+        <v>916</v>
+      </c>
       <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
+      <c r="I74" s="9" t="s">
+        <v>395</v>
+      </c>
       <c r="J74" s="4" t="s">
         <v>393</v>
       </c>
       <c r="K74" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="L74" s="9" t="s">
-        <v>395</v>
+      <c r="L74" s="11" t="s">
+        <v>915</v>
       </c>
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
@@ -6452,10 +6480,10 @@
       <c r="P74" s="4"/>
       <c r="Q74" s="4"/>
       <c r="R74" s="4" t="s">
-        <v>899</v>
+        <v>913</v>
       </c>
       <c r="S74" s="4" t="s">
-        <v>69</v>
+        <v>914</v>
       </c>
       <c r="T74" s="2">
         <v>500</v>
@@ -6544,7 +6572,7 @@
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="I76" s="4"/>
       <c r="J76" s="4" t="s">
@@ -6562,7 +6590,7 @@
       <c r="P76" s="4"/>
       <c r="Q76" s="4"/>
       <c r="R76" s="4" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="S76" s="4" t="s">
         <v>409</v>
@@ -10099,7 +10127,7 @@
         <v>769</v>
       </c>
       <c r="G159" s="11" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="J159" t="s">
         <v>770</v>
@@ -10110,18 +10138,14 @@
       <c r="L159" s="8" t="s">
         <v>772</v>
       </c>
-      <c r="R159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Monument équestre avec ronde-bosse en bronze intégralement conçu par l'artiste, sur un socle en marbre.</t>
-        </is>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bronze pour la statue, marbre pour le socle</t>
-        </is>
+      <c r="R159" t="s">
+        <v>911</v>
+      </c>
+      <c r="S159" t="s">
+        <v>912</v>
       </c>
       <c r="T159" s="15" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="U159" s="15">
         <v>105</v>
@@ -11160,7 +11184,7 @@
         <v>28</v>
       </c>
       <c r="J183" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="L183" s="3" t="s">
         <v>878</v>
@@ -11211,7 +11235,7 @@
     <hyperlink ref="L21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
     <hyperlink ref="L22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
     <hyperlink ref="L23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="L24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="G24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
     <hyperlink ref="L25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
     <hyperlink ref="L26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
     <hyperlink ref="L27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
@@ -11266,120 +11290,124 @@
     <hyperlink ref="L71" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
     <hyperlink ref="L72" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
     <hyperlink ref="L73" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="L74" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="L75" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="L76" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="L77" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="L78" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="L79" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="G80" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="L80" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="L81" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="L82" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="L83" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="L84" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="L85" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="L86" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="L87" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="L88" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="L89" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="L90" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="L91" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="L92" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="L93" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="I94" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="L94" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="I95" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="L95" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="L96" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="L97" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="L98" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="L99" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="L100" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="L101" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="L102" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="L103" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="L104" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="L105" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="L106" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="L107" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="L108" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="L109" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="L110" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="L111" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="L112" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="L113" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="L114" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="L115" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="L116" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="L117" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="L118" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="L119" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="L120" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="L121" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="L122" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="L123" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="L124" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="L125" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="L126" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="L127" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="L128" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="L129" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="L130" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="L131" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="L132" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="L133" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="L134" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="L135" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="L136" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="L137" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="L138" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="L140" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="L141" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="L142" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="L143" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="L144" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="L145" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="L146" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="L147" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="L148" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="L149" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="L150" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="L151" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="L152" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="L153" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="L154" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="L155" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="L156" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="L157" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="L158" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="L159" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="L160" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="L161" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="L162" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="L163" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="L164" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="L165" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="L166" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="L167" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="L168" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="L169" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="L170" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="L171" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="L172" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="L173" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="L174" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="L175" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="L176" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="L177" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="L178" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="L179" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="L180" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="L181" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="L182" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="L183" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="L139" r:id="rId190" xr:uid="{3811C8DC-91E3-43F8-A084-D829848E6D05}"/>
-    <hyperlink ref="G159" r:id="rId191" xr:uid="{B30FE0F5-FC00-4890-AF9F-A0038722E4EC}"/>
+    <hyperlink ref="L75" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="L76" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="L77" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="L78" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="L79" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="G80" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="L80" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="L81" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="L82" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="L83" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="L84" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="L85" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="L86" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="L87" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="L88" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="L89" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="L90" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="L91" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="L92" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="L93" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="I94" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="L94" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="I95" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="L95" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="L96" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="L97" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="L98" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="L99" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="L100" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="L101" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="L102" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="L103" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="L104" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="L105" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="L106" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="L107" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="L108" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="L109" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="L110" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="L111" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="L112" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="L113" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="L114" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="L115" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="L116" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="L117" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="L118" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="L119" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="L120" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="L121" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="L122" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="L123" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="L124" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="L125" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="L126" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="L127" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="L128" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="L129" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="L130" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="L131" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="L132" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="L133" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="L134" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="L135" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="L136" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="L137" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="L138" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="L140" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="L141" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="L142" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="L143" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="L144" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="L145" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="L146" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="L147" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="L148" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="L149" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="L150" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="L151" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="L152" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="L153" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="L154" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="L155" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="L156" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="L157" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="L158" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="L159" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="L160" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="L161" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="L162" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="L163" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="L164" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="L165" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="L166" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="L167" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="L168" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="L169" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="L170" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="L171" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="L172" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="L173" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="L174" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="L175" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="L176" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="L177" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="L178" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="L179" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="L180" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="L181" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="L182" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="L183" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="L139" r:id="rId189" xr:uid="{3811C8DC-91E3-43F8-A084-D829848E6D05}"/>
+    <hyperlink ref="G159" r:id="rId190" xr:uid="{B30FE0F5-FC00-4890-AF9F-A0038722E4EC}"/>
+    <hyperlink ref="L74" r:id="rId191" xr:uid="{66F3859D-BA3C-45BE-B2B2-9E3221A72520}"/>
+    <hyperlink ref="I74" r:id="rId192" xr:uid="{5FEAF7D5-FBAE-475B-8DBC-E8DD8B0CA295}"/>
+    <hyperlink ref="G74" r:id="rId193" xr:uid="{FECE9BFA-B8E8-4206-BD59-6D54AEB83D86}"/>
+    <hyperlink ref="I24" r:id="rId194" xr:uid="{6D83C2C3-0DDA-46DE-B25E-66293EAAED02}"/>
+    <hyperlink ref="L24" r:id="rId195" xr:uid="{B91B73D0-731E-4554-AFB9-908A43D1432E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9FF031-25F9-4730-973C-C7E6E48F393E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2445B2-40A3-4732-9B76-D5B258A79C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="922">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2783,6 +2783,9 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/07/Fontaine_des_Quatre-Saisons_Paris_7_partie_centrale.jpg/1280px-Fontaine_des_Quatre-Saisons_Paris_7_partie_centrale.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Ronde-bosse appartenant à la Fontaine de Trevi.</t>
   </si>
 </sst>
 </file>
@@ -4661,7 +4664,7 @@
         <v>184</v>
       </c>
       <c r="R32" t="s">
-        <v>56</v>
+        <v>921</v>
       </c>
       <c r="S32" t="s">
         <v>32</v>

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2445B2-40A3-4732-9B76-D5B258A79C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC2C2BF-045B-42A1-97E7-4675394EC250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="923">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2170,9 +2170,6 @@
     <t>Marbre et filet de fer</t>
   </si>
   <si>
-    <t>Attique</t>
-  </si>
-  <si>
     <t>L'Automne</t>
   </si>
   <si>
@@ -2786,6 +2783,12 @@
   </si>
   <si>
     <t>Ronde-bosse appartenant à la Fontaine de Trevi.</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ab/Parc_de_Versailles%2C_bassin_de_Neptune%2C_Le_Triomphe_de_Neptune_et_d%27Amphitrite%2C_Lambert-Sigisbert_Adam_01.jpg/1280px-Parc_de_Versailles%2C_bassin_de_Neptune%2C_Le_Triomphe_de_Neptune_et_d%27Amphitrite%2C_Lambert-Sigisbert_Adam_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Versalles_Fuente_de_Neptuno_02.JPG/1280px-Versalles_Fuente_de_Neptuno_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -3306,7 +3309,7 @@
         <v>22</v>
       </c>
       <c r="X1" s="15" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3372,8 +3375,14 @@
       <c r="F3" t="s">
         <v>38</v>
       </c>
+      <c r="G3" s="11" t="s">
+        <v>921</v>
+      </c>
       <c r="H3" t="s">
         <v>39</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>922</v>
       </c>
       <c r="J3" t="s">
         <v>40</v>
@@ -3681,7 +3690,7 @@
         <v>72</v>
       </c>
       <c r="R10" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="S10" t="s">
         <v>32</v>
@@ -3930,7 +3939,7 @@
         <v>101</v>
       </c>
       <c r="R16" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="S16" t="s">
         <v>32</v>
@@ -4009,7 +4018,7 @@
         <v>112</v>
       </c>
       <c r="J18" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="K18" t="s">
         <v>113</v>
@@ -4053,7 +4062,7 @@
         <v>117</v>
       </c>
       <c r="J19" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K19" t="s">
         <v>118</v>
@@ -4062,7 +4071,7 @@
         <v>119</v>
       </c>
       <c r="R19" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="S19" t="s">
         <v>32</v>
@@ -4141,7 +4150,7 @@
         <v>98</v>
       </c>
       <c r="J21" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="K21" t="s">
         <v>126</v>
@@ -4150,7 +4159,7 @@
         <v>127</v>
       </c>
       <c r="R21" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="S21" t="s">
         <v>32</v>
@@ -4279,19 +4288,19 @@
         <v>146</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="J24" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="K24" t="s">
         <v>145</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="R24" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="S24" t="s">
         <v>148</v>
@@ -4664,7 +4673,7 @@
         <v>184</v>
       </c>
       <c r="R32" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="S32" t="s">
         <v>32</v>
@@ -4708,7 +4717,7 @@
         <v>191</v>
       </c>
       <c r="R33" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="S33" t="s">
         <v>192</v>
@@ -4790,7 +4799,7 @@
         <v>203</v>
       </c>
       <c r="J35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="K35" t="s">
         <v>204</v>
@@ -4799,7 +4808,7 @@
         <v>205</v>
       </c>
       <c r="R35" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="S35" t="s">
         <v>32</v>
@@ -5089,7 +5098,7 @@
         <v>238</v>
       </c>
       <c r="R42" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="S42" t="s">
         <v>32</v>
@@ -5221,7 +5230,7 @@
         <v>252</v>
       </c>
       <c r="R45" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="S45" t="s">
         <v>32</v>
@@ -6080,7 +6089,7 @@
         <v>347</v>
       </c>
       <c r="R65" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="S65" t="s">
         <v>201</v>
@@ -6199,6 +6208,12 @@
       <c r="F68" t="s">
         <v>178</v>
       </c>
+      <c r="G68" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>181</v>
+      </c>
       <c r="J68" t="s">
         <v>359</v>
       </c>
@@ -6341,7 +6356,7 @@
         <v>380</v>
       </c>
       <c r="R71" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="S71" t="s">
         <v>381</v>
@@ -6462,7 +6477,7 @@
         <v>392</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="9" t="s">
@@ -6475,7 +6490,7 @@
         <v>394</v>
       </c>
       <c r="L74" s="11" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
@@ -6483,10 +6498,10 @@
       <c r="P74" s="4"/>
       <c r="Q74" s="4"/>
       <c r="R74" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="S74" s="4" t="s">
         <v>913</v>
-      </c>
-      <c r="S74" s="4" t="s">
-        <v>914</v>
       </c>
       <c r="T74" s="2">
         <v>500</v>
@@ -6524,7 +6539,7 @@
       </c>
       <c r="I75" s="4"/>
       <c r="J75" s="4" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>399</v>
@@ -6575,7 +6590,7 @@
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="I76" s="4"/>
       <c r="J76" s="4" t="s">
@@ -6593,7 +6608,7 @@
       <c r="P76" s="4"/>
       <c r="Q76" s="4"/>
       <c r="R76" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="S76" s="4" t="s">
         <v>409</v>
@@ -7098,7 +7113,7 @@
         <v>464</v>
       </c>
       <c r="J88" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="K88" t="s">
         <v>465</v>
@@ -7107,7 +7122,7 @@
         <v>466</v>
       </c>
       <c r="R88" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="S88" t="s">
         <v>32</v>
@@ -7142,7 +7157,7 @@
         <v>98</v>
       </c>
       <c r="J89" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K89" t="s">
         <v>471</v>
@@ -7151,7 +7166,7 @@
         <v>472</v>
       </c>
       <c r="R89" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="S89" t="s">
         <v>32</v>
@@ -7591,7 +7606,7 @@
         <v>533</v>
       </c>
       <c r="J99" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="L99" s="3" t="s">
         <v>534</v>
@@ -9277,10 +9292,10 @@
         <v>596</v>
       </c>
       <c r="J139" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="L139" s="11" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="R139" t="s">
         <v>56</v>
@@ -9529,7 +9544,7 @@
         <v>708</v>
       </c>
       <c r="R145" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="S145" t="s">
         <v>32</v>
@@ -9607,17 +9622,20 @@
       <c r="F147" t="s">
         <v>178</v>
       </c>
-      <c r="H147" t="s">
+      <c r="G147" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="J147" t="s">
         <v>716</v>
       </c>
-      <c r="J147" t="s">
+      <c r="K147" t="s">
         <v>717</v>
       </c>
-      <c r="K147" t="s">
+      <c r="L147" s="8" t="s">
         <v>718</v>
-      </c>
-      <c r="L147" s="8" t="s">
-        <v>719</v>
       </c>
       <c r="R147" t="s">
         <v>56</v>
@@ -9640,10 +9658,10 @@
     </row>
     <row r="148" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>719</v>
+      </c>
+      <c r="B148" t="s">
         <v>720</v>
-      </c>
-      <c r="B148" t="s">
-        <v>721</v>
       </c>
       <c r="D148" t="s">
         <v>339</v>
@@ -9655,16 +9673,16 @@
         <v>98</v>
       </c>
       <c r="J148" t="s">
+        <v>721</v>
+      </c>
+      <c r="K148" t="s">
         <v>722</v>
       </c>
-      <c r="K148" t="s">
+      <c r="L148" s="3" t="s">
         <v>723</v>
       </c>
-      <c r="L148" s="3" t="s">
-        <v>724</v>
-      </c>
       <c r="R148" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="S148" t="s">
         <v>32</v>
@@ -9684,28 +9702,28 @@
     </row>
     <row r="149" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>719</v>
+      </c>
+      <c r="B149" t="s">
         <v>720</v>
-      </c>
-      <c r="B149" t="s">
-        <v>721</v>
       </c>
       <c r="D149" t="s">
         <v>439</v>
       </c>
       <c r="E149" t="s">
+        <v>724</v>
+      </c>
+      <c r="F149" t="s">
         <v>725</v>
       </c>
-      <c r="F149" t="s">
+      <c r="J149" t="s">
         <v>726</v>
       </c>
-      <c r="J149" t="s">
+      <c r="K149" t="s">
         <v>727</v>
       </c>
-      <c r="K149" t="s">
+      <c r="L149" s="3" t="s">
         <v>728</v>
-      </c>
-      <c r="L149" s="3" t="s">
-        <v>729</v>
       </c>
       <c r="R149" t="s">
         <v>56</v>
@@ -9728,10 +9746,10 @@
     </row>
     <row r="150" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>719</v>
+      </c>
+      <c r="B150" t="s">
         <v>720</v>
-      </c>
-      <c r="B150" t="s">
-        <v>721</v>
       </c>
       <c r="D150" t="s">
         <v>403</v>
@@ -9743,13 +9761,13 @@
         <v>136</v>
       </c>
       <c r="J150" t="s">
+        <v>729</v>
+      </c>
+      <c r="K150" t="s">
         <v>730</v>
       </c>
-      <c r="K150" t="s">
+      <c r="L150" s="3" t="s">
         <v>731</v>
-      </c>
-      <c r="L150" s="3" t="s">
-        <v>732</v>
       </c>
       <c r="R150" t="s">
         <v>56</v>
@@ -9772,13 +9790,13 @@
     </row>
     <row r="151" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>719</v>
+      </c>
+      <c r="B151" t="s">
         <v>720</v>
       </c>
-      <c r="B151" t="s">
-        <v>721</v>
-      </c>
       <c r="D151" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E151" t="s">
         <v>97</v>
@@ -9787,13 +9805,13 @@
         <v>122</v>
       </c>
       <c r="J151" t="s">
+        <v>733</v>
+      </c>
+      <c r="K151" t="s">
         <v>734</v>
       </c>
-      <c r="K151" t="s">
+      <c r="L151" s="3" t="s">
         <v>735</v>
-      </c>
-      <c r="L151" s="3" t="s">
-        <v>736</v>
       </c>
       <c r="R151" t="s">
         <v>56</v>
@@ -9816,28 +9834,28 @@
     </row>
     <row r="152" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>719</v>
+      </c>
+      <c r="B152" t="s">
         <v>720</v>
-      </c>
-      <c r="B152" t="s">
-        <v>721</v>
       </c>
       <c r="D152" t="s">
         <v>50</v>
       </c>
       <c r="E152" t="s">
+        <v>736</v>
+      </c>
+      <c r="F152" t="s">
         <v>737</v>
       </c>
-      <c r="F152" t="s">
+      <c r="J152" t="s">
         <v>738</v>
       </c>
-      <c r="J152" t="s">
+      <c r="K152" t="s">
         <v>739</v>
       </c>
-      <c r="K152" t="s">
+      <c r="L152" s="3" t="s">
         <v>740</v>
-      </c>
-      <c r="L152" s="3" t="s">
-        <v>741</v>
       </c>
       <c r="R152" t="s">
         <v>56</v>
@@ -9860,25 +9878,25 @@
     </row>
     <row r="153" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>719</v>
+      </c>
+      <c r="B153" t="s">
         <v>720</v>
       </c>
-      <c r="B153" t="s">
-        <v>721</v>
-      </c>
       <c r="D153" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E153" t="s">
         <v>97</v>
       </c>
       <c r="F153" t="s">
+        <v>742</v>
+      </c>
+      <c r="J153" t="s">
         <v>743</v>
       </c>
-      <c r="J153" t="s">
+      <c r="L153" s="11" t="s">
         <v>744</v>
-      </c>
-      <c r="L153" s="11" t="s">
-        <v>745</v>
       </c>
       <c r="R153" t="s">
         <v>56</v>
@@ -9901,13 +9919,13 @@
     </row>
     <row r="154" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>745</v>
+      </c>
+      <c r="B154" t="s">
         <v>746</v>
       </c>
-      <c r="B154" t="s">
+      <c r="D154" t="s">
         <v>747</v>
-      </c>
-      <c r="D154" t="s">
-        <v>748</v>
       </c>
       <c r="E154" t="s">
         <v>426</v>
@@ -9916,10 +9934,10 @@
         <v>436</v>
       </c>
       <c r="J154" t="s">
+        <v>748</v>
+      </c>
+      <c r="L154" s="8" t="s">
         <v>749</v>
-      </c>
-      <c r="L154" s="8" t="s">
-        <v>750</v>
       </c>
       <c r="R154" t="s">
         <v>56</v>
@@ -9928,7 +9946,7 @@
         <v>61</v>
       </c>
       <c r="T154" s="15" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="U154" s="15">
         <v>70</v>
@@ -9942,13 +9960,13 @@
     </row>
     <row r="155" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>745</v>
+      </c>
+      <c r="B155" t="s">
         <v>746</v>
       </c>
-      <c r="B155" t="s">
+      <c r="D155" t="s">
         <v>747</v>
-      </c>
-      <c r="D155" t="s">
-        <v>748</v>
       </c>
       <c r="E155" t="s">
         <v>157</v>
@@ -9957,13 +9975,13 @@
         <v>158</v>
       </c>
       <c r="J155" t="s">
+        <v>751</v>
+      </c>
+      <c r="K155" t="s">
         <v>752</v>
       </c>
-      <c r="K155" t="s">
+      <c r="L155" s="8" t="s">
         <v>753</v>
-      </c>
-      <c r="L155" s="8" t="s">
-        <v>754</v>
       </c>
       <c r="R155" t="s">
         <v>56</v>
@@ -9978,7 +9996,7 @@
         <v>194</v>
       </c>
       <c r="V155" s="15" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="W155" s="15">
         <v>3</v>
@@ -9986,13 +10004,13 @@
     </row>
     <row r="156" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>745</v>
+      </c>
+      <c r="B156" t="s">
         <v>746</v>
       </c>
-      <c r="B156" t="s">
-        <v>747</v>
-      </c>
       <c r="D156" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E156" t="s">
         <v>157</v>
@@ -10001,13 +10019,13 @@
         <v>158</v>
       </c>
       <c r="J156" t="s">
+        <v>756</v>
+      </c>
+      <c r="K156" t="s">
         <v>757</v>
       </c>
-      <c r="K156" t="s">
+      <c r="L156" s="11" t="s">
         <v>758</v>
-      </c>
-      <c r="L156" s="11" t="s">
-        <v>759</v>
       </c>
       <c r="R156" t="s">
         <v>56</v>
@@ -10016,13 +10034,13 @@
         <v>32</v>
       </c>
       <c r="T156" s="15" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="U156" s="15" t="s">
         <v>194</v>
       </c>
       <c r="V156" s="15" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="W156" s="15">
         <v>3</v>
@@ -10030,13 +10048,13 @@
     </row>
     <row r="157" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>745</v>
+      </c>
+      <c r="B157" t="s">
         <v>746</v>
       </c>
-      <c r="B157" t="s">
-        <v>747</v>
-      </c>
       <c r="D157" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E157" t="s">
         <v>157</v>
@@ -10045,13 +10063,13 @@
         <v>158</v>
       </c>
       <c r="J157" t="s">
+        <v>761</v>
+      </c>
+      <c r="K157" t="s">
         <v>762</v>
       </c>
-      <c r="K157" t="s">
+      <c r="L157" s="8" t="s">
         <v>763</v>
-      </c>
-      <c r="L157" s="8" t="s">
-        <v>764</v>
       </c>
       <c r="R157" t="s">
         <v>56</v>
@@ -10060,13 +10078,13 @@
         <v>32</v>
       </c>
       <c r="T157" s="15" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="U157" s="15" t="s">
         <v>194</v>
       </c>
       <c r="V157" s="15" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="W157" s="15">
         <v>3</v>
@@ -10074,10 +10092,10 @@
     </row>
     <row r="158" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>764</v>
+      </c>
+      <c r="B158" t="s">
         <v>765</v>
-      </c>
-      <c r="B158" t="s">
-        <v>766</v>
       </c>
       <c r="D158">
         <v>1731</v>
@@ -10089,13 +10107,13 @@
         <v>98</v>
       </c>
       <c r="J158" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="L158" s="8" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="R158" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="S158" t="s">
         <v>32</v>
@@ -10115,40 +10133,40 @@
     </row>
     <row r="159" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>764</v>
+      </c>
+      <c r="B159" t="s">
         <v>765</v>
-      </c>
-      <c r="B159" t="s">
-        <v>766</v>
       </c>
       <c r="D159">
         <v>1733</v>
       </c>
       <c r="E159" t="s">
+        <v>767</v>
+      </c>
+      <c r="F159" t="s">
         <v>768</v>
       </c>
-      <c r="F159" t="s">
+      <c r="G159" s="11" t="s">
+        <v>909</v>
+      </c>
+      <c r="J159" t="s">
         <v>769</v>
       </c>
-      <c r="G159" s="11" t="s">
+      <c r="K159" t="s">
+        <v>770</v>
+      </c>
+      <c r="L159" s="8" t="s">
+        <v>771</v>
+      </c>
+      <c r="R159" t="s">
         <v>910</v>
       </c>
-      <c r="J159" t="s">
-        <v>770</v>
-      </c>
-      <c r="K159" t="s">
-        <v>771</v>
-      </c>
-      <c r="L159" s="8" t="s">
-        <v>772</v>
-      </c>
-      <c r="R159" t="s">
+      <c r="S159" t="s">
         <v>911</v>
       </c>
-      <c r="S159" t="s">
-        <v>912</v>
-      </c>
       <c r="T159" s="15" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="U159" s="15">
         <v>105</v>
@@ -10162,10 +10180,10 @@
     </row>
     <row r="160" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>764</v>
+      </c>
+      <c r="B160" t="s">
         <v>765</v>
-      </c>
-      <c r="B160" t="s">
-        <v>766</v>
       </c>
       <c r="D160">
         <v>1737</v>
@@ -10177,13 +10195,13 @@
         <v>98</v>
       </c>
       <c r="J160" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="K160" t="s">
+        <v>772</v>
+      </c>
+      <c r="L160" s="8" t="s">
         <v>773</v>
-      </c>
-      <c r="L160" s="8" t="s">
-        <v>774</v>
       </c>
       <c r="R160" t="s">
         <v>147</v>
@@ -10206,10 +10224,10 @@
     </row>
     <row r="161" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>764</v>
+      </c>
+      <c r="B161" t="s">
         <v>765</v>
-      </c>
-      <c r="B161" t="s">
-        <v>766</v>
       </c>
       <c r="D161">
         <v>1756</v>
@@ -10221,13 +10239,13 @@
         <v>475</v>
       </c>
       <c r="J161" t="s">
+        <v>774</v>
+      </c>
+      <c r="K161" t="s">
         <v>775</v>
       </c>
-      <c r="K161" t="s">
+      <c r="L161" s="11" t="s">
         <v>776</v>
-      </c>
-      <c r="L161" s="11" t="s">
-        <v>777</v>
       </c>
       <c r="R161" t="s">
         <v>56</v>
@@ -10247,25 +10265,25 @@
     </row>
     <row r="162" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>777</v>
+      </c>
+      <c r="B162" t="s">
         <v>778</v>
-      </c>
-      <c r="B162" t="s">
-        <v>779</v>
       </c>
       <c r="D162" t="s">
         <v>362</v>
       </c>
       <c r="E162" t="s">
+        <v>779</v>
+      </c>
+      <c r="F162" t="s">
         <v>780</v>
       </c>
-      <c r="F162" t="s">
+      <c r="J162" t="s">
         <v>781</v>
       </c>
-      <c r="J162" t="s">
+      <c r="L162" s="3" t="s">
         <v>782</v>
-      </c>
-      <c r="L162" s="3" t="s">
-        <v>783</v>
       </c>
       <c r="R162" t="s">
         <v>31</v>
@@ -10288,28 +10306,28 @@
     </row>
     <row r="163" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>777</v>
+      </c>
+      <c r="B163" t="s">
         <v>778</v>
-      </c>
-      <c r="B163" t="s">
-        <v>779</v>
       </c>
       <c r="D163">
         <v>1763</v>
       </c>
       <c r="E163" t="s">
+        <v>779</v>
+      </c>
+      <c r="F163" t="s">
         <v>780</v>
       </c>
-      <c r="F163" t="s">
-        <v>781</v>
-      </c>
       <c r="J163" t="s">
+        <v>783</v>
+      </c>
+      <c r="K163" t="s">
         <v>784</v>
       </c>
-      <c r="K163" t="s">
+      <c r="L163" s="3" t="s">
         <v>785</v>
-      </c>
-      <c r="L163" s="3" t="s">
-        <v>786</v>
       </c>
       <c r="R163" t="s">
         <v>31</v>
@@ -10332,28 +10350,28 @@
     </row>
     <row r="164" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>777</v>
+      </c>
+      <c r="B164" t="s">
         <v>778</v>
-      </c>
-      <c r="B164" t="s">
-        <v>779</v>
       </c>
       <c r="D164" t="s">
         <v>498</v>
       </c>
       <c r="E164" t="s">
+        <v>779</v>
+      </c>
+      <c r="F164" t="s">
         <v>780</v>
       </c>
-      <c r="F164" t="s">
-        <v>781</v>
-      </c>
       <c r="J164" t="s">
+        <v>786</v>
+      </c>
+      <c r="K164" t="s">
         <v>787</v>
       </c>
-      <c r="K164" t="s">
+      <c r="L164" s="3" t="s">
         <v>788</v>
-      </c>
-      <c r="L164" s="3" t="s">
-        <v>789</v>
       </c>
       <c r="R164" t="s">
         <v>31</v>
@@ -10376,28 +10394,28 @@
     </row>
     <row r="165" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>777</v>
+      </c>
+      <c r="B165" t="s">
         <v>778</v>
-      </c>
-      <c r="B165" t="s">
-        <v>779</v>
       </c>
       <c r="D165" t="s">
         <v>439</v>
       </c>
       <c r="E165" t="s">
+        <v>779</v>
+      </c>
+      <c r="F165" t="s">
         <v>780</v>
       </c>
-      <c r="F165" t="s">
-        <v>781</v>
-      </c>
       <c r="J165" t="s">
+        <v>789</v>
+      </c>
+      <c r="K165" t="s">
         <v>790</v>
       </c>
-      <c r="K165" t="s">
+      <c r="L165" s="3" t="s">
         <v>791</v>
-      </c>
-      <c r="L165" s="3" t="s">
-        <v>792</v>
       </c>
       <c r="R165" t="s">
         <v>31</v>
@@ -10420,10 +10438,10 @@
     </row>
     <row r="166" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>792</v>
+      </c>
+      <c r="B166" t="s">
         <v>793</v>
-      </c>
-      <c r="B166" t="s">
-        <v>794</v>
       </c>
       <c r="D166" t="s">
         <v>335</v>
@@ -10435,13 +10453,13 @@
         <v>285</v>
       </c>
       <c r="J166" t="s">
+        <v>794</v>
+      </c>
+      <c r="K166" t="s">
         <v>795</v>
       </c>
-      <c r="K166" t="s">
+      <c r="L166" s="3" t="s">
         <v>796</v>
-      </c>
-      <c r="L166" s="3" t="s">
-        <v>797</v>
       </c>
       <c r="R166" t="s">
         <v>56</v>
@@ -10456,7 +10474,7 @@
         <v>194</v>
       </c>
       <c r="V166" s="15" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="W166" s="15">
         <v>3</v>
@@ -10464,10 +10482,10 @@
     </row>
     <row r="167" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>792</v>
+      </c>
+      <c r="B167" t="s">
         <v>793</v>
-      </c>
-      <c r="B167" t="s">
-        <v>794</v>
       </c>
       <c r="D167" t="s">
         <v>209</v>
@@ -10476,16 +10494,16 @@
         <v>195</v>
       </c>
       <c r="F167" t="s">
+        <v>798</v>
+      </c>
+      <c r="J167" t="s">
         <v>799</v>
       </c>
-      <c r="J167" t="s">
+      <c r="K167" t="s">
         <v>800</v>
       </c>
-      <c r="K167" t="s">
+      <c r="L167" s="3" t="s">
         <v>801</v>
-      </c>
-      <c r="L167" s="3" t="s">
-        <v>802</v>
       </c>
       <c r="R167" t="s">
         <v>56</v>
@@ -10494,7 +10512,7 @@
         <v>32</v>
       </c>
       <c r="T167" s="15" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="U167" s="15" t="s">
         <v>462</v>
@@ -10508,25 +10526,25 @@
     </row>
     <row r="168" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>792</v>
+      </c>
+      <c r="B168" t="s">
         <v>793</v>
       </c>
-      <c r="B168" t="s">
-        <v>794</v>
-      </c>
       <c r="D168" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E168" t="s">
         <v>195</v>
       </c>
       <c r="F168" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J168" t="s">
+        <v>804</v>
+      </c>
+      <c r="L168" s="3" t="s">
         <v>805</v>
-      </c>
-      <c r="L168" s="3" t="s">
-        <v>806</v>
       </c>
       <c r="R168" t="s">
         <v>56</v>
@@ -10549,10 +10567,10 @@
     </row>
     <row r="169" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
+        <v>792</v>
+      </c>
+      <c r="B169" t="s">
         <v>793</v>
-      </c>
-      <c r="B169" t="s">
-        <v>794</v>
       </c>
       <c r="D169" t="s">
         <v>217</v>
@@ -10561,19 +10579,19 @@
         <v>195</v>
       </c>
       <c r="F169" t="s">
+        <v>806</v>
+      </c>
+      <c r="J169" t="s">
+        <v>890</v>
+      </c>
+      <c r="K169" t="s">
         <v>807</v>
       </c>
-      <c r="J169" t="s">
-        <v>891</v>
-      </c>
-      <c r="K169" t="s">
+      <c r="L169" s="3" t="s">
         <v>808</v>
       </c>
-      <c r="L169" s="3" t="s">
-        <v>809</v>
-      </c>
       <c r="R169" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="S169" t="s">
         <v>32</v>
@@ -10593,28 +10611,28 @@
     </row>
     <row r="170" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>809</v>
+      </c>
+      <c r="B170" t="s">
         <v>810</v>
       </c>
-      <c r="B170" t="s">
+      <c r="D170" t="s">
         <v>811</v>
-      </c>
-      <c r="D170" t="s">
-        <v>812</v>
       </c>
       <c r="E170" t="s">
         <v>166</v>
       </c>
       <c r="F170" t="s">
+        <v>812</v>
+      </c>
+      <c r="J170" t="s">
         <v>813</v>
       </c>
-      <c r="J170" t="s">
+      <c r="K170" t="s">
         <v>814</v>
       </c>
-      <c r="K170" t="s">
+      <c r="L170" s="3" t="s">
         <v>815</v>
-      </c>
-      <c r="L170" s="3" t="s">
-        <v>816</v>
       </c>
       <c r="R170" t="s">
         <v>31</v>
@@ -10623,7 +10641,7 @@
         <v>32</v>
       </c>
       <c r="T170" s="15" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="U170" s="15">
         <v>102</v>
@@ -10637,10 +10655,10 @@
     </row>
     <row r="171" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
+        <v>809</v>
+      </c>
+      <c r="B171" t="s">
         <v>810</v>
-      </c>
-      <c r="B171" t="s">
-        <v>811</v>
       </c>
       <c r="D171" t="s">
         <v>456</v>
@@ -10649,22 +10667,22 @@
         <v>166</v>
       </c>
       <c r="F171" t="s">
+        <v>817</v>
+      </c>
+      <c r="J171" t="s">
         <v>818</v>
       </c>
-      <c r="J171" t="s">
+      <c r="K171" t="s">
         <v>819</v>
       </c>
-      <c r="K171" t="s">
+      <c r="L171" s="3" t="s">
         <v>820</v>
-      </c>
-      <c r="L171" s="3" t="s">
-        <v>821</v>
       </c>
       <c r="R171" t="s">
         <v>31</v>
       </c>
       <c r="S171" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="T171" s="15">
         <v>550</v>
@@ -10681,10 +10699,10 @@
     </row>
     <row r="172" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>809</v>
+      </c>
+      <c r="B172" t="s">
         <v>810</v>
-      </c>
-      <c r="B172" t="s">
-        <v>811</v>
       </c>
       <c r="D172" t="s">
         <v>481</v>
@@ -10693,19 +10711,19 @@
         <v>166</v>
       </c>
       <c r="F172" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J172" t="s">
+        <v>891</v>
+      </c>
+      <c r="K172" t="s">
+        <v>822</v>
+      </c>
+      <c r="L172" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="R172" t="s">
         <v>892</v>
-      </c>
-      <c r="K172" t="s">
-        <v>823</v>
-      </c>
-      <c r="L172" s="3" t="s">
-        <v>824</v>
-      </c>
-      <c r="R172" t="s">
-        <v>893</v>
       </c>
       <c r="S172" t="s">
         <v>32</v>
@@ -10725,34 +10743,34 @@
     </row>
     <row r="173" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>809</v>
+      </c>
+      <c r="B173" t="s">
         <v>810</v>
       </c>
-      <c r="B173" t="s">
-        <v>811</v>
-      </c>
       <c r="D173" t="s">
+        <v>824</v>
+      </c>
+      <c r="E173" t="s">
         <v>825</v>
       </c>
-      <c r="E173" t="s">
+      <c r="F173" t="s">
         <v>826</v>
       </c>
-      <c r="F173" t="s">
+      <c r="J173" t="s">
         <v>827</v>
       </c>
-      <c r="J173" t="s">
+      <c r="K173" t="s">
         <v>828</v>
       </c>
-      <c r="K173" t="s">
+      <c r="L173" s="3" t="s">
         <v>829</v>
       </c>
-      <c r="L173" s="3" t="s">
-        <v>830</v>
-      </c>
       <c r="R173" t="s">
         <v>56</v>
       </c>
       <c r="S173" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="T173" s="15" t="s">
         <v>559</v>
@@ -10769,40 +10787,40 @@
     </row>
     <row r="174" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>830</v>
+      </c>
+      <c r="B174" t="s">
         <v>831</v>
       </c>
-      <c r="B174" t="s">
+      <c r="D174" t="s">
         <v>832</v>
       </c>
-      <c r="D174" t="s">
+      <c r="E174" t="s">
         <v>833</v>
       </c>
-      <c r="E174" t="s">
+      <c r="F174" t="s">
         <v>834</v>
       </c>
-      <c r="F174" t="s">
+      <c r="J174" t="s">
         <v>835</v>
       </c>
-      <c r="J174" t="s">
+      <c r="K174" t="s">
         <v>836</v>
       </c>
-      <c r="K174" t="s">
+      <c r="L174" s="3" t="s">
         <v>837</v>
       </c>
-      <c r="L174" s="3" t="s">
+      <c r="R174" t="s">
+        <v>56</v>
+      </c>
+      <c r="S174" t="s">
         <v>838</v>
       </c>
-      <c r="R174" t="s">
-        <v>56</v>
-      </c>
-      <c r="S174" t="s">
+      <c r="T174" s="15" t="s">
         <v>839</v>
       </c>
-      <c r="T174" s="15" t="s">
+      <c r="U174" s="15" t="s">
         <v>840</v>
-      </c>
-      <c r="U174" s="15" t="s">
-        <v>841</v>
       </c>
       <c r="V174" s="15" t="s">
         <v>333</v>
@@ -10813,34 +10831,34 @@
     </row>
     <row r="175" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>830</v>
+      </c>
+      <c r="B175" t="s">
         <v>831</v>
       </c>
-      <c r="B175" t="s">
-        <v>832</v>
-      </c>
       <c r="D175" t="s">
+        <v>841</v>
+      </c>
+      <c r="E175" t="s">
+        <v>833</v>
+      </c>
+      <c r="F175" t="s">
         <v>842</v>
       </c>
-      <c r="E175" t="s">
-        <v>834</v>
-      </c>
-      <c r="F175" t="s">
+      <c r="J175" t="s">
         <v>843</v>
       </c>
-      <c r="J175" t="s">
+      <c r="K175" t="s">
         <v>844</v>
       </c>
-      <c r="K175" t="s">
+      <c r="L175" s="3" t="s">
         <v>845</v>
       </c>
-      <c r="L175" s="3" t="s">
-        <v>846</v>
-      </c>
       <c r="R175" t="s">
         <v>56</v>
       </c>
       <c r="S175" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="T175" s="15" t="s">
         <v>194</v>
@@ -10857,34 +10875,34 @@
     </row>
     <row r="176" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>830</v>
+      </c>
+      <c r="B176" t="s">
         <v>831</v>
       </c>
-      <c r="B176" t="s">
-        <v>832</v>
-      </c>
       <c r="D176" t="s">
+        <v>846</v>
+      </c>
+      <c r="E176" t="s">
+        <v>833</v>
+      </c>
+      <c r="F176" t="s">
         <v>847</v>
       </c>
-      <c r="E176" t="s">
-        <v>834</v>
-      </c>
-      <c r="F176" t="s">
+      <c r="J176" t="s">
         <v>848</v>
       </c>
-      <c r="J176" t="s">
+      <c r="K176" t="s">
         <v>849</v>
       </c>
-      <c r="K176" t="s">
+      <c r="L176" s="3" t="s">
         <v>850</v>
       </c>
-      <c r="L176" s="3" t="s">
-        <v>851</v>
-      </c>
       <c r="R176" t="s">
         <v>56</v>
       </c>
       <c r="S176" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="T176" s="15" t="s">
         <v>194</v>
@@ -10901,37 +10919,37 @@
     </row>
     <row r="177" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>830</v>
+      </c>
+      <c r="B177" t="s">
         <v>831</v>
       </c>
-      <c r="B177" t="s">
-        <v>832</v>
-      </c>
       <c r="D177" t="s">
+        <v>851</v>
+      </c>
+      <c r="E177" t="s">
         <v>852</v>
       </c>
-      <c r="E177" t="s">
+      <c r="F177" t="s">
         <v>853</v>
       </c>
-      <c r="F177" t="s">
+      <c r="J177" t="s">
         <v>854</v>
       </c>
-      <c r="J177" t="s">
+      <c r="K177" t="s">
         <v>855</v>
       </c>
-      <c r="K177" t="s">
+      <c r="L177" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L177" s="3" t="s">
+      <c r="R177" t="s">
+        <v>56</v>
+      </c>
+      <c r="S177" t="s">
+        <v>838</v>
+      </c>
+      <c r="T177" s="15" t="s">
         <v>857</v>
-      </c>
-      <c r="R177" t="s">
-        <v>56</v>
-      </c>
-      <c r="S177" t="s">
-        <v>839</v>
-      </c>
-      <c r="T177" s="15" t="s">
-        <v>858</v>
       </c>
       <c r="U177" s="15">
         <v>80</v>
@@ -10945,34 +10963,34 @@
     </row>
     <row r="178" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>830</v>
+      </c>
+      <c r="B178" t="s">
         <v>831</v>
       </c>
-      <c r="B178" t="s">
-        <v>832</v>
-      </c>
       <c r="D178" t="s">
+        <v>858</v>
+      </c>
+      <c r="E178" t="s">
+        <v>833</v>
+      </c>
+      <c r="F178" t="s">
         <v>859</v>
       </c>
-      <c r="E178" t="s">
-        <v>834</v>
-      </c>
-      <c r="F178" t="s">
+      <c r="J178" t="s">
         <v>860</v>
       </c>
-      <c r="J178" t="s">
+      <c r="K178" t="s">
         <v>861</v>
       </c>
-      <c r="K178" t="s">
+      <c r="L178" s="3" t="s">
         <v>862</v>
       </c>
-      <c r="L178" s="3" t="s">
-        <v>863</v>
-      </c>
       <c r="R178" t="s">
         <v>56</v>
       </c>
       <c r="S178" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="T178" s="15" t="s">
         <v>110</v>
@@ -10989,34 +11007,34 @@
     </row>
     <row r="179" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>830</v>
+      </c>
+      <c r="B179" t="s">
         <v>831</v>
       </c>
-      <c r="B179" t="s">
-        <v>832</v>
-      </c>
       <c r="D179" t="s">
+        <v>858</v>
+      </c>
+      <c r="E179" t="s">
+        <v>833</v>
+      </c>
+      <c r="F179" t="s">
         <v>859</v>
       </c>
-      <c r="E179" t="s">
-        <v>834</v>
-      </c>
-      <c r="F179" t="s">
-        <v>860</v>
-      </c>
       <c r="J179" t="s">
+        <v>863</v>
+      </c>
+      <c r="K179" t="s">
         <v>864</v>
       </c>
-      <c r="K179" t="s">
+      <c r="L179" s="3" t="s">
         <v>865</v>
       </c>
-      <c r="L179" s="3" t="s">
-        <v>866</v>
-      </c>
       <c r="R179" t="s">
         <v>56</v>
       </c>
       <c r="S179" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="T179" s="15" t="s">
         <v>194</v>
@@ -11033,13 +11051,13 @@
     </row>
     <row r="180" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>866</v>
+      </c>
+      <c r="B180" t="s">
         <v>867</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
         <v>868</v>
-      </c>
-      <c r="C180" t="s">
-        <v>869</v>
       </c>
       <c r="D180" t="s">
         <v>165</v>
@@ -11051,13 +11069,13 @@
         <v>188</v>
       </c>
       <c r="J180" t="s">
+        <v>869</v>
+      </c>
+      <c r="K180" t="s">
         <v>870</v>
       </c>
-      <c r="K180" t="s">
+      <c r="L180" s="3" t="s">
         <v>871</v>
-      </c>
-      <c r="L180" s="3" t="s">
-        <v>872</v>
       </c>
       <c r="R180" t="s">
         <v>56</v>
@@ -11069,10 +11087,10 @@
         <v>473</v>
       </c>
       <c r="U180" s="15" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="V180" s="15" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="W180" s="15">
         <v>3</v>
@@ -11080,13 +11098,13 @@
     </row>
     <row r="181" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>866</v>
+      </c>
+      <c r="B181" t="s">
         <v>867</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
         <v>868</v>
-      </c>
-      <c r="C181" t="s">
-        <v>869</v>
       </c>
       <c r="D181" t="s">
         <v>439</v>
@@ -11098,13 +11116,13 @@
         <v>704</v>
       </c>
       <c r="J181" t="s">
+        <v>873</v>
+      </c>
+      <c r="L181" s="3" t="s">
         <v>874</v>
       </c>
-      <c r="L181" s="3" t="s">
-        <v>875</v>
-      </c>
       <c r="R181" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="S181" t="s">
         <v>201</v>
@@ -11124,13 +11142,13 @@
     </row>
     <row r="182" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>866</v>
+      </c>
+      <c r="B182" t="s">
         <v>867</v>
       </c>
-      <c r="B182" t="s">
+      <c r="C182" t="s">
         <v>868</v>
-      </c>
-      <c r="C182" t="s">
-        <v>869</v>
       </c>
       <c r="D182" t="s">
         <v>36</v>
@@ -11142,11 +11160,11 @@
         <v>28</v>
       </c>
       <c r="J182" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="K182" s="3"/>
       <c r="L182" s="11" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="R182" t="s">
         <v>56</v>
@@ -11169,13 +11187,13 @@
     </row>
     <row r="183" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>866</v>
+      </c>
+      <c r="B183" t="s">
         <v>867</v>
       </c>
-      <c r="B183" t="s">
+      <c r="C183" t="s">
         <v>868</v>
-      </c>
-      <c r="C183" t="s">
-        <v>869</v>
       </c>
       <c r="D183" t="s">
         <v>36</v>
@@ -11187,10 +11205,10 @@
         <v>28</v>
       </c>
       <c r="J183" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="L183" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="R183" t="s">
         <v>56</v>
@@ -11411,6 +11429,12 @@
     <hyperlink ref="G74" r:id="rId193" xr:uid="{FECE9BFA-B8E8-4206-BD59-6D54AEB83D86}"/>
     <hyperlink ref="I24" r:id="rId194" xr:uid="{6D83C2C3-0DDA-46DE-B25E-66293EAAED02}"/>
     <hyperlink ref="L24" r:id="rId195" xr:uid="{B91B73D0-731E-4554-AFB9-908A43D1432E}"/>
+    <hyperlink ref="G3" r:id="rId196" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ab/Parc_de_Versailles%2C_bassin_de_Neptune%2C_Le_Triomphe_de_Neptune_et_d%27Amphitrite%2C_Lambert-Sigisbert_Adam_01.jpg/1280px-Parc_de_Versailles%2C_bassin_de_Neptune%2C_Le_Triomphe_de_Neptune_et_d%27Amphitrite%2C_Lambert-Sigisbert_Adam_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{72FA62B2-1813-4099-BD67-C1FED2805585}"/>
+    <hyperlink ref="I3" r:id="rId197" xr:uid="{55A88B90-768A-4756-9011-8B7CCCB25FE0}"/>
+    <hyperlink ref="G68" r:id="rId198" xr:uid="{1C81F1BD-746F-48B3-AB0B-C80D2DC3CD00}"/>
+    <hyperlink ref="I68" r:id="rId199" xr:uid="{75A02989-548F-44F1-9A28-F456FE4ABB58}"/>
+    <hyperlink ref="G147" r:id="rId200" xr:uid="{C16E2F29-9940-49B1-B615-E3E8EA82ABDA}"/>
+    <hyperlink ref="I147" r:id="rId201" xr:uid="{B90670BC-9623-422C-B03E-D099D0AA1EB1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\éléments à uploader\vers quizzes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC2C2BF-045B-42A1-97E7-4675394EC250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E91D8E1-8C62-40A8-8B85-9E3702942CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6174,7 +6174,7 @@
         <v>356</v>
       </c>
       <c r="R67" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="S67" t="s">
         <v>32</v>
